--- a/public/STMG_HUB_Missions_Programmes_Officiels.xlsx
+++ b/public/STMG_HUB_Missions_Programmes_Officiels.xlsx
@@ -528,13 +528,13 @@
       <c r="J2" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Le droit et ses fonctions dans la societe
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Qu'est-ce que le droit et a quoi sert-il e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 9250 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Regle de droit, Droit objectif et Droits subjectifs.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Regle de droit, Droit objectif, Droits subjectifs.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Qu'est-ce que le droit et a quoi sert-il e.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Regle de droit, Droit objectif, Droits subjectifs.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Regle de droit, Droit objectif, Droits subjectifs.</t>
         </is>
       </c>
       <c r="M2" t="n">
@@ -596,13 +596,13 @@
       <c r="J3" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Les sources du droit
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: D'ou vient le droit e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 10500 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Constitution, Loi et Reglement.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Constitution, Loi, Reglement.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: D'ou vient le droit e.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Constitution, Loi, Reglement.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Constitution, Loi, Reglement.</t>
         </is>
       </c>
       <c r="M3" t="n">
@@ -664,13 +664,13 @@
       <c r="J4" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Le droit et ses fonctions dans la societe
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Qu'est-ce que le droit et a quoi sert-il e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 11750 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Regle de droit, Droit objectif et Droits subjectifs.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Regle de droit, Droit objectif, Droits subjectifs.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Qu'est-ce que le droit et a quoi sert-il e.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Regle de droit, Droit objectif, Droits subjectifs.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Regle de droit, Droit objectif, Droits subjectifs.</t>
         </is>
       </c>
       <c r="M4" t="n">
@@ -732,13 +732,13 @@
       <c r="J5" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Les sources du droit
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: D'ou vient le droit e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 13000 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Constitution, Loi et Reglement.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Constitution, Loi, Reglement.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: D'ou vient le droit e.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Constitution, Loi, Reglement.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Constitution, Loi, Reglement.</t>
         </is>
       </c>
       <c r="M5" t="n">
@@ -800,13 +800,13 @@
       <c r="J6" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Le droit et ses fonctions dans la societe
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Qu'est-ce que le droit et a quoi sert-il e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 14250 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Regle de droit, Droit objectif et Droits subjectifs.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Regle de droit, Droit objectif, Droits subjectifs.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Qu'est-ce que le droit et a quoi sert-il e.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Regle de droit, Droit objectif, Droits subjectifs.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Regle de droit, Droit objectif, Droits subjectifs.</t>
         </is>
       </c>
       <c r="M6" t="n">
@@ -868,13 +868,13 @@
       <c r="J7" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Les sources du droit
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: D'ou vient le droit e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 15500 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Constitution, Loi et Reglement.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Constitution, Loi, Reglement.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: D'ou vient le droit e.</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Constitution, Loi, Reglement.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Constitution, Loi, Reglement.</t>
         </is>
       </c>
       <c r="M7" t="n">
@@ -936,13 +936,13 @@
       <c r="J8" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Le droit et ses fonctions dans la societe
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Qu'est-ce que le droit et a quoi sert-il e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 16750 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Regle de droit, Droit objectif et Droits subjectifs.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Regle de droit, Droit objectif, Droits subjectifs.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Qu'est-ce que le droit et a quoi sert-il e.</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Regle de droit, Droit objectif, Droits subjectifs.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Regle de droit, Droit objectif, Droits subjectifs.</t>
         </is>
       </c>
       <c r="M8" t="n">
@@ -1004,13 +1004,13 @@
       <c r="J9" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Les sources du droit
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: D'ou vient le droit e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 18000 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Constitution, Loi et Reglement.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Constitution, Loi, Reglement.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: D'ou vient le droit e.</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Constitution, Loi, Reglement.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Constitution, Loi, Reglement.</t>
         </is>
       </c>
       <c r="M9" t="n">
@@ -1072,13 +1072,13 @@
       <c r="J10" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Le droit et ses fonctions dans la societe
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Qu'est-ce que le droit et a quoi sert-il e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 19250 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Regle de droit, Droit objectif et Droits subjectifs.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Regle de droit, Droit objectif, Droits subjectifs.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Qu'est-ce que le droit et a quoi sert-il e.</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Regle de droit, Droit objectif, Droits subjectifs.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Regle de droit, Droit objectif, Droits subjectifs.</t>
         </is>
       </c>
       <c r="M10" t="n">
@@ -1140,13 +1140,13 @@
       <c r="J11" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Les sources du droit
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: D'ou vient le droit e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 20500 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Constitution, Loi et Reglement.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Constitution, Loi, Reglement.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: D'ou vient le droit e.</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Constitution, Loi, Reglement.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Constitution, Loi, Reglement.</t>
         </is>
       </c>
       <c r="M11" t="n">
@@ -1208,13 +1208,13 @@
       <c r="J12" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Le recours au juge
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Comment faire valoir ses droits e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 9250 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Juridictions civiles, Juridictions penales et Juridictions administratives.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Juridictions civiles, Juridictions penales, Juridictions administratives.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Comment faire valoir ses droits e.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Juridictions civiles, Juridictions penales, Juridictions administratives.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Juridictions civiles, Juridictions penales, Juridictions administratives.</t>
         </is>
       </c>
       <c r="M12" t="n">
@@ -1276,13 +1276,13 @@
       <c r="J13" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Le litige et la preuve
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Comment prouver ses droits e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 10500 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Litige, Preuve et Modes de preuve.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Litige, Preuve, Modes de preuve.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Comment prouver ses droits e.</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Litige, Preuve, Modes de preuve.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Litige, Preuve, Modes de preuve.</t>
         </is>
       </c>
       <c r="M13" t="n">
@@ -1344,13 +1344,13 @@
       <c r="J14" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Le recours au juge
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Comment faire valoir ses droits e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 11750 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Juridictions civiles, Juridictions penales et Juridictions administratives.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Juridictions civiles, Juridictions penales, Juridictions administratives.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Comment faire valoir ses droits e.</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Juridictions civiles, Juridictions penales, Juridictions administratives.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Juridictions civiles, Juridictions penales, Juridictions administratives.</t>
         </is>
       </c>
       <c r="M14" t="n">
@@ -1412,13 +1412,13 @@
       <c r="J15" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Le litige et la preuve
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Comment prouver ses droits e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 13000 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Litige, Preuve et Modes de preuve.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Litige, Preuve, Modes de preuve.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Comment prouver ses droits e.</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Litige, Preuve, Modes de preuve.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Litige, Preuve, Modes de preuve.</t>
         </is>
       </c>
       <c r="M15" t="n">
@@ -1480,13 +1480,13 @@
       <c r="J16" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Le recours au juge
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Comment faire valoir ses droits e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 14250 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Juridictions civiles, Juridictions penales et Juridictions administratives.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Juridictions civiles, Juridictions penales, Juridictions administratives.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Comment faire valoir ses droits e.</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Juridictions civiles, Juridictions penales, Juridictions administratives.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Juridictions civiles, Juridictions penales, Juridictions administratives.</t>
         </is>
       </c>
       <c r="M16" t="n">
@@ -1548,13 +1548,13 @@
       <c r="J17" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Le litige et la preuve
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Comment prouver ses droits e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 15500 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Litige, Preuve et Modes de preuve.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Litige, Preuve, Modes de preuve.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Comment prouver ses droits e.</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Litige, Preuve, Modes de preuve.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Litige, Preuve, Modes de preuve.</t>
         </is>
       </c>
       <c r="M17" t="n">
@@ -1616,13 +1616,13 @@
       <c r="J18" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Le recours au juge
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Comment faire valoir ses droits e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 16750 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Juridictions civiles, Juridictions penales et Juridictions administratives.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Juridictions civiles, Juridictions penales, Juridictions administratives.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Comment faire valoir ses droits e.</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Juridictions civiles, Juridictions penales, Juridictions administratives.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Juridictions civiles, Juridictions penales, Juridictions administratives.</t>
         </is>
       </c>
       <c r="M18" t="n">
@@ -1684,13 +1684,13 @@
       <c r="J19" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Le litige et la preuve
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Comment prouver ses droits e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 18000 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Litige, Preuve et Modes de preuve.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Litige, Preuve, Modes de preuve.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Comment prouver ses droits e.</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Litige, Preuve, Modes de preuve.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Litige, Preuve, Modes de preuve.</t>
         </is>
       </c>
       <c r="M19" t="n">
@@ -1752,13 +1752,13 @@
       <c r="J20" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Le recours au juge
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Comment faire valoir ses droits e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 19250 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Juridictions civiles, Juridictions penales et Juridictions administratives.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Juridictions civiles, Juridictions penales, Juridictions administratives.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Comment faire valoir ses droits e.</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Juridictions civiles, Juridictions penales, Juridictions administratives.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Juridictions civiles, Juridictions penales, Juridictions administratives.</t>
         </is>
       </c>
       <c r="M20" t="n">
@@ -1820,13 +1820,13 @@
       <c r="J21" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Le litige et la preuve
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Comment prouver ses droits e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 20500 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Litige, Preuve et Modes de preuve.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Litige, Preuve, Modes de preuve.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Comment prouver ses droits e.</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Litige, Preuve, Modes de preuve.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Litige, Preuve, Modes de preuve.</t>
         </is>
       </c>
       <c r="M21" t="n">
@@ -1888,13 +1888,13 @@
       <c r="J22" t="inlineStr">
         <is>
           <t>Cas pratique juridique - La personnalite juridique
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Qui sont les sujets de droit e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 9250 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Personnalite juridique, Personne physique et Personne morale.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Personnalite juridique, Personne physique, Personne morale.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Qui sont les sujets de droit e.</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Personnalite juridique, Personne physique, Personne morale.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Personnalite juridique, Personne physique, Personne morale.</t>
         </is>
       </c>
       <c r="M22" t="n">
@@ -1956,13 +1956,13 @@
       <c r="J23" t="inlineStr">
         <is>
           <t>Cas pratique juridique - La capacite et l'incapacite
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Qui peut exercer ses droits e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 10500 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Capacite juridique, Incapacite et Majeur protege.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Capacite juridique, Incapacite, Majeur protege.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Qui peut exercer ses droits e.</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Capacite juridique, Incapacite, Majeur protege.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Capacite juridique, Incapacite, Majeur protege.</t>
         </is>
       </c>
       <c r="M23" t="n">
@@ -2024,13 +2024,13 @@
       <c r="J24" t="inlineStr">
         <is>
           <t>Cas pratique juridique - La personnalite juridique
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Qui sont les sujets de droit e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 11750 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Personnalite juridique, Personne physique et Personne morale.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Personnalite juridique, Personne physique, Personne morale.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Qui sont les sujets de droit e.</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Personnalite juridique, Personne physique, Personne morale.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Personnalite juridique, Personne physique, Personne morale.</t>
         </is>
       </c>
       <c r="M24" t="n">
@@ -2092,13 +2092,13 @@
       <c r="J25" t="inlineStr">
         <is>
           <t>Cas pratique juridique - La capacite et l'incapacite
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Qui peut exercer ses droits e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 13000 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Capacite juridique, Incapacite et Majeur protege.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Capacite juridique, Incapacite, Majeur protege.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Qui peut exercer ses droits e.</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Capacite juridique, Incapacite, Majeur protege.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Capacite juridique, Incapacite, Majeur protege.</t>
         </is>
       </c>
       <c r="M25" t="n">
@@ -2160,13 +2160,13 @@
       <c r="J26" t="inlineStr">
         <is>
           <t>Cas pratique juridique - La personnalite juridique
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Qui sont les sujets de droit e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 14250 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Personnalite juridique, Personne physique et Personne morale.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Personnalite juridique, Personne physique, Personne morale.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Qui sont les sujets de droit e.</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Personnalite juridique, Personne physique, Personne morale.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Personnalite juridique, Personne physique, Personne morale.</t>
         </is>
       </c>
       <c r="M26" t="n">
@@ -2228,13 +2228,13 @@
       <c r="J27" t="inlineStr">
         <is>
           <t>Cas pratique juridique - La capacite et l'incapacite
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Qui peut exercer ses droits e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 15500 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Capacite juridique, Incapacite et Majeur protege.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Capacite juridique, Incapacite, Majeur protege.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Qui peut exercer ses droits e.</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Capacite juridique, Incapacite, Majeur protege.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Capacite juridique, Incapacite, Majeur protege.</t>
         </is>
       </c>
       <c r="M27" t="n">
@@ -2296,13 +2296,13 @@
       <c r="J28" t="inlineStr">
         <is>
           <t>Cas pratique juridique - La personnalite juridique
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Qui sont les sujets de droit e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 16750 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Personnalite juridique, Personne physique et Personne morale.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Personnalite juridique, Personne physique, Personne morale.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Qui sont les sujets de droit e.</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Personnalite juridique, Personne physique, Personne morale.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Personnalite juridique, Personne physique, Personne morale.</t>
         </is>
       </c>
       <c r="M28" t="n">
@@ -2364,13 +2364,13 @@
       <c r="J29" t="inlineStr">
         <is>
           <t>Cas pratique juridique - La capacite et l'incapacite
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Qui peut exercer ses droits e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 18000 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Capacite juridique, Incapacite et Majeur protege.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Capacite juridique, Incapacite, Majeur protege.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Qui peut exercer ses droits e.</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Capacite juridique, Incapacite, Majeur protege.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Capacite juridique, Incapacite, Majeur protege.</t>
         </is>
       </c>
       <c r="M29" t="n">
@@ -2432,13 +2432,13 @@
       <c r="J30" t="inlineStr">
         <is>
           <t>Cas pratique juridique - La personnalite juridique
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Qui sont les sujets de droit e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 19250 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Personnalite juridique, Personne physique et Personne morale.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Personnalite juridique, Personne physique, Personne morale.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Qui sont les sujets de droit e.</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Personnalite juridique, Personne physique, Personne morale.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Personnalite juridique, Personne physique, Personne morale.</t>
         </is>
       </c>
       <c r="M30" t="n">
@@ -2500,13 +2500,13 @@
       <c r="J31" t="inlineStr">
         <is>
           <t>Cas pratique juridique - La capacite et l'incapacite
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Qui peut exercer ses droits e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 20500 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Capacite juridique, Incapacite et Majeur protege.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Capacite juridique, Incapacite, Majeur protege.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Qui peut exercer ses droits e.</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Capacite juridique, Incapacite, Majeur protege.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Capacite juridique, Incapacite, Majeur protege.</t>
         </is>
       </c>
       <c r="M31" t="n">
@@ -2568,13 +2568,13 @@
       <c r="J32" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Le patrimoine
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Qu'est-ce que le patrimoine e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 9250 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Patrimoine, Actif et Passif.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Patrimoine, Actif, Passif.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Qu'est-ce que le patrimoine e.</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Patrimoine, Actif, Passif.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Patrimoine, Actif, Passif.</t>
         </is>
       </c>
       <c r="M32" t="n">
@@ -2636,13 +2636,13 @@
       <c r="J33" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Les droits extrapatrimoniaux
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Quels sont les droits attaches a la personne e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 10500 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Droits extrapatrimoniaux, Droit a l'image et Vie privee.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Droits extrapatrimoniaux, Droit a l'image, Vie privee.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Quels sont les droits attaches a la personne e.</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Droits extrapatrimoniaux, Droit a l'image, Vie privee.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Droits extrapatrimoniaux, Droit a l'image, Vie privee.</t>
         </is>
       </c>
       <c r="M33" t="n">
@@ -2704,13 +2704,13 @@
       <c r="J34" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Le droit de propriete
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Qu'est-ce que le droit de propriete e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 11750 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Droit de propriete, Usus et Fructus.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Droit de propriete, Usus, Fructus.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Qu'est-ce que le droit de propriete e.</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Droit de propriete, Usus, Fructus.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Droit de propriete, Usus, Fructus.</t>
         </is>
       </c>
       <c r="M34" t="n">
@@ -2772,13 +2772,13 @@
       <c r="J35" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Le patrimoine
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Qu'est-ce que le patrimoine e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 13000 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Patrimoine, Actif et Passif.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Patrimoine, Actif, Passif.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Qu'est-ce que le patrimoine e.</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Patrimoine, Actif, Passif.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Patrimoine, Actif, Passif.</t>
         </is>
       </c>
       <c r="M35" t="n">
@@ -2840,13 +2840,13 @@
       <c r="J36" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Les droits extrapatrimoniaux
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Quels sont les droits attaches a la personne e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 14250 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Droits extrapatrimoniaux, Droit a l'image et Vie privee.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Droits extrapatrimoniaux, Droit a l'image, Vie privee.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Quels sont les droits attaches a la personne e.</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Droits extrapatrimoniaux, Droit a l'image, Vie privee.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Droits extrapatrimoniaux, Droit a l'image, Vie privee.</t>
         </is>
       </c>
       <c r="M36" t="n">
@@ -2908,13 +2908,13 @@
       <c r="J37" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Le droit de propriete
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Qu'est-ce que le droit de propriete e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 15500 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Droit de propriete, Usus et Fructus.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Droit de propriete, Usus, Fructus.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Qu'est-ce que le droit de propriete e.</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Droit de propriete, Usus, Fructus.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Droit de propriete, Usus, Fructus.</t>
         </is>
       </c>
       <c r="M37" t="n">
@@ -2976,13 +2976,13 @@
       <c r="J38" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Le patrimoine
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Qu'est-ce que le patrimoine e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 16750 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Patrimoine, Actif et Passif.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Patrimoine, Actif, Passif.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Qu'est-ce que le patrimoine e.</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Patrimoine, Actif, Passif.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Patrimoine, Actif, Passif.</t>
         </is>
       </c>
       <c r="M38" t="n">
@@ -3044,13 +3044,13 @@
       <c r="J39" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Les droits extrapatrimoniaux
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Quels sont les droits attaches a la personne e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 18000 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Droits extrapatrimoniaux, Droit a l'image et Vie privee.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Droits extrapatrimoniaux, Droit a l'image, Vie privee.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Quels sont les droits attaches a la personne e.</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Droits extrapatrimoniaux, Droit a l'image, Vie privee.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Droits extrapatrimoniaux, Droit a l'image, Vie privee.</t>
         </is>
       </c>
       <c r="M39" t="n">
@@ -3112,13 +3112,13 @@
       <c r="J40" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Le droit de propriete
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Qu'est-ce que le droit de propriete e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 19250 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Droit de propriete, Usus et Fructus.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Droit de propriete, Usus, Fructus.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Qu'est-ce que le droit de propriete e.</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Droit de propriete, Usus, Fructus.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Droit de propriete, Usus, Fructus.</t>
         </is>
       </c>
       <c r="M40" t="n">
@@ -3180,13 +3180,13 @@
       <c r="J41" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Le patrimoine
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Qu'est-ce que le patrimoine e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 20500 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Patrimoine, Actif et Passif.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Patrimoine, Actif, Passif.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Qu'est-ce que le patrimoine e.</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Patrimoine, Actif, Passif.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Patrimoine, Actif, Passif.</t>
         </is>
       </c>
       <c r="M41" t="n">
@@ -3247,14 +3247,14 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les agents economiques et les differents types de biens et services
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=127, indice d'emploi=100.
-Problematique: Qui sont les agents economiques et que produisent-ils e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Agents economiques, Menages et Entreprises.
+          <t>Etude economique appliquee - Les agents economiques et les differents types de biens et services
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=99, indice d'emploi=91).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Agents economiques, Menages, Entreprises.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Qui sont les agents economiques et que produisent-ils e.</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Agents economiques, Menages, Entreprises.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Agents economiques, Menages, Entreprises.</t>
         </is>
       </c>
       <c r="M42" t="n">
@@ -3315,14 +3315,14 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les decisions du consommateur et du producteur
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=134, indice d'emploi=105.
-Problematique: Comment les agents economiques prennent-ils leurs decisions e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Rationalite, Utilite marginale et Maximisation.
+          <t>Etude economique appliquee - Les decisions du consommateur et du producteur
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=103, indice d'emploi=94).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Rationalite, Utilite marginale, Maximisation.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment les agents economiques prennent-ils leurs decisions e.</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Rationalite, Utilite marginale, Maximisation.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Rationalite, Utilite marginale, Maximisation.</t>
         </is>
       </c>
       <c r="M43" t="n">
@@ -3383,14 +3383,14 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les agents economiques et les differents types de biens et services
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=141, indice d'emploi=110.
-Problematique: Qui sont les agents economiques et que produisent-ils e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Agents economiques, Menages et Entreprises.
+          <t>Etude economique appliquee - Les agents economiques et les differents types de biens et services
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=107, indice d'emploi=97).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Agents economiques, Menages, Entreprises.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Qui sont les agents economiques et que produisent-ils e.</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Agents economiques, Menages, Entreprises.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Agents economiques, Menages, Entreprises.</t>
         </is>
       </c>
       <c r="M44" t="n">
@@ -3451,14 +3451,14 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les decisions du consommateur et du producteur
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=148, indice d'emploi=115.
-Problematique: Comment les agents economiques prennent-ils leurs decisions e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Rationalite, Utilite marginale et Maximisation.
+          <t>Etude economique appliquee - Les decisions du consommateur et du producteur
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=111, indice d'emploi=100).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Rationalite, Utilite marginale, Maximisation.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment les agents economiques prennent-ils leurs decisions e.</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Rationalite, Utilite marginale, Maximisation.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Rationalite, Utilite marginale, Maximisation.</t>
         </is>
       </c>
       <c r="M45" t="n">
@@ -3519,14 +3519,14 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les agents economiques et les differents types de biens et services
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=155, indice d'emploi=120.
-Problematique: Qui sont les agents economiques et que produisent-ils e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Agents economiques, Menages et Entreprises.
+          <t>Etude economique appliquee - Les agents economiques et les differents types de biens et services
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=115, indice d'emploi=103).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Agents economiques, Menages, Entreprises.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Qui sont les agents economiques et que produisent-ils e.</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Agents economiques, Menages, Entreprises.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Agents economiques, Menages, Entreprises.</t>
         </is>
       </c>
       <c r="M46" t="n">
@@ -3587,14 +3587,14 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les decisions du consommateur et du producteur
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=162, indice d'emploi=125.
-Problematique: Comment les agents economiques prennent-ils leurs decisions e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Rationalite, Utilite marginale et Maximisation.
+          <t>Etude economique appliquee - Les decisions du consommateur et du producteur
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=119, indice d'emploi=106).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Rationalite, Utilite marginale, Maximisation.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment les agents economiques prennent-ils leurs decisions e.</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Rationalite, Utilite marginale, Maximisation.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Rationalite, Utilite marginale, Maximisation.</t>
         </is>
       </c>
       <c r="M47" t="n">
@@ -3655,14 +3655,14 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les agents economiques et les differents types de biens et services
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=169, indice d'emploi=130.
-Problematique: Qui sont les agents economiques et que produisent-ils e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Agents economiques, Menages et Entreprises.
+          <t>Etude economique appliquee - Les agents economiques et les differents types de biens et services
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=123, indice d'emploi=109).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Agents economiques, Menages, Entreprises.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Qui sont les agents economiques et que produisent-ils e.</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Agents economiques, Menages, Entreprises.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Agents economiques, Menages, Entreprises.</t>
         </is>
       </c>
       <c r="M48" t="n">
@@ -3723,14 +3723,14 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les decisions du consommateur et du producteur
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=176, indice d'emploi=135.
-Problematique: Comment les agents economiques prennent-ils leurs decisions e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Rationalite, Utilite marginale et Maximisation.
+          <t>Etude economique appliquee - Les decisions du consommateur et du producteur
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=127, indice d'emploi=112).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Rationalite, Utilite marginale, Maximisation.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment les agents economiques prennent-ils leurs decisions e.</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Rationalite, Utilite marginale, Maximisation.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Rationalite, Utilite marginale, Maximisation.</t>
         </is>
       </c>
       <c r="M49" t="n">
@@ -3791,14 +3791,14 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les agents economiques et les differents types de biens et services
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=183, indice d'emploi=140.
-Problematique: Qui sont les agents economiques et que produisent-ils e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Agents economiques, Menages et Entreprises.
+          <t>Etude economique appliquee - Les agents economiques et les differents types de biens et services
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=131, indice d'emploi=115).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Agents economiques, Menages, Entreprises.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Qui sont les agents economiques et que produisent-ils e.</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Agents economiques, Menages, Entreprises.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Agents economiques, Menages, Entreprises.</t>
         </is>
       </c>
       <c r="M50" t="n">
@@ -3859,14 +3859,14 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les decisions du consommateur et du producteur
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=190, indice d'emploi=145.
-Problematique: Comment les agents economiques prennent-ils leurs decisions e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Rationalite, Utilite marginale et Maximisation.
+          <t>Etude economique appliquee - Les decisions du consommateur et du producteur
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=135, indice d'emploi=118).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Rationalite, Utilite marginale, Maximisation.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment les agents economiques prennent-ils leurs decisions e.</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Rationalite, Utilite marginale, Maximisation.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Rationalite, Utilite marginale, Maximisation.</t>
         </is>
       </c>
       <c r="M51" t="n">
@@ -3927,14 +3927,14 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les echanges economiques
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=127, indice d'emploi=100.
-Problematique: Comment s'organisent les echanges economiques e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Marche, Offre et Demande.
+          <t>Etude economique appliquee - Les echanges economiques
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=99, indice d'emploi=91).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Marche, Offre, Demande.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment s'organisent les echanges economiques e.</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Marche, Offre, Demande.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Marche, Offre, Demande.</t>
         </is>
       </c>
       <c r="M52" t="n">
@@ -3995,14 +3995,14 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les echanges economiques
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=134, indice d'emploi=105.
-Problematique: Comment s'organisent les echanges economiques e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Marche, Offre et Demande.
+          <t>Etude economique appliquee - Les echanges economiques
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=103, indice d'emploi=94).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Marche, Offre, Demande.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment s'organisent les echanges economiques e.</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -4012,7 +4012,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Marche, Offre, Demande.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Marche, Offre, Demande.</t>
         </is>
       </c>
       <c r="M53" t="n">
@@ -4063,14 +4063,14 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les echanges economiques
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=141, indice d'emploi=110.
-Problematique: Comment s'organisent les echanges economiques e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Marche, Offre et Demande.
+          <t>Etude economique appliquee - Les echanges economiques
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=107, indice d'emploi=97).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Marche, Offre, Demande.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment s'organisent les echanges economiques e.</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -4080,7 +4080,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Marche, Offre, Demande.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Marche, Offre, Demande.</t>
         </is>
       </c>
       <c r="M54" t="n">
@@ -4131,14 +4131,14 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les echanges economiques
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=148, indice d'emploi=115.
-Problematique: Comment s'organisent les echanges economiques e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Marche, Offre et Demande.
+          <t>Etude economique appliquee - Les echanges economiques
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=111, indice d'emploi=100).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Marche, Offre, Demande.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment s'organisent les echanges economiques e.</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Marche, Offre, Demande.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Marche, Offre, Demande.</t>
         </is>
       </c>
       <c r="M55" t="n">
@@ -4199,14 +4199,14 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les echanges economiques
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=155, indice d'emploi=120.
-Problematique: Comment s'organisent les echanges economiques e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Marche, Offre et Demande.
+          <t>Etude economique appliquee - Les echanges economiques
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=115, indice d'emploi=103).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Marche, Offre, Demande.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment s'organisent les echanges economiques e.</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Marche, Offre, Demande.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Marche, Offre, Demande.</t>
         </is>
       </c>
       <c r="M56" t="n">
@@ -4267,14 +4267,14 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les echanges economiques
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=162, indice d'emploi=125.
-Problematique: Comment s'organisent les echanges economiques e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Marche, Offre et Demande.
+          <t>Etude economique appliquee - Les echanges economiques
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=119, indice d'emploi=106).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Marche, Offre, Demande.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment s'organisent les echanges economiques e.</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Marche, Offre, Demande.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Marche, Offre, Demande.</t>
         </is>
       </c>
       <c r="M57" t="n">
@@ -4335,14 +4335,14 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les echanges economiques
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=169, indice d'emploi=130.
-Problematique: Comment s'organisent les echanges economiques e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Marche, Offre et Demande.
+          <t>Etude economique appliquee - Les echanges economiques
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=123, indice d'emploi=109).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Marche, Offre, Demande.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment s'organisent les echanges economiques e.</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Marche, Offre, Demande.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Marche, Offre, Demande.</t>
         </is>
       </c>
       <c r="M58" t="n">
@@ -4403,14 +4403,14 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les echanges economiques
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=176, indice d'emploi=135.
-Problematique: Comment s'organisent les echanges economiques e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Marche, Offre et Demande.
+          <t>Etude economique appliquee - Les echanges economiques
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=127, indice d'emploi=112).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Marche, Offre, Demande.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment s'organisent les echanges economiques e.</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Marche, Offre, Demande.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Marche, Offre, Demande.</t>
         </is>
       </c>
       <c r="M59" t="n">
@@ -4471,14 +4471,14 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les echanges economiques
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=183, indice d'emploi=140.
-Problematique: Comment s'organisent les echanges economiques e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Marche, Offre et Demande.
+          <t>Etude economique appliquee - Les echanges economiques
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=131, indice d'emploi=115).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Marche, Offre, Demande.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment s'organisent les echanges economiques e.</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Marche, Offre, Demande.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Marche, Offre, Demande.</t>
         </is>
       </c>
       <c r="M60" t="n">
@@ -4539,14 +4539,14 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les echanges economiques
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=190, indice d'emploi=145.
-Problematique: Comment s'organisent les echanges economiques e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Marche, Offre et Demande.
+          <t>Etude economique appliquee - Les echanges economiques
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=135, indice d'emploi=118).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Marche, Offre, Demande.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment s'organisent les echanges economiques e.</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Marche, Offre, Demande.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Marche, Offre, Demande.</t>
         </is>
       </c>
       <c r="M61" t="n">
@@ -4607,14 +4607,14 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - La combinaison des facteurs de production
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=127, indice d'emploi=100.
-Problematique: Comment les entreprises produisent-elles e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Facteurs de production, Travail et Capital.
+          <t>Etude economique appliquee - La combinaison des facteurs de production
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=99, indice d'emploi=91).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Facteurs de production, Travail, Capital.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment les entreprises produisent-elles e.</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4624,7 +4624,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Facteurs de production, Travail, Capital.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Facteurs de production, Travail, Capital.</t>
         </is>
       </c>
       <c r="M62" t="n">
@@ -4675,14 +4675,14 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - La mesure de la production
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=134, indice d'emploi=105.
-Problematique: Comment mesure-t-on la production nationale e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant PIB, Valeur ajoutee et Production marchande.
+          <t>Etude economique appliquee - La mesure de la production
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=103, indice d'emploi=94).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant PIB, Valeur ajoutee, Production marchande.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment mesure-t-on la production nationale e.</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: PIB, Valeur ajoutee, Production marchande.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: PIB, Valeur ajoutee, Production marchande.</t>
         </is>
       </c>
       <c r="M63" t="n">
@@ -4743,14 +4743,14 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - La combinaison des facteurs de production
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=141, indice d'emploi=110.
-Problematique: Comment les entreprises produisent-elles e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Facteurs de production, Travail et Capital.
+          <t>Etude economique appliquee - La combinaison des facteurs de production
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=107, indice d'emploi=97).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Facteurs de production, Travail, Capital.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment les entreprises produisent-elles e.</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Facteurs de production, Travail, Capital.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Facteurs de production, Travail, Capital.</t>
         </is>
       </c>
       <c r="M64" t="n">
@@ -4811,14 +4811,14 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - La mesure de la production
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=148, indice d'emploi=115.
-Problematique: Comment mesure-t-on la production nationale e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant PIB, Valeur ajoutee et Production marchande.
+          <t>Etude economique appliquee - La mesure de la production
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=111, indice d'emploi=100).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant PIB, Valeur ajoutee, Production marchande.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment mesure-t-on la production nationale e.</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: PIB, Valeur ajoutee, Production marchande.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: PIB, Valeur ajoutee, Production marchande.</t>
         </is>
       </c>
       <c r="M65" t="n">
@@ -4879,14 +4879,14 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - La combinaison des facteurs de production
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=155, indice d'emploi=120.
-Problematique: Comment les entreprises produisent-elles e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Facteurs de production, Travail et Capital.
+          <t>Etude economique appliquee - La combinaison des facteurs de production
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=115, indice d'emploi=103).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Facteurs de production, Travail, Capital.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment les entreprises produisent-elles e.</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Facteurs de production, Travail, Capital.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Facteurs de production, Travail, Capital.</t>
         </is>
       </c>
       <c r="M66" t="n">
@@ -4947,14 +4947,14 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - La mesure de la production
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=162, indice d'emploi=125.
-Problematique: Comment mesure-t-on la production nationale e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant PIB, Valeur ajoutee et Production marchande.
+          <t>Etude economique appliquee - La mesure de la production
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=119, indice d'emploi=106).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant PIB, Valeur ajoutee, Production marchande.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment mesure-t-on la production nationale e.</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: PIB, Valeur ajoutee, Production marchande.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: PIB, Valeur ajoutee, Production marchande.</t>
         </is>
       </c>
       <c r="M67" t="n">
@@ -5015,14 +5015,14 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - La combinaison des facteurs de production
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=169, indice d'emploi=130.
-Problematique: Comment les entreprises produisent-elles e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Facteurs de production, Travail et Capital.
+          <t>Etude economique appliquee - La combinaison des facteurs de production
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=123, indice d'emploi=109).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Facteurs de production, Travail, Capital.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment les entreprises produisent-elles e.</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Facteurs de production, Travail, Capital.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Facteurs de production, Travail, Capital.</t>
         </is>
       </c>
       <c r="M68" t="n">
@@ -5083,14 +5083,14 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - La mesure de la production
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=176, indice d'emploi=135.
-Problematique: Comment mesure-t-on la production nationale e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant PIB, Valeur ajoutee et Production marchande.
+          <t>Etude economique appliquee - La mesure de la production
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=127, indice d'emploi=112).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant PIB, Valeur ajoutee, Production marchande.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment mesure-t-on la production nationale e.</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: PIB, Valeur ajoutee, Production marchande.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: PIB, Valeur ajoutee, Production marchande.</t>
         </is>
       </c>
       <c r="M69" t="n">
@@ -5151,14 +5151,14 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - La combinaison des facteurs de production
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=183, indice d'emploi=140.
-Problematique: Comment les entreprises produisent-elles e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Facteurs de production, Travail et Capital.
+          <t>Etude economique appliquee - La combinaison des facteurs de production
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=131, indice d'emploi=115).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Facteurs de production, Travail, Capital.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment les entreprises produisent-elles e.</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Facteurs de production, Travail, Capital.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Facteurs de production, Travail, Capital.</t>
         </is>
       </c>
       <c r="M70" t="n">
@@ -5219,14 +5219,14 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - La mesure de la production
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=190, indice d'emploi=145.
-Problematique: Comment mesure-t-on la production nationale e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant PIB, Valeur ajoutee et Production marchande.
+          <t>Etude economique appliquee - La mesure de la production
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=135, indice d'emploi=118).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant PIB, Valeur ajoutee, Production marchande.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment mesure-t-on la production nationale e.</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: PIB, Valeur ajoutee, Production marchande.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: PIB, Valeur ajoutee, Production marchande.</t>
         </is>
       </c>
       <c r="M71" t="n">
@@ -5287,14 +5287,14 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - La dynamique de repartition des revenus
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=127, indice d'emploi=100.
-Problematique: Comment les revenus sont-ils repartis e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Salaires, Profits et Revenus de transfert.
+          <t>Etude economique appliquee - La dynamique de repartition des revenus
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=99, indice d'emploi=91).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Salaires, Profits, Revenus de transfert.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment les revenus sont-ils repartis e.</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -5304,7 +5304,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Salaires, Profits, Revenus de transfert.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Salaires, Profits, Revenus de transfert.</t>
         </is>
       </c>
       <c r="M72" t="n">
@@ -5355,14 +5355,14 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - La dynamique de repartition des revenus
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=134, indice d'emploi=105.
-Problematique: Comment les revenus sont-ils repartis e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Salaires, Profits et Revenus de transfert.
+          <t>Etude economique appliquee - La dynamique de repartition des revenus
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=103, indice d'emploi=94).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Salaires, Profits, Revenus de transfert.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment les revenus sont-ils repartis e.</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Salaires, Profits, Revenus de transfert.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Salaires, Profits, Revenus de transfert.</t>
         </is>
       </c>
       <c r="M73" t="n">
@@ -5423,14 +5423,14 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - La dynamique de repartition des revenus
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=141, indice d'emploi=110.
-Problematique: Comment les revenus sont-ils repartis e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Salaires, Profits et Revenus de transfert.
+          <t>Etude economique appliquee - La dynamique de repartition des revenus
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=107, indice d'emploi=97).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Salaires, Profits, Revenus de transfert.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment les revenus sont-ils repartis e.</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Salaires, Profits, Revenus de transfert.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Salaires, Profits, Revenus de transfert.</t>
         </is>
       </c>
       <c r="M74" t="n">
@@ -5491,14 +5491,14 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - La dynamique de repartition des revenus
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=148, indice d'emploi=115.
-Problematique: Comment les revenus sont-ils repartis e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Salaires, Profits et Revenus de transfert.
+          <t>Etude economique appliquee - La dynamique de repartition des revenus
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=111, indice d'emploi=100).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Salaires, Profits, Revenus de transfert.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment les revenus sont-ils repartis e.</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Salaires, Profits, Revenus de transfert.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Salaires, Profits, Revenus de transfert.</t>
         </is>
       </c>
       <c r="M75" t="n">
@@ -5559,14 +5559,14 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - La dynamique de repartition des revenus
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=155, indice d'emploi=120.
-Problematique: Comment les revenus sont-ils repartis e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Salaires, Profits et Revenus de transfert.
+          <t>Etude economique appliquee - La dynamique de repartition des revenus
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=115, indice d'emploi=103).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Salaires, Profits, Revenus de transfert.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment les revenus sont-ils repartis e.</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Salaires, Profits, Revenus de transfert.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Salaires, Profits, Revenus de transfert.</t>
         </is>
       </c>
       <c r="M76" t="n">
@@ -5627,14 +5627,14 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - La dynamique de repartition des revenus
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=162, indice d'emploi=125.
-Problematique: Comment les revenus sont-ils repartis e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Salaires, Profits et Revenus de transfert.
+          <t>Etude economique appliquee - La dynamique de repartition des revenus
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=119, indice d'emploi=106).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Salaires, Profits, Revenus de transfert.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment les revenus sont-ils repartis e.</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5644,7 +5644,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Salaires, Profits, Revenus de transfert.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Salaires, Profits, Revenus de transfert.</t>
         </is>
       </c>
       <c r="M77" t="n">
@@ -5695,14 +5695,14 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - La dynamique de repartition des revenus
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=169, indice d'emploi=130.
-Problematique: Comment les revenus sont-ils repartis e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Salaires, Profits et Revenus de transfert.
+          <t>Etude economique appliquee - La dynamique de repartition des revenus
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=123, indice d'emploi=109).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Salaires, Profits, Revenus de transfert.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment les revenus sont-ils repartis e.</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Salaires, Profits, Revenus de transfert.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Salaires, Profits, Revenus de transfert.</t>
         </is>
       </c>
       <c r="M78" t="n">
@@ -5763,14 +5763,14 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - La dynamique de repartition des revenus
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=176, indice d'emploi=135.
-Problematique: Comment les revenus sont-ils repartis e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Salaires, Profits et Revenus de transfert.
+          <t>Etude economique appliquee - La dynamique de repartition des revenus
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=127, indice d'emploi=112).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Salaires, Profits, Revenus de transfert.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment les revenus sont-ils repartis e.</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Salaires, Profits, Revenus de transfert.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Salaires, Profits, Revenus de transfert.</t>
         </is>
       </c>
       <c r="M79" t="n">
@@ -5831,14 +5831,14 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - La dynamique de repartition des revenus
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=183, indice d'emploi=140.
-Problematique: Comment les revenus sont-ils repartis e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Salaires, Profits et Revenus de transfert.
+          <t>Etude economique appliquee - La dynamique de repartition des revenus
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=131, indice d'emploi=115).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Salaires, Profits, Revenus de transfert.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment les revenus sont-ils repartis e.</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Salaires, Profits, Revenus de transfert.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Salaires, Profits, Revenus de transfert.</t>
         </is>
       </c>
       <c r="M80" t="n">
@@ -5899,14 +5899,14 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - La dynamique de repartition des revenus
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=190, indice d'emploi=145.
-Problematique: Comment les revenus sont-ils repartis e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Salaires, Profits et Revenus de transfert.
+          <t>Etude economique appliquee - La dynamique de repartition des revenus
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=135, indice d'emploi=118).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Salaires, Profits, Revenus de transfert.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment les revenus sont-ils repartis e.</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5916,7 +5916,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Salaires, Profits, Revenus de transfert.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Salaires, Profits, Revenus de transfert.</t>
         </is>
       </c>
       <c r="M81" t="n">
@@ -5967,14 +5967,14 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - L'arbitrage entre consommation et epargne
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=127, indice d'emploi=100.
-Problematique: Comment les menages utilisent-ils leurs revenus e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Consommation, Epargne et Revenu disponible.
+          <t>Etude economique appliquee - L'arbitrage entre consommation et epargne
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=99, indice d'emploi=91).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Consommation, Epargne, Revenu disponible.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment les menages utilisent-ils leurs revenus e.</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Consommation, Epargne, Revenu disponible.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Consommation, Epargne, Revenu disponible.</t>
         </is>
       </c>
       <c r="M82" t="n">
@@ -6035,14 +6035,14 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Pouvoir d'achat et structure de consommation des menages
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=134, indice d'emploi=105.
-Problematique: Comment evolue la consommation des menages e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Pouvoir d'achat, Indice des prix et Structure de consommation.
+          <t>Etude economique appliquee - Pouvoir d'achat et structure de consommation des menages
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=103, indice d'emploi=94).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Pouvoir d'achat, Indice des prix, Structure de consommation.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment evolue la consommation des menages e.</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -6052,7 +6052,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Pouvoir d'achat, Indice des prix, Structure de consommation.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Pouvoir d'achat, Indice des prix, Structure de consommation.</t>
         </is>
       </c>
       <c r="M83" t="n">
@@ -6103,14 +6103,14 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - L'arbitrage entre consommation et epargne
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=141, indice d'emploi=110.
-Problematique: Comment les menages utilisent-ils leurs revenus e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Consommation, Epargne et Revenu disponible.
+          <t>Etude economique appliquee - L'arbitrage entre consommation et epargne
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=107, indice d'emploi=97).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Consommation, Epargne, Revenu disponible.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment les menages utilisent-ils leurs revenus e.</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Consommation, Epargne, Revenu disponible.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Consommation, Epargne, Revenu disponible.</t>
         </is>
       </c>
       <c r="M84" t="n">
@@ -6171,14 +6171,14 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Pouvoir d'achat et structure de consommation des menages
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=148, indice d'emploi=115.
-Problematique: Comment evolue la consommation des menages e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Pouvoir d'achat, Indice des prix et Structure de consommation.
+          <t>Etude economique appliquee - Pouvoir d'achat et structure de consommation des menages
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=111, indice d'emploi=100).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Pouvoir d'achat, Indice des prix, Structure de consommation.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment evolue la consommation des menages e.</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Pouvoir d'achat, Indice des prix, Structure de consommation.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Pouvoir d'achat, Indice des prix, Structure de consommation.</t>
         </is>
       </c>
       <c r="M85" t="n">
@@ -6239,14 +6239,14 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - L'arbitrage entre consommation et epargne
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=155, indice d'emploi=120.
-Problematique: Comment les menages utilisent-ils leurs revenus e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Consommation, Epargne et Revenu disponible.
+          <t>Etude economique appliquee - L'arbitrage entre consommation et epargne
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=115, indice d'emploi=103).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Consommation, Epargne, Revenu disponible.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment les menages utilisent-ils leurs revenus e.</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -6256,7 +6256,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Consommation, Epargne, Revenu disponible.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Consommation, Epargne, Revenu disponible.</t>
         </is>
       </c>
       <c r="M86" t="n">
@@ -6307,14 +6307,14 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Pouvoir d'achat et structure de consommation des menages
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=162, indice d'emploi=125.
-Problematique: Comment evolue la consommation des menages e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Pouvoir d'achat, Indice des prix et Structure de consommation.
+          <t>Etude economique appliquee - Pouvoir d'achat et structure de consommation des menages
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=119, indice d'emploi=106).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Pouvoir d'achat, Indice des prix, Structure de consommation.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment evolue la consommation des menages e.</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Pouvoir d'achat, Indice des prix, Structure de consommation.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Pouvoir d'achat, Indice des prix, Structure de consommation.</t>
         </is>
       </c>
       <c r="M87" t="n">
@@ -6375,14 +6375,14 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - L'arbitrage entre consommation et epargne
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=169, indice d'emploi=130.
-Problematique: Comment les menages utilisent-ils leurs revenus e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Consommation, Epargne et Revenu disponible.
+          <t>Etude economique appliquee - L'arbitrage entre consommation et epargne
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=123, indice d'emploi=109).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Consommation, Epargne, Revenu disponible.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment les menages utilisent-ils leurs revenus e.</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -6392,7 +6392,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Consommation, Epargne, Revenu disponible.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Consommation, Epargne, Revenu disponible.</t>
         </is>
       </c>
       <c r="M88" t="n">
@@ -6443,14 +6443,14 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Pouvoir d'achat et structure de consommation des menages
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=176, indice d'emploi=135.
-Problematique: Comment evolue la consommation des menages e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Pouvoir d'achat, Indice des prix et Structure de consommation.
+          <t>Etude economique appliquee - Pouvoir d'achat et structure de consommation des menages
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=127, indice d'emploi=112).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Pouvoir d'achat, Indice des prix, Structure de consommation.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment evolue la consommation des menages e.</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Pouvoir d'achat, Indice des prix, Structure de consommation.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Pouvoir d'achat, Indice des prix, Structure de consommation.</t>
         </is>
       </c>
       <c r="M89" t="n">
@@ -6511,14 +6511,14 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - L'arbitrage entre consommation et epargne
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=183, indice d'emploi=140.
-Problematique: Comment les menages utilisent-ils leurs revenus e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Consommation, Epargne et Revenu disponible.
+          <t>Etude economique appliquee - L'arbitrage entre consommation et epargne
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=131, indice d'emploi=115).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Consommation, Epargne, Revenu disponible.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment les menages utilisent-ils leurs revenus e.</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Consommation, Epargne, Revenu disponible.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Consommation, Epargne, Revenu disponible.</t>
         </is>
       </c>
       <c r="M90" t="n">
@@ -6579,14 +6579,14 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Pouvoir d'achat et structure de consommation des menages
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=190, indice d'emploi=145.
-Problematique: Comment evolue la consommation des menages e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Pouvoir d'achat, Indice des prix et Structure de consommation.
+          <t>Etude economique appliquee - Pouvoir d'achat et structure de consommation des menages
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=135, indice d'emploi=118).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Pouvoir d'achat, Indice des prix, Structure de consommation.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment evolue la consommation des menages e.</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6596,7 +6596,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Pouvoir d'achat, Indice des prix, Structure de consommation.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Pouvoir d'achat, Indice des prix, Structure de consommation.</t>
         </is>
       </c>
       <c r="M91" t="n">
@@ -6647,14 +6647,14 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - La situation financiere des agents economiques
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=127, indice d'emploi=100.
-Problematique: Comment les agents economiques financent-ils leurs activites e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Capacite de financement, Besoin de financement et Epargne.
+          <t>Etude economique appliquee - La situation financiere des agents economiques
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=99, indice d'emploi=91).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Capacite de financement, Besoin de financement, Epargne.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment les agents economiques financent-ils leurs activites e.</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Capacite de financement, Besoin de financement, Epargne.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Capacite de financement, Besoin de financement, Epargne.</t>
         </is>
       </c>
       <c r="M92" t="n">
@@ -6715,14 +6715,14 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les modalites de financement de l'economie
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=134, indice d'emploi=105.
-Problematique: Comment l'economie se finance-t-elle e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Financement direct, Financement indirect et Marche financier.
+          <t>Etude economique appliquee - Les modalites de financement de l'economie
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=103, indice d'emploi=94).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Financement direct, Financement indirect, Marche financier.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment l'economie se finance-t-elle e.</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6732,7 +6732,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Financement direct, Financement indirect, Marche financier.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Financement direct, Financement indirect, Marche financier.</t>
         </is>
       </c>
       <c r="M93" t="n">
@@ -6783,14 +6783,14 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - La situation financiere des agents economiques
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=141, indice d'emploi=110.
-Problematique: Comment les agents economiques financent-ils leurs activites e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Capacite de financement, Besoin de financement et Epargne.
+          <t>Etude economique appliquee - La situation financiere des agents economiques
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=107, indice d'emploi=97).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Capacite de financement, Besoin de financement, Epargne.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment les agents economiques financent-ils leurs activites e.</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Capacite de financement, Besoin de financement, Epargne.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Capacite de financement, Besoin de financement, Epargne.</t>
         </is>
       </c>
       <c r="M94" t="n">
@@ -6851,14 +6851,14 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les modalites de financement de l'economie
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=148, indice d'emploi=115.
-Problematique: Comment l'economie se finance-t-elle e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Financement direct, Financement indirect et Marche financier.
+          <t>Etude economique appliquee - Les modalites de financement de l'economie
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=111, indice d'emploi=100).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Financement direct, Financement indirect, Marche financier.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment l'economie se finance-t-elle e.</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6868,7 +6868,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Financement direct, Financement indirect, Marche financier.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Financement direct, Financement indirect, Marche financier.</t>
         </is>
       </c>
       <c r="M95" t="n">
@@ -6919,14 +6919,14 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - La situation financiere des agents economiques
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=155, indice d'emploi=120.
-Problematique: Comment les agents economiques financent-ils leurs activites e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Capacite de financement, Besoin de financement et Epargne.
+          <t>Etude economique appliquee - La situation financiere des agents economiques
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=115, indice d'emploi=103).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Capacite de financement, Besoin de financement, Epargne.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment les agents economiques financent-ils leurs activites e.</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Capacite de financement, Besoin de financement, Epargne.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Capacite de financement, Besoin de financement, Epargne.</t>
         </is>
       </c>
       <c r="M96" t="n">
@@ -6987,14 +6987,14 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les modalites de financement de l'economie
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=162, indice d'emploi=125.
-Problematique: Comment l'economie se finance-t-elle e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Financement direct, Financement indirect et Marche financier.
+          <t>Etude economique appliquee - Les modalites de financement de l'economie
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=119, indice d'emploi=106).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Financement direct, Financement indirect, Marche financier.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment l'economie se finance-t-elle e.</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -7004,7 +7004,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Financement direct, Financement indirect, Marche financier.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Financement direct, Financement indirect, Marche financier.</t>
         </is>
       </c>
       <c r="M97" t="n">
@@ -7055,14 +7055,14 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - La situation financiere des agents economiques
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=169, indice d'emploi=130.
-Problematique: Comment les agents economiques financent-ils leurs activites e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Capacite de financement, Besoin de financement et Epargne.
+          <t>Etude economique appliquee - La situation financiere des agents economiques
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=123, indice d'emploi=109).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Capacite de financement, Besoin de financement, Epargne.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment les agents economiques financent-ils leurs activites e.</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -7072,7 +7072,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Capacite de financement, Besoin de financement, Epargne.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Capacite de financement, Besoin de financement, Epargne.</t>
         </is>
       </c>
       <c r="M98" t="n">
@@ -7123,14 +7123,14 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les modalites de financement de l'economie
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=176, indice d'emploi=135.
-Problematique: Comment l'economie se finance-t-elle e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Financement direct, Financement indirect et Marche financier.
+          <t>Etude economique appliquee - Les modalites de financement de l'economie
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=127, indice d'emploi=112).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Financement direct, Financement indirect, Marche financier.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment l'economie se finance-t-elle e.</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -7140,7 +7140,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Financement direct, Financement indirect, Marche financier.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Financement direct, Financement indirect, Marche financier.</t>
         </is>
       </c>
       <c r="M99" t="n">
@@ -7191,14 +7191,14 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - La situation financiere des agents economiques
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=183, indice d'emploi=140.
-Problematique: Comment les agents economiques financent-ils leurs activites e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Capacite de financement, Besoin de financement et Epargne.
+          <t>Etude economique appliquee - La situation financiere des agents economiques
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=131, indice d'emploi=115).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Capacite de financement, Besoin de financement, Epargne.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment les agents economiques financent-ils leurs activites e.</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -7208,7 +7208,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Capacite de financement, Besoin de financement, Epargne.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Capacite de financement, Besoin de financement, Epargne.</t>
         </is>
       </c>
       <c r="M100" t="n">
@@ -7259,14 +7259,14 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les modalites de financement de l'economie
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=190, indice d'emploi=145.
-Problematique: Comment l'economie se finance-t-elle e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Financement direct, Financement indirect et Marche financier.
+          <t>Etude economique appliquee - Les modalites de financement de l'economie
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=135, indice d'emploi=118).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Financement direct, Financement indirect, Marche financier.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment l'economie se finance-t-elle e.</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Financement direct, Financement indirect, Marche financier.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Financement direct, Financement indirect, Marche financier.</t>
         </is>
       </c>
       <c r="M101" t="n">
@@ -7327,14 +7327,14 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - L'intensite de la concurrence selon les marches
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=127, indice d'emploi=100.
-Problematique: Quelles sont les structures de marche e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Concurrence pure et parfaite, Monopole et Oligopole.
+          <t>Etude economique appliquee - L'intensite de la concurrence selon les marches
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=99, indice d'emploi=91).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Concurrence pure et parfaite, Monopole, Oligopole.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Quelles sont les structures de marche e.</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Concurrence pure et parfaite, Monopole, Oligopole.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Concurrence pure et parfaite, Monopole, Oligopole.</t>
         </is>
       </c>
       <c r="M102" t="n">
@@ -7395,14 +7395,14 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les strategies pour depasser l'intensite concurrentielle
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=134, indice d'emploi=105.
-Problematique: Comment les entreprises font-elles face a la concurrence e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Strategies concurrentielles, Differenciation et Innovation.
+          <t>Etude economique appliquee - Les strategies pour depasser l'intensite concurrentielle
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=103, indice d'emploi=94).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Strategies concurrentielles, Differenciation, Innovation.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment les entreprises font-elles face a la concurrence e.</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -7412,7 +7412,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Strategies concurrentielles, Differenciation, Innovation.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Strategies concurrentielles, Differenciation, Innovation.</t>
         </is>
       </c>
       <c r="M103" t="n">
@@ -7463,14 +7463,14 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - L'intensite de la concurrence selon les marches
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=141, indice d'emploi=110.
-Problematique: Quelles sont les structures de marche e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Concurrence pure et parfaite, Monopole et Oligopole.
+          <t>Etude economique appliquee - L'intensite de la concurrence selon les marches
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=107, indice d'emploi=97).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Concurrence pure et parfaite, Monopole, Oligopole.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Quelles sont les structures de marche e.</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Concurrence pure et parfaite, Monopole, Oligopole.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Concurrence pure et parfaite, Monopole, Oligopole.</t>
         </is>
       </c>
       <c r="M104" t="n">
@@ -7531,14 +7531,14 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les strategies pour depasser l'intensite concurrentielle
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=148, indice d'emploi=115.
-Problematique: Comment les entreprises font-elles face a la concurrence e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Strategies concurrentielles, Differenciation et Innovation.
+          <t>Etude economique appliquee - Les strategies pour depasser l'intensite concurrentielle
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=111, indice d'emploi=100).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Strategies concurrentielles, Differenciation, Innovation.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment les entreprises font-elles face a la concurrence e.</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -7548,7 +7548,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Strategies concurrentielles, Differenciation, Innovation.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Strategies concurrentielles, Differenciation, Innovation.</t>
         </is>
       </c>
       <c r="M105" t="n">
@@ -7599,14 +7599,14 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - L'intensite de la concurrence selon les marches
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=155, indice d'emploi=120.
-Problematique: Quelles sont les structures de marche e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Concurrence pure et parfaite, Monopole et Oligopole.
+          <t>Etude economique appliquee - L'intensite de la concurrence selon les marches
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=115, indice d'emploi=103).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Concurrence pure et parfaite, Monopole, Oligopole.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Quelles sont les structures de marche e.</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Concurrence pure et parfaite, Monopole, Oligopole.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Concurrence pure et parfaite, Monopole, Oligopole.</t>
         </is>
       </c>
       <c r="M106" t="n">
@@ -7667,14 +7667,14 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les strategies pour depasser l'intensite concurrentielle
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=162, indice d'emploi=125.
-Problematique: Comment les entreprises font-elles face a la concurrence e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Strategies concurrentielles, Differenciation et Innovation.
+          <t>Etude economique appliquee - Les strategies pour depasser l'intensite concurrentielle
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=119, indice d'emploi=106).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Strategies concurrentielles, Differenciation, Innovation.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment les entreprises font-elles face a la concurrence e.</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -7684,7 +7684,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Strategies concurrentielles, Differenciation, Innovation.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Strategies concurrentielles, Differenciation, Innovation.</t>
         </is>
       </c>
       <c r="M107" t="n">
@@ -7735,14 +7735,14 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - L'intensite de la concurrence selon les marches
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=169, indice d'emploi=130.
-Problematique: Quelles sont les structures de marche e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Concurrence pure et parfaite, Monopole et Oligopole.
+          <t>Etude economique appliquee - L'intensite de la concurrence selon les marches
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=123, indice d'emploi=109).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Concurrence pure et parfaite, Monopole, Oligopole.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Quelles sont les structures de marche e.</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -7752,7 +7752,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Concurrence pure et parfaite, Monopole, Oligopole.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Concurrence pure et parfaite, Monopole, Oligopole.</t>
         </is>
       </c>
       <c r="M108" t="n">
@@ -7803,14 +7803,14 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les strategies pour depasser l'intensite concurrentielle
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=176, indice d'emploi=135.
-Problematique: Comment les entreprises font-elles face a la concurrence e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Strategies concurrentielles, Differenciation et Innovation.
+          <t>Etude economique appliquee - Les strategies pour depasser l'intensite concurrentielle
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=127, indice d'emploi=112).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Strategies concurrentielles, Differenciation, Innovation.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment les entreprises font-elles face a la concurrence e.</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -7820,7 +7820,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Strategies concurrentielles, Differenciation, Innovation.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Strategies concurrentielles, Differenciation, Innovation.</t>
         </is>
       </c>
       <c r="M109" t="n">
@@ -7871,14 +7871,14 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - L'intensite de la concurrence selon les marches
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=183, indice d'emploi=140.
-Problematique: Quelles sont les structures de marche e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Concurrence pure et parfaite, Monopole et Oligopole.
+          <t>Etude economique appliquee - L'intensite de la concurrence selon les marches
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=131, indice d'emploi=115).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Concurrence pure et parfaite, Monopole, Oligopole.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Quelles sont les structures de marche e.</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -7888,7 +7888,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Concurrence pure et parfaite, Monopole, Oligopole.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Concurrence pure et parfaite, Monopole, Oligopole.</t>
         </is>
       </c>
       <c r="M110" t="n">
@@ -7939,14 +7939,14 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les strategies pour depasser l'intensite concurrentielle
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=190, indice d'emploi=145.
-Problematique: Comment les entreprises font-elles face a la concurrence e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Strategies concurrentielles, Differenciation et Innovation.
+          <t>Etude economique appliquee - Les strategies pour depasser l'intensite concurrentielle
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=135, indice d'emploi=118).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Strategies concurrentielles, Differenciation, Innovation.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment les entreprises font-elles face a la concurrence e.</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -7956,7 +7956,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Strategies concurrentielles, Differenciation, Innovation.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Strategies concurrentielles, Differenciation, Innovation.</t>
         </is>
       </c>
       <c r="M111" t="n">
@@ -8007,14 +8007,15 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Etude de cas management - L'organisation de l'action collective
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Pourquoi est-il necessaire d'organiser l'action collective e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Action collective, Objectifs et Interets individuels et collectifs.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - L'organisation de l'action collective
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Action collective, Objectifs, Interets individuels et collectifs.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Pourquoi est-il necessaire d'organiser l'action collective e.</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -8024,7 +8025,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Action collective, Objectifs, Interets individuels et collectifs.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Action collective, Objectifs, Interets individuels et collectifs.</t>
         </is>
       </c>
       <c r="M112" t="n">
@@ -8075,14 +8076,15 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Etude de cas management - Les criteres et les specificites d'une entreprise privee
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Comment apprehender la diversite des organisations e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Finalites, Buts et Biens et services marchands.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - Les criteres et les specificites d'une entreprise privee
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Finalites, Buts, Biens et services marchands.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Comment apprehender la diversite des organisations e.</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -8092,7 +8094,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Finalites, Buts, Biens et services marchands.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Finalites, Buts, Biens et services marchands.</t>
         </is>
       </c>
       <c r="M113" t="n">
@@ -8143,14 +8145,15 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Etude de cas management - Les criteres et les specificites des organisations publiques
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Comment apprehender la diversite des organisations e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Secteur public, Financement public et Organisations publiques.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - Les criteres et les specificites des organisations publiques
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Secteur public, Financement public, Organisations publiques.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Comment apprehender la diversite des organisations e.</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -8160,7 +8163,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Secteur public, Financement public, Organisations publiques.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Secteur public, Financement public, Organisations publiques.</t>
         </is>
       </c>
       <c r="M114" t="n">
@@ -8211,14 +8214,15 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Etude de cas management - Les criteres et les specificites des organisations de la societe civile
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Comment apprehender la diversite des organisations e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant But non lucratif, Associations et ONG.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - Les criteres et les specificites des organisations de la societe civile
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant But non lucratif, Associations, ONG.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Comment apprehender la diversite des organisations e.</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -8228,7 +8232,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: But non lucratif, Associations, ONG.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: But non lucratif, Associations, ONG.</t>
         </is>
       </c>
       <c r="M115" t="n">
@@ -8279,14 +8283,15 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Etude de cas management - Le management des organisations
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Qu'est-ce que le management des organisations e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Definition du management, Fonctions du management et Management strategique.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - Le management des organisations
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Definition du management, Fonctions du management, Management strategique.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Qu'est-ce que le management des organisations e.</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -8296,7 +8301,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Definition du management, Fonctions du management, Management strategique.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Definition du management, Fonctions du management, Management strategique.</t>
         </is>
       </c>
       <c r="M116" t="n">
@@ -8347,14 +8352,15 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Etude de cas management - L'influence de l'environnement sur le management des organisations
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Comment le management permet-il de repondre aux changements de l'environnement e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Organisation comme systeme complexe, Parties prenantes et RSE.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - L'influence de l'environnement sur le management des organisations
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Organisation comme systeme complexe, Parties prenantes, RSE.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Comment le management permet-il de repondre aux changements de l'environnement e.</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -8364,7 +8370,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Organisation comme systeme complexe, Parties prenantes, RSE.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Organisation comme systeme complexe, Parties prenantes, RSE.</t>
         </is>
       </c>
       <c r="M117" t="n">
@@ -8415,14 +8421,15 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Etude de cas management - L'organisation de l'action collective
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Pourquoi est-il necessaire d'organiser l'action collective e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Action collective, Objectifs et Interets individuels et collectifs.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - L'organisation de l'action collective
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Action collective, Objectifs, Interets individuels et collectifs.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Pourquoi est-il necessaire d'organiser l'action collective e.</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -8432,7 +8439,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Action collective, Objectifs, Interets individuels et collectifs.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Action collective, Objectifs, Interets individuels et collectifs.</t>
         </is>
       </c>
       <c r="M118" t="n">
@@ -8483,14 +8490,15 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Etude de cas management - Les criteres et les specificites d'une entreprise privee
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Comment apprehender la diversite des organisations e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Finalites, Buts et Biens et services marchands.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - Les criteres et les specificites d'une entreprise privee
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Finalites, Buts, Biens et services marchands.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Comment apprehender la diversite des organisations e.</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -8500,7 +8508,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Finalites, Buts, Biens et services marchands.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Finalites, Buts, Biens et services marchands.</t>
         </is>
       </c>
       <c r="M119" t="n">
@@ -8551,14 +8559,15 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Etude de cas management - Les criteres et les specificites des organisations publiques
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Comment apprehender la diversite des organisations e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Secteur public, Financement public et Organisations publiques.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - Les criteres et les specificites des organisations publiques
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Secteur public, Financement public, Organisations publiques.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Comment apprehender la diversite des organisations e.</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -8568,7 +8577,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Secteur public, Financement public, Organisations publiques.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Secteur public, Financement public, Organisations publiques.</t>
         </is>
       </c>
       <c r="M120" t="n">
@@ -8619,14 +8628,15 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Etude de cas management - Les criteres et les specificites des organisations de la societe civile
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Comment apprehender la diversite des organisations e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant But non lucratif, Associations et ONG.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - Les criteres et les specificites des organisations de la societe civile
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant But non lucratif, Associations, ONG.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Comment apprehender la diversite des organisations e.</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -8636,7 +8646,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: But non lucratif, Associations, ONG.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: But non lucratif, Associations, ONG.</t>
         </is>
       </c>
       <c r="M121" t="n">
@@ -8687,14 +8697,15 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Etude de cas management - La demarche strategique
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Qu'est-ce que la strategie e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Definition de la strategie, Demarche strategique et Forces.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - La demarche strategique
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Definition de la strategie, Demarche strategique, Forces.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Qu'est-ce que la strategie e.</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -8704,7 +8715,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Definition de la strategie, Demarche strategique, Forces.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Definition de la strategie, Demarche strategique, Forces.</t>
         </is>
       </c>
       <c r="M122" t="n">
@@ -8755,14 +8766,15 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Etude de cas management - Le diagnostic strategique interne
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Comment elaborer le diagnostic strategique e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Diagnostic interne, Forces et Faiblesses.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - Le diagnostic strategique interne
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Diagnostic interne, Forces, Faiblesses.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Comment elaborer le diagnostic strategique e.</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -8772,7 +8784,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Diagnostic interne, Forces, Faiblesses.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Diagnostic interne, Forces, Faiblesses.</t>
         </is>
       </c>
       <c r="M123" t="n">
@@ -8823,14 +8835,15 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Etude de cas management - Le diagnostic strategique externe
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Comment elaborer le diagnostic strategique e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Diagnostic externe, Opportunites et Menaces.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - Le diagnostic strategique externe
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Diagnostic externe, Opportunites, Menaces.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Comment elaborer le diagnostic strategique e.</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -8840,7 +8853,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Diagnostic externe, Opportunites, Menaces.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Diagnostic externe, Opportunites, Menaces.</t>
         </is>
       </c>
       <c r="M124" t="n">
@@ -8891,14 +8904,15 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Etude de cas management - La fixation des objectifs strategiques et leur evaluation
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Comment interpreter le diagnostic et le traduire en objectifs e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Objectifs strategiques, Lien finalite/objectifs et RSE.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - La fixation des objectifs strategiques et leur evaluation
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Objectifs strategiques, Lien finalite/objectifs, RSE.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Comment interpreter le diagnostic et le traduire en objectifs e.</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -8908,7 +8922,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Objectifs strategiques, Lien finalite/objectifs, RSE.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Objectifs strategiques, Lien finalite/objectifs, RSE.</t>
         </is>
       </c>
       <c r="M125" t="n">
@@ -8959,14 +8973,15 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Etude de cas management - La demarche strategique
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Qu'est-ce que la strategie e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Definition de la strategie, Demarche strategique et Forces.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - La demarche strategique
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Definition de la strategie, Demarche strategique, Forces.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Qu'est-ce que la strategie e.</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -8976,7 +8991,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Definition de la strategie, Demarche strategique, Forces.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Definition de la strategie, Demarche strategique, Forces.</t>
         </is>
       </c>
       <c r="M126" t="n">
@@ -9027,14 +9042,15 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Etude de cas management - Le diagnostic strategique interne
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Comment elaborer le diagnostic strategique e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Diagnostic interne, Forces et Faiblesses.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - Le diagnostic strategique interne
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Diagnostic interne, Forces, Faiblesses.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Comment elaborer le diagnostic strategique e.</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -9044,7 +9060,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Diagnostic interne, Forces, Faiblesses.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Diagnostic interne, Forces, Faiblesses.</t>
         </is>
       </c>
       <c r="M127" t="n">
@@ -9095,14 +9111,15 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Etude de cas management - Le diagnostic strategique externe
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Comment elaborer le diagnostic strategique e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Diagnostic externe, Opportunites et Menaces.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - Le diagnostic strategique externe
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Diagnostic externe, Opportunites, Menaces.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Comment elaborer le diagnostic strategique e.</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -9112,7 +9129,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Diagnostic externe, Opportunites, Menaces.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Diagnostic externe, Opportunites, Menaces.</t>
         </is>
       </c>
       <c r="M128" t="n">
@@ -9163,14 +9180,15 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Etude de cas management - La fixation des objectifs strategiques et leur evaluation
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Comment interpreter le diagnostic et le traduire en objectifs e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Objectifs strategiques, Lien finalite/objectifs et RSE.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - La fixation des objectifs strategiques et leur evaluation
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Objectifs strategiques, Lien finalite/objectifs, RSE.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Comment interpreter le diagnostic et le traduire en objectifs e.</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -9180,7 +9198,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Objectifs strategiques, Lien finalite/objectifs, RSE.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Objectifs strategiques, Lien finalite/objectifs, RSE.</t>
         </is>
       </c>
       <c r="M129" t="n">
@@ -9231,14 +9249,15 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Etude de cas management - La demarche strategique
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Qu'est-ce que la strategie e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Definition de la strategie, Demarche strategique et Forces.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - La demarche strategique
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Definition de la strategie, Demarche strategique, Forces.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Qu'est-ce que la strategie e.</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -9248,7 +9267,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Definition de la strategie, Demarche strategique, Forces.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Definition de la strategie, Demarche strategique, Forces.</t>
         </is>
       </c>
       <c r="M130" t="n">
@@ -9299,14 +9318,15 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Etude de cas management - Le diagnostic strategique interne
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Comment elaborer le diagnostic strategique e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Diagnostic interne, Forces et Faiblesses.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - Le diagnostic strategique interne
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Diagnostic interne, Forces, Faiblesses.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Comment elaborer le diagnostic strategique e.</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -9316,7 +9336,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Diagnostic interne, Forces, Faiblesses.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Diagnostic interne, Forces, Faiblesses.</t>
         </is>
       </c>
       <c r="M131" t="n">
@@ -9367,14 +9387,15 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Etude de cas management - Les choix strategiques de l'entreprise
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Quelles options strategiques pour les entreprises e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant DAS, Strategie globale et Specialisation.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - Les choix strategiques de l'entreprise
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant DAS, Strategie globale, Specialisation.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Quelles options strategiques pour les entreprises e.</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -9384,7 +9405,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: DAS, Strategie globale, Specialisation.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: DAS, Strategie globale, Specialisation.</t>
         </is>
       </c>
       <c r="M132" t="n">
@@ -9435,14 +9456,15 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Etude de cas management - Le developpement strategique des entreprises
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Quelles options strategiques pour les entreprises e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Chaine de valeur, Externalisation et Integration.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - Le developpement strategique des entreprises
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Chaine de valeur, Externalisation, Integration.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Quelles options strategiques pour les entreprises e.</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -9452,7 +9474,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Chaine de valeur, Externalisation, Integration.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Chaine de valeur, Externalisation, Integration.</t>
         </is>
       </c>
       <c r="M133" t="n">
@@ -9503,14 +9525,15 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Etude de cas management - L'action strategique des organisations publiques
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Les strategies des organisations publiques : quelles specificites e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Interet general, Service public et Delegation de service public.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - L'action strategique des organisations publiques
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Interet general, Service public, Delegation de service public.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Les strategies des organisations publiques : quelles specificites e.</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -9520,7 +9543,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Interet general, Service public, Delegation de service public.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Interet general, Service public, Delegation de service public.</t>
         </is>
       </c>
       <c r="M134" t="n">
@@ -9571,14 +9594,15 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Etude de cas management - La strategie des organisations de la societe civile
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Les organisations de la societe civile peuvent-elles se passer de strategie e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Objet social, Perennisation des ressources et Developpement.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - La strategie des organisations de la societe civile
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Objet social, Perennisation des ressources, Developpement.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Les organisations de la societe civile peuvent-elles se passer de strategie e.</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -9588,7 +9612,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Objet social, Perennisation des ressources, Developpement.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Objet social, Perennisation des ressources, Developpement.</t>
         </is>
       </c>
       <c r="M135" t="n">
@@ -9639,14 +9663,15 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Etude de cas management - Les choix strategiques de l'entreprise
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Quelles options strategiques pour les entreprises e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant DAS, Strategie globale et Specialisation.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - Les choix strategiques de l'entreprise
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant DAS, Strategie globale, Specialisation.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Quelles options strategiques pour les entreprises e.</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -9656,7 +9681,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: DAS, Strategie globale, Specialisation.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: DAS, Strategie globale, Specialisation.</t>
         </is>
       </c>
       <c r="M136" t="n">
@@ -9707,14 +9732,15 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Etude de cas management - Le developpement strategique des entreprises
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Quelles options strategiques pour les entreprises e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Chaine de valeur, Externalisation et Integration.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - Le developpement strategique des entreprises
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Chaine de valeur, Externalisation, Integration.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Quelles options strategiques pour les entreprises e.</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -9724,7 +9750,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Chaine de valeur, Externalisation, Integration.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Chaine de valeur, Externalisation, Integration.</t>
         </is>
       </c>
       <c r="M137" t="n">
@@ -9775,14 +9801,15 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Etude de cas management - L'action strategique des organisations publiques
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Les strategies des organisations publiques : quelles specificites e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Interet general, Service public et Delegation de service public.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - L'action strategique des organisations publiques
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Interet general, Service public, Delegation de service public.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Les strategies des organisations publiques : quelles specificites e.</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -9792,7 +9819,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Interet general, Service public, Delegation de service public.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Interet general, Service public, Delegation de service public.</t>
         </is>
       </c>
       <c r="M138" t="n">
@@ -9843,14 +9870,15 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Etude de cas management - La strategie des organisations de la societe civile
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Les organisations de la societe civile peuvent-elles se passer de strategie e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Objet social, Perennisation des ressources et Developpement.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - La strategie des organisations de la societe civile
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Objet social, Perennisation des ressources, Developpement.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Les organisations de la societe civile peuvent-elles se passer de strategie e.</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -9860,7 +9888,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Objet social, Perennisation des ressources, Developpement.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Objet social, Perennisation des ressources, Developpement.</t>
         </is>
       </c>
       <c r="M139" t="n">
@@ -9911,14 +9939,15 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Etude de cas management - Les choix strategiques de l'entreprise
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Quelles options strategiques pour les entreprises e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant DAS, Strategie globale et Specialisation.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - Les choix strategiques de l'entreprise
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant DAS, Strategie globale, Specialisation.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Quelles options strategiques pour les entreprises e.</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -9928,7 +9957,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: DAS, Strategie globale, Specialisation.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: DAS, Strategie globale, Specialisation.</t>
         </is>
       </c>
       <c r="M140" t="n">
@@ -9979,14 +10008,15 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Etude de cas management - Le developpement strategique des entreprises
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Quelles options strategiques pour les entreprises e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Chaine de valeur, Externalisation et Integration.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - Le developpement strategique des entreprises
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Chaine de valeur, Externalisation, Integration.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Quelles options strategiques pour les entreprises e.</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -9996,7 +10026,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Chaine de valeur, Externalisation, Integration.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Chaine de valeur, Externalisation, Integration.</t>
         </is>
       </c>
       <c r="M141" t="n">
@@ -10047,14 +10077,15 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Etude de situation - Les differents types d'organisation
-Contexte: au sein d'une organisation, une tension apparait entre plusieurs acteurs et nuit a la cooperation.
-Problematique: Comment definir les differents types d'organisation e.
-Travail demande:
-1) Analyse la situation relationnelle en mobilisant les notions Gouvernement des organisations, Mode de controle et Buts de l'organisation.
-2) Identifie les causes des incomprehensions (roles, perceptions, communication, statut, pouvoir...).
-3) Propose deux actions manageriales realistes pour restaurer une dynamique collective efficace.
-4) Justifie l'action prioritaire et precise l'effet attendu sur le fonctionnement de l'organisation.</t>
+          <t>Dossier d'activites - Les differents types d'organisation
+Contexte: dans une organisation, un conflit relationnel perturbe le travail collectif (malentendus, tensions, baisse de coordination).
+Objectif: analyser les comportements individuels et la communication interpersonnelle.
+Travail demande (a l'aide des documents proposes):
+1) Caracterise la situation en mobilisant Gouvernement des organisations, Mode de controle et Buts de l'organisation.
+2) Identifie les signes observables (attitudes, posture, tonalite, comportements verbaux/non verbaux) et explique leur impact sur l'echange.
+3) Montre en quoi la situation freine l'action collective et la performance du groupe.
+4) Propose un plan d'amelioration concret (actions manageriales, communication, regles de fonctionnement) et justifie ta priorite.
+Problematique de chapitre: Comment definir les differents types d'organisation e.</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -10064,7 +10095,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>Correction attendue: mobilisation precise des notions du chapitre, analyse structuree de la situation et decision de gestion coherente. Si le sujet comporte des donnees, calculs justifies et interpretation obligatoire. Notions cibles: Gouvernement des organisations, Mode de controle, Buts de l'organisation.</t>
+          <t>Attendus: mobilisation pertinente des notions de chapitre, analyse structuree et recommandation de gestion. Si donnees chiffrees: calculs justifies + interpretation obligatoire. Notions cibles: Gouvernement des organisations, Mode de controle, Buts de l'organisation.</t>
         </is>
       </c>
       <c r="M142" t="n">
@@ -10115,14 +10146,15 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Etude de situation - L'identite et le fonctionnement de l'individu
-Contexte: au sein d'une organisation, une tension apparait entre plusieurs acteurs et nuit a la cooperation.
-Problematique: Comment un individu devient-il acteur dans une organisation e.
-Travail demande:
-1) Analyse la situation relationnelle en mobilisant les notions Personnalite, Emotion et Perception.
-2) Identifie les causes des incomprehensions (roles, perceptions, communication, statut, pouvoir...).
-3) Propose deux actions manageriales realistes pour restaurer une dynamique collective efficace.
-4) Justifie l'action prioritaire et precise l'effet attendu sur le fonctionnement de l'organisation.</t>
+          <t>Dossier d'activites - L'identite et le fonctionnement de l'individu
+Contexte: dans une organisation, un conflit relationnel perturbe le travail collectif (malentendus, tensions, baisse de coordination).
+Objectif: analyser les comportements individuels et la communication interpersonnelle.
+Travail demande (a l'aide des documents proposes):
+1) Caracterise la situation en mobilisant Personnalite, Emotion et Perception.
+2) Identifie les signes observables (attitudes, posture, tonalite, comportements verbaux/non verbaux) et explique leur impact sur l'echange.
+3) Montre en quoi la situation freine l'action collective et la performance du groupe.
+4) Propose un plan d'amelioration concret (actions manageriales, communication, regles de fonctionnement) et justifie ta priorite.
+Problematique de chapitre: Comment un individu devient-il acteur dans une organisation e.</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -10132,7 +10164,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>Correction attendue: mobilisation precise des notions du chapitre, analyse structuree de la situation et decision de gestion coherente. Si le sujet comporte des donnees, calculs justifies et interpretation obligatoire. Notions cibles: Personnalite, Emotion, Perception.</t>
+          <t>Attendus: mobilisation pertinente des notions de chapitre, analyse structuree et recommandation de gestion. Si donnees chiffrees: calculs justifies + interpretation obligatoire. Notions cibles: Personnalite, Emotion, Perception.</t>
         </is>
       </c>
       <c r="M143" t="n">
@@ -10183,14 +10215,15 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Etude de situation - L'individu dans l'organisation : un acteur en interaction
-Contexte: au sein d'une organisation, une tension apparait entre plusieurs acteurs et nuit a la cooperation.
-Problematique: Comment un individu devient-il acteur dans une organisation e.
-Travail demande:
-1) Analyse la situation relationnelle en mobilisant les notions Communication interpersonnelle, Interactions individu/groupe et Leadership.
-2) Identifie les causes des incomprehensions (roles, perceptions, communication, statut, pouvoir...).
-3) Propose deux actions manageriales realistes pour restaurer une dynamique collective efficace.
-4) Justifie l'action prioritaire et precise l'effet attendu sur le fonctionnement de l'organisation.</t>
+          <t>Dossier d'activites - L'individu dans l'organisation : un acteur en interaction
+Contexte: dans une organisation, un conflit relationnel perturbe le travail collectif (malentendus, tensions, baisse de coordination).
+Objectif: analyser les comportements individuels et la communication interpersonnelle.
+Travail demande (a l'aide des documents proposes):
+1) Caracterise la situation en mobilisant Communication interpersonnelle, Interactions individu/groupe et Leadership.
+2) Identifie les signes observables (attitudes, posture, tonalite, comportements verbaux/non verbaux) et explique leur impact sur l'echange.
+3) Montre en quoi la situation freine l'action collective et la performance du groupe.
+4) Propose un plan d'amelioration concret (actions manageriales, communication, regles de fonctionnement) et justifie ta priorite.
+Problematique de chapitre: Comment un individu devient-il acteur dans une organisation e.</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -10200,7 +10233,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>Correction attendue: mobilisation precise des notions du chapitre, analyse structuree de la situation et decision de gestion coherente. Si le sujet comporte des donnees, calculs justifies et interpretation obligatoire. Notions cibles: Communication interpersonnelle, Interactions individu/groupe, Leadership.</t>
+          <t>Attendus: mobilisation pertinente des notions de chapitre, analyse structuree et recommandation de gestion. Si donnees chiffrees: calculs justifies + interpretation obligatoire. Notions cibles: Communication interpersonnelle, Interactions individu/groupe, Leadership.</t>
         </is>
       </c>
       <c r="M144" t="n">
@@ -10251,14 +10284,15 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Etude de situation - L'activite de travail au sein des organisations
-Contexte: au sein d'une organisation, une tension apparait entre plusieurs acteurs et nuit a la cooperation.
-Problematique: Comment concilier gestion efficace des ressources humaines et cout du travail e.
-Travail demande:
-1) Analyse la situation relationnelle en mobilisant les notions Activite de travail, Conditions de travail et Competences.
-2) Identifie les causes des incomprehensions (roles, perceptions, communication, statut, pouvoir...).
-3) Propose deux actions manageriales realistes pour restaurer une dynamique collective efficace.
-4) Justifie l'action prioritaire et precise l'effet attendu sur le fonctionnement de l'organisation.</t>
+          <t>Dossier d'activites - L'activite de travail au sein des organisations
+Contexte: dans une organisation, un conflit relationnel perturbe le travail collectif (malentendus, tensions, baisse de coordination).
+Objectif: analyser les comportements individuels et la communication interpersonnelle.
+Travail demande (a l'aide des documents proposes):
+1) Caracterise la situation en mobilisant Activite de travail, Conditions de travail et Competences.
+2) Identifie les signes observables (attitudes, posture, tonalite, comportements verbaux/non verbaux) et explique leur impact sur l'echange.
+3) Montre en quoi la situation freine l'action collective et la performance du groupe.
+4) Propose un plan d'amelioration concret (actions manageriales, communication, regles de fonctionnement) et justifie ta priorite.
+Problematique de chapitre: Comment concilier gestion efficace des ressources humaines et cout du travail e.</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -10268,7 +10302,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>Correction attendue: mobilisation precise des notions du chapitre, analyse structuree de la situation et decision de gestion coherente. Si le sujet comporte des donnees, calculs justifies et interpretation obligatoire. Notions cibles: Activite de travail, Conditions de travail, Competences.</t>
+          <t>Attendus: mobilisation pertinente des notions de chapitre, analyse structuree et recommandation de gestion. Si donnees chiffrees: calculs justifies + interpretation obligatoire. Notions cibles: Activite de travail, Conditions de travail, Competences.</t>
         </is>
       </c>
       <c r="M145" t="n">
@@ -10319,14 +10353,15 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Etude de situation - L'evaluation et la retribution de l'activite de travail
-Contexte: au sein d'une organisation, une tension apparait entre plusieurs acteurs et nuit a la cooperation.
-Problematique: Comment concilier gestion efficace des ressources humaines et cout du travail e.
-Travail demande:
-1) Analyse la situation relationnelle en mobilisant les notions Tableaux de bord, Indicateurs d'activite et Productivite.
-2) Identifie les causes des incomprehensions (roles, perceptions, communication, statut, pouvoir...).
-3) Propose deux actions manageriales realistes pour restaurer une dynamique collective efficace.
-4) Justifie l'action prioritaire et precise l'effet attendu sur le fonctionnement de l'organisation.</t>
+          <t>Dossier d'activites - L'evaluation et la retribution de l'activite de travail
+Contexte: dans une organisation, un conflit relationnel perturbe le travail collectif (malentendus, tensions, baisse de coordination).
+Objectif: analyser les comportements individuels et la communication interpersonnelle.
+Travail demande (a l'aide des documents proposes):
+1) Caracterise la situation en mobilisant Tableaux de bord, Indicateurs d'activite et Productivite.
+2) Identifie les signes observables (attitudes, posture, tonalite, comportements verbaux/non verbaux) et explique leur impact sur l'echange.
+3) Montre en quoi la situation freine l'action collective et la performance du groupe.
+4) Propose un plan d'amelioration concret (actions manageriales, communication, regles de fonctionnement) et justifie ta priorite.
+Problematique de chapitre: Comment concilier gestion efficace des ressources humaines et cout du travail e.</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -10336,7 +10371,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>Correction attendue: mobilisation precise des notions du chapitre, analyse structuree de la situation et decision de gestion coherente. Si le sujet comporte des donnees, calculs justifies et interpretation obligatoire. Notions cibles: Tableaux de bord, Indicateurs d'activite, Productivite.</t>
+          <t>Attendus: mobilisation pertinente des notions de chapitre, analyse structuree et recommandation de gestion. Si donnees chiffrees: calculs justifies + interpretation obligatoire. Notions cibles: Tableaux de bord, Indicateurs d'activite, Productivite.</t>
         </is>
       </c>
       <c r="M146" t="n">
@@ -10387,14 +10422,15 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Etude de situation - Les differents types d'organisation
-Contexte: au sein d'une organisation, une tension apparait entre plusieurs acteurs et nuit a la cooperation.
-Problematique: Comment definir les differents types d'organisation e.
-Travail demande:
-1) Analyse la situation relationnelle en mobilisant les notions Gouvernement des organisations, Mode de controle et Buts de l'organisation.
-2) Identifie les causes des incomprehensions (roles, perceptions, communication, statut, pouvoir...).
-3) Propose deux actions manageriales realistes pour restaurer une dynamique collective efficace.
-4) Justifie l'action prioritaire et precise l'effet attendu sur le fonctionnement de l'organisation.</t>
+          <t>Dossier d'activites - Les differents types d'organisation
+Contexte: dans une organisation, un conflit relationnel perturbe le travail collectif (malentendus, tensions, baisse de coordination).
+Objectif: analyser les comportements individuels et la communication interpersonnelle.
+Travail demande (a l'aide des documents proposes):
+1) Caracterise la situation en mobilisant Gouvernement des organisations, Mode de controle et Buts de l'organisation.
+2) Identifie les signes observables (attitudes, posture, tonalite, comportements verbaux/non verbaux) et explique leur impact sur l'echange.
+3) Montre en quoi la situation freine l'action collective et la performance du groupe.
+4) Propose un plan d'amelioration concret (actions manageriales, communication, regles de fonctionnement) et justifie ta priorite.
+Problematique de chapitre: Comment definir les differents types d'organisation e.</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -10404,7 +10440,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>Correction attendue: mobilisation precise des notions du chapitre, analyse structuree de la situation et decision de gestion coherente. Si le sujet comporte des donnees, calculs justifies et interpretation obligatoire. Notions cibles: Gouvernement des organisations, Mode de controle, Buts de l'organisation.</t>
+          <t>Attendus: mobilisation pertinente des notions de chapitre, analyse structuree et recommandation de gestion. Si donnees chiffrees: calculs justifies + interpretation obligatoire. Notions cibles: Gouvernement des organisations, Mode de controle, Buts de l'organisation.</t>
         </is>
       </c>
       <c r="M147" t="n">
@@ -10455,14 +10491,15 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Etude de situation - L'identite et le fonctionnement de l'individu
-Contexte: au sein d'une organisation, une tension apparait entre plusieurs acteurs et nuit a la cooperation.
-Problematique: Comment un individu devient-il acteur dans une organisation e.
-Travail demande:
-1) Analyse la situation relationnelle en mobilisant les notions Personnalite, Emotion et Perception.
-2) Identifie les causes des incomprehensions (roles, perceptions, communication, statut, pouvoir...).
-3) Propose deux actions manageriales realistes pour restaurer une dynamique collective efficace.
-4) Justifie l'action prioritaire et precise l'effet attendu sur le fonctionnement de l'organisation.</t>
+          <t>Dossier d'activites - L'identite et le fonctionnement de l'individu
+Contexte: dans une organisation, un conflit relationnel perturbe le travail collectif (malentendus, tensions, baisse de coordination).
+Objectif: analyser les comportements individuels et la communication interpersonnelle.
+Travail demande (a l'aide des documents proposes):
+1) Caracterise la situation en mobilisant Personnalite, Emotion et Perception.
+2) Identifie les signes observables (attitudes, posture, tonalite, comportements verbaux/non verbaux) et explique leur impact sur l'echange.
+3) Montre en quoi la situation freine l'action collective et la performance du groupe.
+4) Propose un plan d'amelioration concret (actions manageriales, communication, regles de fonctionnement) et justifie ta priorite.
+Problematique de chapitre: Comment un individu devient-il acteur dans une organisation e.</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -10472,7 +10509,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>Correction attendue: mobilisation precise des notions du chapitre, analyse structuree de la situation et decision de gestion coherente. Si le sujet comporte des donnees, calculs justifies et interpretation obligatoire. Notions cibles: Personnalite, Emotion, Perception.</t>
+          <t>Attendus: mobilisation pertinente des notions de chapitre, analyse structuree et recommandation de gestion. Si donnees chiffrees: calculs justifies + interpretation obligatoire. Notions cibles: Personnalite, Emotion, Perception.</t>
         </is>
       </c>
       <c r="M148" t="n">
@@ -10523,14 +10560,15 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Etude de situation - L'individu dans l'organisation : un acteur en interaction
-Contexte: au sein d'une organisation, une tension apparait entre plusieurs acteurs et nuit a la cooperation.
-Problematique: Comment un individu devient-il acteur dans une organisation e.
-Travail demande:
-1) Analyse la situation relationnelle en mobilisant les notions Communication interpersonnelle, Interactions individu/groupe et Leadership.
-2) Identifie les causes des incomprehensions (roles, perceptions, communication, statut, pouvoir...).
-3) Propose deux actions manageriales realistes pour restaurer une dynamique collective efficace.
-4) Justifie l'action prioritaire et precise l'effet attendu sur le fonctionnement de l'organisation.</t>
+          <t>Dossier d'activites - L'individu dans l'organisation : un acteur en interaction
+Contexte: dans une organisation, un conflit relationnel perturbe le travail collectif (malentendus, tensions, baisse de coordination).
+Objectif: analyser les comportements individuels et la communication interpersonnelle.
+Travail demande (a l'aide des documents proposes):
+1) Caracterise la situation en mobilisant Communication interpersonnelle, Interactions individu/groupe et Leadership.
+2) Identifie les signes observables (attitudes, posture, tonalite, comportements verbaux/non verbaux) et explique leur impact sur l'echange.
+3) Montre en quoi la situation freine l'action collective et la performance du groupe.
+4) Propose un plan d'amelioration concret (actions manageriales, communication, regles de fonctionnement) et justifie ta priorite.
+Problematique de chapitre: Comment un individu devient-il acteur dans une organisation e.</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -10540,7 +10578,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>Correction attendue: mobilisation precise des notions du chapitre, analyse structuree de la situation et decision de gestion coherente. Si le sujet comporte des donnees, calculs justifies et interpretation obligatoire. Notions cibles: Communication interpersonnelle, Interactions individu/groupe, Leadership.</t>
+          <t>Attendus: mobilisation pertinente des notions de chapitre, analyse structuree et recommandation de gestion. Si donnees chiffrees: calculs justifies + interpretation obligatoire. Notions cibles: Communication interpersonnelle, Interactions individu/groupe, Leadership.</t>
         </is>
       </c>
       <c r="M149" t="n">
@@ -10591,14 +10629,15 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Etude de situation - L'activite de travail au sein des organisations
-Contexte: au sein d'une organisation, une tension apparait entre plusieurs acteurs et nuit a la cooperation.
-Problematique: Comment concilier gestion efficace des ressources humaines et cout du travail e.
-Travail demande:
-1) Analyse la situation relationnelle en mobilisant les notions Activite de travail, Conditions de travail et Competences.
-2) Identifie les causes des incomprehensions (roles, perceptions, communication, statut, pouvoir...).
-3) Propose deux actions manageriales realistes pour restaurer une dynamique collective efficace.
-4) Justifie l'action prioritaire et precise l'effet attendu sur le fonctionnement de l'organisation.</t>
+          <t>Dossier d'activites - L'activite de travail au sein des organisations
+Contexte: dans une organisation, un conflit relationnel perturbe le travail collectif (malentendus, tensions, baisse de coordination).
+Objectif: analyser les comportements individuels et la communication interpersonnelle.
+Travail demande (a l'aide des documents proposes):
+1) Caracterise la situation en mobilisant Activite de travail, Conditions de travail et Competences.
+2) Identifie les signes observables (attitudes, posture, tonalite, comportements verbaux/non verbaux) et explique leur impact sur l'echange.
+3) Montre en quoi la situation freine l'action collective et la performance du groupe.
+4) Propose un plan d'amelioration concret (actions manageriales, communication, regles de fonctionnement) et justifie ta priorite.
+Problematique de chapitre: Comment concilier gestion efficace des ressources humaines et cout du travail e.</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -10608,7 +10647,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>Correction attendue: mobilisation precise des notions du chapitre, analyse structuree de la situation et decision de gestion coherente. Si le sujet comporte des donnees, calculs justifies et interpretation obligatoire. Notions cibles: Activite de travail, Conditions de travail, Competences.</t>
+          <t>Attendus: mobilisation pertinente des notions de chapitre, analyse structuree et recommandation de gestion. Si donnees chiffrees: calculs justifies + interpretation obligatoire. Notions cibles: Activite de travail, Conditions de travail, Competences.</t>
         </is>
       </c>
       <c r="M150" t="n">
@@ -10659,14 +10698,15 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Etude de situation - L'evaluation et la retribution de l'activite de travail
-Contexte: au sein d'une organisation, une tension apparait entre plusieurs acteurs et nuit a la cooperation.
-Problematique: Comment concilier gestion efficace des ressources humaines et cout du travail e.
-Travail demande:
-1) Analyse la situation relationnelle en mobilisant les notions Tableaux de bord, Indicateurs d'activite et Productivite.
-2) Identifie les causes des incomprehensions (roles, perceptions, communication, statut, pouvoir...).
-3) Propose deux actions manageriales realistes pour restaurer une dynamique collective efficace.
-4) Justifie l'action prioritaire et precise l'effet attendu sur le fonctionnement de l'organisation.</t>
+          <t>Dossier d'activites - L'evaluation et la retribution de l'activite de travail
+Contexte: dans une organisation, un conflit relationnel perturbe le travail collectif (malentendus, tensions, baisse de coordination).
+Objectif: analyser les comportements individuels et la communication interpersonnelle.
+Travail demande (a l'aide des documents proposes):
+1) Caracterise la situation en mobilisant Tableaux de bord, Indicateurs d'activite et Productivite.
+2) Identifie les signes observables (attitudes, posture, tonalite, comportements verbaux/non verbaux) et explique leur impact sur l'echange.
+3) Montre en quoi la situation freine l'action collective et la performance du groupe.
+4) Propose un plan d'amelioration concret (actions manageriales, communication, regles de fonctionnement) et justifie ta priorite.
+Problematique de chapitre: Comment concilier gestion efficace des ressources humaines et cout du travail e.</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -10676,7 +10716,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>Correction attendue: mobilisation precise des notions du chapitre, analyse structuree de la situation et decision de gestion coherente. Si le sujet comporte des donnees, calculs justifies et interpretation obligatoire. Notions cibles: Tableaux de bord, Indicateurs d'activite, Productivite.</t>
+          <t>Attendus: mobilisation pertinente des notions de chapitre, analyse structuree et recommandation de gestion. Si donnees chiffrees: calculs justifies + interpretation obligatoire. Notions cibles: Tableaux de bord, Indicateurs d'activite, Productivite.</t>
         </is>
       </c>
       <c r="M151" t="n">
@@ -10727,14 +10767,15 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Cas d'usage numerique - Le role des technologies dans la transformation de l'information en ressource
-Contexte: une organisation veut ameliorer son fonctionnement grace aux outils numeriques mais rencontre des limites de coordination.
-Problematique: En quoi les technologies transforment-elles l'information en ressource e.
-Travail demande:
-1) Montre comment les notions Donnee, Information et Connaissance eclairent la situation.
-2) Analyse les opportunites et les risques du dispositif numerique actuel.
-3) Propose une organisation cible du partage d'information (roles, regles, outils, securisation).
-4) Definis trois indicateurs de suivi pour mesurer l'amelioration attendue.</t>
+          <t>Etude de cas numerique - Le role des technologies dans la transformation de l'information en ressource
+Contexte: une organisation veut mieux exploiter ses donnees et fluidifier la circulation de l'information entre services.
+Objectif: analyser l'apport du numerique sur la coordination et l'intelligence collective.
+Travail demande:
+1) Repere les flux d'information utiles au pilotage de l'activite.
+2) Montre comment Donnee, Information et Connaissance peuvent ameliorer la prise de decision.
+3) Identifie deux risques majeurs (qualite de donnees, securite, surcharge informationnelle, mauvaise coordination) et propose des parades.
+4) Construis un schema cible de fonctionnement numerique (acteurs, outils, roles, regles de partage).
+Problematique de chapitre: En quoi les technologies transforment-elles l'information en ressource e.</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -10744,7 +10785,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>Correction attendue: mobilisation precise des notions du chapitre, analyse structuree de la situation et decision de gestion coherente. Si le sujet comporte des donnees, calculs justifies et interpretation obligatoire. Notions cibles: Donnee, Information, Connaissance.</t>
+          <t>Attendus: mobilisation pertinente des notions de chapitre, analyse structuree et recommandation de gestion. Si donnees chiffrees: calculs justifies + interpretation obligatoire. Notions cibles: Donnee, Information, Connaissance.</t>
         </is>
       </c>
       <c r="M152" t="n">
@@ -10795,14 +10836,15 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Cas d'usage numerique - Les technologies numeriques au service de la collaboration dans les organisations
-Contexte: une organisation veut ameliorer son fonctionnement grace aux outils numeriques mais rencontre des limites de coordination.
-Problematique: Comment le partage de l'information contribue-t-il a l'emergence d'une intelligence collective e.
-Travail demande:
-1) Montre comment les notions E-communication, Partage de l'information et Collaboration eclairent la situation.
-2) Analyse les opportunites et les risques du dispositif numerique actuel.
-3) Propose une organisation cible du partage d'information (roles, regles, outils, securisation).
-4) Definis trois indicateurs de suivi pour mesurer l'amelioration attendue.</t>
+          <t>Etude de cas numerique - Les technologies numeriques au service de la collaboration dans les organisations
+Contexte: une organisation veut mieux exploiter ses donnees et fluidifier la circulation de l'information entre services.
+Objectif: analyser l'apport du numerique sur la coordination et l'intelligence collective.
+Travail demande:
+1) Repere les flux d'information utiles au pilotage de l'activite.
+2) Montre comment E-communication, Partage de l'information et Collaboration peuvent ameliorer la prise de decision.
+3) Identifie deux risques majeurs (qualite de donnees, securite, surcharge informationnelle, mauvaise coordination) et propose des parades.
+4) Construis un schema cible de fonctionnement numerique (acteurs, outils, roles, regles de partage).
+Problematique de chapitre: Comment le partage de l'information contribue-t-il a l'emergence d'une intelligence collective e.</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -10812,7 +10854,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>Correction attendue: mobilisation precise des notions du chapitre, analyse structuree de la situation et decision de gestion coherente. Si le sujet comporte des donnees, calculs justifies et interpretation obligatoire. Notions cibles: E-communication, Partage de l'information, Collaboration.</t>
+          <t>Attendus: mobilisation pertinente des notions de chapitre, analyse structuree et recommandation de gestion. Si donnees chiffrees: calculs justifies + interpretation obligatoire. Notions cibles: E-communication, Partage de l'information, Collaboration.</t>
         </is>
       </c>
       <c r="M153" t="n">
@@ -10863,14 +10905,15 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>Cas d'usage numerique - L'influence du numerique sur l'organisation du travail
-Contexte: une organisation veut ameliorer son fonctionnement grace aux outils numeriques mais rencontre des limites de coordination.
-Problematique: Le numerique cree-t-il de l'agilite ou de la rigidite organisationnelle e.
-Travail demande:
-1) Montre comment les notions Processus, PGI et Applications metier eclairent la situation.
-2) Analyse les opportunites et les risques du dispositif numerique actuel.
-3) Propose une organisation cible du partage d'information (roles, regles, outils, securisation).
-4) Definis trois indicateurs de suivi pour mesurer l'amelioration attendue.</t>
+          <t>Etude de cas numerique - L'influence du numerique sur l'organisation du travail
+Contexte: une organisation veut mieux exploiter ses donnees et fluidifier la circulation de l'information entre services.
+Objectif: analyser l'apport du numerique sur la coordination et l'intelligence collective.
+Travail demande:
+1) Repere les flux d'information utiles au pilotage de l'activite.
+2) Montre comment Processus, PGI et Applications metier peuvent ameliorer la prise de decision.
+3) Identifie deux risques majeurs (qualite de donnees, securite, surcharge informationnelle, mauvaise coordination) et propose des parades.
+4) Construis un schema cible de fonctionnement numerique (acteurs, outils, roles, regles de partage).
+Problematique de chapitre: Le numerique cree-t-il de l'agilite ou de la rigidite organisationnelle e.</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -10880,7 +10923,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>Correction attendue: mobilisation precise des notions du chapitre, analyse structuree de la situation et decision de gestion coherente. Si le sujet comporte des donnees, calculs justifies et interpretation obligatoire. Notions cibles: Processus, PGI, Applications metier.</t>
+          <t>Attendus: mobilisation pertinente des notions de chapitre, analyse structuree et recommandation de gestion. Si donnees chiffrees: calculs justifies + interpretation obligatoire. Notions cibles: Processus, PGI, Applications metier.</t>
         </is>
       </c>
       <c r="M154" t="n">
@@ -10931,14 +10974,15 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>Cas d'usage numerique - Le role des technologies dans la transformation de l'information en ressource
-Contexte: une organisation veut ameliorer son fonctionnement grace aux outils numeriques mais rencontre des limites de coordination.
-Problematique: En quoi les technologies transforment-elles l'information en ressource e.
-Travail demande:
-1) Montre comment les notions Donnee, Information et Connaissance eclairent la situation.
-2) Analyse les opportunites et les risques du dispositif numerique actuel.
-3) Propose une organisation cible du partage d'information (roles, regles, outils, securisation).
-4) Definis trois indicateurs de suivi pour mesurer l'amelioration attendue.</t>
+          <t>Etude de cas numerique - Le role des technologies dans la transformation de l'information en ressource
+Contexte: une organisation veut mieux exploiter ses donnees et fluidifier la circulation de l'information entre services.
+Objectif: analyser l'apport du numerique sur la coordination et l'intelligence collective.
+Travail demande:
+1) Repere les flux d'information utiles au pilotage de l'activite.
+2) Montre comment Donnee, Information et Connaissance peuvent ameliorer la prise de decision.
+3) Identifie deux risques majeurs (qualite de donnees, securite, surcharge informationnelle, mauvaise coordination) et propose des parades.
+4) Construis un schema cible de fonctionnement numerique (acteurs, outils, roles, regles de partage).
+Problematique de chapitre: En quoi les technologies transforment-elles l'information en ressource e.</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -10948,7 +10992,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>Correction attendue: mobilisation precise des notions du chapitre, analyse structuree de la situation et decision de gestion coherente. Si le sujet comporte des donnees, calculs justifies et interpretation obligatoire. Notions cibles: Donnee, Information, Connaissance.</t>
+          <t>Attendus: mobilisation pertinente des notions de chapitre, analyse structuree et recommandation de gestion. Si donnees chiffrees: calculs justifies + interpretation obligatoire. Notions cibles: Donnee, Information, Connaissance.</t>
         </is>
       </c>
       <c r="M155" t="n">
@@ -10999,14 +11043,15 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>Cas d'usage numerique - Les technologies numeriques au service de la collaboration dans les organisations
-Contexte: une organisation veut ameliorer son fonctionnement grace aux outils numeriques mais rencontre des limites de coordination.
-Problematique: Comment le partage de l'information contribue-t-il a l'emergence d'une intelligence collective e.
-Travail demande:
-1) Montre comment les notions E-communication, Partage de l'information et Collaboration eclairent la situation.
-2) Analyse les opportunites et les risques du dispositif numerique actuel.
-3) Propose une organisation cible du partage d'information (roles, regles, outils, securisation).
-4) Definis trois indicateurs de suivi pour mesurer l'amelioration attendue.</t>
+          <t>Etude de cas numerique - Les technologies numeriques au service de la collaboration dans les organisations
+Contexte: une organisation veut mieux exploiter ses donnees et fluidifier la circulation de l'information entre services.
+Objectif: analyser l'apport du numerique sur la coordination et l'intelligence collective.
+Travail demande:
+1) Repere les flux d'information utiles au pilotage de l'activite.
+2) Montre comment E-communication, Partage de l'information et Collaboration peuvent ameliorer la prise de decision.
+3) Identifie deux risques majeurs (qualite de donnees, securite, surcharge informationnelle, mauvaise coordination) et propose des parades.
+4) Construis un schema cible de fonctionnement numerique (acteurs, outils, roles, regles de partage).
+Problematique de chapitre: Comment le partage de l'information contribue-t-il a l'emergence d'une intelligence collective e.</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -11016,7 +11061,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>Correction attendue: mobilisation precise des notions du chapitre, analyse structuree de la situation et decision de gestion coherente. Si le sujet comporte des donnees, calculs justifies et interpretation obligatoire. Notions cibles: E-communication, Partage de l'information, Collaboration.</t>
+          <t>Attendus: mobilisation pertinente des notions de chapitre, analyse structuree et recommandation de gestion. Si donnees chiffrees: calculs justifies + interpretation obligatoire. Notions cibles: E-communication, Partage de l'information, Collaboration.</t>
         </is>
       </c>
       <c r="M156" t="n">
@@ -11067,14 +11112,15 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Cas d'usage numerique - L'influence du numerique sur l'organisation du travail
-Contexte: une organisation veut ameliorer son fonctionnement grace aux outils numeriques mais rencontre des limites de coordination.
-Problematique: Le numerique cree-t-il de l'agilite ou de la rigidite organisationnelle e.
-Travail demande:
-1) Montre comment les notions Processus, PGI et Applications metier eclairent la situation.
-2) Analyse les opportunites et les risques du dispositif numerique actuel.
-3) Propose une organisation cible du partage d'information (roles, regles, outils, securisation).
-4) Definis trois indicateurs de suivi pour mesurer l'amelioration attendue.</t>
+          <t>Etude de cas numerique - L'influence du numerique sur l'organisation du travail
+Contexte: une organisation veut mieux exploiter ses donnees et fluidifier la circulation de l'information entre services.
+Objectif: analyser l'apport du numerique sur la coordination et l'intelligence collective.
+Travail demande:
+1) Repere les flux d'information utiles au pilotage de l'activite.
+2) Montre comment Processus, PGI et Applications metier peuvent ameliorer la prise de decision.
+3) Identifie deux risques majeurs (qualite de donnees, securite, surcharge informationnelle, mauvaise coordination) et propose des parades.
+4) Construis un schema cible de fonctionnement numerique (acteurs, outils, roles, regles de partage).
+Problematique de chapitre: Le numerique cree-t-il de l'agilite ou de la rigidite organisationnelle e.</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -11084,7 +11130,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>Correction attendue: mobilisation precise des notions du chapitre, analyse structuree de la situation et decision de gestion coherente. Si le sujet comporte des donnees, calculs justifies et interpretation obligatoire. Notions cibles: Processus, PGI, Applications metier.</t>
+          <t>Attendus: mobilisation pertinente des notions de chapitre, analyse structuree et recommandation de gestion. Si donnees chiffrees: calculs justifies + interpretation obligatoire. Notions cibles: Processus, PGI, Applications metier.</t>
         </is>
       </c>
       <c r="M157" t="n">
@@ -11135,14 +11181,15 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>Cas d'usage numerique - Le role des technologies dans la transformation de l'information en ressource
-Contexte: une organisation veut ameliorer son fonctionnement grace aux outils numeriques mais rencontre des limites de coordination.
-Problematique: En quoi les technologies transforment-elles l'information en ressource e.
-Travail demande:
-1) Montre comment les notions Donnee, Information et Connaissance eclairent la situation.
-2) Analyse les opportunites et les risques du dispositif numerique actuel.
-3) Propose une organisation cible du partage d'information (roles, regles, outils, securisation).
-4) Definis trois indicateurs de suivi pour mesurer l'amelioration attendue.</t>
+          <t>Etude de cas numerique - Le role des technologies dans la transformation de l'information en ressource
+Contexte: une organisation veut mieux exploiter ses donnees et fluidifier la circulation de l'information entre services.
+Objectif: analyser l'apport du numerique sur la coordination et l'intelligence collective.
+Travail demande:
+1) Repere les flux d'information utiles au pilotage de l'activite.
+2) Montre comment Donnee, Information et Connaissance peuvent ameliorer la prise de decision.
+3) Identifie deux risques majeurs (qualite de donnees, securite, surcharge informationnelle, mauvaise coordination) et propose des parades.
+4) Construis un schema cible de fonctionnement numerique (acteurs, outils, roles, regles de partage).
+Problematique de chapitre: En quoi les technologies transforment-elles l'information en ressource e.</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -11152,7 +11199,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>Correction attendue: mobilisation precise des notions du chapitre, analyse structuree de la situation et decision de gestion coherente. Si le sujet comporte des donnees, calculs justifies et interpretation obligatoire. Notions cibles: Donnee, Information, Connaissance.</t>
+          <t>Attendus: mobilisation pertinente des notions de chapitre, analyse structuree et recommandation de gestion. Si donnees chiffrees: calculs justifies + interpretation obligatoire. Notions cibles: Donnee, Information, Connaissance.</t>
         </is>
       </c>
       <c r="M158" t="n">
@@ -11203,14 +11250,15 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>Cas d'usage numerique - Les technologies numeriques au service de la collaboration dans les organisations
-Contexte: une organisation veut ameliorer son fonctionnement grace aux outils numeriques mais rencontre des limites de coordination.
-Problematique: Comment le partage de l'information contribue-t-il a l'emergence d'une intelligence collective e.
-Travail demande:
-1) Montre comment les notions E-communication, Partage de l'information et Collaboration eclairent la situation.
-2) Analyse les opportunites et les risques du dispositif numerique actuel.
-3) Propose une organisation cible du partage d'information (roles, regles, outils, securisation).
-4) Definis trois indicateurs de suivi pour mesurer l'amelioration attendue.</t>
+          <t>Etude de cas numerique - Les technologies numeriques au service de la collaboration dans les organisations
+Contexte: une organisation veut mieux exploiter ses donnees et fluidifier la circulation de l'information entre services.
+Objectif: analyser l'apport du numerique sur la coordination et l'intelligence collective.
+Travail demande:
+1) Repere les flux d'information utiles au pilotage de l'activite.
+2) Montre comment E-communication, Partage de l'information et Collaboration peuvent ameliorer la prise de decision.
+3) Identifie deux risques majeurs (qualite de donnees, securite, surcharge informationnelle, mauvaise coordination) et propose des parades.
+4) Construis un schema cible de fonctionnement numerique (acteurs, outils, roles, regles de partage).
+Problematique de chapitre: Comment le partage de l'information contribue-t-il a l'emergence d'une intelligence collective e.</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -11220,7 +11268,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>Correction attendue: mobilisation precise des notions du chapitre, analyse structuree de la situation et decision de gestion coherente. Si le sujet comporte des donnees, calculs justifies et interpretation obligatoire. Notions cibles: E-communication, Partage de l'information, Collaboration.</t>
+          <t>Attendus: mobilisation pertinente des notions de chapitre, analyse structuree et recommandation de gestion. Si donnees chiffrees: calculs justifies + interpretation obligatoire. Notions cibles: E-communication, Partage de l'information, Collaboration.</t>
         </is>
       </c>
       <c r="M159" t="n">
@@ -11271,14 +11319,15 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>Cas d'usage numerique - L'influence du numerique sur l'organisation du travail
-Contexte: une organisation veut ameliorer son fonctionnement grace aux outils numeriques mais rencontre des limites de coordination.
-Problematique: Le numerique cree-t-il de l'agilite ou de la rigidite organisationnelle e.
-Travail demande:
-1) Montre comment les notions Processus, PGI et Applications metier eclairent la situation.
-2) Analyse les opportunites et les risques du dispositif numerique actuel.
-3) Propose une organisation cible du partage d'information (roles, regles, outils, securisation).
-4) Definis trois indicateurs de suivi pour mesurer l'amelioration attendue.</t>
+          <t>Etude de cas numerique - L'influence du numerique sur l'organisation du travail
+Contexte: une organisation veut mieux exploiter ses donnees et fluidifier la circulation de l'information entre services.
+Objectif: analyser l'apport du numerique sur la coordination et l'intelligence collective.
+Travail demande:
+1) Repere les flux d'information utiles au pilotage de l'activite.
+2) Montre comment Processus, PGI et Applications metier peuvent ameliorer la prise de decision.
+3) Identifie deux risques majeurs (qualite de donnees, securite, surcharge informationnelle, mauvaise coordination) et propose des parades.
+4) Construis un schema cible de fonctionnement numerique (acteurs, outils, roles, regles de partage).
+Problematique de chapitre: Le numerique cree-t-il de l'agilite ou de la rigidite organisationnelle e.</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -11288,7 +11337,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>Correction attendue: mobilisation precise des notions du chapitre, analyse structuree de la situation et decision de gestion coherente. Si le sujet comporte des donnees, calculs justifies et interpretation obligatoire. Notions cibles: Processus, PGI, Applications metier.</t>
+          <t>Attendus: mobilisation pertinente des notions de chapitre, analyse structuree et recommandation de gestion. Si donnees chiffrees: calculs justifies + interpretation obligatoire. Notions cibles: Processus, PGI, Applications metier.</t>
         </is>
       </c>
       <c r="M160" t="n">
@@ -11339,14 +11388,15 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>Cas d'usage numerique - Le role des technologies dans la transformation de l'information en ressource
-Contexte: une organisation veut ameliorer son fonctionnement grace aux outils numeriques mais rencontre des limites de coordination.
-Problematique: En quoi les technologies transforment-elles l'information en ressource e.
-Travail demande:
-1) Montre comment les notions Donnee, Information et Connaissance eclairent la situation.
-2) Analyse les opportunites et les risques du dispositif numerique actuel.
-3) Propose une organisation cible du partage d'information (roles, regles, outils, securisation).
-4) Definis trois indicateurs de suivi pour mesurer l'amelioration attendue.</t>
+          <t>Etude de cas numerique - Le role des technologies dans la transformation de l'information en ressource
+Contexte: une organisation veut mieux exploiter ses donnees et fluidifier la circulation de l'information entre services.
+Objectif: analyser l'apport du numerique sur la coordination et l'intelligence collective.
+Travail demande:
+1) Repere les flux d'information utiles au pilotage de l'activite.
+2) Montre comment Donnee, Information et Connaissance peuvent ameliorer la prise de decision.
+3) Identifie deux risques majeurs (qualite de donnees, securite, surcharge informationnelle, mauvaise coordination) et propose des parades.
+4) Construis un schema cible de fonctionnement numerique (acteurs, outils, roles, regles de partage).
+Problematique de chapitre: En quoi les technologies transforment-elles l'information en ressource e.</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -11356,7 +11406,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>Correction attendue: mobilisation precise des notions du chapitre, analyse structuree de la situation et decision de gestion coherente. Si le sujet comporte des donnees, calculs justifies et interpretation obligatoire. Notions cibles: Donnee, Information, Connaissance.</t>
+          <t>Attendus: mobilisation pertinente des notions de chapitre, analyse structuree et recommandation de gestion. Si donnees chiffrees: calculs justifies + interpretation obligatoire. Notions cibles: Donnee, Information, Connaissance.</t>
         </is>
       </c>
       <c r="M161" t="n">
@@ -11407,14 +11457,15 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>Dossier chiffre - La construction de la valeur percue
-Contexte: une organisation presente les donnees suivantes: CA=189000 EUR, consommations intermediaires=99500 EUR, resultat net=23800 EUR, capitaux propres=73500 EUR.
-Problematique: Peut-on mesurer la contribution de chaque acteur a la creation de valeur e.
-Travail demande:
-1) Effectue les calculs pertinents pour evaluer la creation de valeur et la performance.
-2) Interprete les resultats obtenus a l'aide des notions Valeur percue, Image de marque et Notoriete.
-3) Discute les limites de la performance mesuree (financiere, commerciale, sociale ou environnementale).
-4) Propose une decision de gestion argumentee pour ameliorer durablement la performance globale.</t>
+          <t>Dossier chiffre et interpretation - La construction de la valeur percue
+Contexte: l'organisation etudie ses resultats pour evaluer sa performance globale.
+Donnees: CA=246000 EUR ; consommations intermediaires=133600 EUR ; resultat net=43400 EUR ; capitaux propres=106200 EUR.
+Travail demande:
+1) Realise les calculs pertinents pour evaluer creation de valeur et performance (indicateurs adaptes au chapitre).
+2) Interprete les resultats obtenus a l'aide de Valeur percue, Image de marque et Notoriete.
+3) Discute les limites des indicateurs utilises (financiere, commerciale, sociale, environnementale).
+4) Propose une decision de gestion argumentee pour ameliorer la performance.
+Problematique de chapitre: Peut-on mesurer la contribution de chaque acteur a la creation de valeur e.</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -11424,7 +11475,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>Correction attendue: mobilisation precise des notions du chapitre, analyse structuree de la situation et decision de gestion coherente. Si le sujet comporte des donnees, calculs justifies et interpretation obligatoire. Notions cibles: Valeur percue, Image de marque, Notoriete.</t>
+          <t>Attendus: mobilisation pertinente des notions de chapitre, analyse structuree et recommandation de gestion. Si donnees chiffrees: calculs justifies + interpretation obligatoire. Notions cibles: Valeur percue, Image de marque, Notoriete.</t>
         </is>
       </c>
       <c r="M162" t="n">
@@ -11475,14 +11526,15 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>Dossier chiffre - Le calcul de la valeur financiere et de la valeur boursiere
-Contexte: une organisation presente les donnees suivantes: CA=198000 EUR, consommations intermediaires=104000 EUR, resultat net=25600 EUR, capitaux propres=77000 EUR.
-Problematique: Peut-on mesurer la contribution de chaque acteur a la creation de valeur e.
-Travail demande:
-1) Effectue les calculs pertinents pour evaluer la creation de valeur et la performance.
-2) Interprete les resultats obtenus a l'aide des notions Valeur financiere, Valeur actionnariale et Valeur boursiere.
-3) Discute les limites de la performance mesuree (financiere, commerciale, sociale ou environnementale).
-4) Propose une decision de gestion argumentee pour ameliorer durablement la performance globale.</t>
+          <t>Dossier chiffre et interpretation - Le calcul de la valeur financiere et de la valeur boursiere
+Contexte: l'organisation etudie ses resultats pour evaluer sa performance globale.
+Donnees: CA=333500 EUR ; consommations intermediaires=186100 EUR ; resultat net=65900 EUR ; capitaux propres=148700 EUR.
+Travail demande:
+1) Realise les calculs pertinents pour evaluer creation de valeur et performance (indicateurs adaptes au chapitre).
+2) Interprete les resultats obtenus a l'aide de Valeur financiere, Valeur actionnariale et Valeur boursiere.
+3) Discute les limites des indicateurs utilises (financiere, commerciale, sociale, environnementale).
+4) Propose une decision de gestion argumentee pour ameliorer la performance.
+Problematique de chapitre: Peut-on mesurer la contribution de chaque acteur a la creation de valeur e.</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -11492,7 +11544,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>Correction attendue: mobilisation precise des notions du chapitre, analyse structuree de la situation et decision de gestion coherente. Si le sujet comporte des donnees, calculs justifies et interpretation obligatoire. Notions cibles: Valeur financiere, Valeur actionnariale, Valeur boursiere.</t>
+          <t>Attendus: mobilisation pertinente des notions de chapitre, analyse structuree et recommandation de gestion. Si donnees chiffrees: calculs justifies + interpretation obligatoire. Notions cibles: Valeur financiere, Valeur actionnariale, Valeur boursiere.</t>
         </is>
       </c>
       <c r="M163" t="n">
@@ -11543,14 +11595,15 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>Dossier chiffre - La valeur ajoutee et la valeur partenariale
-Contexte: une organisation presente les donnees suivantes: CA=207000 EUR, consommations intermediaires=108500 EUR, resultat net=27400 EUR, capitaux propres=80500 EUR.
-Problematique: Peut-on mesurer la contribution de chaque acteur a la creation de valeur e.
-Travail demande:
-1) Effectue les calculs pertinents pour evaluer la creation de valeur et la performance.
-2) Interprete les resultats obtenus a l'aide des notions Valeur ajoutee, Repartition de la valeur ajoutee et Valeur partenariale.
-3) Discute les limites de la performance mesuree (financiere, commerciale, sociale ou environnementale).
-4) Propose une decision de gestion argumentee pour ameliorer durablement la performance globale.</t>
+          <t>Dossier chiffre et interpretation - La valeur ajoutee et la valeur partenariale
+Contexte: l'organisation etudie ses resultats pour evaluer sa performance globale.
+Donnees: CA=281000 EUR ; consommations intermediaires=154600 EUR ; resultat net=52400 EUR ; capitaux propres=123200 EUR.
+Travail demande:
+1) Realise les calculs pertinents pour evaluer creation de valeur et performance (indicateurs adaptes au chapitre).
+2) Interprete les resultats obtenus a l'aide de Valeur ajoutee, Repartition de la valeur ajoutee et Valeur partenariale.
+3) Discute les limites des indicateurs utilises (financiere, commerciale, sociale, environnementale).
+4) Propose une decision de gestion argumentee pour ameliorer la performance.
+Problematique de chapitre: Peut-on mesurer la contribution de chaque acteur a la creation de valeur e.</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -11560,7 +11613,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>Correction attendue: mobilisation precise des notions du chapitre, analyse structuree de la situation et decision de gestion coherente. Si le sujet comporte des donnees, calculs justifies et interpretation obligatoire. Notions cibles: Valeur ajoutee, Repartition de la valeur ajoutee, Valeur partenariale.</t>
+          <t>Attendus: mobilisation pertinente des notions de chapitre, analyse structuree et recommandation de gestion. Si donnees chiffrees: calculs justifies + interpretation obligatoire. Notions cibles: Valeur ajoutee, Repartition de la valeur ajoutee, Valeur partenariale.</t>
         </is>
       </c>
       <c r="M164" t="n">
@@ -11611,14 +11664,15 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>Dossier chiffre - La relation prix, cout, marge
-Contexte: une organisation presente les donnees suivantes: CA=216000 EUR, consommations intermediaires=113000 EUR, resultat net=29200 EUR, capitaux propres=84000 EUR.
-Problematique: Peut-on mesurer la contribution de chaque acteur a la creation de valeur e.
-Travail demande:
-1) Effectue les calculs pertinents pour evaluer la creation de valeur et la performance.
-2) Interprete les resultats obtenus a l'aide des notions Prix, Cout et Marge.
-3) Discute les limites de la performance mesuree (financiere, commerciale, sociale ou environnementale).
-4) Propose une decision de gestion argumentee pour ameliorer durablement la performance globale.</t>
+          <t>Dossier chiffre et interpretation - La relation prix, cout, marge
+Contexte: l'organisation etudie ses resultats pour evaluer sa performance globale.
+Donnees: CA=235500 EUR ; consommations intermediaires=127300 EUR ; resultat net=40700 EUR ; capitaux propres=101100 EUR.
+Travail demande:
+1) Realise les calculs pertinents pour evaluer creation de valeur et performance (indicateurs adaptes au chapitre).
+2) Interprete les resultats obtenus a l'aide de Prix, Cout et Marge.
+3) Discute les limites des indicateurs utilises (financiere, commerciale, sociale, environnementale).
+4) Propose une decision de gestion argumentee pour ameliorer la performance.
+Problematique de chapitre: Peut-on mesurer la contribution de chaque acteur a la creation de valeur e.</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -11628,7 +11682,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>Correction attendue: mobilisation precise des notions du chapitre, analyse structuree de la situation et decision de gestion coherente. Si le sujet comporte des donnees, calculs justifies et interpretation obligatoire. Notions cibles: Prix, Cout, Marge.</t>
+          <t>Attendus: mobilisation pertinente des notions de chapitre, analyse structuree et recommandation de gestion. Si donnees chiffrees: calculs justifies + interpretation obligatoire. Notions cibles: Prix, Cout, Marge.</t>
         </is>
       </c>
       <c r="M165" t="n">
@@ -11679,14 +11733,15 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>Dossier chiffre - L'analyse des performances commerciale et financiere
-Contexte: une organisation presente les donnees suivantes: CA=225000 EUR, consommations intermediaires=117500 EUR, resultat net=31000 EUR, capitaux propres=87500 EUR.
-Problematique: La creation de valeur conduit-elle toujours a une performance globale e.
-Travail demande:
-1) Effectue les calculs pertinents pour evaluer la creation de valeur et la performance.
-2) Interprete les resultats obtenus a l'aide des notions Performance commerciale, Performance financiere et Rentabilite.
-3) Discute les limites de la performance mesuree (financiere, commerciale, sociale ou environnementale).
-4) Propose une decision de gestion argumentee pour ameliorer durablement la performance globale.</t>
+          <t>Dossier chiffre et interpretation - L'analyse des performances commerciale et financiere
+Contexte: l'organisation etudie ses resultats pour evaluer sa performance globale.
+Donnees: CA=319500 EUR ; consommations intermediaires=177700 EUR ; resultat net=62300 EUR ; capitaux propres=141900 EUR.
+Travail demande:
+1) Realise les calculs pertinents pour evaluer creation de valeur et performance (indicateurs adaptes au chapitre).
+2) Interprete les resultats obtenus a l'aide de Performance commerciale, Performance financiere et Rentabilite.
+3) Discute les limites des indicateurs utilises (financiere, commerciale, sociale, environnementale).
+4) Propose une decision de gestion argumentee pour ameliorer la performance.
+Problematique de chapitre: La creation de valeur conduit-elle toujours a une performance globale e.</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -11696,7 +11751,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>Correction attendue: mobilisation precise des notions du chapitre, analyse structuree de la situation et decision de gestion coherente. Si le sujet comporte des donnees, calculs justifies et interpretation obligatoire. Notions cibles: Performance commerciale, Performance financiere, Rentabilite.</t>
+          <t>Attendus: mobilisation pertinente des notions de chapitre, analyse structuree et recommandation de gestion. Si donnees chiffrees: calculs justifies + interpretation obligatoire. Notions cibles: Performance commerciale, Performance financiere, Rentabilite.</t>
         </is>
       </c>
       <c r="M166" t="n">
@@ -11747,14 +11802,15 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>Dossier chiffre - La performance sociale et environnementale
-Contexte: une organisation presente les donnees suivantes: CA=234000 EUR, consommations intermediaires=122000 EUR, resultat net=32800 EUR, capitaux propres=91000 EUR.
-Problematique: La creation de valeur conduit-elle toujours a une performance globale e.
-Travail demande:
-1) Effectue les calculs pertinents pour evaluer la creation de valeur et la performance.
-2) Interprete les resultats obtenus a l'aide des notions Performance sociale, Bilan social et Performance environnementale.
-3) Discute les limites de la performance mesuree (financiere, commerciale, sociale ou environnementale).
-4) Propose une decision de gestion argumentee pour ameliorer durablement la performance globale.</t>
+          <t>Dossier chiffre et interpretation - La performance sociale et environnementale
+Contexte: l'organisation etudie ses resultats pour evaluer sa performance globale.
+Donnees: CA=288000 EUR ; consommations intermediaires=158800 EUR ; resultat net=54200 EUR ; capitaux propres=126600 EUR.
+Travail demande:
+1) Realise les calculs pertinents pour evaluer creation de valeur et performance (indicateurs adaptes au chapitre).
+2) Interprete les resultats obtenus a l'aide de Performance sociale, Bilan social et Performance environnementale.
+3) Discute les limites des indicateurs utilises (financiere, commerciale, sociale, environnementale).
+4) Propose une decision de gestion argumentee pour ameliorer la performance.
+Problematique de chapitre: La creation de valeur conduit-elle toujours a une performance globale e.</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -11764,7 +11820,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>Correction attendue: mobilisation precise des notions du chapitre, analyse structuree de la situation et decision de gestion coherente. Si le sujet comporte des donnees, calculs justifies et interpretation obligatoire. Notions cibles: Performance sociale, Bilan social, Performance environnementale.</t>
+          <t>Attendus: mobilisation pertinente des notions de chapitre, analyse structuree et recommandation de gestion. Si donnees chiffrees: calculs justifies + interpretation obligatoire. Notions cibles: Performance sociale, Bilan social, Performance environnementale.</t>
         </is>
       </c>
       <c r="M167" t="n">
@@ -11815,14 +11871,15 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>Dossier chiffre - La construction de la valeur percue
-Contexte: une organisation presente les donnees suivantes: CA=243000 EUR, consommations intermediaires=126500 EUR, resultat net=34600 EUR, capitaux propres=94500 EUR.
-Problematique: Peut-on mesurer la contribution de chaque acteur a la creation de valeur e.
-Travail demande:
-1) Effectue les calculs pertinents pour evaluer la creation de valeur et la performance.
-2) Interprete les resultats obtenus a l'aide des notions Valeur percue, Image de marque et Notoriete.
-3) Discute les limites de la performance mesuree (financiere, commerciale, sociale ou environnementale).
-4) Propose une decision de gestion argumentee pour ameliorer durablement la performance globale.</t>
+          <t>Dossier chiffre et interpretation - La construction de la valeur percue
+Contexte: l'organisation etudie ses resultats pour evaluer sa performance globale.
+Donnees: CA=267000 EUR ; consommations intermediaires=146200 EUR ; resultat net=48800 EUR ; capitaux propres=116400 EUR.
+Travail demande:
+1) Realise les calculs pertinents pour evaluer creation de valeur et performance (indicateurs adaptes au chapitre).
+2) Interprete les resultats obtenus a l'aide de Valeur percue, Image de marque et Notoriete.
+3) Discute les limites des indicateurs utilises (financiere, commerciale, sociale, environnementale).
+4) Propose une decision de gestion argumentee pour ameliorer la performance.
+Problematique de chapitre: Peut-on mesurer la contribution de chaque acteur a la creation de valeur e.</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -11832,7 +11889,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>Correction attendue: mobilisation precise des notions du chapitre, analyse structuree de la situation et decision de gestion coherente. Si le sujet comporte des donnees, calculs justifies et interpretation obligatoire. Notions cibles: Valeur percue, Image de marque, Notoriete.</t>
+          <t>Attendus: mobilisation pertinente des notions de chapitre, analyse structuree et recommandation de gestion. Si donnees chiffrees: calculs justifies + interpretation obligatoire. Notions cibles: Valeur percue, Image de marque, Notoriete.</t>
         </is>
       </c>
       <c r="M168" t="n">
@@ -11883,14 +11940,15 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>Dossier chiffre - Le calcul de la valeur financiere et de la valeur boursiere
-Contexte: une organisation presente les donnees suivantes: CA=252000 EUR, consommations intermediaires=131000 EUR, resultat net=36400 EUR, capitaux propres=98000 EUR.
-Problematique: Peut-on mesurer la contribution de chaque acteur a la creation de valeur e.
-Travail demande:
-1) Effectue les calculs pertinents pour evaluer la creation de valeur et la performance.
-2) Interprete les resultats obtenus a l'aide des notions Valeur financiere, Valeur actionnariale et Valeur boursiere.
-3) Discute les limites de la performance mesuree (financiere, commerciale, sociale ou environnementale).
-4) Propose une decision de gestion argumentee pour ameliorer durablement la performance globale.</t>
+          <t>Dossier chiffre et interpretation - Le calcul de la valeur financiere et de la valeur boursiere
+Contexte: l'organisation etudie ses resultats pour evaluer sa performance globale.
+Donnees: CA=354500 EUR ; consommations intermediaires=198700 EUR ; resultat net=71300 EUR ; capitaux propres=158900 EUR.
+Travail demande:
+1) Realise les calculs pertinents pour evaluer creation de valeur et performance (indicateurs adaptes au chapitre).
+2) Interprete les resultats obtenus a l'aide de Valeur financiere, Valeur actionnariale et Valeur boursiere.
+3) Discute les limites des indicateurs utilises (financiere, commerciale, sociale, environnementale).
+4) Propose une decision de gestion argumentee pour ameliorer la performance.
+Problematique de chapitre: Peut-on mesurer la contribution de chaque acteur a la creation de valeur e.</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -11900,7 +11958,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>Correction attendue: mobilisation precise des notions du chapitre, analyse structuree de la situation et decision de gestion coherente. Si le sujet comporte des donnees, calculs justifies et interpretation obligatoire. Notions cibles: Valeur financiere, Valeur actionnariale, Valeur boursiere.</t>
+          <t>Attendus: mobilisation pertinente des notions de chapitre, analyse structuree et recommandation de gestion. Si donnees chiffrees: calculs justifies + interpretation obligatoire. Notions cibles: Valeur financiere, Valeur actionnariale, Valeur boursiere.</t>
         </is>
       </c>
       <c r="M169" t="n">
@@ -11951,14 +12009,15 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>Dossier chiffre - La valeur ajoutee et la valeur partenariale
-Contexte: une organisation presente les donnees suivantes: CA=261000 EUR, consommations intermediaires=135500 EUR, resultat net=38200 EUR, capitaux propres=101500 EUR.
-Problematique: Peut-on mesurer la contribution de chaque acteur a la creation de valeur e.
-Travail demande:
-1) Effectue les calculs pertinents pour evaluer la creation de valeur et la performance.
-2) Interprete les resultats obtenus a l'aide des notions Valeur ajoutee, Repartition de la valeur ajoutee et Valeur partenariale.
-3) Discute les limites de la performance mesuree (financiere, commerciale, sociale ou environnementale).
-4) Propose une decision de gestion argumentee pour ameliorer durablement la performance globale.</t>
+          <t>Dossier chiffre et interpretation - La valeur ajoutee et la valeur partenariale
+Contexte: l'organisation etudie ses resultats pour evaluer sa performance globale.
+Donnees: CA=302000 EUR ; consommations intermediaires=167200 EUR ; resultat net=57800 EUR ; capitaux propres=133400 EUR.
+Travail demande:
+1) Realise les calculs pertinents pour evaluer creation de valeur et performance (indicateurs adaptes au chapitre).
+2) Interprete les resultats obtenus a l'aide de Valeur ajoutee, Repartition de la valeur ajoutee et Valeur partenariale.
+3) Discute les limites des indicateurs utilises (financiere, commerciale, sociale, environnementale).
+4) Propose une decision de gestion argumentee pour ameliorer la performance.
+Problematique de chapitre: Peut-on mesurer la contribution de chaque acteur a la creation de valeur e.</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -11968,7 +12027,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>Correction attendue: mobilisation precise des notions du chapitre, analyse structuree de la situation et decision de gestion coherente. Si le sujet comporte des donnees, calculs justifies et interpretation obligatoire. Notions cibles: Valeur ajoutee, Repartition de la valeur ajoutee, Valeur partenariale.</t>
+          <t>Attendus: mobilisation pertinente des notions de chapitre, analyse structuree et recommandation de gestion. Si donnees chiffrees: calculs justifies + interpretation obligatoire. Notions cibles: Valeur ajoutee, Repartition de la valeur ajoutee, Valeur partenariale.</t>
         </is>
       </c>
       <c r="M170" t="n">
@@ -12019,14 +12078,15 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>Dossier chiffre - La relation prix, cout, marge
-Contexte: une organisation presente les donnees suivantes: CA=270000 EUR, consommations intermediaires=140000 EUR, resultat net=40000 EUR, capitaux propres=105000 EUR.
-Problematique: Peut-on mesurer la contribution de chaque acteur a la creation de valeur e.
-Travail demande:
-1) Effectue les calculs pertinents pour evaluer la creation de valeur et la performance.
-2) Interprete les resultats obtenus a l'aide des notions Prix, Cout et Marge.
-3) Discute les limites de la performance mesuree (financiere, commerciale, sociale ou environnementale).
-4) Propose une decision de gestion argumentee pour ameliorer durablement la performance globale.</t>
+          <t>Dossier chiffre et interpretation - La relation prix, cout, marge
+Contexte: l'organisation etudie ses resultats pour evaluer sa performance globale.
+Donnees: CA=256500 EUR ; consommations intermediaires=139900 EUR ; resultat net=46100 EUR ; capitaux propres=111300 EUR.
+Travail demande:
+1) Realise les calculs pertinents pour evaluer creation de valeur et performance (indicateurs adaptes au chapitre).
+2) Interprete les resultats obtenus a l'aide de Prix, Cout et Marge.
+3) Discute les limites des indicateurs utilises (financiere, commerciale, sociale, environnementale).
+4) Propose une decision de gestion argumentee pour ameliorer la performance.
+Problematique de chapitre: Peut-on mesurer la contribution de chaque acteur a la creation de valeur e.</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -12036,7 +12096,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>Correction attendue: mobilisation precise des notions du chapitre, analyse structuree de la situation et decision de gestion coherente. Si le sujet comporte des donnees, calculs justifies et interpretation obligatoire. Notions cibles: Prix, Cout, Marge.</t>
+          <t>Attendus: mobilisation pertinente des notions de chapitre, analyse structuree et recommandation de gestion. Si donnees chiffrees: calculs justifies + interpretation obligatoire. Notions cibles: Prix, Cout, Marge.</t>
         </is>
       </c>
       <c r="M171" t="n">
@@ -12088,13 +12148,13 @@
       <c r="J172" t="inlineStr">
         <is>
           <t>Cas pratique juridique - La formation du contrat
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Quel est le role du contrat e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 9250 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Contrat, Conditions de validite et Consentement.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Contrat, Conditions de validite, Consentement.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Quel est le role du contrat e.</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -12104,7 +12164,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Contrat, Conditions de validite, Consentement.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Contrat, Conditions de validite, Consentement.</t>
         </is>
       </c>
       <c r="M172" t="n">
@@ -12156,13 +12216,13 @@
       <c r="J173" t="inlineStr">
         <is>
           <t>Cas pratique juridique - L'execution du contrat
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Quel est le role du contrat e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 10500 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Execution, Inexecution et Mise en demeure.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Execution, Inexecution, Mise en demeure.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Quel est le role du contrat e.</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -12172,7 +12232,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Execution, Inexecution, Mise en demeure.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Execution, Inexecution, Mise en demeure.</t>
         </is>
       </c>
       <c r="M173" t="n">
@@ -12224,13 +12284,13 @@
       <c r="J174" t="inlineStr">
         <is>
           <t>Cas pratique juridique - La formation du contrat
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Quel est le role du contrat e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 11750 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Contrat, Conditions de validite et Consentement.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Contrat, Conditions de validite, Consentement.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Quel est le role du contrat e.</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -12240,7 +12300,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Contrat, Conditions de validite, Consentement.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Contrat, Conditions de validite, Consentement.</t>
         </is>
       </c>
       <c r="M174" t="n">
@@ -12292,13 +12352,13 @@
       <c r="J175" t="inlineStr">
         <is>
           <t>Cas pratique juridique - L'execution du contrat
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Quel est le role du contrat e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 13000 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Execution, Inexecution et Mise en demeure.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Execution, Inexecution, Mise en demeure.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Quel est le role du contrat e.</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -12308,7 +12368,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Execution, Inexecution, Mise en demeure.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Execution, Inexecution, Mise en demeure.</t>
         </is>
       </c>
       <c r="M175" t="n">
@@ -12360,13 +12420,13 @@
       <c r="J176" t="inlineStr">
         <is>
           <t>Cas pratique juridique - La formation du contrat
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Quel est le role du contrat e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 14250 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Contrat, Conditions de validite et Consentement.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Contrat, Conditions de validite, Consentement.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Quel est le role du contrat e.</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -12376,7 +12436,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Contrat, Conditions de validite, Consentement.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Contrat, Conditions de validite, Consentement.</t>
         </is>
       </c>
       <c r="M176" t="n">
@@ -12428,13 +12488,13 @@
       <c r="J177" t="inlineStr">
         <is>
           <t>Cas pratique juridique - L'execution du contrat
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Quel est le role du contrat e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 15500 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Execution, Inexecution et Mise en demeure.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Execution, Inexecution, Mise en demeure.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Quel est le role du contrat e.</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -12444,7 +12504,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Execution, Inexecution, Mise en demeure.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Execution, Inexecution, Mise en demeure.</t>
         </is>
       </c>
       <c r="M177" t="n">
@@ -12496,13 +12556,13 @@
       <c r="J178" t="inlineStr">
         <is>
           <t>Cas pratique juridique - La formation du contrat
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Quel est le role du contrat e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 16750 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Contrat, Conditions de validite et Consentement.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Contrat, Conditions de validite, Consentement.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Quel est le role du contrat e.</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -12512,7 +12572,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Contrat, Conditions de validite, Consentement.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Contrat, Conditions de validite, Consentement.</t>
         </is>
       </c>
       <c r="M178" t="n">
@@ -12564,13 +12624,13 @@
       <c r="J179" t="inlineStr">
         <is>
           <t>Cas pratique juridique - L'execution du contrat
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Quel est le role du contrat e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 18000 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Execution, Inexecution et Mise en demeure.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Execution, Inexecution, Mise en demeure.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Quel est le role du contrat e.</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -12580,7 +12640,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Execution, Inexecution, Mise en demeure.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Execution, Inexecution, Mise en demeure.</t>
         </is>
       </c>
       <c r="M179" t="n">
@@ -12632,13 +12692,13 @@
       <c r="J180" t="inlineStr">
         <is>
           <t>Cas pratique juridique - La formation du contrat
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Quel est le role du contrat e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 19250 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Contrat, Conditions de validite et Consentement.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Contrat, Conditions de validite, Consentement.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Quel est le role du contrat e.</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -12648,7 +12708,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Contrat, Conditions de validite, Consentement.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Contrat, Conditions de validite, Consentement.</t>
         </is>
       </c>
       <c r="M180" t="n">
@@ -12700,13 +12760,13 @@
       <c r="J181" t="inlineStr">
         <is>
           <t>Cas pratique juridique - L'execution du contrat
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Quel est le role du contrat e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 20500 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Execution, Inexecution et Mise en demeure.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Execution, Inexecution, Mise en demeure.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Quel est le role du contrat e.</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -12716,7 +12776,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Execution, Inexecution, Mise en demeure.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Execution, Inexecution, Mise en demeure.</t>
         </is>
       </c>
       <c r="M181" t="n">
@@ -12768,13 +12828,13 @@
       <c r="J182" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Le dommage reparable
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Qu'est-ce qu'etre responsable e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 9250 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Responsabilite civile, Responsabilite penale et Prejudice.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Responsabilite civile, Responsabilite penale, Prejudice.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Qu'est-ce qu'etre responsable e.</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -12784,7 +12844,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Responsabilite civile, Responsabilite penale, Prejudice.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Responsabilite civile, Responsabilite penale, Prejudice.</t>
         </is>
       </c>
       <c r="M182" t="n">
@@ -12836,13 +12896,13 @@
       <c r="J183" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Les differents regimes de responsabilite
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Qu'est-ce qu'etre responsable e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 10500 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Responsabilite contractuelle, Responsabilite extracontractuelle et Fait personnel.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Responsabilite contractuelle, Responsabilite extracontractuelle, Fait personnel.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Qu'est-ce qu'etre responsable e.</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -12852,7 +12912,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Responsabilite contractuelle, Responsabilite extracontractuelle, Fait personnel.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Responsabilite contractuelle, Responsabilite extracontractuelle, Fait personnel.</t>
         </is>
       </c>
       <c r="M183" t="n">
@@ -12904,13 +12964,13 @@
       <c r="J184" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Les moyens d'exoneration de la responsabilite
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Qu'est-ce qu'etre responsable e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 11750 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Exoneration, Force majeure et Cause etrangere.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Exoneration, Force majeure, Cause etrangere.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Qu'est-ce qu'etre responsable e.</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -12920,7 +12980,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Exoneration, Force majeure, Cause etrangere.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Exoneration, Force majeure, Cause etrangere.</t>
         </is>
       </c>
       <c r="M184" t="n">
@@ -12972,13 +13032,13 @@
       <c r="J185" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Le dommage reparable
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Qu'est-ce qu'etre responsable e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 13000 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Responsabilite civile, Responsabilite penale et Prejudice.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Responsabilite civile, Responsabilite penale, Prejudice.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Qu'est-ce qu'etre responsable e.</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -12988,7 +13048,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Responsabilite civile, Responsabilite penale, Prejudice.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Responsabilite civile, Responsabilite penale, Prejudice.</t>
         </is>
       </c>
       <c r="M185" t="n">
@@ -13040,13 +13100,13 @@
       <c r="J186" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Les differents regimes de responsabilite
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Qu'est-ce qu'etre responsable e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 14250 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Responsabilite contractuelle, Responsabilite extracontractuelle et Fait personnel.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Responsabilite contractuelle, Responsabilite extracontractuelle, Fait personnel.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Qu'est-ce qu'etre responsable e.</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -13056,7 +13116,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Responsabilite contractuelle, Responsabilite extracontractuelle, Fait personnel.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Responsabilite contractuelle, Responsabilite extracontractuelle, Fait personnel.</t>
         </is>
       </c>
       <c r="M186" t="n">
@@ -13108,13 +13168,13 @@
       <c r="J187" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Les moyens d'exoneration de la responsabilite
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Qu'est-ce qu'etre responsable e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 15500 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Exoneration, Force majeure et Cause etrangere.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Exoneration, Force majeure, Cause etrangere.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Qu'est-ce qu'etre responsable e.</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -13124,7 +13184,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Exoneration, Force majeure, Cause etrangere.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Exoneration, Force majeure, Cause etrangere.</t>
         </is>
       </c>
       <c r="M187" t="n">
@@ -13176,13 +13236,13 @@
       <c r="J188" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Le dommage reparable
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Qu'est-ce qu'etre responsable e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 16750 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Responsabilite civile, Responsabilite penale et Prejudice.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Responsabilite civile, Responsabilite penale, Prejudice.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Qu'est-ce qu'etre responsable e.</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -13192,7 +13252,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Responsabilite civile, Responsabilite penale, Prejudice.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Responsabilite civile, Responsabilite penale, Prejudice.</t>
         </is>
       </c>
       <c r="M188" t="n">
@@ -13244,13 +13304,13 @@
       <c r="J189" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Les differents regimes de responsabilite
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Qu'est-ce qu'etre responsable e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 18000 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Responsabilite contractuelle, Responsabilite extracontractuelle et Fait personnel.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Responsabilite contractuelle, Responsabilite extracontractuelle, Fait personnel.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Qu'est-ce qu'etre responsable e.</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -13260,7 +13320,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Responsabilite contractuelle, Responsabilite extracontractuelle, Fait personnel.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Responsabilite contractuelle, Responsabilite extracontractuelle, Fait personnel.</t>
         </is>
       </c>
       <c r="M189" t="n">
@@ -13312,13 +13372,13 @@
       <c r="J190" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Les moyens d'exoneration de la responsabilite
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Qu'est-ce qu'etre responsable e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 19250 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Exoneration, Force majeure et Cause etrangere.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Exoneration, Force majeure, Cause etrangere.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Qu'est-ce qu'etre responsable e.</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -13328,7 +13388,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Exoneration, Force majeure, Cause etrangere.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Exoneration, Force majeure, Cause etrangere.</t>
         </is>
       </c>
       <c r="M190" t="n">
@@ -13380,13 +13440,13 @@
       <c r="J191" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Le dommage reparable
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Qu'est-ce qu'etre responsable e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 20500 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Responsabilite civile, Responsabilite penale et Prejudice.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Responsabilite civile, Responsabilite penale, Prejudice.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Qu'est-ce qu'etre responsable e.</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -13396,7 +13456,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Responsabilite civile, Responsabilite penale, Prejudice.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Responsabilite civile, Responsabilite penale, Prejudice.</t>
         </is>
       </c>
       <c r="M191" t="n">
@@ -13448,13 +13508,13 @@
       <c r="J192" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Les differentes formes de contrat de travail
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Comment le droit encadre-t-il le travail salarie e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 9250 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Contrat de travail, Lien de subordination et CDI.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Contrat de travail, Lien de subordination, CDI.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Comment le droit encadre-t-il le travail salarie e.</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -13464,7 +13524,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Contrat de travail, Lien de subordination, CDI.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Contrat de travail, Lien de subordination, CDI.</t>
         </is>
       </c>
       <c r="M192" t="n">
@@ -13516,13 +13576,13 @@
       <c r="J193" t="inlineStr">
         <is>
           <t>Cas pratique juridique - La rupture du contrat de travail
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Comment le droit encadre-t-il le travail salarie e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 10500 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Demission, Licenciement et Rupture conventionnelle.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Demission, Licenciement, Rupture conventionnelle.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Comment le droit encadre-t-il le travail salarie e.</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -13532,7 +13592,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Demission, Licenciement, Rupture conventionnelle.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Demission, Licenciement, Rupture conventionnelle.</t>
         </is>
       </c>
       <c r="M193" t="n">
@@ -13584,13 +13644,13 @@
       <c r="J194" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Les libertes individuelles et collectives des salaries
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Comment le droit encadre-t-il le travail salarie e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 11750 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Liberte d'expression, Vie privee et Droit de greve.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Liberte d'expression, Vie privee, Droit de greve.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Comment le droit encadre-t-il le travail salarie e.</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -13600,7 +13660,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Liberte d'expression, Vie privee, Droit de greve.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Liberte d'expression, Vie privee, Droit de greve.</t>
         </is>
       </c>
       <c r="M194" t="n">
@@ -13652,13 +13712,13 @@
       <c r="J195" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Les differentes formes de contrat de travail
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Comment le droit encadre-t-il le travail salarie e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 13000 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Contrat de travail, Lien de subordination et CDI.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Contrat de travail, Lien de subordination, CDI.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Comment le droit encadre-t-il le travail salarie e.</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -13668,7 +13728,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Contrat de travail, Lien de subordination, CDI.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Contrat de travail, Lien de subordination, CDI.</t>
         </is>
       </c>
       <c r="M195" t="n">
@@ -13720,13 +13780,13 @@
       <c r="J196" t="inlineStr">
         <is>
           <t>Cas pratique juridique - La rupture du contrat de travail
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Comment le droit encadre-t-il le travail salarie e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 14250 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Demission, Licenciement et Rupture conventionnelle.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Demission, Licenciement, Rupture conventionnelle.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Comment le droit encadre-t-il le travail salarie e.</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
@@ -13736,7 +13796,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Demission, Licenciement, Rupture conventionnelle.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Demission, Licenciement, Rupture conventionnelle.</t>
         </is>
       </c>
       <c r="M196" t="n">
@@ -13788,13 +13848,13 @@
       <c r="J197" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Les libertes individuelles et collectives des salaries
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Comment le droit encadre-t-il le travail salarie e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 15500 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Liberte d'expression, Vie privee et Droit de greve.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Liberte d'expression, Vie privee, Droit de greve.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Comment le droit encadre-t-il le travail salarie e.</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -13804,7 +13864,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Liberte d'expression, Vie privee, Droit de greve.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Liberte d'expression, Vie privee, Droit de greve.</t>
         </is>
       </c>
       <c r="M197" t="n">
@@ -13856,13 +13916,13 @@
       <c r="J198" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Les differentes formes de contrat de travail
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Comment le droit encadre-t-il le travail salarie e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 16750 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Contrat de travail, Lien de subordination et CDI.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Contrat de travail, Lien de subordination, CDI.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Comment le droit encadre-t-il le travail salarie e.</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -13872,7 +13932,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Contrat de travail, Lien de subordination, CDI.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Contrat de travail, Lien de subordination, CDI.</t>
         </is>
       </c>
       <c r="M198" t="n">
@@ -13924,13 +13984,13 @@
       <c r="J199" t="inlineStr">
         <is>
           <t>Cas pratique juridique - La rupture du contrat de travail
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Comment le droit encadre-t-il le travail salarie e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 18000 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Demission, Licenciement et Rupture conventionnelle.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Demission, Licenciement, Rupture conventionnelle.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Comment le droit encadre-t-il le travail salarie e.</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -13940,7 +14000,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Demission, Licenciement, Rupture conventionnelle.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Demission, Licenciement, Rupture conventionnelle.</t>
         </is>
       </c>
       <c r="M199" t="n">
@@ -13992,13 +14052,13 @@
       <c r="J200" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Les libertes individuelles et collectives des salaries
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Comment le droit encadre-t-il le travail salarie e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 19250 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Liberte d'expression, Vie privee et Droit de greve.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Liberte d'expression, Vie privee, Droit de greve.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Comment le droit encadre-t-il le travail salarie e.</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -14008,7 +14068,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Liberte d'expression, Vie privee, Droit de greve.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Liberte d'expression, Vie privee, Droit de greve.</t>
         </is>
       </c>
       <c r="M200" t="n">
@@ -14060,13 +14120,13 @@
       <c r="J201" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Les differentes formes de contrat de travail
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Comment le droit encadre-t-il le travail salarie e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 20500 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Contrat de travail, Lien de subordination et CDI.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Contrat de travail, Lien de subordination, CDI.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Comment le droit encadre-t-il le travail salarie e.</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -14076,7 +14136,7 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Contrat de travail, Lien de subordination, CDI.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Contrat de travail, Lien de subordination, CDI.</t>
         </is>
       </c>
       <c r="M201" t="n">
@@ -14128,13 +14188,13 @@
       <c r="J202" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Les differentes formes d'entreprises
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Dans quel cadre et comment entreprendre e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 9250 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Entreprise individuelle, Societe commerciale et Contrat de societe.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Entreprise individuelle, Societe commerciale, Contrat de societe.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Dans quel cadre et comment entreprendre e.</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -14144,7 +14204,7 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Entreprise individuelle, Societe commerciale, Contrat de societe.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Entreprise individuelle, Societe commerciale, Contrat de societe.</t>
         </is>
       </c>
       <c r="M202" t="n">
@@ -14196,13 +14256,13 @@
       <c r="J203" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Le respect de la concurrence
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Dans quel cadre et comment entreprendre e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 10500 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Liberte du commerce, Concurrence deloyale et Entente illicite.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Liberte du commerce, Concurrence deloyale, Entente illicite.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Dans quel cadre et comment entreprendre e.</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -14212,7 +14272,7 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Liberte du commerce, Concurrence deloyale, Entente illicite.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Liberte du commerce, Concurrence deloyale, Entente illicite.</t>
         </is>
       </c>
       <c r="M203" t="n">
@@ -14264,13 +14324,13 @@
       <c r="J204" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Les partenariats contractuels
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Dans quel cadre et comment entreprendre e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 11750 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Contrat de franchise, Contrat d'entreprise et Sous-traitance.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Contrat de franchise, Contrat d'entreprise, Sous-traitance.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Dans quel cadre et comment entreprendre e.</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -14280,7 +14340,7 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Contrat de franchise, Contrat d'entreprise, Sous-traitance.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Contrat de franchise, Contrat d'entreprise, Sous-traitance.</t>
         </is>
       </c>
       <c r="M204" t="n">
@@ -14332,13 +14392,13 @@
       <c r="J205" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Les differentes formes d'entreprises
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Dans quel cadre et comment entreprendre e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 13000 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Entreprise individuelle, Societe commerciale et Contrat de societe.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Entreprise individuelle, Societe commerciale, Contrat de societe.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Dans quel cadre et comment entreprendre e.</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
@@ -14348,7 +14408,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Entreprise individuelle, Societe commerciale, Contrat de societe.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Entreprise individuelle, Societe commerciale, Contrat de societe.</t>
         </is>
       </c>
       <c r="M205" t="n">
@@ -14400,13 +14460,13 @@
       <c r="J206" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Le respect de la concurrence
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Dans quel cadre et comment entreprendre e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 14250 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Liberte du commerce, Concurrence deloyale et Entente illicite.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Liberte du commerce, Concurrence deloyale, Entente illicite.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Dans quel cadre et comment entreprendre e.</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
@@ -14416,7 +14476,7 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Liberte du commerce, Concurrence deloyale, Entente illicite.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Liberte du commerce, Concurrence deloyale, Entente illicite.</t>
         </is>
       </c>
       <c r="M206" t="n">
@@ -14468,13 +14528,13 @@
       <c r="J207" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Les partenariats contractuels
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Dans quel cadre et comment entreprendre e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 15500 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Contrat de franchise, Contrat d'entreprise et Sous-traitance.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Contrat de franchise, Contrat d'entreprise, Sous-traitance.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Dans quel cadre et comment entreprendre e.</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -14484,7 +14544,7 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Contrat de franchise, Contrat d'entreprise, Sous-traitance.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Contrat de franchise, Contrat d'entreprise, Sous-traitance.</t>
         </is>
       </c>
       <c r="M207" t="n">
@@ -14536,13 +14596,13 @@
       <c r="J208" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Les differentes formes d'entreprises
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Dans quel cadre et comment entreprendre e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 16750 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Entreprise individuelle, Societe commerciale et Contrat de societe.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Entreprise individuelle, Societe commerciale, Contrat de societe.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Dans quel cadre et comment entreprendre e.</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -14552,7 +14612,7 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Entreprise individuelle, Societe commerciale, Contrat de societe.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Entreprise individuelle, Societe commerciale, Contrat de societe.</t>
         </is>
       </c>
       <c r="M208" t="n">
@@ -14604,13 +14664,13 @@
       <c r="J209" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Le respect de la concurrence
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Dans quel cadre et comment entreprendre e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 18000 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Liberte du commerce, Concurrence deloyale et Entente illicite.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Liberte du commerce, Concurrence deloyale, Entente illicite.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Dans quel cadre et comment entreprendre e.</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
@@ -14620,7 +14680,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Liberte du commerce, Concurrence deloyale, Entente illicite.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Liberte du commerce, Concurrence deloyale, Entente illicite.</t>
         </is>
       </c>
       <c r="M209" t="n">
@@ -14672,13 +14732,13 @@
       <c r="J210" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Les partenariats contractuels
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Dans quel cadre et comment entreprendre e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 19250 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Contrat de franchise, Contrat d'entreprise et Sous-traitance.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Contrat de franchise, Contrat d'entreprise, Sous-traitance.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Dans quel cadre et comment entreprendre e.</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -14688,7 +14748,7 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Contrat de franchise, Contrat d'entreprise, Sous-traitance.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Contrat de franchise, Contrat d'entreprise, Sous-traitance.</t>
         </is>
       </c>
       <c r="M210" t="n">
@@ -14740,13 +14800,13 @@
       <c r="J211" t="inlineStr">
         <is>
           <t>Cas pratique juridique - Les differentes formes d'entreprises
-Situation: un litige oppose deux parties au sujet d'une obligation contestee.
-Question juridique: Dans quel cadre et comment entreprendre e.
+Situation: un litige oppose deux parties autour d'une obligation contestee (enjeu financier: 20500 EUR).
 Travail demande:
 1) Qualifie juridiquement les faits et les parties.
-2) Identifie la ou les regles applicables en mobilisant notamment Entreprise individuelle, Societe commerciale et Contrat de societe.
-3) Applique la regle au cas en repondant aux arguments de chaque partie.
-4) Conclus par une solution juridique motivee et precise les consequences possibles.</t>
+2) Selectionne les regles de droit pertinentes en mobilisant Entreprise individuelle, Societe commerciale, Contrat de societe.
+3) Applique la regle au cas en traitant les arguments de chaque partie.
+4) Conclus par une solution motivee (et indique, si necessaire, voies de recours / consequences juridiques).
+Question juridique: Dans quel cadre et comment entreprendre e.</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -14756,7 +14816,7 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>Correction attendue: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Entreprise individuelle, Societe commerciale, Contrat de societe.</t>
+          <t>Attendus: qualification juridique rigoureuse des faits, identification de la regle applicable, application argumentee au cas et solution juridiquement defendable. Notions cibles: Entreprise individuelle, Societe commerciale, Contrat de societe.</t>
         </is>
       </c>
       <c r="M211" t="n">
@@ -14807,14 +14867,14 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - L'intervention de l'Etat dans l'economie
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=127, indice d'emploi=100.
-Problematique: Comment l'Etat peut-il intervenir dans l'economie e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Etat gendarme, Etat providence et Depenses publiques.
+          <t>Etude economique appliquee - L'intervention de l'Etat dans l'economie
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=99, indice d'emploi=91).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Etat gendarme, Etat providence, Depenses publiques.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment l'Etat peut-il intervenir dans l'economie e.</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
@@ -14824,7 +14884,7 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Etat gendarme, Etat providence, Depenses publiques.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Etat gendarme, Etat providence, Depenses publiques.</t>
         </is>
       </c>
       <c r="M212" t="n">
@@ -14875,14 +14935,14 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Defaillances de marche et defaillances de l'Etat
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=134, indice d'emploi=105.
-Problematique: Comment l'Etat peut-il intervenir dans l'economie e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Defaillances de marche, Asymetries d'information et Externalites.
+          <t>Etude economique appliquee - Defaillances de marche et defaillances de l'Etat
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=103, indice d'emploi=94).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Defaillances de marche, Asymetries d'information, Externalites.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment l'Etat peut-il intervenir dans l'economie e.</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
@@ -14892,7 +14952,7 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Defaillances de marche, Asymetries d'information, Externalites.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Defaillances de marche, Asymetries d'information, Externalites.</t>
         </is>
       </c>
       <c r="M213" t="n">
@@ -14943,14 +15003,14 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les politiques economiques de l'Etat et de l'Europe
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=141, indice d'emploi=110.
-Problematique: Comment l'Etat peut-il intervenir dans l'economie e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Politique budgetaire, Politique monetaire et Politique de relance.
+          <t>Etude economique appliquee - Les politiques economiques de l'Etat et de l'Europe
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=107, indice d'emploi=97).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Politique budgetaire, Politique monetaire, Politique de relance.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment l'Etat peut-il intervenir dans l'economie e.</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -14960,7 +15020,7 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Politique budgetaire, Politique monetaire, Politique de relance.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Politique budgetaire, Politique monetaire, Politique de relance.</t>
         </is>
       </c>
       <c r="M214" t="n">
@@ -15011,14 +15071,14 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les politiques sociales de l'Etat
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=148, indice d'emploi=115.
-Problematique: Comment l'Etat peut-il intervenir dans l'economie e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Protection sociale, Redistribution horizontale et Redistribution verticale.
+          <t>Etude economique appliquee - Les politiques sociales de l'Etat
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=111, indice d'emploi=100).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Protection sociale, Redistribution horizontale, Redistribution verticale.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment l'Etat peut-il intervenir dans l'economie e.</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
@@ -15028,7 +15088,7 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Protection sociale, Redistribution horizontale, Redistribution verticale.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Protection sociale, Redistribution horizontale, Redistribution verticale.</t>
         </is>
       </c>
       <c r="M215" t="n">
@@ -15079,14 +15139,14 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - L'intervention de l'Etat dans l'economie
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=155, indice d'emploi=120.
-Problematique: Comment l'Etat peut-il intervenir dans l'economie e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Etat gendarme, Etat providence et Depenses publiques.
+          <t>Etude economique appliquee - L'intervention de l'Etat dans l'economie
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=115, indice d'emploi=103).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Etat gendarme, Etat providence, Depenses publiques.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment l'Etat peut-il intervenir dans l'economie e.</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
@@ -15096,7 +15156,7 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Etat gendarme, Etat providence, Depenses publiques.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Etat gendarme, Etat providence, Depenses publiques.</t>
         </is>
       </c>
       <c r="M216" t="n">
@@ -15147,14 +15207,14 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Defaillances de marche et defaillances de l'Etat
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=162, indice d'emploi=125.
-Problematique: Comment l'Etat peut-il intervenir dans l'economie e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Defaillances de marche, Asymetries d'information et Externalites.
+          <t>Etude economique appliquee - Defaillances de marche et defaillances de l'Etat
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=119, indice d'emploi=106).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Defaillances de marche, Asymetries d'information, Externalites.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment l'Etat peut-il intervenir dans l'economie e.</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
@@ -15164,7 +15224,7 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Defaillances de marche, Asymetries d'information, Externalites.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Defaillances de marche, Asymetries d'information, Externalites.</t>
         </is>
       </c>
       <c r="M217" t="n">
@@ -15215,14 +15275,14 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les politiques economiques de l'Etat et de l'Europe
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=169, indice d'emploi=130.
-Problematique: Comment l'Etat peut-il intervenir dans l'economie e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Politique budgetaire, Politique monetaire et Politique de relance.
+          <t>Etude economique appliquee - Les politiques economiques de l'Etat et de l'Europe
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=123, indice d'emploi=109).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Politique budgetaire, Politique monetaire, Politique de relance.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment l'Etat peut-il intervenir dans l'economie e.</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
@@ -15232,7 +15292,7 @@
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Politique budgetaire, Politique monetaire, Politique de relance.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Politique budgetaire, Politique monetaire, Politique de relance.</t>
         </is>
       </c>
       <c r="M218" t="n">
@@ -15283,14 +15343,14 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les politiques sociales de l'Etat
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=176, indice d'emploi=135.
-Problematique: Comment l'Etat peut-il intervenir dans l'economie e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Protection sociale, Redistribution horizontale et Redistribution verticale.
+          <t>Etude economique appliquee - Les politiques sociales de l'Etat
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=127, indice d'emploi=112).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Protection sociale, Redistribution horizontale, Redistribution verticale.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment l'Etat peut-il intervenir dans l'economie e.</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
@@ -15300,7 +15360,7 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Protection sociale, Redistribution horizontale, Redistribution verticale.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Protection sociale, Redistribution horizontale, Redistribution verticale.</t>
         </is>
       </c>
       <c r="M219" t="n">
@@ -15351,14 +15411,14 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - L'intervention de l'Etat dans l'economie
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=183, indice d'emploi=140.
-Problematique: Comment l'Etat peut-il intervenir dans l'economie e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Etat gendarme, Etat providence et Depenses publiques.
+          <t>Etude economique appliquee - L'intervention de l'Etat dans l'economie
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=131, indice d'emploi=115).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Etat gendarme, Etat providence, Depenses publiques.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment l'Etat peut-il intervenir dans l'economie e.</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
@@ -15368,7 +15428,7 @@
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Etat gendarme, Etat providence, Depenses publiques.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Etat gendarme, Etat providence, Depenses publiques.</t>
         </is>
       </c>
       <c r="M220" t="n">
@@ -15419,14 +15479,14 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Defaillances de marche et defaillances de l'Etat
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=190, indice d'emploi=145.
-Problematique: Comment l'Etat peut-il intervenir dans l'economie e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Defaillances de marche, Asymetries d'information et Externalites.
+          <t>Etude economique appliquee - Defaillances de marche et defaillances de l'Etat
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=135, indice d'emploi=118).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Defaillances de marche, Asymetries d'information, Externalites.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment l'Etat peut-il intervenir dans l'economie e.</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
@@ -15436,7 +15496,7 @@
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Defaillances de marche, Asymetries d'information, Externalites.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Defaillances de marche, Asymetries d'information, Externalites.</t>
         </is>
       </c>
       <c r="M221" t="n">
@@ -15487,14 +15547,14 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Chomage et marche du travail
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=127, indice d'emploi=100.
-Problematique: Quelle est l'influence de l'Etat sur l'evolution de l'emploi et du chomage e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Chomage, Taux de chomage et Taux d'emploi.
+          <t>Etude economique appliquee - Chomage et marche du travail
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=99, indice d'emploi=91).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Chomage, Taux de chomage, Taux d'emploi.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Quelle est l'influence de l'Etat sur l'evolution de l'emploi et du chomage e.</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
@@ -15504,7 +15564,7 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Chomage, Taux de chomage, Taux d'emploi.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Chomage, Taux de chomage, Taux d'emploi.</t>
         </is>
       </c>
       <c r="M222" t="n">
@@ -15555,14 +15615,14 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les politiques de l'emploi
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=134, indice d'emploi=105.
-Problematique: Quelle est l'influence de l'Etat sur l'evolution de l'emploi et du chomage e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Politiques actives de l'emploi, Politiques passives de l'emploi et Chomage structurel.
+          <t>Etude economique appliquee - Les politiques de l'emploi
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=103, indice d'emploi=94).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Politiques actives de l'emploi, Politiques passives de l'emploi, Chomage structurel.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Quelle est l'influence de l'Etat sur l'evolution de l'emploi et du chomage e.</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
@@ -15572,7 +15632,7 @@
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Politiques actives de l'emploi, Politiques passives de l'emploi, Chomage structurel.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Politiques actives de l'emploi, Politiques passives de l'emploi, Chomage structurel.</t>
         </is>
       </c>
       <c r="M223" t="n">
@@ -15623,14 +15683,14 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Chomage et marche du travail
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=141, indice d'emploi=110.
-Problematique: Quelle est l'influence de l'Etat sur l'evolution de l'emploi et du chomage e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Chomage, Taux de chomage et Taux d'emploi.
+          <t>Etude economique appliquee - Chomage et marche du travail
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=107, indice d'emploi=97).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Chomage, Taux de chomage, Taux d'emploi.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Quelle est l'influence de l'Etat sur l'evolution de l'emploi et du chomage e.</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
@@ -15640,7 +15700,7 @@
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Chomage, Taux de chomage, Taux d'emploi.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Chomage, Taux de chomage, Taux d'emploi.</t>
         </is>
       </c>
       <c r="M224" t="n">
@@ -15691,14 +15751,14 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les politiques de l'emploi
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=148, indice d'emploi=115.
-Problematique: Quelle est l'influence de l'Etat sur l'evolution de l'emploi et du chomage e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Politiques actives de l'emploi, Politiques passives de l'emploi et Chomage structurel.
+          <t>Etude economique appliquee - Les politiques de l'emploi
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=111, indice d'emploi=100).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Politiques actives de l'emploi, Politiques passives de l'emploi, Chomage structurel.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Quelle est l'influence de l'Etat sur l'evolution de l'emploi et du chomage e.</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
@@ -15708,7 +15768,7 @@
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Politiques actives de l'emploi, Politiques passives de l'emploi, Chomage structurel.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Politiques actives de l'emploi, Politiques passives de l'emploi, Chomage structurel.</t>
         </is>
       </c>
       <c r="M225" t="n">
@@ -15759,14 +15819,14 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Chomage et marche du travail
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=155, indice d'emploi=120.
-Problematique: Quelle est l'influence de l'Etat sur l'evolution de l'emploi et du chomage e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Chomage, Taux de chomage et Taux d'emploi.
+          <t>Etude economique appliquee - Chomage et marche du travail
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=115, indice d'emploi=103).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Chomage, Taux de chomage, Taux d'emploi.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Quelle est l'influence de l'Etat sur l'evolution de l'emploi et du chomage e.</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
@@ -15776,7 +15836,7 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Chomage, Taux de chomage, Taux d'emploi.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Chomage, Taux de chomage, Taux d'emploi.</t>
         </is>
       </c>
       <c r="M226" t="n">
@@ -15827,14 +15887,14 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les politiques de l'emploi
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=162, indice d'emploi=125.
-Problematique: Quelle est l'influence de l'Etat sur l'evolution de l'emploi et du chomage e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Politiques actives de l'emploi, Politiques passives de l'emploi et Chomage structurel.
+          <t>Etude economique appliquee - Les politiques de l'emploi
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=119, indice d'emploi=106).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Politiques actives de l'emploi, Politiques passives de l'emploi, Chomage structurel.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Quelle est l'influence de l'Etat sur l'evolution de l'emploi et du chomage e.</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
@@ -15844,7 +15904,7 @@
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Politiques actives de l'emploi, Politiques passives de l'emploi, Chomage structurel.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Politiques actives de l'emploi, Politiques passives de l'emploi, Chomage structurel.</t>
         </is>
       </c>
       <c r="M227" t="n">
@@ -15895,14 +15955,14 @@
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Chomage et marche du travail
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=169, indice d'emploi=130.
-Problematique: Quelle est l'influence de l'Etat sur l'evolution de l'emploi et du chomage e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Chomage, Taux de chomage et Taux d'emploi.
+          <t>Etude economique appliquee - Chomage et marche du travail
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=123, indice d'emploi=109).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Chomage, Taux de chomage, Taux d'emploi.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Quelle est l'influence de l'Etat sur l'evolution de l'emploi et du chomage e.</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
@@ -15912,7 +15972,7 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Chomage, Taux de chomage, Taux d'emploi.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Chomage, Taux de chomage, Taux d'emploi.</t>
         </is>
       </c>
       <c r="M228" t="n">
@@ -15963,14 +16023,14 @@
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les politiques de l'emploi
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=176, indice d'emploi=135.
-Problematique: Quelle est l'influence de l'Etat sur l'evolution de l'emploi et du chomage e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Politiques actives de l'emploi, Politiques passives de l'emploi et Chomage structurel.
+          <t>Etude economique appliquee - Les politiques de l'emploi
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=127, indice d'emploi=112).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Politiques actives de l'emploi, Politiques passives de l'emploi, Chomage structurel.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Quelle est l'influence de l'Etat sur l'evolution de l'emploi et du chomage e.</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
@@ -15980,7 +16040,7 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Politiques actives de l'emploi, Politiques passives de l'emploi, Chomage structurel.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Politiques actives de l'emploi, Politiques passives de l'emploi, Chomage structurel.</t>
         </is>
       </c>
       <c r="M229" t="n">
@@ -16031,14 +16091,14 @@
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Chomage et marche du travail
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=183, indice d'emploi=140.
-Problematique: Quelle est l'influence de l'Etat sur l'evolution de l'emploi et du chomage e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Chomage, Taux de chomage et Taux d'emploi.
+          <t>Etude economique appliquee - Chomage et marche du travail
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=131, indice d'emploi=115).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Chomage, Taux de chomage, Taux d'emploi.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Quelle est l'influence de l'Etat sur l'evolution de l'emploi et du chomage e.</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
@@ -16048,7 +16108,7 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Chomage, Taux de chomage, Taux d'emploi.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Chomage, Taux de chomage, Taux d'emploi.</t>
         </is>
       </c>
       <c r="M230" t="n">
@@ -16099,14 +16159,14 @@
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les politiques de l'emploi
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=190, indice d'emploi=145.
-Problematique: Quelle est l'influence de l'Etat sur l'evolution de l'emploi et du chomage e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Politiques actives de l'emploi, Politiques passives de l'emploi et Chomage structurel.
+          <t>Etude economique appliquee - Les politiques de l'emploi
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=135, indice d'emploi=118).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Politiques actives de l'emploi, Politiques passives de l'emploi, Chomage structurel.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Quelle est l'influence de l'Etat sur l'evolution de l'emploi et du chomage e.</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
@@ -16116,7 +16176,7 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Politiques actives de l'emploi, Politiques passives de l'emploi, Chomage structurel.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Politiques actives de l'emploi, Politiques passives de l'emploi, Chomage structurel.</t>
         </is>
       </c>
       <c r="M231" t="n">
@@ -16167,14 +16227,14 @@
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les transformations du commerce mondial
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=127, indice d'emploi=100.
-Problematique: Comment organiser le commerce international dans un contexte d'ouverture des echanges e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Importations, Exportations et Balance commerciale.
+          <t>Etude economique appliquee - Les transformations du commerce mondial
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=99, indice d'emploi=91).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Importations, Exportations, Balance commerciale.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment organiser le commerce international dans un contexte d'ouverture des echanges e.</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
@@ -16184,7 +16244,7 @@
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Importations, Exportations, Balance commerciale.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Importations, Exportations, Balance commerciale.</t>
         </is>
       </c>
       <c r="M232" t="n">
@@ -16235,14 +16295,14 @@
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les politiques commerciales et l'organisation mondiale des echanges
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=134, indice d'emploi=105.
-Problematique: Comment organiser le commerce international dans un contexte d'ouverture des echanges e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Libre-echange, Protectionnisme et Droits de douane.
+          <t>Etude economique appliquee - Les politiques commerciales et l'organisation mondiale des echanges
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=103, indice d'emploi=94).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Libre-echange, Protectionnisme, Droits de douane.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment organiser le commerce international dans un contexte d'ouverture des echanges e.</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
@@ -16252,7 +16312,7 @@
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Libre-echange, Protectionnisme, Droits de douane.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Libre-echange, Protectionnisme, Droits de douane.</t>
         </is>
       </c>
       <c r="M233" t="n">
@@ -16303,14 +16363,14 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les transformations du commerce mondial
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=141, indice d'emploi=110.
-Problematique: Comment organiser le commerce international dans un contexte d'ouverture des echanges e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Importations, Exportations et Balance commerciale.
+          <t>Etude economique appliquee - Les transformations du commerce mondial
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=107, indice d'emploi=97).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Importations, Exportations, Balance commerciale.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment organiser le commerce international dans un contexte d'ouverture des echanges e.</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
@@ -16320,7 +16380,7 @@
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Importations, Exportations, Balance commerciale.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Importations, Exportations, Balance commerciale.</t>
         </is>
       </c>
       <c r="M234" t="n">
@@ -16371,14 +16431,14 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les politiques commerciales et l'organisation mondiale des echanges
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=148, indice d'emploi=115.
-Problematique: Comment organiser le commerce international dans un contexte d'ouverture des echanges e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Libre-echange, Protectionnisme et Droits de douane.
+          <t>Etude economique appliquee - Les politiques commerciales et l'organisation mondiale des echanges
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=111, indice d'emploi=100).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Libre-echange, Protectionnisme, Droits de douane.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment organiser le commerce international dans un contexte d'ouverture des echanges e.</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
@@ -16388,7 +16448,7 @@
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Libre-echange, Protectionnisme, Droits de douane.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Libre-echange, Protectionnisme, Droits de douane.</t>
         </is>
       </c>
       <c r="M235" t="n">
@@ -16439,14 +16499,14 @@
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les transformations du commerce mondial
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=155, indice d'emploi=120.
-Problematique: Comment organiser le commerce international dans un contexte d'ouverture des echanges e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Importations, Exportations et Balance commerciale.
+          <t>Etude economique appliquee - Les transformations du commerce mondial
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=115, indice d'emploi=103).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Importations, Exportations, Balance commerciale.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment organiser le commerce international dans un contexte d'ouverture des echanges e.</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
@@ -16456,7 +16516,7 @@
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Importations, Exportations, Balance commerciale.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Importations, Exportations, Balance commerciale.</t>
         </is>
       </c>
       <c r="M236" t="n">
@@ -16507,14 +16567,14 @@
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les politiques commerciales et l'organisation mondiale des echanges
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=162, indice d'emploi=125.
-Problematique: Comment organiser le commerce international dans un contexte d'ouverture des echanges e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Libre-echange, Protectionnisme et Droits de douane.
+          <t>Etude economique appliquee - Les politiques commerciales et l'organisation mondiale des echanges
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=119, indice d'emploi=106).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Libre-echange, Protectionnisme, Droits de douane.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment organiser le commerce international dans un contexte d'ouverture des echanges e.</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
@@ -16524,7 +16584,7 @@
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Libre-echange, Protectionnisme, Droits de douane.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Libre-echange, Protectionnisme, Droits de douane.</t>
         </is>
       </c>
       <c r="M237" t="n">
@@ -16575,14 +16635,14 @@
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les transformations du commerce mondial
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=169, indice d'emploi=130.
-Problematique: Comment organiser le commerce international dans un contexte d'ouverture des echanges e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Importations, Exportations et Balance commerciale.
+          <t>Etude economique appliquee - Les transformations du commerce mondial
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=123, indice d'emploi=109).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Importations, Exportations, Balance commerciale.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment organiser le commerce international dans un contexte d'ouverture des echanges e.</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
@@ -16592,7 +16652,7 @@
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Importations, Exportations, Balance commerciale.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Importations, Exportations, Balance commerciale.</t>
         </is>
       </c>
       <c r="M238" t="n">
@@ -16643,14 +16703,14 @@
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les politiques commerciales et l'organisation mondiale des echanges
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=176, indice d'emploi=135.
-Problematique: Comment organiser le commerce international dans un contexte d'ouverture des echanges e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Libre-echange, Protectionnisme et Droits de douane.
+          <t>Etude economique appliquee - Les politiques commerciales et l'organisation mondiale des echanges
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=127, indice d'emploi=112).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Libre-echange, Protectionnisme, Droits de douane.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment organiser le commerce international dans un contexte d'ouverture des echanges e.</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
@@ -16660,7 +16720,7 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Libre-echange, Protectionnisme, Droits de douane.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Libre-echange, Protectionnisme, Droits de douane.</t>
         </is>
       </c>
       <c r="M239" t="n">
@@ -16711,14 +16771,14 @@
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les transformations du commerce mondial
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=183, indice d'emploi=140.
-Problematique: Comment organiser le commerce international dans un contexte d'ouverture des echanges e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Importations, Exportations et Balance commerciale.
+          <t>Etude economique appliquee - Les transformations du commerce mondial
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=131, indice d'emploi=115).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Importations, Exportations, Balance commerciale.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment organiser le commerce international dans un contexte d'ouverture des echanges e.</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
@@ -16728,7 +16788,7 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Importations, Exportations, Balance commerciale.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Importations, Exportations, Balance commerciale.</t>
         </is>
       </c>
       <c r="M240" t="n">
@@ -16779,14 +16839,14 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les politiques commerciales et l'organisation mondiale des echanges
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=190, indice d'emploi=145.
-Problematique: Comment organiser le commerce international dans un contexte d'ouverture des echanges e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Libre-echange, Protectionnisme et Droits de douane.
+          <t>Etude economique appliquee - Les politiques commerciales et l'organisation mondiale des echanges
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=135, indice d'emploi=118).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Libre-echange, Protectionnisme, Droits de douane.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment organiser le commerce international dans un contexte d'ouverture des echanges e.</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
@@ -16796,7 +16856,7 @@
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Libre-echange, Protectionnisme, Droits de douane.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Libre-echange, Protectionnisme, Droits de douane.</t>
         </is>
       </c>
       <c r="M241" t="n">
@@ -16847,14 +16907,14 @@
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les sources et les limites de la croissance economique
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=127, indice d'emploi=100.
-Problematique: Comment concilier la croissance economique et le developpement durable e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Croissance economique, Developpement durable et Progres technique.
+          <t>Etude economique appliquee - Les sources et les limites de la croissance economique
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=99, indice d'emploi=91).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Croissance economique, Developpement durable, Progres technique.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment concilier la croissance economique et le developpement durable e.</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
@@ -16864,7 +16924,7 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Croissance economique, Developpement durable, Progres technique.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Croissance economique, Developpement durable, Progres technique.</t>
         </is>
       </c>
       <c r="M242" t="n">
@@ -16915,14 +16975,14 @@
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - L'education et la formation, moteurs de lutte contre la pauvrete
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=134, indice d'emploi=105.
-Problematique: Comment concilier la croissance economique et le developpement durable e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Pauvrete absolue, Pauvrete relative et Capital humain.
+          <t>Etude economique appliquee - L'education et la formation, moteurs de lutte contre la pauvrete
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=103, indice d'emploi=94).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Pauvrete absolue, Pauvrete relative, Capital humain.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment concilier la croissance economique et le developpement durable e.</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
@@ -16932,7 +16992,7 @@
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Pauvrete absolue, Pauvrete relative, Capital humain.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Pauvrete absolue, Pauvrete relative, Capital humain.</t>
         </is>
       </c>
       <c r="M243" t="n">
@@ -16983,14 +17043,14 @@
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les sources et les limites de la croissance economique
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=141, indice d'emploi=110.
-Problematique: Comment concilier la croissance economique et le developpement durable e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Croissance economique, Developpement durable et Progres technique.
+          <t>Etude economique appliquee - Les sources et les limites de la croissance economique
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=107, indice d'emploi=97).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Croissance economique, Developpement durable, Progres technique.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment concilier la croissance economique et le developpement durable e.</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
@@ -17000,7 +17060,7 @@
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Croissance economique, Developpement durable, Progres technique.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Croissance economique, Developpement durable, Progres technique.</t>
         </is>
       </c>
       <c r="M244" t="n">
@@ -17051,14 +17111,14 @@
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - L'education et la formation, moteurs de lutte contre la pauvrete
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=148, indice d'emploi=115.
-Problematique: Comment concilier la croissance economique et le developpement durable e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Pauvrete absolue, Pauvrete relative et Capital humain.
+          <t>Etude economique appliquee - L'education et la formation, moteurs de lutte contre la pauvrete
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=111, indice d'emploi=100).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Pauvrete absolue, Pauvrete relative, Capital humain.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment concilier la croissance economique et le developpement durable e.</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
@@ -17068,7 +17128,7 @@
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Pauvrete absolue, Pauvrete relative, Capital humain.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Pauvrete absolue, Pauvrete relative, Capital humain.</t>
         </is>
       </c>
       <c r="M245" t="n">
@@ -17119,14 +17179,14 @@
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les sources et les limites de la croissance economique
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=155, indice d'emploi=120.
-Problematique: Comment concilier la croissance economique et le developpement durable e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Croissance economique, Developpement durable et Progres technique.
+          <t>Etude economique appliquee - Les sources et les limites de la croissance economique
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=115, indice d'emploi=103).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Croissance economique, Developpement durable, Progres technique.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment concilier la croissance economique et le developpement durable e.</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
@@ -17136,7 +17196,7 @@
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Croissance economique, Developpement durable, Progres technique.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Croissance economique, Developpement durable, Progres technique.</t>
         </is>
       </c>
       <c r="M246" t="n">
@@ -17187,14 +17247,14 @@
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - L'education et la formation, moteurs de lutte contre la pauvrete
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=162, indice d'emploi=125.
-Problematique: Comment concilier la croissance economique et le developpement durable e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Pauvrete absolue, Pauvrete relative et Capital humain.
+          <t>Etude economique appliquee - L'education et la formation, moteurs de lutte contre la pauvrete
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=119, indice d'emploi=106).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Pauvrete absolue, Pauvrete relative, Capital humain.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment concilier la croissance economique et le developpement durable e.</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
@@ -17204,7 +17264,7 @@
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Pauvrete absolue, Pauvrete relative, Capital humain.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Pauvrete absolue, Pauvrete relative, Capital humain.</t>
         </is>
       </c>
       <c r="M247" t="n">
@@ -17255,14 +17315,14 @@
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les sources et les limites de la croissance economique
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=169, indice d'emploi=130.
-Problematique: Comment concilier la croissance economique et le developpement durable e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Croissance economique, Developpement durable et Progres technique.
+          <t>Etude economique appliquee - Les sources et les limites de la croissance economique
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=123, indice d'emploi=109).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Croissance economique, Developpement durable, Progres technique.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment concilier la croissance economique et le developpement durable e.</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
@@ -17272,7 +17332,7 @@
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Croissance economique, Developpement durable, Progres technique.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Croissance economique, Developpement durable, Progres technique.</t>
         </is>
       </c>
       <c r="M248" t="n">
@@ -17323,14 +17383,14 @@
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - L'education et la formation, moteurs de lutte contre la pauvrete
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=176, indice d'emploi=135.
-Problematique: Comment concilier la croissance economique et le developpement durable e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Pauvrete absolue, Pauvrete relative et Capital humain.
+          <t>Etude economique appliquee - L'education et la formation, moteurs de lutte contre la pauvrete
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=127, indice d'emploi=112).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Pauvrete absolue, Pauvrete relative, Capital humain.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment concilier la croissance economique et le developpement durable e.</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
@@ -17340,7 +17400,7 @@
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Pauvrete absolue, Pauvrete relative, Capital humain.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Pauvrete absolue, Pauvrete relative, Capital humain.</t>
         </is>
       </c>
       <c r="M249" t="n">
@@ -17391,14 +17451,14 @@
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - Les sources et les limites de la croissance economique
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=183, indice d'emploi=140.
-Problematique: Comment concilier la croissance economique et le developpement durable e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Croissance economique, Developpement durable et Progres technique.
+          <t>Etude economique appliquee - Les sources et les limites de la croissance economique
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=131, indice d'emploi=115).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Croissance economique, Developpement durable, Progres technique.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment concilier la croissance economique et le developpement durable e.</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
@@ -17408,7 +17468,7 @@
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Croissance economique, Developpement durable, Progres technique.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Croissance economique, Developpement durable, Progres technique.</t>
         </is>
       </c>
       <c r="M250" t="n">
@@ -17459,14 +17519,14 @@
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>Analyse economique appliquee - L'education et la formation, moteurs de lutte contre la pauvrete
-Contexte: un territoire observe une evolution des indicateurs suivants: indice d'activite=190, indice d'emploi=145.
-Problematique: Comment concilier la croissance economique et le developpement durable e.
-Travail demande:
-1) Explique le mecanisme economique en jeu en mobilisant Pauvrete absolue, Pauvrete relative et Capital humain.
+          <t>Etude economique appliquee - L'education et la formation, moteurs de lutte contre la pauvrete
+Contexte: un territoire observe une evolution de ses indicateurs (indice d'activite=135, indice d'emploi=118).
+Travail demande:
+1) Explique le mecanisme economique en jeu en mobilisant Pauvrete absolue, Pauvrete relative, Capital humain.
 2) Interprete les donnees et formule des hypotheses coherentes.
-3) Discute au moins une limite de l'analyse (hypotheses, causalite, contexte).
-4) Propose une orientation d'action economique argumentee.</t>
+3) Discute une limite de l'analyse (contexte, causalite, hypothese).
+4) Propose une orientation d'action economique argumentee.
+Problematique de chapitre: Comment concilier la croissance economique et le developpement durable e.</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
@@ -17476,7 +17536,7 @@
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>Correction attendue: explication des mecanismes economiques, interpretation correcte des donnees, discussion des limites et proposition argumentee. Notions cibles: Pauvrete absolue, Pauvrete relative, Capital humain.</t>
+          <t>Attendus: mecanisme economique correctement explique, interpretation des donnees, discussion des limites et orientation argumentee. Notions cibles: Pauvrete absolue, Pauvrete relative, Capital humain.</t>
         </is>
       </c>
       <c r="M251" t="n">
@@ -17527,14 +17587,15 @@
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>Etude de cas management - Quels produits ou quels services pour quels besoins e
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Quels produits ou quels services pour quels besoins e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Demarche marketing, Approches marketing et Etude de marche.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - Quels produits ou quels services pour quels besoins e
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Demarche marketing, Approches marketing, Etude de marche.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Quels produits ou quels services pour quels besoins e.</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
@@ -17544,7 +17605,7 @@
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Demarche marketing, Approches marketing, Etude de marche.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Demarche marketing, Approches marketing, Etude de marche.</t>
         </is>
       </c>
       <c r="M252" t="n">
@@ -17595,14 +17656,15 @@
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>Etude de cas management - Comment creer de la valeur et la mesurer e
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Comment creer de la valeur et la mesurer e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Valeur ajoutee, Indicateurs de creation de valeur et Compte de resultat.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - Comment creer de la valeur et la mesurer e
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Valeur ajoutee, Indicateurs de creation de valeur, Compte de resultat.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Comment creer de la valeur et la mesurer e.</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
@@ -17612,7 +17674,7 @@
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Valeur ajoutee, Indicateurs de creation de valeur, Compte de resultat.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Valeur ajoutee, Indicateurs de creation de valeur, Compte de resultat.</t>
         </is>
       </c>
       <c r="M253" t="n">
@@ -17663,14 +17725,15 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>Etude de cas management - Quelles ressources financieres pour produire e
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Quelles ressources financieres pour produire e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Ressources tangibles et intangibles, Financement de l'investissement et Autofinancement.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - Quelles ressources financieres pour produire e
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Ressources tangibles et intangibles, Financement de l'investissement, Autofinancement.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Quelles ressources financieres pour produire e.</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
@@ -17680,7 +17743,7 @@
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Ressources tangibles et intangibles, Financement de l'investissement, Autofinancement.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Ressources tangibles et intangibles, Financement de l'investissement, Autofinancement.</t>
         </is>
       </c>
       <c r="M254" t="n">
@@ -17731,14 +17794,15 @@
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>Etude de cas management - Quelles ressources humaines pour produire e
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Quelles ressources humaines pour produire e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant GPEC, Recrutement et Formation.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - Quelles ressources humaines pour produire e
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant GPEC, Recrutement, Formation.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Quelles ressources humaines pour produire e.</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
@@ -17748,7 +17812,7 @@
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: GPEC, Recrutement, Formation.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: GPEC, Recrutement, Formation.</t>
         </is>
       </c>
       <c r="M255" t="n">
@@ -17799,14 +17863,15 @@
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>Etude de cas management - Quels choix d'organisation de la production pour concilier flexibilite et qualite e
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Quels choix d'organisation de la production pour concilier flexibilite, qualite et maitrise des couts e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Innovation de procedes, Logistique et Supply chain.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - Quels choix d'organisation de la production pour concilier flexibilite et qualite e
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Innovation de procedes, Logistique, Supply chain.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Quels choix d'organisation de la production pour concilier flexibilite, qualite et maitrise des couts e.</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
@@ -17816,7 +17881,7 @@
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Innovation de procedes, Logistique, Supply chain.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Innovation de procedes, Logistique, Supply chain.</t>
         </is>
       </c>
       <c r="M256" t="n">
@@ -17867,14 +17932,15 @@
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>Etude de cas management - Pourquoi controler les couts e
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Pourquoi controler les couts e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Cout complet, Cout specifique et Charges directes.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - Pourquoi controler les couts e
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Cout complet, Cout specifique, Charges directes.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Pourquoi controler les couts e.</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
@@ -17884,7 +17950,7 @@
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Cout complet, Cout specifique, Charges directes.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Cout complet, Cout specifique, Charges directes.</t>
         </is>
       </c>
       <c r="M257" t="n">
@@ -17935,14 +18001,15 @@
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>Etude de cas management - Quel est le role des technologies numeriques dans la production e
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Les transformations numeriques, une chance pour la production e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Dematerialisation, Automatisation et Cloud computing.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - Quel est le role des technologies numeriques dans la production e
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Dematerialisation, Automatisation, Cloud computing.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Les transformations numeriques, une chance pour la production e.</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
@@ -17952,7 +18019,7 @@
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Dematerialisation, Automatisation, Cloud computing.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Dematerialisation, Automatisation, Cloud computing.</t>
         </is>
       </c>
       <c r="M258" t="n">
@@ -18003,14 +18070,15 @@
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>Etude de cas management - Comment organiser et coordonner le travail e
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Comment assurer un fonctionnement coherent des organisations e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Organisation du travail, Flexibilite et Reactivite.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - Comment organiser et coordonner le travail e
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Organisation du travail, Flexibilite, Reactivite.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Comment assurer un fonctionnement coherent des organisations e.</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
@@ -18020,7 +18088,7 @@
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Organisation du travail, Flexibilite, Reactivite.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Organisation du travail, Flexibilite, Reactivite.</t>
         </is>
       </c>
       <c r="M259" t="n">
@@ -18071,14 +18139,15 @@
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>Etude de cas management - Quels produits ou quels services pour quels besoins e
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Quels produits ou quels services pour quels besoins e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Demarche marketing, Approches marketing et Etude de marche.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - Quels produits ou quels services pour quels besoins e
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Demarche marketing, Approches marketing, Etude de marche.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Quels produits ou quels services pour quels besoins e.</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
@@ -18088,7 +18157,7 @@
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Demarche marketing, Approches marketing, Etude de marche.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Demarche marketing, Approches marketing, Etude de marche.</t>
         </is>
       </c>
       <c r="M260" t="n">
@@ -18139,14 +18208,15 @@
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>Etude de cas management - Comment creer de la valeur et la mesurer e
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Comment creer de la valeur et la mesurer e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Valeur ajoutee, Indicateurs de creation de valeur et Compte de resultat.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - Comment creer de la valeur et la mesurer e
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Valeur ajoutee, Indicateurs de creation de valeur, Compte de resultat.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Comment creer de la valeur et la mesurer e.</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
@@ -18156,7 +18226,7 @@
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Valeur ajoutee, Indicateurs de creation de valeur, Compte de resultat.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Valeur ajoutee, Indicateurs de creation de valeur, Compte de resultat.</t>
         </is>
       </c>
       <c r="M261" t="n">
@@ -18207,14 +18277,15 @@
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>Etude de cas management - Comment le management prend-il en compte les attentes des acteurs e
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Comment federer les acteurs de l'organisation e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Interets des acteurs, Culture de l'organisation et Motivation.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - Comment le management prend-il en compte les attentes des acteurs e
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Interets des acteurs, Culture de l'organisation, Motivation.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Comment federer les acteurs de l'organisation e.</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
@@ -18224,7 +18295,7 @@
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Interets des acteurs, Culture de l'organisation, Motivation.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Interets des acteurs, Culture de l'organisation, Motivation.</t>
         </is>
       </c>
       <c r="M262" t="n">
@@ -18275,14 +18346,15 @@
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>Etude de cas management - Comment federer les acteurs de l'organisation e
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Comment federer les acteurs de l'organisation e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Style de direction, Leadership et Cooperation.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - Comment federer les acteurs de l'organisation e
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Style de direction, Leadership, Cooperation.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Comment federer les acteurs de l'organisation e.</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
@@ -18292,7 +18364,7 @@
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Style de direction, Leadership, Cooperation.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Style de direction, Leadership, Cooperation.</t>
         </is>
       </c>
       <c r="M263" t="n">
@@ -18343,14 +18415,15 @@
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>Etude de cas management - Les transformations numeriques, vecteurs d'amelioration de la relation clients e
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Les transformations numeriques, vecteur d'amelioration de la relation avec les clients et usagers e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Consommateur, Processus d'achat et Digitalisation relation client.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - Les transformations numeriques, vecteurs d'amelioration de la relation clients e
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Consommateur, Processus d'achat, Digitalisation relation client.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Les transformations numeriques, vecteur d'amelioration de la relation avec les clients et usagers e.</t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
@@ -18360,7 +18433,7 @@
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Consommateur, Processus d'achat, Digitalisation relation client.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Consommateur, Processus d'achat, Digitalisation relation client.</t>
         </is>
       </c>
       <c r="M264" t="n">
@@ -18411,14 +18484,15 @@
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>Etude de cas management - Comment une organisation communique-t-elle avec ses differents acteurs e
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Communique-t-on de la meme maniere avec tous les acteurs e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Strategie de communication, Communication interne et Communication externe.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - Comment une organisation communique-t-elle avec ses differents acteurs e
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Strategie de communication, Communication interne, Communication externe.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Communique-t-on de la meme maniere avec tous les acteurs e.</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
@@ -18428,7 +18502,7 @@
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Strategie de communication, Communication interne, Communication externe.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Strategie de communication, Communication interne, Communication externe.</t>
         </is>
       </c>
       <c r="M265" t="n">
@@ -18479,14 +18553,15 @@
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>Etude de cas management - Comment le management prend-il en compte les attentes des acteurs e
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Comment federer les acteurs de l'organisation e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Interets des acteurs, Culture de l'organisation et Motivation.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - Comment le management prend-il en compte les attentes des acteurs e
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Interets des acteurs, Culture de l'organisation, Motivation.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Comment federer les acteurs de l'organisation e.</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
@@ -18496,7 +18571,7 @@
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Interets des acteurs, Culture de l'organisation, Motivation.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Interets des acteurs, Culture de l'organisation, Motivation.</t>
         </is>
       </c>
       <c r="M266" t="n">
@@ -18547,14 +18622,15 @@
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>Etude de cas management - Comment federer les acteurs de l'organisation e
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Comment federer les acteurs de l'organisation e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Style de direction, Leadership et Cooperation.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - Comment federer les acteurs de l'organisation e
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Style de direction, Leadership, Cooperation.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Comment federer les acteurs de l'organisation e.</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
@@ -18564,7 +18640,7 @@
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Style de direction, Leadership, Cooperation.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Style de direction, Leadership, Cooperation.</t>
         </is>
       </c>
       <c r="M267" t="n">
@@ -18615,14 +18691,15 @@
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>Etude de cas management - Les transformations numeriques, vecteurs d'amelioration de la relation clients e
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Les transformations numeriques, vecteur d'amelioration de la relation avec les clients et usagers e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Consommateur, Processus d'achat et Digitalisation relation client.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - Les transformations numeriques, vecteurs d'amelioration de la relation clients e
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Consommateur, Processus d'achat, Digitalisation relation client.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Les transformations numeriques, vecteur d'amelioration de la relation avec les clients et usagers e.</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
@@ -18632,7 +18709,7 @@
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Consommateur, Processus d'achat, Digitalisation relation client.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Consommateur, Processus d'achat, Digitalisation relation client.</t>
         </is>
       </c>
       <c r="M268" t="n">
@@ -18683,14 +18760,15 @@
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>Etude de cas management - Comment une organisation communique-t-elle avec ses differents acteurs e
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Communique-t-on de la meme maniere avec tous les acteurs e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Strategie de communication, Communication interne et Communication externe.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - Comment une organisation communique-t-elle avec ses differents acteurs e
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Strategie de communication, Communication interne, Communication externe.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Communique-t-on de la meme maniere avec tous les acteurs e.</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
@@ -18700,7 +18778,7 @@
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Strategie de communication, Communication interne, Communication externe.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Strategie de communication, Communication interne, Communication externe.</t>
         </is>
       </c>
       <c r="M269" t="n">
@@ -18751,14 +18829,15 @@
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>Etude de cas management - Comment le management prend-il en compte les attentes des acteurs e
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Comment federer les acteurs de l'organisation e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Interets des acteurs, Culture de l'organisation et Motivation.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - Comment le management prend-il en compte les attentes des acteurs e
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Interets des acteurs, Culture de l'organisation, Motivation.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Comment federer les acteurs de l'organisation e.</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
@@ -18768,7 +18847,7 @@
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Interets des acteurs, Culture de l'organisation, Motivation.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Interets des acteurs, Culture de l'organisation, Motivation.</t>
         </is>
       </c>
       <c r="M270" t="n">
@@ -18819,14 +18898,15 @@
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>Etude de cas management - Comment federer les acteurs de l'organisation e
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Comment federer les acteurs de l'organisation e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Style de direction, Leadership et Cooperation.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - Comment federer les acteurs de l'organisation e
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Style de direction, Leadership, Cooperation.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Comment federer les acteurs de l'organisation e.</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
@@ -18836,7 +18916,7 @@
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Style de direction, Leadership, Cooperation.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Style de direction, Leadership, Cooperation.</t>
         </is>
       </c>
       <c r="M271" t="n">
@@ -18887,14 +18967,15 @@
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>Etude de cas management - Quels enjeux ethiques dans l'activite des organisations e
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Les organisations peuvent-elles s'affranchir des questions de societe e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Ethique, Deontologie et RSE.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - Quels enjeux ethiques dans l'activite des organisations e
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Ethique, Deontologie, RSE.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Les organisations peuvent-elles s'affranchir des questions de societe e.</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
@@ -18904,7 +18985,7 @@
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Ethique, Deontologie, RSE.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Ethique, Deontologie, RSE.</t>
         </is>
       </c>
       <c r="M272" t="n">
@@ -18955,14 +19036,15 @@
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>Etude de cas management - Comment les organisations prennent-elles en compte les changements des modes de vie e
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Les changements de modes de vie s'imposent-ils aux organisations e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Rapport au travail, Teletravail et Modes de consommation.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - Comment les organisations prennent-elles en compte les changements des modes de vie e
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Rapport au travail, Teletravail, Modes de consommation.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Les changements de modes de vie s'imposent-ils aux organisations e.</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
@@ -18972,7 +19054,7 @@
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Rapport au travail, Teletravail, Modes de consommation.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Rapport au travail, Teletravail, Modes de consommation.</t>
         </is>
       </c>
       <c r="M273" t="n">
@@ -19023,14 +19105,15 @@
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>Etude de cas management - Quelles responsabilites le numerique cree-t-il pour les organisations e
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Les transformations numeriques, de nouvelles responsabilites pour les organisations e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Protection des donnees personnelles, RGPD et Transparence des algorithmes.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - Quelles responsabilites le numerique cree-t-il pour les organisations e
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Protection des donnees personnelles, RGPD, Transparence des algorithmes.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Les transformations numeriques, de nouvelles responsabilites pour les organisations e.</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
@@ -19040,7 +19123,7 @@
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Protection des donnees personnelles, RGPD, Transparence des algorithmes.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Protection des donnees personnelles, RGPD, Transparence des algorithmes.</t>
         </is>
       </c>
       <c r="M274" t="n">
@@ -19091,14 +19174,15 @@
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>Etude de cas management - Quelles relations entre les organisations et leur ecosysteme e
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Quelles relations entre les organisations et leur ecosysteme e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Strategie d'implantation, Ecosysteme d'affaires et Cluster.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - Quelles relations entre les organisations et leur ecosysteme e
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Strategie d'implantation, Ecosysteme d'affaires, Cluster.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Quelles relations entre les organisations et leur ecosysteme e.</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
@@ -19108,7 +19192,7 @@
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Strategie d'implantation, Ecosysteme d'affaires, Cluster.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Strategie d'implantation, Ecosysteme d'affaires, Cluster.</t>
         </is>
       </c>
       <c r="M275" t="n">
@@ -19159,14 +19243,15 @@
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>Etude de cas management - Quels enjeux ethiques dans l'activite des organisations e
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Les organisations peuvent-elles s'affranchir des questions de societe e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Ethique, Deontologie et RSE.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - Quels enjeux ethiques dans l'activite des organisations e
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Ethique, Deontologie, RSE.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Les organisations peuvent-elles s'affranchir des questions de societe e.</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
@@ -19176,7 +19261,7 @@
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Ethique, Deontologie, RSE.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Ethique, Deontologie, RSE.</t>
         </is>
       </c>
       <c r="M276" t="n">
@@ -19227,14 +19312,15 @@
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>Etude de cas management - Comment les organisations prennent-elles en compte les changements des modes de vie e
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Les changements de modes de vie s'imposent-ils aux organisations e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Rapport au travail, Teletravail et Modes de consommation.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - Comment les organisations prennent-elles en compte les changements des modes de vie e
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Rapport au travail, Teletravail, Modes de consommation.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Les changements de modes de vie s'imposent-ils aux organisations e.</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
@@ -19244,7 +19330,7 @@
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Rapport au travail, Teletravail, Modes de consommation.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Rapport au travail, Teletravail, Modes de consommation.</t>
         </is>
       </c>
       <c r="M277" t="n">
@@ -19295,14 +19381,15 @@
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>Etude de cas management - Quelles responsabilites le numerique cree-t-il pour les organisations e
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Les transformations numeriques, de nouvelles responsabilites pour les organisations e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Protection des donnees personnelles, RGPD et Transparence des algorithmes.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - Quelles responsabilites le numerique cree-t-il pour les organisations e
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Protection des donnees personnelles, RGPD, Transparence des algorithmes.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Les transformations numeriques, de nouvelles responsabilites pour les organisations e.</t>
         </is>
       </c>
       <c r="K278" t="inlineStr">
@@ -19312,7 +19399,7 @@
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Protection des donnees personnelles, RGPD, Transparence des algorithmes.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Protection des donnees personnelles, RGPD, Transparence des algorithmes.</t>
         </is>
       </c>
       <c r="M278" t="n">
@@ -19363,14 +19450,15 @@
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>Etude de cas management - Quelles relations entre les organisations et leur ecosysteme e
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Quelles relations entre les organisations et leur ecosysteme e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Strategie d'implantation, Ecosysteme d'affaires et Cluster.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - Quelles relations entre les organisations et leur ecosysteme e
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Strategie d'implantation, Ecosysteme d'affaires, Cluster.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Quelles relations entre les organisations et leur ecosysteme e.</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
@@ -19380,7 +19468,7 @@
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Strategie d'implantation, Ecosysteme d'affaires, Cluster.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Strategie d'implantation, Ecosysteme d'affaires, Cluster.</t>
         </is>
       </c>
       <c r="M279" t="n">
@@ -19431,14 +19519,15 @@
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>Etude de cas management - Quels enjeux ethiques dans l'activite des organisations e
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Les organisations peuvent-elles s'affranchir des questions de societe e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Ethique, Deontologie et RSE.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - Quels enjeux ethiques dans l'activite des organisations e
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Ethique, Deontologie, RSE.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Les organisations peuvent-elles s'affranchir des questions de societe e.</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
@@ -19448,7 +19537,7 @@
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Ethique, Deontologie, RSE.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Ethique, Deontologie, RSE.</t>
         </is>
       </c>
       <c r="M280" t="n">
@@ -19499,14 +19588,15 @@
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>Etude de cas management - Comment les organisations prennent-elles en compte les changements des modes de vie e
-Contexte: une organisation doit prendre une decision importante dans un environnement incertain.
-Problematique: Les changements de modes de vie s'imposent-ils aux organisations e.
-Travail demande:
-1) Etablis le diagnostic de la situation en mobilisant Rapport au travail, Teletravail et Modes de consommation.
-2) Identifie les parties prenantes, leurs interets et les tensions possibles.
-3) Propose deux options strategiques/manageriales realistes et compare leurs consequences.
-4) Defends l'option retenue et presente un plan d'action concret en 3 etapes.</t>
+          <t>Dossier management - Comment les organisations prennent-elles en compte les changements des modes de vie e
+Contexte: une organisation doit trancher une decision strategique dans un environnement instable.
+Objectif: mobiliser les concepts de management pour justifier un choix realiste.
+Travail demande:
+1) Etablis un diagnostic de situation (enjeux, contraintes, opportunites) en mobilisant Rapport au travail, Teletravail, Modes de consommation.
+2) Identifie les parties prenantes et les tensions possibles entre leurs objectifs.
+3) Propose deux options strategiques/manageriales et compare leurs avantages-risques.
+4) Defends l'option retenue et presente un plan d'action (3 etapes + indicateurs de suivi).
+Problematique de chapitre: Les changements de modes de vie s'imposent-ils aux organisations e.</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
@@ -19516,7 +19606,7 @@
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>Correction attendue: diagnostic clair, prise en compte des acteurs, comparaison d'options, choix argumente et plan d'action realiste. Notions cibles: Rapport au travail, Teletravail, Modes de consommation.</t>
+          <t>Attendus: diagnostic solide, analyse des parties prenantes, comparaison d'options, decision argumentee et plan d'action concret. Notions cibles: Rapport au travail, Teletravail, Modes de consommation.</t>
         </is>
       </c>
       <c r="M281" t="n">

--- a/public/STMG_HUB_Missions_Programmes_Officiels.xlsx
+++ b/public/STMG_HUB_Missions_Programmes_Officiels.xlsx
@@ -14826,22 +14826,22 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>pdf-sdgn-t01-001</t>
+          <t>pdf-droit-t05-001</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>premiere</t>
+          <t>terminale</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>sciences de gestion</t>
+          <t>droit</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Theme 1 : De lindividu a lacteur</t>
+          <t>Theme 5 : Quel est le role du contrat '</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -14857,27 +14857,27 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Definir ce quest une action collective organisee et preciser le role de lorganisation.</t>
+          <t>Definir la notion de contrat et preciser limportance de lobligation dinformation et de con</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>Exercice source PDF (sciences de gestion premiere).</t>
+          <t>Exercice source PDF (droit terminale).</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>Definir ce quest une action collective organisee et preciser le role de lorganisation.</t>
+          <t>Definir la notion de contrat et preciser limportance de lobligation dinformation et de conseil.</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>sciences de gestion | Theme 1 : De lindividu a lacteur | Niveau 1 : Maitrise des concepts</t>
+          <t>droit | Theme 5 : Quel est le role du contrat ' | Niveau 1 : Maitrise des concepts</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>Une action collective organisee se forme lorsque plusieurs individus se regroupent pour atteindre un but commun quils ne pourraient pas atteindre seuls. Lorganisation (entreprise, association, administration) fournit le cadre juridique, materiel et hierarchique pour coordonner cette action collective dans le temps.</t>
+          <t>Le contrat est un accord de volontes entre deux ou plusieurs personnes, destine a creer, modifier, transmettre ou eteindre des obligations. Lobligation dinformation et de conseil (imposee par la loi au professionnel) est fondamentale car elle permet au cocontractant (notamment le consommateur) de sengager en toute connaissance de cause, reequilibrant ainsi lasymetrie de connaissances entre les deux parties.</t>
         </is>
       </c>
       <c r="M212" t="n">
@@ -14887,22 +14887,22 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>pdf-sdgn-t01-002</t>
+          <t>pdf-droit-t05-002</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>premiere</t>
+          <t>terminale</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>sciences de gestion</t>
+          <t>droit</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Theme 1 : De lindividu a lacteur</t>
+          <t>Theme 5 : Quel est le role du contrat '</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -14918,27 +14918,27 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Quelle est la difference entre la qualification et la competence dun individu '</t>
+          <t>Identifier et expliquer les conditions de validite indispensables a la formation dun contr</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>Exercice source PDF (sciences de gestion premiere).</t>
+          <t>Exercice source PDF (droit terminale).</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>Quelle est la difference entre la qualification et la competence dun individu '</t>
+          <t>Identifier et expliquer les conditions de validite indispensables a la formation dun contrat.</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>sciences de gestion | Theme 1 : De lindividu a lacteur | Niveau 1 : Maitrise des concepts</t>
+          <t>droit | Theme 5 : Quel est le role du contrat ' | Niveau 1 : Maitrise des concepts</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>La qualification repose sur la formation initiale, les diplomes obtenus et lexperience reconnue (souvent liee a une grille tarifaire conventionnelle). La competence est plus dynamique: cest la capacite dun individu a mobiliser des savoirs (connaissances), des savoir-faire (pratiques) et des savoir-etre (comportements) pour accomplir une tache precise en situation reelle de travail.</t>
+          <t>Pour etre valide, un contrat exige trois conditions cumulatives: 1) Le consentement, qui doit etre libre et eclaire (exempt derreur, de dol ou de violence). 2) La capacite juridique de contracter (etre majeur et non soumis a une mesure de protection type tutelle). 3) Un contenu licite et certain (lobjet du contrat doit exister, etre determine ou determinable, et ne pas etre contraire a lordre public).</t>
         </is>
       </c>
       <c r="M213" t="n">
@@ -14948,22 +14948,22 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>pdf-sdgn-t01-003</t>
+          <t>pdf-droit-t05-003</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>premiere</t>
+          <t>terminale</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>sciences de gestion</t>
+          <t>droit</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Theme 1 : De lindividu a lacteur</t>
+          <t>Theme 5 : Quel est le role du contrat '</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -14979,27 +14979,27 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Distinguer la communication formelle de la communication informelle au sein dune organis</t>
+          <t>Distinguer une obligation de moyens dune obligation de resultat.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>Exercice source PDF (sciences de gestion premiere).</t>
+          <t>Exercice source PDF (droit terminale).</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>Distinguer la communication formelle de la communication informelle au sein dune organisation.</t>
+          <t>Distinguer une obligation de moyens dune obligation de resultat.</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>sciences de gestion | Theme 1 : De lindividu a lacteur | Niveau 1 : Maitrise des concepts</t>
+          <t>droit | Theme 5 : Quel est le role du contrat ' | Niveau 1 : Maitrise des concepts</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>La communication formelle est officielle, planifiee et suit les voies hierarchiques prevues par lorganigramme (ex: une reunion de service, une note de service). La communication informelle est spontanee, non planifiee et repose sur les affinites personnelles (ex: echanges a la machine a cafe). Linformel favorise la cohesion mais peut generer des rumeurs.</t>
+          <t>Dans une obligation de moyens, le debiteur sengage a deployer tous les efforts possibles pour atteindre le resultat espere (ex: un medecin sengage a soigner son patient avec les meilleures pratiques, mais ne garantit pas la guerison). Dans une obligation de resultat, le debiteur garantit latteinte dun resultat precis (ex: un transporteur doit livrer la marchandise au bon endroit).</t>
         </is>
       </c>
       <c r="M214" t="n">
@@ -15009,22 +15009,22 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>pdf-sdgn-t01-004</t>
+          <t>pdf-droit-t05-004</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>premiere</t>
+          <t>terminale</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>sciences de gestion</t>
+          <t>droit</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Theme 1 : De lindividu a lacteur</t>
+          <t>Theme 5 : Quel est le role du contrat '</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -15040,27 +15040,27 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Quest-ce que la culture dentreprise et quels sont ses elements constitutifs '</t>
+          <t>Definir le droit de retractation et preciser son utilite pour le cyberconsommateur.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>Exercice source PDF (sciences de gestion premiere).</t>
+          <t>Exercice source PDF (droit terminale).</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>Quest-ce que la culture dentreprise et quels sont ses elements constitutifs '</t>
+          <t>Definir le droit de retractation et preciser son utilite pour le cyberconsommateur.</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>sciences de gestion | Theme 1 : De lindividu a lacteur | Niveau 1 : Maitrise des concepts</t>
+          <t>droit | Theme 5 : Quel est le role du contrat ' | Niveau 1 : Maitrise des concepts</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>La culture dentreprise est lensemble des valeurs, croyances, normes, mythes et rituels partages par les membres dune organisation. Elle cree un sentiment dappartenance, soude le collectif et differencie lentreprise de ses concurrents.</t>
+          <t>Le droit de retractation est un delai legal (generalement de 14 jours) permettant au consommateur de revenir sur son consentement et dannuler un contrat conclu a distance, sans avoir a se justifier. Il est crucial pour le cyberconsommateur car il compense limpossibilite de voir, toucher ou essayer le produit avant la conclusion de la vente.</t>
         </is>
       </c>
       <c r="M215" t="n">
@@ -15070,22 +15070,22 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>pdf-sdgn-t01-005</t>
+          <t>pdf-droit-t05-005</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>premiere</t>
+          <t>terminale</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>sciences de gestion</t>
+          <t>droit</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Theme 1 : De lindividu a lacteur</t>
+          <t>Theme 5 : Quel est le role du contrat '</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -15101,27 +15101,27 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Definir le leadership et expliquer son impact sur le groupe.</t>
+          <t>Quelle est la difference entre la nullite relative et la nullite absolue dun contrat '</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>Exercice source PDF (sciences de gestion premiere).</t>
+          <t>Exercice source PDF (droit terminale).</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>Definir le leadership et expliquer son impact sur le groupe.</t>
+          <t>Quelle est la difference entre la nullite relative et la nullite absolue dun contrat '</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>sciences de gestion | Theme 1 : De lindividu a lacteur | Niveau 1 : Maitrise des concepts</t>
+          <t>droit | Theme 5 : Quel est le role du contrat ' | Niveau 1 : Maitrise des concepts</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>Le leadership est la capacite dun individu (le leader) a influencer le comportement et les attitudes des autres membres du groupe pour les federer autour dun objectif commun, sans forcement utiliser lautorite hierarchique formelle. Un bon leadership favorise la motivation et la performance collective. 1.2 Niveau 2: Application et calculs</t>
+          <t>La nullite relative sanctionne la violation dune regle visant a proteger un interet prive (ex: un vice du consentement ou lincapacite dune partie); seule la personne protegee peut linvoquer. La nullite absolue sanctionne la violation dune regle protegeant linteret general (ex: un contrat portant sur la vente dorganes); elle peut etre demandee par toute personne y ayant un interet, ainsi que par le ministere public.</t>
         </is>
       </c>
       <c r="M216" t="n">
@@ -15131,327 +15131,327 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>pdf-sdgn-t01-006</t>
+          <t>pdf-droit-t05-006</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>premiere</t>
+          <t>terminale</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>sciences de gestion</t>
+          <t>droit</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Theme 1 : De lindividu a lacteur</t>
+          <t>Theme 5 : Quel est le role du contrat '</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Niveau 1 : Maitrise des concepts - Exercice 6</t>
+          <t>Niveau 2 : Application et analyse - Exercice 6</t>
         </is>
       </c>
       <c r="F217" t="n">
         <v>6</v>
       </c>
       <c r="G217" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Calcul du cout global du travail: Lentreprise de menuiserie BoisDesign emploie M. Karim</t>
+          <t>Cas pratique: Un mineur de 16 ans achete seul un ordinateur de grande valeur sur le site</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>Exercice source PDF (sciences de gestion premiere).</t>
+          <t>Exercice source PDF (droit terminale).</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>Calcul du cout global du travail: Lentreprise de menuiserie BoisDesign emploie M. Karim comme chef datelier. Son salaire brut mensuel est de2 500. Les cotisations salariales selevent a 22% du salaire brut. Les cotisations patronales selevent a 42% du salaire brut. Calculez: a) Le salaire net verse a M. Karim. b) Le cout global du travail supporte par lentreprise BoisDesign pour ce salarie.</t>
+          <t>Cas pratique: Un mineur de 16 ans achete seul un ordinateur de grande valeur sur le site de e-commerce TechBoutique. Qualifiez juridiquement les parties et determinez si ce contrat est valablement forme.</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>sciences de gestion | Theme 1 : De lindividu a lacteur | Niveau 1 : Maitrise des concepts</t>
+          <t>droit | Theme 5 : Quel est le role du contrat ' | Niveau 2 : Application et analyse</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>detaillee: - a) Salaire net: Cest le salaire brut moins les cotisations salariales. Calcul des cotisations salariales: 2 500 0, 22 = 550. Salaire net = 2 500 550 = 1 950. (Cest ce que percoit le salarie). - b) Cout global du travail: Pour lemployeur, le cout correspond au salaire brut PLUS les charges patronales. Calcul des cotisations patronales: 2 500 0, 42 = 1 050. Cout global = Salaire brut ( 2 500 ) + Cotisations patronales ( 1 050 ) = 3 550. Lemployeur debourse 3 550 pour verser un net de 1 950 au salarie. 2</t>
+          <t>Les parties: TechBoutique est une personne morale de droit prive, ayant la qualite de professionnel. Le jeune de 16 ans est une personne physique, ayant la qualite de mineur non emancipe (donc incapable juridiquement). Lachat dun ordinateur de grande valeur depasse les actes courants de la vie quotidienne. Le contrat nest donc pas valablement forme pour defaut de capacite. Il encourt la nullite relative.</t>
         </is>
       </c>
       <c r="M217" t="n">
-        <v>250</v>
+        <v>275</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>pdf-sdgn-t01-007</t>
+          <t>pdf-droit-t05-007</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>premiere</t>
+          <t>terminale</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>sciences de gestion</t>
+          <t>droit</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Theme 1 : De lindividu a lacteur</t>
+          <t>Theme 5 : Quel est le role du contrat '</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Niveau 1 : Maitrise des concepts - Exercice 7</t>
+          <t>Niveau 2 : Application et analyse - Exercice 7</t>
         </is>
       </c>
       <c r="F218" t="n">
         <v>7</v>
       </c>
       <c r="G218" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Analyse des interactions: Lors dune reunion chez MarketWeb, la directrice, Mme Martin,</t>
+          <t>Cas pratique: Lentreprise ProprePlus sest engagee aupres de la societe BuroTop a entreten</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>Exercice source PDF (sciences de gestion premiere).</t>
+          <t>Exercice source PDF (droit terminale).</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>Analyse des interactions: Lors dune reunion chez MarketWeb, la directrice, Mme Martin, impose ses decisions sans consulter son equipe de graphistes, utilisant un ton sec et autoritaire. Analysez cette situation de communication et ses effets potentiels.</t>
+          <t>Cas pratique: Lentreprise ProprePlus sest engagee aupres de la societe BuroTop a entretenir ses locaux, mais nintervient plus depuis un mois sans justification. Identifiez le 2 moyen daction prealable avant de saisir la justice (mise en demeure) et expliquez lexception dinexecution.</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>sciences de gestion | Theme 1 : De lindividu a lacteur | Niveau 1 : Maitrise des concepts</t>
+          <t>droit | Theme 5 : Quel est le role du contrat ' | Niveau 2 : Application et analyse</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>Contexte: Communication formelle descendante. Style: Autoritaire (leadership directif). Effets potentiels: Si ce style peut etre efficace en situation durgence, a long terme, il risque de generer de la frustration, une baisse de motivation, un manque de creativite des graphistes, voire un climat conflictuel ou un fort taux de rotation du personnel (turnover).</t>
+          <t>Laction prealable est la mise en demeure, un acte juridique formel (souvent par lettre recommandee) par lequel BuroTop somme officiellement ProprePlus dexecuter son obligation. En reponse a cette inexecution, BuroTop peut invoquer lexception dinexecution: il sagit du droit de suspendre sa propre obligation (ici, le paiement des factures dentretien) tant que son cocontractant nexecute pas la sienne.</t>
         </is>
       </c>
       <c r="M218" t="n">
-        <v>250</v>
+        <v>275</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>pdf-sdgn-t01-008</t>
+          <t>pdf-droit-t05-008</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>premiere</t>
+          <t>terminale</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>sciences de gestion</t>
+          <t>droit</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Theme 1 : De lindividu a lacteur</t>
+          <t>Theme 5 : Quel est le role du contrat '</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Niveau 1 : Maitrise des concepts - Exercice 8</t>
+          <t>Niveau 2 : Application et analyse - Exercice 8</t>
         </is>
       </c>
       <c r="F219" t="n">
         <v>8</v>
       </c>
       <c r="G219" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Gestion des conflits: Deux commerciaux de lagence AutoVente, Marc et Sophie, se dispute</t>
+          <t>Analyse de clause: M. Martin a souscrit un abonnement chez loperateur TelecomPlus. Son co</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>Exercice source PDF (sciences de gestion premiere).</t>
+          <t>Exercice source PDF (droit terminale).</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>Gestion des conflits: Deux commerciaux de lagence AutoVente, Marc et Sophie, se disputent violemment lattribution dun client tres rentable. Qualifiez ce type de conflit et proposez une methode de resolution.</t>
+          <t>Analyse de clause: M. Martin a souscrit un abonnement chez loperateur TelecomPlus. Son contrat contient une clause lui interdisant de resilier, meme en cas de modification unilaterale du tarif par loperateur. Qualifiez cette clause et donnez sa consequence juridique.</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>sciences de gestion | Theme 1 : De lindividu a lacteur | Niveau 1 : Maitrise des concepts</t>
+          <t>droit | Theme 5 : Quel est le role du contrat ' | Niveau 2 : Application et analyse</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>Il sagit dun conflit dinteret (ou conflit dobjectifs) base sur la repartition dune ressource rare (la commission sur la vente). Resolution: Le manager doit recourir a larbitrage (imposer une regle de repartition, par exemple en fonction du secteur geographique de chacun) ou a la mediation (les reunir pour quils trouvent un compromis ensemble, comme se partager la commission sils travaillent en binome). 1.3 Niveau 3: Entrainement type Bac</t>
+          <t>Il sagit dune clause abusive. En droit de la consommation, une clause est consideree comme abusive lorsquelle cree un desequilibre significatif entre les droits et obligations des parties, au detriment du consommateur. La consequence juridique est que cette clause est reputee non ecrite: elle est annulee et disparait du contrat, mais le reste du contrat demeure valable.</t>
         </is>
       </c>
       <c r="M219" t="n">
-        <v>250</v>
+        <v>275</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>pdf-sdgn-t01-009</t>
+          <t>pdf-droit-t05-009</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>premiere</t>
+          <t>terminale</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>sciences de gestion</t>
+          <t>droit</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Theme 1 : De lindividu a lacteur</t>
+          <t>Theme 5 : Quel est le role du contrat '</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Niveau 1 : Maitrise des concepts - Exercice 9</t>
+          <t>Niveau 3 : Entrainement type Bac - Exercice 9</t>
         </is>
       </c>
       <c r="F220" t="n">
         <v>9</v>
       </c>
       <c r="G220" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Cas dentreprise TechSolutions: Cette entreprise de services informatiques subit une baiss</t>
+          <t>Mise en situation: M. Dupont a fait appel a lartisan couvreur M. Renard pour refaire sa t</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>Exercice source PDF (sciences de gestion premiere).</t>
+          <t>Exercice source PDF (droit terminale).</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>Cas dentreprise TechSolutions: Cette entreprise de services informatiques subit une baisse de productivite de 15% depuis six mois. Les arrets maladie ont double. Les salaries se plaignent dobjectifs inatteignables et de labsence de reconnaissance de leur hierarchie. A laide de vos connaissances, montrez comment les conditions de travail influencent le comportement des acteurs et la performance de lorganisation.</t>
+          <t>Mise en situation: M. Dupont a fait appel a lartisan couvreur M. Renard pour refaire sa toiture. Les travaux presentent de graves defauts provoquant des fuites. Redigez une argumentation juridique (Faits, Probleme de droit, Regles applicables, Solution) pour conseiller M. Dupont sur la resolution du contrat et la mise en jeu de la responsabilite.</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>sciences de gestion | Theme 1 : De lindividu a lacteur | Niveau 1 : Maitrise des concepts</t>
+          <t>droit | Theme 5 : Quel est le role du contrat ' | Niveau 3 : Entrainement type Bac</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>structuree: Identification du probleme: Degradation du climat social chez TechSolutions (absenteisme, baisse de productivite) liee a de mauvaises conditions de travail psychosociales (stress, manque de reconnaissance). Lien Conditions de travail / Comportement: Les individus reagissent a leur environnement. Des objectifs irrealistes generent du stress (charge mentale). Labsence de reconnaissance touche lestime de soi et reduit la motivation au travail. Le comportement se modifie: desengagement, absenteisme (maladie). Impact sur lorganisation: Lorganisation est une action collective. Si les acteurs se desengagent, le collectif seffrite. Les couts caches explosent (remplacement des malades, retards), ce qui detruit la performance globale de TechSolutions (chute de la productivite de 15%). Conclusion: Lactivite humaine est une ressource a preserver. La direction doit imperativement revoir ses modes devaluation, fixer des objectifs concertes (methode participative) et instaurer des gratifications (financieres ou symboliques) pour restaurer la motivation.</t>
+          <t>Faits: Un client a fait realiser des travaux de toiture par un artisan. Des malfacons sont apparues, entrainant des infiltrations deau. Probleme de droit: De quels recours dispose le creancier face a linexecution dune obligation de resultat de la part de son cocontractant ' Regles de droit: Le contrat tient lieu de loi a ceux qui lont valablement forme. Lentrepreneur est tenu a une obligation de resultat. En cas dinexecution, le creancier peut, apres mise en demeure, demander la resolution du contrat (son aneantissement) et engager la responsabilite contractuelle du debiteur pour obtenir des dommages et interets si linexecution lui cause un prejudice. Solution: M. Dupont doit mettre M. Renard en demeure de reparer. Sil refuse, M. Dupont pourra saisir le juge pour demander la resolution du contrat et lindemnisation de son prejudice materiel et de jouissance.</t>
         </is>
       </c>
       <c r="M220" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>pdf-sdgn-t01-010</t>
+          <t>pdf-droit-t05-010</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>premiere</t>
+          <t>terminale</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>sciences de gestion</t>
+          <t>droit</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Theme 1 : De lindividu a lacteur</t>
+          <t>Theme 5 : Quel est le role du contrat '</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Niveau 1 : Maitrise des concepts - Exercice 10</t>
+          <t>Niveau 3 : Entrainement type Bac - Exercice 10</t>
         </is>
       </c>
       <c r="F221" t="n">
         <v>10</v>
       </c>
       <c r="G221" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Question de reflexion: Lintegration de la personnalite et des emotions des salaries dans</t>
+          <t>Developpement structure: Dans quelle mesure le droit encadre-t-il la liberte contractue</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>Exercice source PDF (sciences de gestion premiere).</t>
+          <t>Exercice source PDF (droit terminale).</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>Question de reflexion: Lintegration de la personnalite et des emotions des salaries dans la gestion des ressources humaines est-elle un atout ou une contrainte pour lorganisation '</t>
+          <t>Developpement structure: Dans quelle mesure le droit encadre-t-il la liberte contractuelle pour proteger le consommateur '</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>sciences de gestion | Theme 1 : De lindividu a lacteur | Niveau 1 : Maitrise des concepts</t>
+          <t>droit | Theme 5 : Quel est le role du contrat ' | Niveau 3 : Entrainement type Bac</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>Cest a la fois une contrainte (car gerer des individus complexes, avec leurs sautes dhumeur et leurs sensibilites demande du temps, des competences manageriales fortes et expose lorganisation a des conflits interpersonnels chronophages) et un atout majeur (car lenthousiasme, lempathie, ou le trait de personnalite creatif dun individu sont des moteurs dinnovation et de cohesion). Un manager qui sait mobiliser lintelligence emotionnelle de ses equipes obtiendra un engagement bien superieur a une gestion purement comptable et tayloriste des ressources humaines. 3</t>
+          <t>Le principe fondateur du droit des contrats est la liberte contractuelle (liberte de choisir son cocontractant, le contenu et la forme du contrat). Cependant, dans les relations BtoC (professionnel a consommateur), cette liberte genere une asymetrie de pouvoir. Le droit encadre donc strictement la phase de formation (obligation lourde dinformation et de conseil, interdiction des pratiques trompeuses) et dexecution (droit de retractation accordant un droit de repentir, traque des clauses abusives). Cet encadrement, issu de lordre public de protection, est imperatif: le professionnel ne peut y deroger, limitant ainsi sa propre liberte pour reequilibrer la relation contractuelle.</t>
         </is>
       </c>
       <c r="M221" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>pdf-sdgn-t02-001</t>
+          <t>pdf-droit-t06-001</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>premiere</t>
+          <t>terminale</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>sciences de gestion</t>
+          <t>droit</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Theme 2 : Numerique et intelligence collective</t>
+          <t>Theme 6 : Quest-ce quetre responsable '</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -15467,27 +15467,27 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Definir et distinguer: Donnee, Information, Connaissance.</t>
+          <t>Expliquer la difference de finalite entre la responsabilite civile et la responsabilite pe</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>Exercice source PDF (sciences de gestion premiere).</t>
+          <t>Exercice source PDF (droit terminale).</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>Definir et distinguer: Donnee, Information, Connaissance.</t>
+          <t>Expliquer la difference de finalite entre la responsabilite civile et la responsabilite penale.</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>sciences de gestion | Theme 2 : Numerique et intelligence collective | Niveau 1 : Maitrise des concepts</t>
+          <t>droit | Theme 6 : Quest-ce quetre responsable ' | Niveau 1 : Maitrise des concepts</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>Donnee: Un element brut, un chiffre, un fait sans contexte (ex: 39). Information: Une donnee traitee et replacee dans son contexte qui prend du sens (ex: Le patient a 39C de fievre). Connaissance: Lappropriation de linformation par un individu, combinee a son experience, permettant de prendre une decision ou dagir (ex: Le medecin sait que 39C indique une infection et prescrit un traitement).</t>
+          <t>La responsabilite penale a pour but de proteger la societe en sanctionnant et punissant (amende, prison) lauteur dune infraction (contravention, delit, crime). La responsabilite civile, en revanche, a une fonction reparatrice: son but exclusif est de remettre 3 la victime dans letat ou elle se trouvait avant le dommage, via le versement de dommagesinterets, sans finalite punitive.</t>
         </is>
       </c>
       <c r="M222" t="n">
@@ -15497,22 +15497,22 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>pdf-sdgn-t02-002</t>
+          <t>pdf-droit-t06-002</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>premiere</t>
+          <t>terminale</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>sciences de gestion</t>
+          <t>droit</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Theme 2 : Numerique et intelligence collective</t>
+          <t>Theme 6 : Quest-ce quetre responsable '</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -15528,27 +15528,27 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Quest-ce quune donnee a caractere personnel et quel texte la protege en Europe '</t>
+          <t>Quels sont les trois elements cumulatifs a prouver pour engager la responsabilite extrac</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>Exercice source PDF (sciences de gestion premiere).</t>
+          <t>Exercice source PDF (droit terminale).</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>Quest-ce quune donnee a caractere personnel et quel texte la protege en Europe '</t>
+          <t>Quels sont les trois elements cumulatifs a prouver pour engager la responsabilite extracontractuelle '</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>sciences de gestion | Theme 2 : Numerique et intelligence collective | Niveau 1 : Maitrise des concepts</t>
+          <t>droit | Theme 6 : Quest-ce quetre responsable ' | Niveau 1 : Maitrise des concepts</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>Cest toute information se rapportant a une personne physique identifiee ou identifiable (nom, photo, adresse IP, numero de securite sociale). En Europe, ces donnees sont protegees par le RGPD (Reglement General sur la Protection des Donnees), qui impose aux organisations dobtenir le consentement, de securiser les donnees et de garantir le droit a loubli.</t>
+          <t>Pour que la responsabilite extracontractuelle soit engagee, la victime doit prouver la reunion de trois elements: 1) Un fait generateur (une faute, le fait dune chose, ou le fait dautrui). 2) Un dommage (materiel, corporel ou moral). 3) Un lien de causalite direct et certain entre le fait generateur et le dommage subi.</t>
         </is>
       </c>
       <c r="M223" t="n">
@@ -15558,22 +15558,22 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>pdf-sdgn-t02-003</t>
+          <t>pdf-droit-t06-003</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>premiere</t>
+          <t>terminale</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>sciences de gestion</t>
+          <t>droit</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Theme 2 : Numerique et intelligence collective</t>
+          <t>Theme 6 : Quest-ce quetre responsable '</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -15589,27 +15589,27 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Expliquer ce quest un PGI (Progiciel de Gestion Integre) ou ERP.</t>
+          <t>Citer les trois caracteristiques quun dommage doit presenter pour etre juridiquement rep</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>Exercice source PDF (sciences de gestion premiere).</t>
+          <t>Exercice source PDF (droit terminale).</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>Expliquer ce quest un PGI (Progiciel de Gestion Integre) ou ERP.</t>
+          <t>Citer les trois caracteristiques quun dommage doit presenter pour etre juridiquement reparable.</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>sciences de gestion | Theme 2 : Numerique et intelligence collective | Niveau 1 : Maitrise des concepts</t>
+          <t>droit | Theme 6 : Quest-ce quetre responsable ' | Niveau 1 : Maitrise des concepts</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>Un PGI est un systeme informatique unique (une grande base de donnees centralisee) qui permet de gerer lensemble des processus operationnels dune entreprise (ressources humaines, comptabilite, ventes, stocks). Il garantit lunicite de linformation: une donnee saisie une fois met a jour tous les modules en temps reel.</t>
+          <t>Un dommage reparable doit etre personnel (la personne qui agit doit avoir subi elle-meme le prejudice), direct (decouler directement du fait generateur) et certain (il ne doit pas etre hypothetique, bien quun prejudice futur mais ineluctable puisse etre admis). Il doit egalement porter atteinte a un interet legitime.</t>
         </is>
       </c>
       <c r="M224" t="n">
@@ -15619,22 +15619,22 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>pdf-sdgn-t02-004</t>
+          <t>pdf-droit-t06-004</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>premiere</t>
+          <t>terminale</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>sciences de gestion</t>
+          <t>droit</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Theme 2 : Numerique et intelligence collective</t>
+          <t>Theme 6 : Quest-ce quetre responsable '</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -15650,27 +15650,27 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Que signifie lexpression Intelligence Collective '</t>
+          <t>Definir les trois causes dexoneration de la responsabilite (force majeure, fait dun tiers,</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>Exercice source PDF (sciences de gestion premiere).</t>
+          <t>Exercice source PDF (droit terminale).</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>Que signifie lexpression Intelligence Collective '</t>
+          <t>Definir les trois causes dexoneration de la responsabilite (force majeure, fait dun tiers, faute de la victime).</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>sciences de gestion | Theme 2 : Numerique et intelligence collective | Niveau 1 : Maitrise des concepts</t>
+          <t>droit | Theme 6 : Quest-ce quetre responsable ' | Niveau 1 : Maitrise des concepts</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>Cest la capacite dun groupe dindividus a resoudre des problemes complexes et a innover, grace a la collaboration, au partage des connaissances et aux interactions, souvent facilitees par les outils numeriques. Le resultat du groupe est superieur a la simple somme des intelligences individuelles ( 1 + 1 = 3 ).</t>
+          <t>Ce sont des causes etrangeres permettant au defendeur de sexonerer. La force majeure est un evenement imprevisible, irresistible et exterieur. Le fait dun tiers est lintervention exclusive dune personne exterieure ayant provoque le dommage. La faute de la victime est le comportement fautif de la personne ayant subi le dommage, qui a concouru a sa propre realisation (exoneration partielle ou totale si elle presente les caracteres de la force majeure).</t>
         </is>
       </c>
       <c r="M225" t="n">
@@ -15680,22 +15680,22 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>pdf-sdgn-t02-005</t>
+          <t>pdf-droit-t06-005</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>premiere</t>
+          <t>terminale</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>sciences de gestion</t>
+          <t>droit</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Theme 2 : Numerique et intelligence collective</t>
+          <t>Theme 6 : Quest-ce quetre responsable '</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -15711,27 +15711,27 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Definir le Cloud Computing (linformatique en nuage).</t>
+          <t>Quest-ce que le prejudice ecologique '</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>Exercice source PDF (sciences de gestion premiere).</t>
+          <t>Exercice source PDF (droit terminale).</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>Definir le Cloud Computing (linformatique en nuage).</t>
+          <t>Quest-ce que le prejudice ecologique '</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>sciences de gestion | Theme 2 : Numerique et intelligence collective | Niveau 1 : Maitrise des concepts</t>
+          <t>droit | Theme 6 : Quest-ce quetre responsable ' | Niveau 1 : Maitrise des concepts</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>Cest un modele informatique permettant un acces via Internet (a la demande) a un ensemble partage de ressources informatiques (serveurs, stockage, applications) hebergees sur des serveurs distants (data centers), plutot que sur le disque dur local de lutilisateur. 2.2 Niveau 2: Application et analyse</t>
+          <t>Le prejudice ecologique est une atteinte non negligeable aux elements ou aux fonctions des ecosystemes ou aux benefices collectifs tires par lhomme de lenvironnement (ex: maree noire, pollution dune riviere). Cest un prejudice objectif, distinct du prejudice personnel des individus, qui vise a reparer latteinte a la nature elle-meme.</t>
         </is>
       </c>
       <c r="M226" t="n">
@@ -15741,327 +15741,327 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>pdf-sdgn-t02-006</t>
+          <t>pdf-droit-t06-006</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>premiere</t>
+          <t>terminale</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>sciences de gestion</t>
+          <t>droit</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Theme 2 : Numerique et intelligence collective</t>
+          <t>Theme 6 : Quest-ce quetre responsable '</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Niveau 1 : Maitrise des concepts - Exercice 6</t>
+          <t>Niveau 2 : Application et analyse - Exercice 6</t>
         </is>
       </c>
       <c r="F227" t="n">
         <v>6</v>
       </c>
       <c r="G227" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Transformation de linformation: La boutique en ligne SneakPeak enregistre que 45% des vis</t>
+          <t>Cas pratique: Mme Garcia se blesse gravement en glissant sur un sol mouille non signale d</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>Exercice source PDF (sciences de gestion premiere).</t>
+          <t>Exercice source PDF (droit terminale).</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>Transformation de linformation: La boutique en ligne SneakPeak enregistre que 45% des visiteurs cliquent sur un modele precis de baskets rouges, mais que seulement 2% lachetent. Le gestionnaire decide alors de baisser le prix de ce modele de 10%. Retracez le passage de la donnee a laction.</t>
+          <t>Cas pratique: Mme Garcia se blesse gravement en glissant sur un sol mouille non signale dans les allees du supermarche SuperPrix. Identifiez le regime de responsabilite applicable et les conditions de sa mise en uvre.</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>sciences de gestion | Theme 2 : Numerique et intelligence collective | Niveau 1 : Maitrise des concepts</t>
+          <t>droit | Theme 6 : Quest-ce quetre responsable ' | Niveau 2 : Application et analyse</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>Donnees brutes: Nombre de clics, nombre dachats. Information: Taux dabandon panier extremement eleve sur le modele de baskets rouges.Connaissance/Analyse: Le gestionnaire comprend (grace a son experience du marche) que le produit attire (bon design) mais que le prix constitue un frein a lachat. Action: Prise de decision de gestion: baisse strategique du prix de 10% pour convertir linteret en ventes.</t>
+          <t>Il sagit de la responsabilite extracontractuelle du fait des choses. Les conditions sont: lintervention dune chose (le sol mouille) qui a ete linstrument du dommage, et lidentification du gardien de la chose, cest-a-dire celui qui en a lusage, la direction et le controle (ici, la direction du supermarche SuperPrix). La faute du gardien na pas a etre prouvee (responsabilite de plein droit).</t>
         </is>
       </c>
       <c r="M227" t="n">
-        <v>250</v>
+        <v>275</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>pdf-sdgn-t02-007</t>
+          <t>pdf-droit-t06-007</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>premiere</t>
+          <t>terminale</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>sciences de gestion</t>
+          <t>droit</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Theme 2 : Numerique et intelligence collective</t>
+          <t>Theme 6 : Quest-ce quetre responsable '</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Niveau 1 : Maitrise des concepts - Exercice 7</t>
+          <t>Niveau 2 : Application et analyse - Exercice 7</t>
         </is>
       </c>
       <c r="F228" t="n">
         <v>7</v>
       </c>
       <c r="G228" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Automatisation et processus:Chez le fabricant MecaPro, la validation dune commande client</t>
+          <t>Cas pratique: Le telephone portable neuf de M. Leroy explose spontanement dans sa poche,</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>Exercice source PDF (sciences de gestion premiere).</t>
+          <t>Exercice source PDF (droit terminale).</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>Automatisation et processus:Chez le fabricant MecaPro, la validation dune commande client prenait 3 jours (transferts papier entre commercial, stock et compta). Limplantation dun PGI a automatise ce processus. Quels sont les effets immediats de cette automatisation ' 4</t>
+          <t>Cas pratique: Le telephone portable neuf de M. Leroy explose spontanement dans sa poche, le blessant a la jambe. Quel regime special dindemnisation sapplique ici ' Justifiez.</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>sciences de gestion | Theme 2 : Numerique et intelligence collective | Niveau 1 : Maitrise des concepts</t>
+          <t>droit | Theme 6 : Quest-ce quetre responsable ' | Niveau 2 : Application et analyse</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>Lautomatisation fluidifie le processus. Les effets sont: gain de temps considerable (de 3 jours a quelques secondes), reduction des erreurs de saisie (plus de recopies manuelles), diminution des couts administratifs, et agilite accrue (la production peut demarrer immediatement apres le clic du commercial). Cependant, le role des employes administratifs est rigidifie par la procedure imposee par le logiciel.</t>
+          <t>Le regime special de la responsabilite du fait des produits defectueux sapplique. Il protege les consommateurs contre les dommages causes par un defaut de securite dun produit mis en circulation. Le fabricant est responsable de plein droit des blessures causees par lexplosion anormale de la batterie de son telephone.</t>
         </is>
       </c>
       <c r="M228" t="n">
-        <v>250</v>
+        <v>275</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>pdf-sdgn-t02-008</t>
+          <t>pdf-droit-t06-008</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>premiere</t>
+          <t>terminale</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>sciences de gestion</t>
+          <t>droit</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Theme 2 : Numerique et intelligence collective</t>
+          <t>Theme 6 : Quest-ce quetre responsable '</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Niveau 1 : Maitrise des concepts - Exercice 8</t>
+          <t>Niveau 2 : Application et analyse - Exercice 8</t>
         </is>
       </c>
       <c r="F229" t="n">
         <v>8</v>
       </c>
       <c r="G229" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Cas RGPD: Lapplication mobile FitRun geolocalise ses utilisateurs 24h/24 pour ameliorer</t>
+          <t>Mecanisme dassurance: Expliquez comment lassurance permet de socialiser et de mutualise</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>Exercice source PDF (sciences de gestion premiere).</t>
+          <t>Exercice source PDF (droit terminale).</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>Cas RGPD: Lapplication mobile FitRun geolocalise ses utilisateurs 24h/24 pour ameliorer le service, et revend ces historiques de deplacements a des societes publicitaires sans en informer clairement les utilisateurs. Identifiez les failles juridiques et ethiques.</t>
+          <t>Mecanisme dassurance: Expliquez comment lassurance permet de socialiser et de mutualiser la reparation des dommages.</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>sciences de gestion | Theme 2 : Numerique et intelligence collective | Niveau 1 : Maitrise des concepts</t>
+          <t>droit | Theme 6 : Quest-ce quetre responsable ' | Niveau 2 : Application et analyse</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>Lentreprise enfreint le RGPD sur plusieurs points: defaut de consentement explicite et eclaire pour la revente, manque de transparence (finalite cachee), et non-respect du principe de minimisation (geolocaliser 24h/24 nest pas necessaire pour une simple application de course a pied). Le risque est une lourde sanction financiere par la CNIL et une destruction de la reputation de lentreprise (perte de confiance client). 2.3 Niveau 3: Entrainement type Bac</t>
+          <t>Lassurance repose sur la mutualisation des risques. Chaque assure verse une prime reguliere a lassureur. Ce fonds commun permet dindemniser la minorite dassures 4 qui subissent ou causent un dommage. Ainsi, le poids financier de la reparation (parfois tres lourd) nest plus supporte par un seul individu responsable, mais socialise et reparti sur lensemble de la communaute des assures.</t>
         </is>
       </c>
       <c r="M229" t="n">
-        <v>250</v>
+        <v>275</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>pdf-sdgn-t02-009</t>
+          <t>pdf-droit-t06-009</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>premiere</t>
+          <t>terminale</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>sciences de gestion</t>
+          <t>droit</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Theme 2 : Numerique et intelligence collective</t>
+          <t>Theme 6 : Quest-ce quetre responsable '</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Niveau 1 : Maitrise des concepts - Exercice 9</t>
+          <t>Niveau 3 : Entrainement type Bac - Exercice 9</t>
         </is>
       </c>
       <c r="F230" t="n">
         <v>9</v>
       </c>
       <c r="G230" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Cas dentreprise ArchiConcept: Ce cabinet darchitectes reunit 50 collaborateurs repartis</t>
+          <t>Mise en situation: Lors dune livraison, M. Jules, salarie de lentreprise de transport Li-</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>Exercice source PDF (sciences de gestion premiere).</t>
+          <t>Exercice source PDF (droit terminale).</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>Cas dentreprise ArchiConcept: Ce cabinet darchitectes reunit 50 collaborateurs repartis sur 3 sites. Pour ameliorer la coordination, la direction impose un Reseau Social dEntreprise (RSE) et le basculement de tous les dossiers sur le Cloud. Un an plus tard, on constate une acceleration des projets, mais certains architectes seniors se plaignent dune surcharge dinformations, dun controle permanent et refusent dutiliser la plateforme. A partir de ce constat, analysez si le numerique cree de lagilite ou de la rigidite organisationnelle.</t>
+          <t>Mise en situation: Lors dune livraison, M. Jules, salarie de lentreprise de transport LivraisonExpress, abime le portail du client M. Fabre avec la camionnette de la societe. En vous appuyant sur le syllogisme juridique, demontrez qui devra reparer le prejudice subi par le client (fait dautrui).</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>sciences de gestion | Theme 2 : Numerique et intelligence collective | Niveau 1 : Maitrise des concepts</t>
+          <t>droit | Theme 6 : Quest-ce quetre responsable ' | Niveau 3 : Entrainement type Bac</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>structuree: Lagilite creee par le numerique: Lusage du Cloud et du RSE chez ArchiConcept dematerialise les frontieres physiques. Le partage dinformation en temps reel permet le travail collaboratif a distance, accelerant le processus de conception des projets. Lentreprise devient agile, capable de reagir rapidement aux demandes clients grace a lintelligence collective mobilisee sur le RSE. La rigidite et les risques generes: Cependant, loutil impose sa propre logique. Lhyper-connexion genere une surcharge cognitive (infobesite) pour les salaries. Le partage total peut etre percu comme un outil de flicage et de controle managerial permanent (rigidite sociale). De plus, lexclusion numerique (fracture numerique) de certains seniors montre que la technologie seule ne suffit pas: sans accompagnement humain ni formation, loutil se heurte a des resistances au changement qui bloquent le fonctionnement de lorganisation. Conclusion: Le numerique est un paradoxe: il fluidifie les processus techniques (agilite) mais peut rigidifier les relations humaines et le cadre de travail sil est impose de maniere technocentree sans prendre en compte la sociologie des acteurs.</t>
+          <t>Faits: Un salarie endommage un bien appartenant a un tiers pendant lexecution de son travail. Majeure (Regle): Larticle 1242 du Code civil prevoit que lon est responsable non seulement du dommage que lon cause par son propre fait, mais encore de celui qui est cause par le fait des personnes dont on doit repondre. Ainsi, les commettants sont civilement responsables des dommages causes par leurs preposes dans les fonctions auxquelles ils les ont employes. Mineure (Application): En lespece, M. Jules est le prepose (salarie) de la societe LivraisonExpress (commettant). Il a commis une faute dommageable dans le cadre de ses fonctions de livreur. Conclusion: Cest la societe LivraisonExpress (le commettant) qui est civilement responsable et qui devra indemniser M. Fabre, souvent via son assurance professionnelle.</t>
         </is>
       </c>
       <c r="M230" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>pdf-sdgn-t02-010</t>
+          <t>pdf-droit-t06-010</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>premiere</t>
+          <t>terminale</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>sciences de gestion</t>
+          <t>droit</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Theme 2 : Numerique et intelligence collective</t>
+          <t>Theme 6 : Quest-ce quetre responsable '</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Niveau 1 : Maitrise des concepts - Exercice 10</t>
+          <t>Niveau 3 : Entrainement type Bac - Exercice 10</t>
         </is>
       </c>
       <c r="F231" t="n">
         <v>10</v>
       </c>
       <c r="G231" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Question de reflexion: En quoi louverture des donnees (Open Data) constitue-t-elle une op</t>
+          <t>Developpement structure: Levolution des differents regimes de responsabilite civile offre</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>Exercice source PDF (sciences de gestion premiere).</t>
+          <t>Exercice source PDF (droit terminale).</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>Question de reflexion: En quoi louverture des donnees (Open Data) constitue-t-elle une opportunite de creation de valeur economique et societale '</t>
+          <t>Developpement structure: Levolution des differents regimes de responsabilite civile offre-t-elle toujours une indemnisation systematique aux victimes '</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>sciences de gestion | Theme 2 : Numerique et intelligence collective | Niveau 1 : Maitrise des concepts</t>
+          <t>droit | Theme 6 : Quest-ce quetre responsable ' | Niveau 3 : Entrainement type Bac</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>LOpen Data (mise a disposition gratuite et libre de droits de grandes bases de donnees publiques, comme les horaires de transport ou les donnees meteorologiques) est une matiere premiere. Sur le plan economique, des startups utilisent ces donnees pour creer des applications innovantes a forte valeur ajoutee (ex: Citymapper pour les trajets, applications agricoles doptimisation des semis selon la meteo). Sur le plan societal, lOpen Data ameliore la transparence de laction publique et permet aux citoyens detre mieux informes et de collaborer, generant ainsi une intelligence collective a lechelle de la nation. 5</t>
+          <t>Levolution du droit tend effectivement vers une amelioration de lindemnisation des victimes, passant dune logique de faute a une logique de reparation et dobjectivation (developpement de la responsabilite de plein droit, regimes speciaux tres protecteurs comme la loi Badinter sur les accidents de la circulation). Cependant, lindemnisation nest pas systematique. La victime doit toujours prouver le lien de causalite et letendue de son dommage. De plus, le defendeur conserve des moyens de sexonerer de sa responsabilite sil prouve une cause etrangere (force majeure, faute exclusive de la victime), ce qui peut priver cette derniere de toute indemnisation.</t>
         </is>
       </c>
       <c r="M231" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>pdf-sdgn-t03-001</t>
+          <t>pdf-droit-t07-001</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>premiere</t>
+          <t>terminale</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>sciences de gestion</t>
+          <t>droit</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Theme 3 : Creation de valeur et performance</t>
+          <t>Theme 7 : Comment le droit encadre-t-il le travail salarie '</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -16077,27 +16077,27 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Differencier lefficacite de lefficience au sein dune organisation.</t>
+          <t>Definir le contrat de travail a laide de ses trois elements constitutifs, en insistant sur</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>Exercice source PDF (sciences de gestion premiere).</t>
+          <t>Exercice source PDF (droit terminale).</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>Differencier lefficacite de lefficience au sein dune organisation.</t>
+          <t>Definir le contrat de travail a laide de ses trois elements constitutifs, en insistant sur le lien de subordination.</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>sciences de gestion | Theme 3 : Creation de valeur et performance | Niveau 1 : Maitrise des concepts</t>
+          <t>droit | Theme 7 : Comment le droit encadre-t-il le travail salarie ' | Niveau 1 : Maitrise des concepts</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>Lefficaciteest la capacite dune organisation a atteindre lobjectif quelle sest fixe (ex: produire 1000 voitures).Lefficienceest la capacite a atteindre cet objectif en minimisant les ressources utilisees (ex: produire 1000 voitures en reduisant la consommation denergie et le temps de travail de 20%). Lefficience integre donc la notion de cout et de rationalite.</t>
+          <t>Le contrat de travail est caracterise par trois elements: 1) Une prestation de travail (tache a accomplir). 2) Une remuneration (le salaire). 3) Le lien de subordination juridique, qui est lelement determinant. Il se caracterise par le pouvoir de lemployeur de donner des ordres et des directives, den controler lexecution et de sanctionner les manquements de son subordonne.</t>
         </is>
       </c>
       <c r="M232" t="n">
@@ -16107,22 +16107,22 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>pdf-sdgn-t03-002</t>
+          <t>pdf-droit-t07-002</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>premiere</t>
+          <t>terminale</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>sciences de gestion</t>
+          <t>droit</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Theme 3 : Creation de valeur et performance</t>
+          <t>Theme 7 : Comment le droit encadre-t-il le travail salarie '</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -16138,27 +16138,27 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Quest-ce que la Valeur Ajoutee (VA) et comment la calcule-t-on de maniere simplifiee '</t>
+          <t>Quelles sont les differences fondamentales entre un contrat de travail et un contrat den-</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>Exercice source PDF (sciences de gestion premiere).</t>
+          <t>Exercice source PDF (droit terminale).</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>Quest-ce que la Valeur Ajoutee (VA) et comment la calcule-t-on de maniere simplifiee '</t>
+          <t>Quelles sont les differences fondamentales entre un contrat de travail et un contrat dentreprise (prestation de services) '</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>sciences de gestion | Theme 3 : Creation de valeur et performance | Niveau 1 : Maitrise des concepts</t>
+          <t>droit | Theme 7 : Comment le droit encadre-t-il le travail salarie ' | Niveau 1 : Maitrise des concepts</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>La valeur ajoutee mesure la veritable richesse creee par lactivite de lentreprise elle-meme. Elle se calcule par la difference entre le Chiffre dAffaires (CA) et les Consommations Intermediaires (CI, biens et services detruits ou transformes pendant le processus). Formule: VA = CA CI.</t>
+          <t>La distinction majeure reside dans le lien de subordination juridique present dans le contrat de travail, qui place le salarie sous lautorite de lemployeur. Dans un contrat dentreprise, le prestataire de services (un travailleur independant) conserve une totale independance dans lorganisation de son travail et les moyens mis en uvre pour atteindre le resultat demande par son client.</t>
         </is>
       </c>
       <c r="M233" t="n">
@@ -16168,22 +16168,22 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>pdf-sdgn-t03-003</t>
+          <t>pdf-droit-t07-003</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>premiere</t>
+          <t>terminale</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>sciences de gestion</t>
+          <t>droit</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Theme 3 : Creation de valeur et performance</t>
+          <t>Theme 7 : Comment le droit encadre-t-il le travail salarie '</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -16199,27 +16199,27 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Definir la valeur percue par le client.</t>
+          <t>Lister les differents pouvoirs reconnus a lemployeur.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>Exercice source PDF (sciences de gestion premiere).</t>
+          <t>Exercice source PDF (droit terminale).</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>Definir la valeur percue par le client.</t>
+          <t>Lister les differents pouvoirs reconnus a lemployeur.</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>sciences de gestion | Theme 3 : Creation de valeur et performance | Niveau 1 : Maitrise des concepts</t>
+          <t>droit | Theme 7 : Comment le droit encadre-t-il le travail salarie ' | Niveau 1 : Maitrise des concepts</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>Cest la valeur subjective quun client attribue a un produit ou un service. Elle repose sur limage de marque, la notoriete, la qualite ressentie et les recommandations sociales. Cest le prix maximum que le client est psychologiquement pret a payer, qui peut etre tres superieur au cout de fabrication reel (ex: les produits de luxe ou les smartphones haut de gamme).</t>
+          <t>Lemployeur detient trois grands pouvoirs issus de son droit de propriete et 5 du contrat: le pouvoir de direction (organiser le travail, fixer les objectifs et les methodes), le pouvoir reglementaire (edicter des regles generales et permanentes, notamment via le reglement interieur pour lhygiene, la securite et la discipline) et le pouvoir disciplinaire (droit de sanctionner une faute du salarie).</t>
         </is>
       </c>
       <c r="M234" t="n">
@@ -16229,22 +16229,22 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>pdf-sdgn-t03-004</t>
+          <t>pdf-droit-t07-004</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>premiere</t>
+          <t>terminale</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>sciences de gestion</t>
+          <t>droit</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Theme 3 : Creation de valeur et performance</t>
+          <t>Theme 7 : Comment le droit encadre-t-il le travail salarie '</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -16260,27 +16260,27 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Quest-ce quun Bilan Social et quelle performance permet-il de mesurer '</t>
+          <t>Distinguer le licenciement pour motif personnel du licenciement pour motif economique.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>Exercice source PDF (sciences de gestion premiere).</t>
+          <t>Exercice source PDF (droit terminale).</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>Quest-ce quun Bilan Social et quelle performance permet-il de mesurer '</t>
+          <t>Distinguer le licenciement pour motif personnel du licenciement pour motif economique.</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>sciences de gestion | Theme 3 : Creation de valeur et performance | Niveau 1 : Maitrise des concepts</t>
+          <t>droit | Theme 7 : Comment le droit encadre-t-il le travail salarie ' | Niveau 1 : Maitrise des concepts</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>Le bilan social est un document recapitulant les principales donnees chiffrees permettant dapprecier la situation sociale dune organisation (effectifs, remunerations, accidents du travail, absenteisme, budget formation). Il permet de mesurer la performance sociale de lentreprise vis-a-vis de ses salaries.</t>
+          <t>Le licenciement pour motif personnel est inherent a la personne du salarie (ex: faute disciplinaire grave, incompetence, inaptitude physique). Le licenciement pour motif economique nest pas lie au salarie, mais resulte dune suppression ou transformation demploi causee par des difficultes economiques averees, des mutations technologiques ou la cessation dactivite de lentreprise.</t>
         </is>
       </c>
       <c r="M235" t="n">
@@ -16290,22 +16290,22 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>pdf-sdgn-t03-005</t>
+          <t>pdf-droit-t07-005</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>premiere</t>
+          <t>terminale</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>sciences de gestion</t>
+          <t>droit</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Theme 3 : Creation de valeur et performance</t>
+          <t>Theme 7 : Comment le droit encadre-t-il le travail salarie '</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -16321,27 +16321,27 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Quelles sont les composantes de la Performance globale dune organisation '</t>
+          <t>Quest-ce quune convention collective et quel est son role vis-a-vis du Code du travail '</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>Exercice source PDF (sciences de gestion premiere).</t>
+          <t>Exercice source PDF (droit terminale).</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>Quelles sont les composantes de la Performance globale dune organisation '</t>
+          <t>Quest-ce quune convention collective et quel est son role vis-a-vis du Code du travail '</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>sciences de gestion | Theme 3 : Creation de valeur et performance | Niveau 1 : Maitrise des concepts</t>
+          <t>droit | Theme 7 : Comment le droit encadre-t-il le travail salarie ' | Niveau 1 : Maitrise des concepts</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>Aujourdhui, la performance ne se limite plus a la finance. La performance globale est un equilibre integrant 4 dimensions: financiere (rentabilite), commerciale (parts de marche), sociale (bien-etre au travail) et environnementale (empreinte ecologique reduite). 3.2 Niveau 2: Application et calculs</t>
+          <t>Une convention collective est un accord ecrit negocie entre les syndicats de salaries et les organisations patronales dune branche dactivite (ex: Batiment, Restauration). Son role est dadapter les dispositions generales du Code du travail aux conditions particulieres de la profession. En principe, elle ne peut prevoir que des dispositions plus favorables aux salaries que la loi (principe de faveur), bien que des derogations existent aujourdhui.</t>
         </is>
       </c>
       <c r="M236" t="n">
@@ -16351,327 +16351,327 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>pdf-sdgn-t03-006</t>
+          <t>pdf-droit-t07-006</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>premiere</t>
+          <t>terminale</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>sciences de gestion</t>
+          <t>droit</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Theme 3 : Creation de valeur et performance</t>
+          <t>Theme 7 : Comment le droit encadre-t-il le travail salarie '</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Niveau 1 : Maitrise des concepts - Exercice 6</t>
+          <t>Niveau 2 : Application et analyse - Exercice 6</t>
         </is>
       </c>
       <c r="F237" t="n">
         <v>6</v>
       </c>
       <c r="G237" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Calcul de Creation de Valeur et Repartition: La boulangerie PainDore a realise un Chiffre</t>
+          <t>Cas pratique: M. Bernard, comptable chez ComptaPlus a Lyon, refuse detre mute a Paris alo</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>Exercice source PDF (sciences de gestion premiere).</t>
+          <t>Exercice source PDF (droit terminale).</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>Calcul de Creation de Valeur et Repartition: La boulangerie PainDore a realise un Chiffre dAffaires de 150 000. Pour cela, elle a achete pour 40 000 de farine, levure et electricite (Consommations Intermediaires). Elle paie 50 000 de salaires et charges, et verse 10 000 dimpots a lEtat. Calculez: a) La Valeur Ajoutee (VA) creee. b) La part de la VA (en %) redistribuee aux salaries.</t>
+          <t>Cas pratique: M. Bernard, comptable chez ComptaPlus a Lyon, refuse detre mute a Paris alors que son contrat de travail contient une clause de mobilite. Analysez la situation et les consequences de son refus.</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>sciences de gestion | Theme 3 : Creation de valeur et performance | Niveau 1 : Maitrise des concepts</t>
+          <t>droit | Theme 7 : Comment le droit encadre-t-il le travail salarie ' | Niveau 2 : Application et analyse</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>detaillee: - a) Calcul de la Valeur Ajoutee (VA): VA = CA CI. VA = 150 000 40 000 = 110 000. La boulangerie a reellement cree 110 000 de richesse. - b) Part redistribuee aux salaries:(Salaires verses / Valeur Ajoutee)100. (50 000/110 000) 100 45, 45%. Les salaries captent environ 45, 5% de la richesse creee. LEtat en capte 9%(10 000/110 000).</t>
+          <t>La clause de mobilite, si elle est indispensable aux interets de lentreprise et precise une zone geographique definie lors de la signature, est opposable au salarie. Le changement du lieu de travail dans cette zone nest quun changement des conditions de travail, que lemployeur peut imposer. Le refus de M. Bernard constitue donc un acte dinsubordination (une faute), justifiant un licenciement pour motif personnel disciplinaire.</t>
         </is>
       </c>
       <c r="M237" t="n">
-        <v>250</v>
+        <v>275</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>pdf-sdgn-t03-007</t>
+          <t>pdf-droit-t07-007</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>premiere</t>
+          <t>terminale</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>sciences de gestion</t>
+          <t>droit</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Theme 3 : Creation de valeur et performance</t>
+          <t>Theme 7 : Comment le droit encadre-t-il le travail salarie '</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Niveau 1 : Maitrise des concepts - Exercice 7</t>
+          <t>Niveau 2 : Application et analyse - Exercice 7</t>
         </is>
       </c>
       <c r="F238" t="n">
         <v>7</v>
       </c>
       <c r="G238" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Calcul de Part de Marche et Performance Commerciale: Sur le marche local de la vente de v</t>
+          <t>Cas pratique: Le directeur de lentreprise WebDev lit systematiquement les e-mails ident</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>Exercice source PDF (sciences de gestion premiere).</t>
+          <t>Exercice source PDF (droit terminale).</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>Calcul de Part de Marche et Performance Commerciale: Sur le marche local de la vente de velos (estime a 2 000 000 de ventes totales), le magasin CycloPlus a realise un chiffre daffaires de 500 000. Quel est son indicateur de performance commerciale principal ici ' 6 Calculez-le.</t>
+          <t>Cas pratique: Le directeur de lentreprise WebDev lit systematiquement les e-mails identifies comme Personnels envoyes par sa salariee Mme Petit depuis son ordinateur professionnel. Est-ce legal ' Expliquez la protection de la vie privee au travail.</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>sciences de gestion | Theme 3 : Creation de valeur et performance | Niveau 1 : Maitrise des concepts</t>
+          <t>droit | Theme 7 : Comment le droit encadre-t-il le travail salarie ' | Niveau 2 : Application et analyse</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>detaillee: Lindicateur pertinent est la Part de Marche (en valeur). Formule: (CA de lentreprise/CA total du marche ) 100. Calcul: (500 000/2 000 000) 100 = 25 %. CycloPlus detient 25% de part de marche, ce qui indique une tres forte position concurrentielle sur son secteur.</t>
+          <t>Cette pratique est illegale. Bien que lemployeur puisse controler loutil informatique fourni a ses salaries, le salarie a droit au respect de sa vie privee meme au temps et au lieu de travail. Par consequent, les correspondances identifiees explicitement comme personnelles ou privees sont couvertes par le secret des correspondances. Lemployeur ne peut les ouvrir quen presence de la salariee ou apres lavoir dument appelee, sauf risque ou evenement exceptionnel pour lentreprise.</t>
         </is>
       </c>
       <c r="M238" t="n">
-        <v>250</v>
+        <v>275</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>pdf-sdgn-t03-008</t>
+          <t>pdf-droit-t07-008</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>premiere</t>
+          <t>terminale</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>sciences de gestion</t>
+          <t>droit</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Theme 3 : Creation de valeur et performance</t>
+          <t>Theme 7 : Comment le droit encadre-t-il le travail salarie '</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Niveau 1 : Maitrise des concepts - Exercice 8</t>
+          <t>Niveau 2 : Application et analyse - Exercice 8</t>
         </is>
       </c>
       <c r="F239" t="n">
         <v>8</v>
       </c>
       <c r="G239" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Marge et Rentabilite: Lentreprise TechPhone fabrique un telephone dont le cout total de r</t>
+          <t>Libertes collectives: Les salaries de lusine AutoParts decident darreter le travail pour</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>Exercice source PDF (sciences de gestion premiere).</t>
+          <t>Exercice source PDF (droit terminale).</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>Marge et Rentabilite: Lentreprise TechPhone fabrique un telephone dont le cout total de revient est de 200. Elle decide de le vendre au prix de 800 grace a une image de marque exceptionnelle. Identifiez la source de creation de valeur et deduisez-en la marge unitaire.</t>
+          <t>Libertes collectives: Les salaries de lusine AutoParts decident darreter le travail pour reclamer une augmentation de salaire et bloquent totalement lacces a lusine. Qualifiez ce mouvement et verifiez sil respecte les conditions du droit de greve.</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>sciences de gestion | Theme 3 : Creation de valeur et performance | Niveau 1 : Maitrise des concepts</t>
+          <t>droit | Theme 7 : Comment le droit encadre-t-il le travail salarie ' | Niveau 2 : Application et analyse</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>La source de creation de valeur repose entierement sur la valeur percue (image de marque, design, reputation) qui permet dimposer un prix de vente tres largement superieur au cout de production. Marge unitaire = Prix de vente - Cout de revient = 800 200 = 600 de marge brute par appareil, garantissant une immense performance financiere (profitabilite). 3.3 Niveau 3: Entrainement type Bac</t>
+          <t>Larret de travail pour des revendications professionnelles (augmentation de salaire) est lexercice normal du droit de greve (liberte collective protegee par la Constitution). Cependant, le blocage total de lacces a lusine par des piquets de greve constitue une entrave a la liberte de travail des non-grevistes et de la direction. Ce comportement rend cette action illicite, ce qui peut justifier des sanctions disciplinaires (pour faute lourde) contre les auteurs des blocages.</t>
         </is>
       </c>
       <c r="M239" t="n">
-        <v>250</v>
+        <v>275</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>pdf-sdgn-t03-009</t>
+          <t>pdf-droit-t07-009</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>premiere</t>
+          <t>terminale</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>sciences de gestion</t>
+          <t>droit</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Theme 3 : Creation de valeur et performance</t>
+          <t>Theme 7 : Comment le droit encadre-t-il le travail salarie '</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Niveau 1 : Maitrise des concepts - Exercice 9</t>
+          <t>Niveau 3 : Entrainement type Bac - Exercice 9</t>
         </is>
       </c>
       <c r="F240" t="n">
         <v>9</v>
       </c>
       <c r="G240" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Cas dentreprise BioSaveurs: Cette cooperative agricole produit des jus de fruits 100% bio</t>
+          <t>Mise en situation: Mme Y, secretaire medicale au cabinet SantePlus, est licenciee car ell</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>Exercice source PDF (sciences de gestion premiere).</t>
+          <t>Exercice source PDF (droit terminale).</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>Cas dentreprise BioSaveurs: Cette cooperative agricole produit des jus de fruits 100% bio. Recemment, la direction a investi lourdement dans des bouteilles en verre recycle et consignables, ainsi que dans des salaires 15% au-dessus du SMIC pour ses ouvriers. Cependant, ses couts de production ayant explose, ses benefices nets (resultat financier) ont chute de 30% cette annee, inquietant les banques. A partir de ce cas, analysez comment les differentes dimensions de la performance peuvent etre contradictoires.</t>
+          <t>Mise en situation: Mme Y, secretaire medicale au cabinet SantePlus, est licenciee car elle arrive systematiquement en retard depuis 3 mois malgre plusieurs avertissements. 6 Construisez largumentation juridique justifiant ce licenciement (cause reelle et serieuse, procedure).</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>sciences de gestion | Theme 3 : Creation de valeur et performance | Niveau 1 : Maitrise des concepts</t>
+          <t>droit | Theme 7 : Comment le droit encadre-t-il le travail salarie ' | Niveau 3 : Entrainement type Bac</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>structuree: Analyse des performances par dimension:BioSaveurs excelle dans deux domaines. Performance sociale: en payant bien au-dessus du SMIC, elle fidelise et motive ses salaries. Performance environnementale: lusage du verre consigne reduit drastiquement son empreinte ecologique. La contradiction des performances: La recherche de lefficience environnementale et sociale a un cout tres eleve. Lachat de materiaux ecologiques (verre vs plastique) et les hauts salaires augmentent les charges de lentreprise. Consequence: la marge se reduit et la performance financiere seffondre (-30% de benefices). Conclusion: Ce cas illustre le conflit dinteret entre les acteurs (les salaries et ONG ecologiques sont satisfaits, mais les financeurs/banques sont inquiets). Lentreprise doit imperativement trouver un equilibre, par exemple en augmentant son prix de vente (en misant sur la valeur percue du produit ethique par le consommateur) pour restaurer sa rentabilite financiere sans renier ses engagements responsables. La performance globale est un compromis permanent.</t>
+          <t>Pour etre valide, tout licenciement pour motif personnel doit reposer sur une cause reelle et serieuse. Reelle: les faits doivent etre objectifs, exacts et verifiables (ici, les retards systematiques depuis 3 mois sont tangibles, les avertissements prouvent lexactitude des faits). Serieuse: la faute commise doit rendre impossible la poursuite normale du contrat sans dommage pour lentreprise (ici, les retards repetes dune secretaire medicale desorganisent laccueil des patients et le fonctionnement du cabinet). Lemployeur est donc fonde a engager une procedure de licenciement disciplinaire (convocation, entretien prealable, lettre de notification motivee).</t>
         </is>
       </c>
       <c r="M240" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>pdf-sdgn-t03-010</t>
+          <t>pdf-droit-t07-010</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>premiere</t>
+          <t>terminale</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>sciences de gestion</t>
+          <t>droit</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Theme 3 : Creation de valeur et performance</t>
+          <t>Theme 7 : Comment le droit encadre-t-il le travail salarie '</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Niveau 1 : Maitrise des concepts - Exercice 10</t>
+          <t>Niveau 3 : Entrainement type Bac - Exercice 10</t>
         </is>
       </c>
       <c r="F241" t="n">
         <v>10</v>
       </c>
       <c r="G241" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Question de reflexion: Pourquoi la maximisation de la seule valeur actionnariale (les di-</t>
+          <t>Developpement structure: Comment le droit du travail cherche-t-il a concilier le pouvoir</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>Exercice source PDF (sciences de gestion premiere).</t>
+          <t>Exercice source PDF (droit terminale).</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>Question de reflexion: Pourquoi la maximisation de la seule valeur actionnariale (les dividendes) peut-elle menacer la perennite de lorganisation a long terme '</t>
+          <t>Developpement structure: Comment le droit du travail cherche-t-il a concilier le pouvoir de direction de lemployeur et le respect des libertes individuelles des salaries '</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>sciences de gestion | Theme 3 : Creation de valeur et performance | Niveau 1 : Maitrise des concepts</t>
+          <t>droit | Theme 7 : Comment le droit encadre-t-il le travail salarie ' | Niveau 3 : Entrainement type Bac</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>Si une entreprise repartit la quasi-totalite de sa valeur ajoutee sous forme de dividendes a ses actionnaires, elle sappauvrit sur dautres tableaux critiques. Elle ne conserve plus de marges dautofinancement pour investir dans la Recherche &amp; Developpement ou le numerique, perdant sa competitivite future. De plus, au niveau social, bloquer les salaires pour verser des dividendes genere de la frustration, des greves et la fuite des talents (turnover). A terme, cette vision court-termiste (financiarisation) detruit la valeur partenariale et sociale, condamnant lentreprise au declin. 7</t>
+          <t>Lemployeur est le proprietaire de lentreprise et doit pouvoir la diriger (imposer des horaires, des directives, controler lactivite). Cependant, le salarie ne renonce pas a ses droits fondamentaux en signant son contrat (liberte dexpression, vie privee, convictions religieuses). Pour concilier ces imperatifs, le droit du travail pose un principe de proportionnalite fondamental: Nul ne peut apporter aux droits des personnes et aux libertes individuelles et collectives de restrictions qui ne seraient pas justifiees par la nature de la tache a accomplir ni proportionnees au but recherche. Toute limitation imposee par lemployeur (ex: interdiction dutiliser son telephone personnel, code vestimentaire) doit donc repondre strictement a un imperatif de securite, dhygiene ou dimage lie au poste.</t>
         </is>
       </c>
       <c r="M241" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>pdf-sdgn-t04-001</t>
+          <t>pdf-droit-t08-001</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>premiere</t>
+          <t>terminale</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>sciences de gestion</t>
+          <t>droit</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Theme 4 : Temps et risque</t>
+          <t>Theme 8 : Dans quel cadre et comment entreprendre '</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -16687,27 +16687,27 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Expliquer pourquoi le facteur temps est source dincertitude pour le gestionnaire.</t>
+          <t>Expliquer le principe de lunicite du patrimoine et son risque pour lentrepreneur individ</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>Exercice source PDF (sciences de gestion premiere).</t>
+          <t>Exercice source PDF (droit terminale).</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>Expliquer pourquoi le facteur temps est source dincertitude pour le gestionnaire.</t>
+          <t>Expliquer le principe de lunicite du patrimoine et son risque pour lentrepreneur individuel.</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>sciences de gestion | Theme 4 : Temps et risque | Niveau 1 : Maitrise des concepts</t>
+          <t>droit | Theme 8 : Dans quel cadre et comment entreprendre ' | Niveau 1 : Maitrise des concepts</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>Plus la decision porte sur un horizon temporel eloigne (le long terme, ex: construire une usine pour dans 5 ans), plus il est difficile de prevoir avec certitude levolution de lenvironnement (comportement des concurrents, ruptures technologiques, crises economiques). Lavenir etant par nature imprevisible, le decalage temporel genere un risque systematique.</t>
+          <t>Historiquement, le principe de lunicite du patrimoine signifie quune personne juridique ne possede quun seul patrimoine, compose de lensemble de ses biens et de ses dettes, sans distinction entre sa vie personnelle et professionnelle. Le risque majeur pour lentrepreneur individuel classique etait quen cas de faillite de son activite, ses creanciers professionnels pouvaient saisir ses biens personnels (maison, epargne) pour se rembourser.</t>
         </is>
       </c>
       <c r="M242" t="n">
@@ -16717,22 +16717,22 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>pdf-sdgn-t04-002</t>
+          <t>pdf-droit-t08-002</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>premiere</t>
+          <t>terminale</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>sciences de gestion</t>
+          <t>droit</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Theme 4 : Temps et risque</t>
+          <t>Theme 8 : Dans quel cadre et comment entreprendre '</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -16748,27 +16748,27 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Quest-ce quune veille informationnelle et a quoi sert-elle '</t>
+          <t>Quest-ce que laffectio societatis dans le cadre dun contrat de societe '</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>Exercice source PDF (sciences de gestion premiere).</t>
+          <t>Exercice source PDF (droit terminale).</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>Quest-ce quune veille informationnelle et a quoi sert-elle '</t>
+          <t>Quest-ce que laffectio societatis dans le cadre dun contrat de societe '</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>sciences de gestion | Theme 4 : Temps et risque | Niveau 1 : Maitrise des concepts</t>
+          <t>droit | Theme 8 : Dans quel cadre et comment entreprendre ' | Niveau 1 : Maitrise des concepts</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>La veille est un processus de surveillance continue, systematique et organisee de lenvironnement de lentreprise (concurrentiel, technologique, juridique). Elle sert a capter les signaux faibles afin danticiper les menaces (nouveau concurrent) et de saisir les opportunites avant les autres, reduisant ainsi le risque lie a lignorance ou a lobsolescence.</t>
+          <t>Laffectio societatis est une notion jurisprudentielle qui designe la volonte commune des associes de collaborer activement, de facon volontaire et sur un pied degalite, a lexploitation de lentreprise et au succes du projet societaire. Cest lesprit dequipe indispensable a la qualification dun contrat de societe.</t>
         </is>
       </c>
       <c r="M243" t="n">
@@ -16778,22 +16778,22 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>pdf-sdgn-t04-003</t>
+          <t>pdf-droit-t08-003</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>premiere</t>
+          <t>terminale</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>sciences de gestion</t>
+          <t>droit</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Theme 4 : Temps et risque</t>
+          <t>Theme 8 : Dans quel cadre et comment entreprendre '</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -16809,27 +16809,27 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Definir la notion de Seuil de Rentabilite (SR) dans la gestion financiere.</t>
+          <t>Distinguer une entente illicite dun abus de position dominante.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>Exercice source PDF (sciences de gestion premiere).</t>
+          <t>Exercice source PDF (droit terminale).</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>Definir la notion de Seuil de Rentabilite (SR) dans la gestion financiere.</t>
+          <t>Distinguer une entente illicite dun abus de position dominante.</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>sciences de gestion | Theme 4 : Temps et risque | Niveau 1 : Maitrise des concepts</t>
+          <t>droit | Theme 8 : Dans quel cadre et comment entreprendre ' | Niveau 1 : Maitrise des concepts</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>Le seuil de rentabilite est le niveau de Chiffre dAffaires quune entreprise doit imperativement atteindre pour couvrir lintegralite de ses charges (fixes et variables). A ce niveau exact, le resultat de lentreprise est nul (ni benefice, ni perte). Cest un indicateur de risque fondamental.</t>
+          <t>Une entente illicite (ou cartel) est un accord ou une concertation secrete entre plusieurs entreprises independantes visant a fausser la concurrence sur un marche (ex: fixation commune des prix, repartition des territoires). Labus de position dominante concerne une entreprise isolee qui profite de son pouvoir de marche ecrasant pour imposer des conditions deloyales, evincer ses concurrents ou empecher larrivee de nouveaux entrants.</t>
         </is>
       </c>
       <c r="M244" t="n">
@@ -16839,22 +16839,22 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>pdf-sdgn-t04-004</t>
+          <t>pdf-droit-t08-004</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>premiere</t>
+          <t>terminale</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>sciences de gestion</t>
+          <t>droit</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Theme 4 : Temps et risque</t>
+          <t>Theme 8 : Dans quel cadre et comment entreprendre '</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -16870,27 +16870,27 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Citer deux facteurs de risques externes et deux facteurs de risques internes pouvant frap-</t>
+          <t>Identifier les obligations principales du franchiseur et du franchise dans un contrat de f</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>Exercice source PDF (sciences de gestion premiere).</t>
+          <t>Exercice source PDF (droit terminale).</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>Citer deux facteurs de risques externes et deux facteurs de risques internes pouvant frapper une organisation.</t>
+          <t>Identifier les obligations principales du franchiseur et du franchise dans un contrat de franchise.</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>sciences de gestion | Theme 4 : Temps et risque | Niveau 1 : Maitrise des concepts</t>
+          <t>droit | Theme 8 : Dans quel cadre et comment entreprendre ' | Niveau 1 : Maitrise des concepts</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>Externes: Rupture dapprovisionnement (crise geopolitique), rupture technologique (obsolescence subite du produit face a une innovation concurrente). Internes: Panne des machines (defaut de maintenance), greve du personnel (mauvais climat social).</t>
+          <t>Le franchiseur est tenu de transmettre son savoir-faire secret et substantiel, 7 de mettre a disposition sa marque et son enseigne, et de fournir une assistance technique et commerciale continue. En contrepartie, le franchise a lobligation de payer un droit dentree et/ou des redevances (royalties), de respecter strictement le concept (cahier des charges) pour preserver limage du reseau, et de sapprovisionner parfois exclusivement aupres du franchiseur.</t>
         </is>
       </c>
       <c r="M245" t="n">
@@ -16900,22 +16900,22 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>pdf-sdgn-t04-005</t>
+          <t>pdf-droit-t08-005</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>premiere</t>
+          <t>terminale</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>sciences de gestion</t>
+          <t>droit</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Theme 4 : Temps et risque</t>
+          <t>Theme 8 : Dans quel cadre et comment entreprendre '</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -16931,27 +16931,27 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Quest-ce que lasymetrie dinformation au sein dune organisation '</t>
+          <t>Quelles sont les specificites dune societe cooperative (SCOP) par rapport a une societe co</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>Exercice source PDF (sciences de gestion premiere).</t>
+          <t>Exercice source PDF (droit terminale).</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>Quest-ce que lasymetrie dinformation au sein dune organisation '</t>
+          <t>Quelles sont les specificites dune societe cooperative (SCOP) par rapport a une societe commerciale classique '</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>sciences de gestion | Theme 4 : Temps et risque | Niveau 1 : Maitrise des concepts</t>
+          <t>droit | Theme 8 : Dans quel cadre et comment entreprendre ' | Niveau 1 : Maitrise des concepts</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>Lasymetrie dinformation intervient lorsquun acteur (ex: un manager de terrain) detient une information cruciale quil ne transmet pas a un autre acteur (ex: la direction generale). Cette retention dinformation (volontaire par pouvoir, ou involontaire par mauvaise communication) fausse la prise de decision globale qui se base alors sur des donnees erronees ou obsoletes. 4.2 Niveau 2: Application et calculs</t>
+          <t>La SCOP se distingue par une finalite sociale et democratique. Les salaries sont les associes majoritaires (ils detiennent au moins 51% du capital). La prise de decision respecte le principe une personne = une voix, quel que soit le montant du capital detenu par lassocie. Enfin, une grande part des benefices est obligatoirement reinvestie dans lentreprise (reserves impartageables) ou redistribuee aux salaries, seloignant de la logique de profit pur pour les actionnaires.</t>
         </is>
       </c>
       <c r="M246" t="n">
@@ -16961,637 +16961,637 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>pdf-sdgn-t04-006</t>
+          <t>pdf-droit-t08-006</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>premiere</t>
+          <t>terminale</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>sciences de gestion</t>
+          <t>droit</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Theme 4 : Temps et risque</t>
+          <t>Theme 8 : Dans quel cadre et comment entreprendre '</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Niveau 1 : Maitrise des concepts - Exercice 6</t>
+          <t>Niveau 2 : Application et analyse - Exercice 6</t>
         </is>
       </c>
       <c r="F247" t="n">
         <v>6</v>
       </c>
       <c r="G247" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Calcul du Seuil de Rentabilite: La start-up EcoVelo fabrique des bicyclettes electriques.</t>
+          <t>Cas pratique: M. Durand, createur dune entreprise de menuiserie, souhaite proteger sa mai</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>Exercice source PDF (sciences de gestion premiere).</t>
+          <t>Exercice source PDF (droit terminale).</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>Calcul du Seuil de Rentabilite: La start-up EcoVelo fabrique des bicyclettes electriques. Ses Charges Fixes (CF) annuelles (loyers de lusine, salaires administratifs, assurances) selevent a 100 000. Le Prix de Vente (PV) unitaire dun velo est de 800. Le Cout Variable (CV) unitaire pour fabriquer un velo (pieces, main duvre de fabrication) est de 300. Calculez: a) La Marge sur Cout Variable unitaire (MSCV unitaire). b) Le Taux de Marge sur Cout Variable (TMSCV). c) Le Seuil de Rentabilite en valeur (en ). d) Le Seuil de Rentabilite en volume (nombre de velos a vendre).</t>
+          <t>Cas pratique: M. Durand, createur dune entreprise de menuiserie, souhaite proteger sa maison personnelle en cas de faillite de son activite. Quels mecanismes juridiques ou choix de structure soffrent a lui '</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>sciences de gestion | Theme 4 : Temps et risque | Niveau 1 : Maitrise des concepts</t>
+          <t>droit | Theme 8 : Dans quel cadre et comment entreprendre ' | Niveau 2 : Application et analyse</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>detaillee pas a pas: - a) MSCV unitaire: Cest la marge degagee sur chaque velo pour rembourser les charges fixes. MSCV = PV CV. MSCV = 800 300 = 500. Chaque velo vendu degage 500 nets. - b) TMSCV: Cest le pourcentage que represente la marge par rapport au prix de vente. (MSCV/PV) 100. (500/800) 100 = 62, 5%. 8 - c) Seuil de Rentabilite (SR) en valeur: Le CA a atteindre. Formule: CF /TMSCV. SR = 100 000/0, 625 = 160 000. EcoVelo commencera a faire des benefices a partir de 160 000 de chiffre daffaires. - d) Seuil de Rentabilite en volume:Le nombre dunites a vendre. Formule: CF/MSCV unitaire (ou SR en / Prix unitaire).100 000/500 = 200 velos. Il faut vendre exactement 200 velos pour ne pas faire de perte.</t>
+          <t>Plusieurs options juridiques sont possibles. Il peut opter pour la creation dune societe unipersonnelle (EURL ou SASU), ce qui cree une nouvelle personne morale (lentreprise) dotee de son propre patrimoine, limitant ainsi la responsabilite de M. Durand au montant de ses apports. Sil souhaite rester entrepreneur individuel, il beneficie desormais automatiquement du nouveau statut unique de lEI (depuis 2022) qui instaure une separation de plein droit entre le patrimoine professionnel (seul saisissable par les creanciers professionnels) et le patrimoine personnel, protegeant ainsi de fait sa maison.</t>
         </is>
       </c>
       <c r="M247" t="n">
-        <v>250</v>
+        <v>275</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>pdf-sdgn-t04-007</t>
+          <t>pdf-droit-t08-007</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>premiere</t>
+          <t>terminale</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>sciences de gestion</t>
+          <t>droit</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Theme 4 : Temps et risque</t>
+          <t>Theme 8 : Dans quel cadre et comment entreprendre '</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Niveau 1 : Maitrise des concepts - Exercice 7</t>
+          <t>Niveau 2 : Application et analyse - Exercice 7</t>
         </is>
       </c>
       <c r="F248" t="n">
         <v>7</v>
       </c>
       <c r="G248" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Lien entre Temps et Valeur Financiere:Lentreprise DecoPro a facture des travaux pour 50 0</t>
+          <t>Cas pratique: M. Blanc, ancien boulanger salarie chez La Bonne Miche, ouvre sa propre bou</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>Exercice source PDF (sciences de gestion premiere).</t>
+          <t>Exercice source PDF (droit terminale).</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>Lien entre Temps et Valeur Financiere:Lentreprise DecoPro a facture des travaux pour 50 000. Le client ne paiera que dans 90 jours (delai de paiement). Lentreprise doit payer ses fournisseurs et ses salaries des la fin du mois. Expliquez le risque genere par ce decalage temporel.</t>
+          <t>Cas pratique: M. Blanc, ancien boulanger salarie chez La Bonne Miche, ouvre sa propre boulangerie juste en face et imite les couleurs et lenseigne de son ancien employeur pour detourner la clientele. Qualifiez juridiquement ces faits (concurrence deloyale).</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>sciences de gestion | Theme 4 : Temps et risque | Niveau 1 : Maitrise des concepts</t>
+          <t>droit | Theme 8 : Dans quel cadre et comment entreprendre ' | Niveau 2 : Application et analyse</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>Cest un risque dilliquidite (ou de defaillance de tresorerie). Le decalage temporel entre les decaissements (immediats) et les encaissements (retardes de 90 jours) cree un besoin en fonds de roulement. Meme si lentreprise est rentable sur le papier (valeur), labsence de liquidites au moment T peut la conduire a lincapacite de payer ses dettes, la menant directement a la cessation de paiement (faillite).</t>
+          <t>La libre concurrence permet a M. Blanc de sinstaller. Cependant, limitation servile de lenseigne et des couleurs de son ancien employeur, creant un risque reel de confusion dans lesprit de la clientele, constitue une faute civile. Si La Bonne Miche subit une perte de chiffre daffaires (prejudice) directement liee a ce comportement (lien de causalite), il sagit dune pratique de concurrence deloyale parasitaire, sanctionnable sur le fondement de la responsabilite extracontractuelle.</t>
         </is>
       </c>
       <c r="M248" t="n">
-        <v>250</v>
+        <v>275</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>pdf-sdgn-t04-008</t>
+          <t>pdf-droit-t08-008</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>premiere</t>
+          <t>terminale</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>sciences de gestion</t>
+          <t>droit</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Theme 4 : Temps et risque</t>
+          <t>Theme 8 : Dans quel cadre et comment entreprendre '</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Niveau 1 : Maitrise des concepts - Exercice 8</t>
+          <t>Niveau 2 : Application et analyse - Exercice 8</t>
         </is>
       </c>
       <c r="F249" t="n">
         <v>8</v>
       </c>
       <c r="G249" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Evaluation des risques et obsolescence: Une chaine de location de DVD refuse dinvestir da</t>
+          <t>Analyse de partenariat: Lentreprise de logistique LogiTrans decide de confier le nettoy</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>Exercice source PDF (sciences de gestion premiere).</t>
+          <t>Exercice source PDF (droit terminale).</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>Evaluation des risques et obsolescence: Une chaine de location de DVD refuse dinvestir dans la diffusion en ligne (streaming), considerant que son activite physique est encore tres rentable aujourdhui. Qualifiez lattitude de la direction face au risque technologique et les consequences possibles a moyen terme.</t>
+          <t>Analyse de partenariat: Lentreprise de logistique LogiTrans decide de confier le nettoyage et la securite de ses entrepots a la societe exterieure SecurNet. Qualifiez ce partenariat contractuel (sous-traitance).</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>sciences de gestion | Theme 4 : Temps et risque | Niveau 1 : Maitrise des concepts</t>
+          <t>droit | Theme 8 : Dans quel cadre et comment entreprendre ' | Niveau 2 : Application et analyse</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>La direction refuse de sortir de sa zone de confort et occulte le risque de rupture technologique. Elle prend des decisions basees sur la valeur dune information passee/presente sans recourir a la prospective. La consequence est fatale: lobsolescence ultra-rapide de son modele daffaires, conduisant a la disparition de lentreprise (ex: le cas historique de Blockbuster face a Netflix). 4.3 Niveau 3: Entrainement type Bac</t>
+          <t>Il sagit dun contrat dentreprise (ou contrat de prestation de services), souvent appele sous-traitance dans le langage courant. LogiTrans (le donneur dordre) externalise une tache specifique de son fonctionnement vers un partenaire (SecurNet) qui realisera la prestation en toute independance, sans aucun lien de subordination, en echange dune remuneration.</t>
         </is>
       </c>
       <c r="M249" t="n">
-        <v>250</v>
+        <v>275</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>pdf-sdgn-t04-009</t>
+          <t>pdf-droit-t08-009</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>premiere</t>
+          <t>terminale</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>sciences de gestion</t>
+          <t>droit</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Theme 4 : Temps et risque</t>
+          <t>Theme 8 : Dans quel cadre et comment entreprendre '</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Niveau 1 : Maitrise des concepts - Exercice 9</t>
+          <t>Niveau 3 : Entrainement type Bac - Exercice 9</t>
         </is>
       </c>
       <c r="F250" t="n">
         <v>9</v>
       </c>
       <c r="G250" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Cas dentreprise SolarMove: Lentreprise fabrique des trottinettes solaires. Son cycle de p</t>
+          <t>Mise en situation:Les operateurs telephoniques Alpha, Beta et Gamma se reunissent secrete</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>Exercice source PDF (sciences de gestion premiere).</t>
+          <t>Exercice source PDF (droit terminale).</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>Cas dentreprise SolarMove: Lentreprise fabrique des trottinettes solaires. Son cycle de production est tres long (6 mois entre la conception et la vente). La directrice souhaite lancer une nouvelle gamme pour Noel, mais craint que la demande des consommateurs ait evolue entre-temps, ou que le fournisseur asiatique de batteries prenne du retard. A laide de vos connaissances, conseillez la dirigeante sur les outils de gestion du temps et des risques a mettre en place pour securiser son projet.</t>
+          <t>Mise en situation:Les operateurs telephoniques Alpha, Beta et Gamma se reunissent secretement pour fixer des prix minimums sur le marche et se repartir les zones geographiques. Formulez une argumentation juridique pour qualifier et sanctionner cette pratique selon le droit de la concurrence.</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>sciences de gestion | Theme 4 : Temps et risque | Niveau 1 : Maitrise des concepts</t>
+          <t>droit | Theme 8 : Dans quel cadre et comment entreprendre ' | Niveau 3 : Entrainement type Bac</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>structuree: Analyse des risques: Le long cycle de production genere deux risques temporels majeurs. Un risque externe commercial (evolution de la demande ou effet de mode qui passe) et un risque dapprovisionnement (dependance technologique envers lAsie et risque logistique). Rater la periode de Noel (contrainte sectorielle saisonniere) serait une catastrophe financiere. Outils de gestion proposes: 1) Gestion du temps: La directrice doit imperativement utiliser un outil de planification (ex: un diagramme de Gantt ou un calendrier previsionnel retroactif) pour piloter lenchainement critique des taches, integrer des marges de manuvre (jours de securite) et anticiper les retards logistiques. 2) Gestion des risques / Prospective: Pour le risque commercial, il faut instaurer une veille tendancielle et realiser des etudes de marche en amont. Pour le risque fournisseur, lentreprise doit securiser la chaine (strategie multi-fournisseurs pour reduire la dependance, ou relocaliser une partie de lassemblage). 3) Gestion financiere: Elaborer un budget de tresorerie strict pour sassurer que les 6 mois de depenses sans rentrees dargent pourront etre supportes par lentreprise.</t>
+          <t>Faits: Trois entreprises majeures saccordent secretement sur les prix et les 8 territoires. Probleme de droit: De tels comportements concertes sont-ils licites sur un marche concurrentiel ' Regle de droit: Le droit interne et europeen prohibe les actions concertees, conventions, ou ententes expresses ou tacites dont lobjet ou leffet est dempecher, de restreindre ou de fausser le jeu de la concurrence sur un marche, notamment en fixant artificiellement les prix ou en repartissant les marches. Solution: Les operateurs commettent une entente illicite (cartel). Cette pratique, gravement prejudiciable aux consommateurs qui subissent des prix gonfles, est passible de tres lourdes sanctions pecuniaires (amendes) imposees par lAutorite de la concurrence.</t>
         </is>
       </c>
       <c r="M250" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>pdf-sdgn-t04-010</t>
+          <t>pdf-droit-t08-010</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>premiere</t>
+          <t>terminale</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>sciences de gestion</t>
+          <t>droit</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Theme 4 : Temps et risque</t>
+          <t>Theme 8 : Dans quel cadre et comment entreprendre '</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Niveau 1 : Maitrise des concepts - Exercice 10</t>
+          <t>Niveau 3 : Entrainement type Bac - Exercice 10</t>
         </is>
       </c>
       <c r="F251" t="n">
         <v>10</v>
       </c>
       <c r="G251" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Developpement structure: Prendre des risques est consubstantiel a la gestion dune organ</t>
+          <t>Developpement structure: Pourquoi la creation dune societe commerciale est-elle souvent</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>Exercice source PDF (sciences de gestion premiere).</t>
+          <t>Exercice source PDF (droit terminale).</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>Developpement structure: Prendre des risques est consubstantiel a la gestion dune organisation. La recherche de la performance justifie-t-elle la prise de nimporte quel risque 9 par les dirigeants '</t>
+          <t>Developpement structure: Pourquoi la creation dune societe commerciale est-elle souvent privilegiee par les entrepreneurs face aux risques de lactivite economique '</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>sciences de gestion | Theme 4 : Temps et risque | Niveau 1 : Maitrise des concepts</t>
+          <t>droit | Theme 8 : Dans quel cadre et comment entreprendre ' | Niveau 3 : Entrainement type Bac</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>Sans prise de risque (investir, recruter, lancer un nouveau produit), lentreprise stagne et meurt, car lenvironnement economique est mouvant. Linnovation implique par essence le saut dans linconnu. Neanmoins, lappetence au risque dun dirigeant ne peut pas etre aveugle et infinie. Les consequences dune mauvaise gestion des risques depassent le seul cadre de lentreprise: un risque inconsidere peut provoquer un plan social (impact humain dramatique), la ruine des petits actionnaires ou une catastrophe ecologique (empreinte environnementale, maree noire). Le dirigeant a donc une responsabilite morale, juridique et societale. La performance globale moderne impose un pilotage modere et maitrise du risque (demarche RSE, plan de prevention), prouvant que la performance ne justifie pas le sacrifice de la securite humaine ou de lecosysteme. 10</t>
+          <t>Entreprendre comporte dimportants risques financiers et personnels. La creation dune societe commerciale (comme la SARL ou la SAS) permet de creer une fiction juridique: la personne morale. Celle-ci dispose de son propre patrimoine, de son propre nom et de ses propres droits. Linteret majeur est la limitation de responsabilite: en cas de faillite, lentrepreneur (lassocie) ne perd que le montant de ses apports au capital, ses biens personnels sont a labri (sauf faute de gestion ou caution personnelle). Par ailleurs, la forme societaire permet de sassocier pour lever des capitaux plus importants, dacceder plus facilement au credit bancaire, et de faciliter la transmission de lentreprise (vente de parts sociales), assurant ainsi la perennite de lactivite au-dela de la personne de lentrepreneur. 9</t>
         </is>
       </c>
       <c r="M251" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>pdf-droit-t05-001</t>
+          <t>T1-01</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>terminale</t>
+          <t>premiere</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>droit</t>
+          <t>sciences de gestion</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Theme 5 : Quel est le role du contrat '</t>
+          <t>Thème 1 : De l'individu à l'acteur</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Niveau 1 : Maitrise des concepts - Exercice 1</t>
+          <t>L'individu et le groupe</t>
         </is>
       </c>
       <c r="F252" t="n">
         <v>1</v>
       </c>
       <c r="G252" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Definir la notion de contrat et preciser limportance de lobligation dinformation et de con</t>
+          <t>Action collective et organisation</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>Exercice source PDF (droit terminale).</t>
+          <t>Général</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>Definir la notion de contrat et preciser limportance de lobligation dinformation et de conseil.</t>
+          <t>Définir ce qu'est une action collective organisée et préciser le rôle de l'organisation.</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>droit | Theme 5 : Quel est le role du contrat ' | Niveau 1 : Maitrise des concepts</t>
+          <t>action collective | organisation | but commun | coordination</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>Le contrat est un accord de volontes entre deux ou plusieurs personnes, destine a creer, modifier, transmettre ou eteindre des obligations. Lobligation dinformation et de conseil (imposee par la loi au professionnel) est fondamentale car elle permet au cocontractant (notamment le consommateur) de sengager en toute connaissance de cause, reequilibrant ainsi lasymetrie de connaissances entre les deux parties.</t>
+          <t>Une action collective organisée se forme lorsque plusieurs individus se regroupent pour atteindre un but commun qu'ils ne pourraient pas atteindre seuls. L'organisation (entreprise, association, administration) fournit le cadre juridique, matériel et hiérarchique pour coordonner cette action collective dans le temps.</t>
         </is>
       </c>
       <c r="M252" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>pdf-droit-t05-002</t>
+          <t>T1-02</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>terminale</t>
+          <t>premiere</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>droit</t>
+          <t>sciences de gestion</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Theme 5 : Quel est le role du contrat '</t>
+          <t>Thème 1 : De l'individu à l'acteur</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Niveau 1 : Maitrise des concepts - Exercice 2</t>
+          <t>L'individu et le groupe</t>
         </is>
       </c>
       <c r="F253" t="n">
         <v>2</v>
       </c>
       <c r="G253" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Identifier et expliquer les conditions de validite indispensables a la formation dun contr</t>
+          <t>Qualification et compétence</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>Exercice source PDF (droit terminale).</t>
+          <t>Général</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>Identifier et expliquer les conditions de validite indispensables a la formation dun contrat.</t>
+          <t>Quelle est la différence entre la qualification et la compétence d'un individu ?</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>droit | Theme 5 : Quel est le role du contrat ' | Niveau 1 : Maitrise des concepts</t>
+          <t>qualification | compétence | savoir-faire | diplôme</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>Pour etre valide, un contrat exige trois conditions cumulatives: 1) Le consentement, qui doit etre libre et eclaire (exempt derreur, de dol ou de violence). 2) La capacite juridique de contracter (etre majeur et non soumis a une mesure de protection type tutelle). 3) Un contenu licite et certain (lobjet du contrat doit exister, etre determine ou determinable, et ne pas etre contraire a lordre public).</t>
+          <t>La qualification repose sur la formation initiale, les diplômes obtenus et l'expérience reconnue (souvent liée à une grille tarifaire conventionnelle). La compétence est plus dynamique : c'est la capacité d'un individu à mobiliser des savoirs (connaissances), des savoir-faire (pratiques) et des savoir-être (comportements) pour accomplir une tâche précise en situation réelle de travail.</t>
         </is>
       </c>
       <c r="M253" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>pdf-droit-t05-003</t>
+          <t>T1-03</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>terminale</t>
+          <t>premiere</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>droit</t>
+          <t>sciences de gestion</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Theme 5 : Quel est le role du contrat '</t>
+          <t>Thème 1 : De l'individu à l'acteur</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Niveau 1 : Maitrise des concepts - Exercice 3</t>
+          <t>Les phénomènes relationnels</t>
         </is>
       </c>
       <c r="F254" t="n">
         <v>3</v>
       </c>
       <c r="G254" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Distinguer une obligation de moyens dune obligation de resultat.</t>
+          <t>Communication interne</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>Exercice source PDF (droit terminale).</t>
+          <t>Général</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>Distinguer une obligation de moyens dune obligation de resultat.</t>
+          <t>Distinguer la communication formelle de la communication informelle au sein d'une organisation.</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>droit | Theme 5 : Quel est le role du contrat ' | Niveau 1 : Maitrise des concepts</t>
+          <t>communication formelle | communication informelle | hiérarchie | affinités</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>Dans une obligation de moyens, le debiteur sengage a deployer tous les efforts possibles pour atteindre le resultat espere (ex: un medecin sengage a soigner son patient avec les meilleures pratiques, mais ne garantit pas la guerison). Dans une obligation de resultat, le debiteur garantit latteinte dun resultat precis (ex: un transporteur doit livrer la marchandise au bon endroit).</t>
+          <t>La communication formelle est officielle, planifiée et suit les voies hiérarchiques prévues par l'organigramme (ex: une réunion de service, une note de service). La communication informelle est spontanée, non planifiée et repose sur les affinités personnelles (ex: échanges à la machine à café). L'informel favorise la cohésion mais peut générer des rumeurs.</t>
         </is>
       </c>
       <c r="M254" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>pdf-droit-t05-004</t>
+          <t>T1-04</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>terminale</t>
+          <t>premiere</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>droit</t>
+          <t>sciences de gestion</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Theme 5 : Quel est le role du contrat '</t>
+          <t>Thème 1 : De l'individu à l'acteur</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Niveau 1 : Maitrise des concepts - Exercice 4</t>
+          <t>Les phénomènes relationnels</t>
         </is>
       </c>
       <c r="F255" t="n">
         <v>4</v>
       </c>
       <c r="G255" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Definir le droit de retractation et preciser son utilite pour le cyberconsommateur.</t>
+          <t>Culture d'entreprise</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>Exercice source PDF (droit terminale).</t>
+          <t>Général</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>Definir le droit de retractation et preciser son utilite pour le cyberconsommateur.</t>
+          <t>Qu'est-ce que la culture d'entreprise et quels sont ses éléments constitutifs ?</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>droit | Theme 5 : Quel est le role du contrat ' | Niveau 1 : Maitrise des concepts</t>
+          <t>culture d'entreprise | valeurs | normes | rituels</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>Le droit de retractation est un delai legal (generalement de 14 jours) permettant au consommateur de revenir sur son consentement et dannuler un contrat conclu a distance, sans avoir a se justifier. Il est crucial pour le cyberconsommateur car il compense limpossibilite de voir, toucher ou essayer le produit avant la conclusion de la vente.</t>
+          <t>La culture d'entreprise est l'ensemble des valeurs, croyances, normes, mythes et rituels partagés par les membres d'une organisation. Elle crée un sentiment d'appartenance, soude le collectif et différencie l'entreprise de ses concurrents.</t>
         </is>
       </c>
       <c r="M255" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>pdf-droit-t05-005</t>
+          <t>T1-05</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>terminale</t>
+          <t>premiere</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>droit</t>
+          <t>sciences de gestion</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Theme 5 : Quel est le role du contrat '</t>
+          <t>Thème 1 : De l'individu à l'acteur</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Niveau 1 : Maitrise des concepts - Exercice 5</t>
+          <t>Les phénomènes relationnels</t>
         </is>
       </c>
       <c r="F256" t="n">
         <v>5</v>
       </c>
       <c r="G256" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Quelle est la difference entre la nullite relative et la nullite absolue dun contrat '</t>
+          <t>Le leadership</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>Exercice source PDF (droit terminale).</t>
+          <t>Général</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>Quelle est la difference entre la nullite relative et la nullite absolue dun contrat '</t>
+          <t>Définir le leadership et expliquer son impact sur le groupe.</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>droit | Theme 5 : Quel est le role du contrat ' | Niveau 1 : Maitrise des concepts</t>
+          <t>leadership | influence | motivation | performance</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>La nullite relative sanctionne la violation dune regle visant a proteger un interet prive (ex: un vice du consentement ou lincapacite dune partie); seule la personne protegee peut linvoquer. La nullite absolue sanctionne la violation dune regle protegeant linteret general (ex: un contrat portant sur la vente dorganes); elle peut etre demandee par toute personne y ayant un interet, ainsi que par le ministere public.</t>
+          <t>Le leadership est la capacité d'un individu (le leader) à influencer le comportement et les attitudes des autres membres du groupe pour les fédérer autour d'un objectif commun, sans forcément utiliser l'autorité hiérarchique formelle. Un bon leadership favorise la motivation et la performance collective.</t>
         </is>
       </c>
       <c r="M256" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>pdf-droit-t05-006</t>
+          <t>T1-06</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>terminale</t>
+          <t>premiere</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>droit</t>
+          <t>sciences de gestion</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Theme 5 : Quel est le role du contrat '</t>
+          <t>Thème 1 : De l'individu à l'acteur</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Niveau 2 : Application et analyse - Exercice 6</t>
+          <t>Évaluation et rétribution</t>
         </is>
       </c>
       <c r="F257" t="n">
@@ -17602,57 +17602,58 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Cas pratique: Un mineur de 16 ans achete seul un ordinateur de grande valeur sur le site</t>
+          <t>Calcul du coût global du travail</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>Exercice source PDF (droit terminale).</t>
+          <t>L'entreprise de menuiserie "BoisDesign" emploie M. Karim comme chef d'atelier. Son salaire brut mensuel est de 2 500 €. Les cotisations salariales s'élèvent à 22% du salaire brut. Les cotisations patronales s'élèvent à 42% du salaire brut.</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>Cas pratique: Un mineur de 16 ans achete seul un ordinateur de grande valeur sur le site de e-commerce TechBoutique. Qualifiez juridiquement les parties et determinez si ce contrat est valablement forme.</t>
+          <t>Calculez : a) Le salaire net versé à M. Karim. b) Le coût global du travail supporté par l'entreprise "BoisDesign" pour ce salarié.</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>droit | Theme 5 : Quel est le role du contrat ' | Niveau 2 : Application et analyse</t>
+          <t>coût du travail | salaire net | cotisations patronales | charges</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>Les parties: TechBoutique est une personne morale de droit prive, ayant la qualite de professionnel. Le jeune de 16 ans est une personne physique, ayant la qualite de mineur non emancipe (donc incapable juridiquement). Lachat dun ordinateur de grande valeur depasse les actes courants de la vie quotidienne. Le contrat nest donc pas valablement forme pour defaut de capacite. Il encourt la nullite relative.</t>
+          <t>a) Salaire net : C'est le salaire brut moins les cotisations salariales. Calcul des cotisations salariales : 2 500 x 0,22 = 550 €. Salaire net = 2 500 - 550 = 1 950 €. (C'est ce que perçoit le salarié).
+b) Coût global du travail : Pour l'employeur, le coût correspond au salaire brut PLUS les charges patronales. Calcul des cotisations patronales : 2 500 x 0,42 = 1 050 €. Coût global = Salaire brut (2 500) + Cotisations patronales (1 050) = 3 550 €. L'employeur débourse 3 550 € pour verser un net de 1 950 € au salarié.</t>
         </is>
       </c>
       <c r="M257" t="n">
-        <v>275</v>
+        <v>260</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>pdf-droit-t05-007</t>
+          <t>T1-07</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>terminale</t>
+          <t>premiere</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>droit</t>
+          <t>sciences de gestion</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Theme 5 : Quel est le role du contrat '</t>
+          <t>Thème 1 : De l'individu à l'acteur</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Niveau 2 : Application et analyse - Exercice 7</t>
+          <t>Les phénomènes relationnels</t>
         </is>
       </c>
       <c r="F258" t="n">
@@ -17663,57 +17664,57 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Cas pratique: Lentreprise ProprePlus sest engagee aupres de la societe BuroTop a entreten</t>
+          <t>Analyse des interactions</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>Exercice source PDF (droit terminale).</t>
+          <t>Lors d'une réunion chez "MarketWeb", la directrice, Mme Martin, impose ses décisions sans consulter son équipe de graphistes, utilisant un ton sec et autoritaire.</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>Cas pratique: Lentreprise ProprePlus sest engagee aupres de la societe BuroTop a entretenir ses locaux, mais nintervient plus depuis un mois sans justification. Identifiez le 2 moyen daction prealable avant de saisir la justice (mise en demeure) et expliquez lexception dinexecution.</t>
+          <t>Analysez cette situation de communication et ses effets potentiels.</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>droit | Theme 5 : Quel est le role du contrat ' | Niveau 2 : Application et analyse</t>
+          <t>communication descendante | autoritaire | motivation | climat social</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>Laction prealable est la mise en demeure, un acte juridique formel (souvent par lettre recommandee) par lequel BuroTop somme officiellement ProprePlus dexecuter son obligation. En reponse a cette inexecution, BuroTop peut invoquer lexception dinexecution: il sagit du droit de suspendre sa propre obligation (ici, le paiement des factures dentretien) tant que son cocontractant nexecute pas la sienne.</t>
+          <t>Contexte : Communication formelle descendante. Style : Autoritaire (leadership directif). Effets potentiels : Si ce style peut être efficace en situation d'urgence, à long terme, il risque de générer de la frustration, une baisse de motivation, un manque de créativité des graphistes, voire un climat conflictuel ou un fort taux de rotation du personnel (turnover).</t>
         </is>
       </c>
       <c r="M258" t="n">
-        <v>275</v>
+        <v>260</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>pdf-droit-t05-008</t>
+          <t>T1-08</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>terminale</t>
+          <t>premiere</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>droit</t>
+          <t>sciences de gestion</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Theme 5 : Quel est le role du contrat '</t>
+          <t>Thème 1 : De l'individu à l'acteur</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Niveau 2 : Application et analyse - Exercice 8</t>
+          <t>Les phénomènes relationnels</t>
         </is>
       </c>
       <c r="F259" t="n">
@@ -17724,57 +17725,57 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Analyse de clause: M. Martin a souscrit un abonnement chez loperateur TelecomPlus. Son co</t>
+          <t>Gestion des conflits</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>Exercice source PDF (droit terminale).</t>
+          <t>Deux commerciaux de l'agence "AutoVente", Marc et Sophie, se disputent violemment l'attribution d'un client très rentable.</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>Analyse de clause: M. Martin a souscrit un abonnement chez loperateur TelecomPlus. Son contrat contient une clause lui interdisant de resilier, meme en cas de modification unilaterale du tarif par loperateur. Qualifiez cette clause et donnez sa consequence juridique.</t>
+          <t>Qualifiez ce type de conflit et proposez une méthode de résolution.</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>droit | Theme 5 : Quel est le role du contrat ' | Niveau 2 : Application et analyse</t>
+          <t>conflit d'intérêt | arbitrage | médiation | résolution</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>Il sagit dune clause abusive. En droit de la consommation, une clause est consideree comme abusive lorsquelle cree un desequilibre significatif entre les droits et obligations des parties, au detriment du consommateur. La consequence juridique est que cette clause est reputee non ecrite: elle est annulee et disparait du contrat, mais le reste du contrat demeure valable.</t>
+          <t>Il s'agit d'un conflit d'intérêt (ou conflit d'objectifs) basé sur la répartition d'une ressource rare (la commission sur la vente). Résolution : Le manager doit recourir à l'arbitrage (imposer une règle de répartition, par exemple en fonction du secteur géographique de chacun) ou à la médiation (les réunir pour qu'ils trouvent un compromis ensemble, comme se partager la commission s'ils travaillent en binôme).</t>
         </is>
       </c>
       <c r="M259" t="n">
-        <v>275</v>
+        <v>260</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>pdf-droit-t05-009</t>
+          <t>T1-09</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>terminale</t>
+          <t>premiere</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>droit</t>
+          <t>sciences de gestion</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Theme 5 : Quel est le role du contrat '</t>
+          <t>Thème 1 : De l'individu à l'acteur</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Niveau 3 : Entrainement type Bac - Exercice 9</t>
+          <t>Conditions de travail</t>
         </is>
       </c>
       <c r="F260" t="n">
@@ -17785,57 +17786,60 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Mise en situation: M. Dupont a fait appel a lartisan couvreur M. Renard pour refaire sa t</t>
+          <t>Cas d'entreprise "TechSolutions"</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>Exercice source PDF (droit terminale).</t>
+          <t>Cette entreprise de services informatiques subit une baisse de productivité de 15% depuis six mois. Les arrêts maladie ont doublé. Les salariés se plaignent d'objectifs inatteignables et de l'absence de reconnaissance de leur hiérarchie.</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>Mise en situation: M. Dupont a fait appel a lartisan couvreur M. Renard pour refaire sa toiture. Les travaux presentent de graves defauts provoquant des fuites. Redigez une argumentation juridique (Faits, Probleme de droit, Regles applicables, Solution) pour conseiller M. Dupont sur la resolution du contrat et la mise en jeu de la responsabilite.</t>
+          <t>À l'aide de vos connaissances, montrez comment les conditions de travail influencent le comportement des acteurs et la performance de l'organisation.</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>droit | Theme 5 : Quel est le role du contrat ' | Niveau 3 : Entrainement type Bac</t>
+          <t>conditions de travail | absentéisme | performance | reconnaissance</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>Faits: Un client a fait realiser des travaux de toiture par un artisan. Des malfacons sont apparues, entrainant des infiltrations deau. Probleme de droit: De quels recours dispose le creancier face a linexecution dune obligation de resultat de la part de son cocontractant ' Regles de droit: Le contrat tient lieu de loi a ceux qui lont valablement forme. Lentrepreneur est tenu a une obligation de resultat. En cas dinexecution, le creancier peut, apres mise en demeure, demander la resolution du contrat (son aneantissement) et engager la responsabilite contractuelle du debiteur pour obtenir des dommages et interets si linexecution lui cause un prejudice. Solution: M. Dupont doit mettre M. Renard en demeure de reparer. Sil refuse, M. Dupont pourra saisir le juge pour demander la resolution du contrat et lindemnisation de son prejudice materiel et de jouissance.</t>
+          <t>Identification du problème : Dégradation du climat social chez TechSolutions (absentéisme, baisse de productivité) liée à de mauvaises conditions de travail psychosociales (stress, manque de reconnaissance).
+Lien Conditions de travail / Comportement : Les individus réagissent à leur environnement. Des objectifs irréalistes génèrent du stress (charge mentale). L'absence de reconnaissance touche l'estime de soi et réduit la motivation au travail. Le comportement se modifie : désengagement, absentéisme (maladie).
+Impact sur l'organisation : L'organisation est une action collective. Si les acteurs se désengagent, le collectif s'effrite. Les coûts cachés explosent (remplacement des malades, retards), ce qui détruit la performance globale de "TechSolutions" (chute de la productivité de 15%).
+Conclusion : L'activité humaine est une ressource à préserver. La direction doit impérativement revoir ses modes d'évaluation, fixer des objectifs concertés (méthode participative) et instaurer des gratifications (financières ou symboliques) pour restaurer la motivation.</t>
         </is>
       </c>
       <c r="M260" t="n">
-        <v>325</v>
+        <v>350</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>pdf-droit-t05-010</t>
+          <t>T1-10</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>terminale</t>
+          <t>premiere</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>droit</t>
+          <t>sciences de gestion</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Theme 5 : Quel est le role du contrat '</t>
+          <t>Thème 1 : De l'individu à l'acteur</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Niveau 3 : Entrainement type Bac - Exercice 10</t>
+          <t>L'individu et le groupe</t>
         </is>
       </c>
       <c r="F261" t="n">
@@ -17846,362 +17850,362 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Developpement structure: Dans quelle mesure le droit encadre-t-il la liberte contractue</t>
+          <t>Question de réflexion</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>Exercice source PDF (droit terminale).</t>
+          <t>Général</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>Developpement structure: Dans quelle mesure le droit encadre-t-il la liberte contractuelle pour proteger le consommateur '</t>
+          <t>L'intégration de la personnalité et des émotions des salariés dans la gestion des ressources humaines est-elle un atout ou une contrainte pour l'organisation ?</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>droit | Theme 5 : Quel est le role du contrat ' | Niveau 3 : Entrainement type Bac</t>
+          <t>personnalité | émotions | atout | contrainte | intelligence émotionnelle</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>Le principe fondateur du droit des contrats est la liberte contractuelle (liberte de choisir son cocontractant, le contenu et la forme du contrat). Cependant, dans les relations BtoC (professionnel a consommateur), cette liberte genere une asymetrie de pouvoir. Le droit encadre donc strictement la phase de formation (obligation lourde dinformation et de conseil, interdiction des pratiques trompeuses) et dexecution (droit de retractation accordant un droit de repentir, traque des clauses abusives). Cet encadrement, issu de lordre public de protection, est imperatif: le professionnel ne peut y deroger, limitant ainsi sa propre liberte pour reequilibrer la relation contractuelle.</t>
+          <t>C'est à la fois une contrainte (car gérer des individus complexes, avec leurs sautes d'humeur et leurs sensibilités demande du temps, des compétences managériales fortes et expose l'organisation à des conflits interpersonnels chronophages) et un atout majeur (car l'enthousiasme, l'empathie, ou le trait de personnalité "créatif" d'un individu sont des moteurs d'innovation et de cohésion). Un manager qui sait mobiliser l'intelligence émotionnelle de ses équipes obtiendra un engagement bien supérieur à une gestion purement comptable et tayloriste des ressources humaines.</t>
         </is>
       </c>
       <c r="M261" t="n">
-        <v>325</v>
+        <v>350</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>pdf-droit-t06-001</t>
+          <t>T2-01</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>terminale</t>
+          <t>premiere</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>droit</t>
+          <t>sciences de gestion</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Theme 6 : Quest-ce quetre responsable '</t>
+          <t>Thème 2 : Numérique et intelligence collective</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Niveau 1 : Maitrise des concepts - Exercice 1</t>
+          <t>L'information ressource</t>
         </is>
       </c>
       <c r="F262" t="n">
         <v>1</v>
       </c>
       <c r="G262" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Expliquer la difference de finalite entre la responsabilite civile et la responsabilite pe</t>
+          <t>Donnée, Information, Connaissance</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>Exercice source PDF (droit terminale).</t>
+          <t>Général</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>Expliquer la difference de finalite entre la responsabilite civile et la responsabilite penale.</t>
+          <t>Définir et distinguer : Donnée, Information, Connaissance.</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>droit | Theme 6 : Quest-ce quetre responsable ' | Niveau 1 : Maitrise des concepts</t>
+          <t>donnée | information | connaissance | traitement</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>La responsabilite penale a pour but de proteger la societe en sanctionnant et punissant (amende, prison) lauteur dune infraction (contravention, delit, crime). La responsabilite civile, en revanche, a une fonction reparatrice: son but exclusif est de remettre 3 la victime dans letat ou elle se trouvait avant le dommage, via le versement de dommagesinterets, sans finalite punitive.</t>
+          <t>Donnée : Un élément brut, un chiffre, un fait sans contexte (ex: "39"). Information : Une donnée traitée et replacée dans son contexte qui prend du sens (ex: "Le patient a 39°C de fièvre"). Connaissance : L'appropriation de l'information par un individu, combinée à son expérience, permettant de prendre une décision ou d'agir (ex: "Le médecin sait que 39°C indique une infection et prescrit un traitement").</t>
         </is>
       </c>
       <c r="M262" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>pdf-droit-t06-002</t>
+          <t>T2-02</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>terminale</t>
+          <t>premiere</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>droit</t>
+          <t>sciences de gestion</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Theme 6 : Quest-ce quetre responsable '</t>
+          <t>Thème 2 : Numérique et intelligence collective</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Niveau 1 : Maitrise des concepts - Exercice 2</t>
+          <t>L'information ressource</t>
         </is>
       </c>
       <c r="F263" t="n">
         <v>2</v>
       </c>
       <c r="G263" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Quels sont les trois elements cumulatifs a prouver pour engager la responsabilite extrac</t>
+          <t>Données à caractère personnel</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>Exercice source PDF (droit terminale).</t>
+          <t>Général</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>Quels sont les trois elements cumulatifs a prouver pour engager la responsabilite extracontractuelle '</t>
+          <t>Qu'est-ce qu'une donnée à caractère personnel et quel texte la protège en Europe ?</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t>droit | Theme 6 : Quest-ce quetre responsable ' | Niveau 1 : Maitrise des concepts</t>
+          <t>donnée personnelle | RGPD | protection | confidentialité</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>Pour que la responsabilite extracontractuelle soit engagee, la victime doit prouver la reunion de trois elements: 1) Un fait generateur (une faute, le fait dune chose, ou le fait dautrui). 2) Un dommage (materiel, corporel ou moral). 3) Un lien de causalite direct et certain entre le fait generateur et le dommage subi.</t>
+          <t>C'est toute information se rapportant à une personne physique identifiée ou identifiable (nom, photo, adresse IP, numéro de sécurité sociale). En Europe, ces données sont protégées par le RGPD (Règlement Général sur la Protection des Données), qui impose aux organisations d'obtenir le consentement, de sécuriser les données et de garantir le droit à l'oubli.</t>
         </is>
       </c>
       <c r="M263" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>pdf-droit-t06-003</t>
+          <t>T2-03</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>terminale</t>
+          <t>premiere</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>droit</t>
+          <t>sciences de gestion</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Theme 6 : Quest-ce quetre responsable '</t>
+          <t>Thème 2 : Numérique et intelligence collective</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Niveau 1 : Maitrise des concepts - Exercice 3</t>
+          <t>Système d'information</t>
         </is>
       </c>
       <c r="F264" t="n">
         <v>3</v>
       </c>
       <c r="G264" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Citer les trois caracteristiques quun dommage doit presenter pour etre juridiquement rep</t>
+          <t>Système d'information (PGI/ERP)</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>Exercice source PDF (droit terminale).</t>
+          <t>Général</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>Citer les trois caracteristiques quun dommage doit presenter pour etre juridiquement reparable.</t>
+          <t>Expliquer ce qu'est un PGI (Progiciel de Gestion Intégré) ou ERP.</t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t>droit | Theme 6 : Quest-ce quetre responsable ' | Niveau 1 : Maitrise des concepts</t>
+          <t>PGI | ERP | base de données | unicité</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>Un dommage reparable doit etre personnel (la personne qui agit doit avoir subi elle-meme le prejudice), direct (decouler directement du fait generateur) et certain (il ne doit pas etre hypothetique, bien quun prejudice futur mais ineluctable puisse etre admis). Il doit egalement porter atteinte a un interet legitime.</t>
+          <t>Un PGI est un système informatique unique (une grande base de données centralisée) qui permet de gérer l'ensemble des processus opérationnels d'une entreprise (ressources humaines, comptabilité, ventes, stocks). Il garantit l'unicité de l'information : une donnée saisie une fois met à jour tous les modules en temps réel.</t>
         </is>
       </c>
       <c r="M264" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>pdf-droit-t06-004</t>
+          <t>T2-04</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>terminale</t>
+          <t>premiere</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>droit</t>
+          <t>sciences de gestion</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Theme 6 : Quest-ce quetre responsable '</t>
+          <t>Thème 2 : Numérique et intelligence collective</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Niveau 1 : Maitrise des concepts - Exercice 4</t>
+          <t>Le travail collaboratif</t>
         </is>
       </c>
       <c r="F265" t="n">
         <v>4</v>
       </c>
       <c r="G265" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>Definir les trois causes dexoneration de la responsabilite (force majeure, fait dun tiers,</t>
+          <t>Intelligence collective</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>Exercice source PDF (droit terminale).</t>
+          <t>Général</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>Definir les trois causes dexoneration de la responsabilite (force majeure, fait dun tiers, faute de la victime).</t>
+          <t>Que signifie l'expression "Intelligence Collective" ?</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t>droit | Theme 6 : Quest-ce quetre responsable ' | Niveau 1 : Maitrise des concepts</t>
+          <t>intelligence collective | collaboration | synergie | numérique</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>Ce sont des causes etrangeres permettant au defendeur de sexonerer. La force majeure est un evenement imprevisible, irresistible et exterieur. Le fait dun tiers est lintervention exclusive dune personne exterieure ayant provoque le dommage. La faute de la victime est le comportement fautif de la personne ayant subi le dommage, qui a concouru a sa propre realisation (exoneration partielle ou totale si elle presente les caracteres de la force majeure).</t>
+          <t>C'est la capacité d'un groupe d'individus à résoudre des problèmes complexes et à innover, grâce à la collaboration, au partage des connaissances et aux interactions, souvent facilitées par les outils numériques. Le résultat du groupe est supérieur à la simple somme des intelligences individuelles (1+1=3).</t>
         </is>
       </c>
       <c r="M265" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>pdf-droit-t06-005</t>
+          <t>T2-05</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>terminale</t>
+          <t>premiere</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>droit</t>
+          <t>sciences de gestion</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Theme 6 : Quest-ce quetre responsable '</t>
+          <t>Thème 2 : Numérique et intelligence collective</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Niveau 1 : Maitrise des concepts - Exercice 5</t>
+          <t>Le travail collaboratif</t>
         </is>
       </c>
       <c r="F266" t="n">
         <v>5</v>
       </c>
       <c r="G266" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>Quest-ce que le prejudice ecologique '</t>
+          <t>Cloud Computing</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>Exercice source PDF (droit terminale).</t>
+          <t>Général</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>Quest-ce que le prejudice ecologique '</t>
+          <t>Définir le "Cloud Computing" (l'informatique en nuage).</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>droit | Theme 6 : Quest-ce quetre responsable ' | Niveau 1 : Maitrise des concepts</t>
+          <t>cloud computing | serveurs | partage | externalisation</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>Le prejudice ecologique est une atteinte non negligeable aux elements ou aux fonctions des ecosystemes ou aux benefices collectifs tires par lhomme de lenvironnement (ex: maree noire, pollution dune riviere). Cest un prejudice objectif, distinct du prejudice personnel des individus, qui vise a reparer latteinte a la nature elle-meme.</t>
+          <t>C'est un modèle informatique permettant un accès via Internet (à la demande) à un ensemble partagé de ressources informatiques (serveurs, stockage, applications) hébergées sur des serveurs distants (data centers), plutôt que sur le disque dur local de l'utilisateur.</t>
         </is>
       </c>
       <c r="M266" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>pdf-droit-t06-006</t>
+          <t>T2-06</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>terminale</t>
+          <t>premiere</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>droit</t>
+          <t>sciences de gestion</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Theme 6 : Quest-ce quetre responsable '</t>
+          <t>Thème 2 : Numérique et intelligence collective</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Niveau 2 : Application et analyse - Exercice 6</t>
+          <t>L'information ressource</t>
         </is>
       </c>
       <c r="F267" t="n">
@@ -18212,57 +18216,57 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>Cas pratique: Mme Garcia se blesse gravement en glissant sur un sol mouille non signale d</t>
+          <t>Transformation de l'information</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>Exercice source PDF (droit terminale).</t>
+          <t>La boutique en ligne "SneakPeak" enregistre que 45% des visiteurs cliquent sur un modèle précis de baskets rouges, mais que seulement 2% l'achètent. Le gestionnaire décide alors de baisser le prix de ce modèle de 10%.</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>Cas pratique: Mme Garcia se blesse gravement en glissant sur un sol mouille non signale dans les allees du supermarche SuperPrix. Identifiez le regime de responsabilite applicable et les conditions de sa mise en uvre.</t>
+          <t>Retracez le passage de la donnée à l'action.</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t>droit | Theme 6 : Quest-ce quetre responsable ' | Niveau 2 : Application et analyse</t>
+          <t>donnée brute | analyse | décision | conversion</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>Il sagit de la responsabilite extracontractuelle du fait des choses. Les conditions sont: lintervention dune chose (le sol mouille) qui a ete linstrument du dommage, et lidentification du gardien de la chose, cest-a-dire celui qui en a lusage, la direction et le controle (ici, la direction du supermarche SuperPrix). La faute du gardien na pas a etre prouvee (responsabilite de plein droit).</t>
+          <t>Données brutes : Nombre de clics, nombre d'achats. Information : Taux d'abandon panier extrêmement élevé sur le modèle de baskets rouges. Connaissance/Analyse : Le gestionnaire comprend (grâce à son expérience du marché) que le produit attire (bon design) mais que le prix constitue un frein à l'achat. Action : Prise de décision de gestion : baisse stratégique du prix de 10% pour convertir l'intérêt en ventes.</t>
         </is>
       </c>
       <c r="M267" t="n">
-        <v>275</v>
+        <v>260</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>pdf-droit-t06-007</t>
+          <t>T2-07</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>terminale</t>
+          <t>premiere</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>droit</t>
+          <t>sciences de gestion</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Theme 6 : Quest-ce quetre responsable '</t>
+          <t>Thème 2 : Numérique et intelligence collective</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Niveau 2 : Application et analyse - Exercice 7</t>
+          <t>Système d'information</t>
         </is>
       </c>
       <c r="F268" t="n">
@@ -18273,57 +18277,57 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Cas pratique: Le telephone portable neuf de M. Leroy explose spontanement dans sa poche,</t>
+          <t>Automatisation et processus</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>Exercice source PDF (droit terminale).</t>
+          <t>Chez le fabricant "MecaPro", la validation d'une commande client prenait 3 jours (transferts papier entre commercial, stock et compta). L'implantation d'un PGI a automatisé ce processus.</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>Cas pratique: Le telephone portable neuf de M. Leroy explose spontanement dans sa poche, le blessant a la jambe. Quel regime special dindemnisation sapplique ici ' Justifiez.</t>
+          <t>Quels sont les effets immédiats de cette automatisation ?</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>droit | Theme 6 : Quest-ce quetre responsable ' | Niveau 2 : Application et analyse</t>
+          <t>automatisation | processus | PGI | agilité | rigidité</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>Le regime special de la responsabilite du fait des produits defectueux sapplique. Il protege les consommateurs contre les dommages causes par un defaut de securite dun produit mis en circulation. Le fabricant est responsable de plein droit des blessures causees par lexplosion anormale de la batterie de son telephone.</t>
+          <t>L'automatisation fluidifie le processus. Les effets sont : gain de temps considérable (de 3 jours à quelques secondes), réduction des erreurs de saisie (plus de recopies manuelles), diminution des coûts administratifs, et agilité accrue (la production peut démarrer immédiatement après le clic du commercial). Cependant, le rôle des employés administratifs est rigidifié par la procédure imposée par le logiciel.</t>
         </is>
       </c>
       <c r="M268" t="n">
-        <v>275</v>
+        <v>260</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>pdf-droit-t06-008</t>
+          <t>T2-08</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>terminale</t>
+          <t>premiere</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>droit</t>
+          <t>sciences de gestion</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Theme 6 : Quest-ce quetre responsable '</t>
+          <t>Thème 2 : Numérique et intelligence collective</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Niveau 2 : Application et analyse - Exercice 8</t>
+          <t>L'information ressource</t>
         </is>
       </c>
       <c r="F269" t="n">
@@ -18334,57 +18338,57 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>Mecanisme dassurance: Expliquez comment lassurance permet de socialiser et de mutualise</t>
+          <t>Cas RGPD</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>Exercice source PDF (droit terminale).</t>
+          <t>L'application mobile "FitRun" géolocalise ses utilisateurs 24h/24 pour "améliorer le service", et revend ces historiques de déplacements à des sociétés publicitaires sans en informer clairement les utilisateurs.</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>Mecanisme dassurance: Expliquez comment lassurance permet de socialiser et de mutualiser la reparation des dommages.</t>
+          <t>Identifiez les failles juridiques et éthiques.</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t>droit | Theme 6 : Quest-ce quetre responsable ' | Niveau 2 : Application et analyse</t>
+          <t>RGPD | consentement | transparence | sanction</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>Lassurance repose sur la mutualisation des risques. Chaque assure verse une prime reguliere a lassureur. Ce fonds commun permet dindemniser la minorite dassures 4 qui subissent ou causent un dommage. Ainsi, le poids financier de la reparation (parfois tres lourd) nest plus supporte par un seul individu responsable, mais socialise et reparti sur lensemble de la communaute des assures.</t>
+          <t>L'entreprise enfreint le RGPD sur plusieurs points : défaut de consentement explicite et éclairé pour la revente, manque de transparence (finalité cachée), et non-respect du principe de minimisation (géolocaliser 24h/24 n'est pas nécessaire pour une simple application de course à pied). Le risque est une lourde sanction financière par la CNIL et une destruction de la réputation de l'entreprise (perte de confiance client).</t>
         </is>
       </c>
       <c r="M269" t="n">
-        <v>275</v>
+        <v>260</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>pdf-droit-t06-009</t>
+          <t>T2-09</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>terminale</t>
+          <t>premiere</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>droit</t>
+          <t>sciences de gestion</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Theme 6 : Quest-ce quetre responsable '</t>
+          <t>Thème 2 : Numérique et intelligence collective</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Niveau 3 : Entrainement type Bac - Exercice 9</t>
+          <t>Le travail collaboratif</t>
         </is>
       </c>
       <c r="F270" t="n">
@@ -18395,57 +18399,59 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>Mise en situation: Lors dune livraison, M. Jules, salarie de lentreprise de transport Li-</t>
+          <t>Cas d'entreprise "ArchiConcept"</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>Exercice source PDF (droit terminale).</t>
+          <t>Ce cabinet d'architectes réunit 50 collaborateurs répartis sur 3 sites. Pour améliorer la coordination, la direction impose un Réseau Social d'Entreprise (RSE) et le basculement de tous les dossiers sur le Cloud. Un an plus tard, on constate une accélération des projets, mais certains architectes seniors se plaignent d'une surcharge d'informations, d'un contrôle permanent et refusent d'utiliser la plateforme.</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>Mise en situation: Lors dune livraison, M. Jules, salarie de lentreprise de transport LivraisonExpress, abime le portail du client M. Fabre avec la camionnette de la societe. En vous appuyant sur le syllogisme juridique, demontrez qui devra reparer le prejudice subi par le client (fait dautrui).</t>
+          <t>À partir de ce constat, analysez si le numérique crée de l'agilité ou de la rigidité organisationnelle.</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t>droit | Theme 6 : Quest-ce quetre responsable ' | Niveau 3 : Entrainement type Bac</t>
+          <t>agilité | rigidité | RSE | infobésité | résistance au changement</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>Faits: Un salarie endommage un bien appartenant a un tiers pendant lexecution de son travail. Majeure (Regle): Larticle 1242 du Code civil prevoit que lon est responsable non seulement du dommage que lon cause par son propre fait, mais encore de celui qui est cause par le fait des personnes dont on doit repondre. Ainsi, les commettants sont civilement responsables des dommages causes par leurs preposes dans les fonctions auxquelles ils les ont employes. Mineure (Application): En lespece, M. Jules est le prepose (salarie) de la societe LivraisonExpress (commettant). Il a commis une faute dommageable dans le cadre de ses fonctions de livreur. Conclusion: Cest la societe LivraisonExpress (le commettant) qui est civilement responsable et qui devra indemniser M. Fabre, souvent via son assurance professionnelle.</t>
+          <t>L'agilité créée par le numérique : L'usage du Cloud et du RSE chez "ArchiConcept" dématérialise les frontières physiques. Le partage d'information en temps réel permet le travail collaboratif à distance, accélérant le processus de conception des projets. L'entreprise devient agile, capable de réagir rapidement aux demandes clients grâce à l'intelligence collective mobilisée sur le RSE.
+La rigidité et les risques générés : Cependant, l'outil impose sa propre logique. L'hyper-connexion génère une surcharge cognitive (infobésité) pour les salariés. Le partage total peut être perçu comme un outil de flicage et de contrôle managérial permanent (rigidité sociale). De plus, l'exclusion numérique (fracture numérique) de certains seniors montre que la technologie seule ne suffit pas : sans accompagnement humain ni formation, l'outil se heurte à des résistances au changement qui bloquent le fonctionnement de l'organisation.
+Conclusion : Le numérique est un paradoxe : il fluidifie les processus techniques (agilité) mais peut rigidifier les relations humaines et le cadre de travail s'il est imposé de manière technocentrée sans prendre en compte la sociologie des acteurs.</t>
         </is>
       </c>
       <c r="M270" t="n">
-        <v>325</v>
+        <v>350</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>pdf-droit-t06-010</t>
+          <t>T2-10</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>terminale</t>
+          <t>premiere</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>droit</t>
+          <t>sciences de gestion</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Theme 6 : Quest-ce quetre responsable '</t>
+          <t>Thème 2 : Numérique et intelligence collective</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Niveau 3 : Entrainement type Bac - Exercice 10</t>
+          <t>L'information ressource</t>
         </is>
       </c>
       <c r="F271" t="n">
@@ -18456,362 +18462,362 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>Developpement structure: Levolution des differents regimes de responsabilite civile offre</t>
+          <t>Question de réflexion (Open Data)</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>Exercice source PDF (droit terminale).</t>
+          <t>Général</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>Developpement structure: Levolution des differents regimes de responsabilite civile offre-t-elle toujours une indemnisation systematique aux victimes '</t>
+          <t>En quoi l'ouverture des données (Open Data) constitue-t-elle une opportunité de création de valeur économique et sociétale ?</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t>droit | Theme 6 : Quest-ce quetre responsable ' | Niveau 3 : Entrainement type Bac</t>
+          <t>open data | valeur économique | valeur sociétale | transparence</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>Levolution du droit tend effectivement vers une amelioration de lindemnisation des victimes, passant dune logique de faute a une logique de reparation et dobjectivation (developpement de la responsabilite de plein droit, regimes speciaux tres protecteurs comme la loi Badinter sur les accidents de la circulation). Cependant, lindemnisation nest pas systematique. La victime doit toujours prouver le lien de causalite et letendue de son dommage. De plus, le defendeur conserve des moyens de sexonerer de sa responsabilite sil prouve une cause etrangere (force majeure, faute exclusive de la victime), ce qui peut priver cette derniere de toute indemnisation.</t>
+          <t>L'Open Data (mise à disposition gratuite et libre de droits de grandes bases de données publiques, comme les horaires de transport ou les données météorologiques) est une matière première. Sur le plan économique, des startups utilisent ces données pour créer des applications innovantes à forte valeur ajoutée (ex: Citymapper pour les trajets, applications agricoles d'optimisation des semis selon la météo). Sur le plan sociétal, l'Open Data améliore la transparence de l'action publique et permet aux citoyens d'être mieux informés et de collaborer, générant ainsi une intelligence collective à l'échelle de la nation.</t>
         </is>
       </c>
       <c r="M271" t="n">
-        <v>325</v>
+        <v>350</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>pdf-droit-t07-001</t>
+          <t>T3-01</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>terminale</t>
+          <t>premiere</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>droit</t>
+          <t>sciences de gestion</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Theme 7 : Comment le droit encadre-t-il le travail salarie '</t>
+          <t>Thème 3 : Création de valeur et performance</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Niveau 1 : Maitrise des concepts - Exercice 1</t>
+          <t>La performance</t>
         </is>
       </c>
       <c r="F272" t="n">
         <v>1</v>
       </c>
       <c r="G272" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>Definir le contrat de travail a laide de ses trois elements constitutifs, en insistant sur</t>
+          <t>Efficacité et efficience</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>Exercice source PDF (droit terminale).</t>
+          <t>Général</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>Definir le contrat de travail a laide de ses trois elements constitutifs, en insistant sur le lien de subordination.</t>
+          <t>Différencier l'efficacité de l'efficience au sein d'une organisation.</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t>droit | Theme 7 : Comment le droit encadre-t-il le travail salarie ' | Niveau 1 : Maitrise des concepts</t>
+          <t>efficacité | efficience | ressources | objectifs</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>Le contrat de travail est caracterise par trois elements: 1) Une prestation de travail (tache a accomplir). 2) Une remuneration (le salaire). 3) Le lien de subordination juridique, qui est lelement determinant. Il se caracterise par le pouvoir de lemployeur de donner des ordres et des directives, den controler lexecution et de sanctionner les manquements de son subordonne.</t>
+          <t>L'efficacité est la capacité d'une organisation à atteindre l'objectif qu'elle s'est fixé (ex: produire 1000 voitures). L'efficience est la capacité à atteindre cet objectif en minimisant les ressources utilisées (ex: produire 1000 voitures en réduisant la consommation d'énergie et le temps de travail de 20%). L'efficience intègre donc la notion de coût et de rationalité.</t>
         </is>
       </c>
       <c r="M272" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>pdf-droit-t07-002</t>
+          <t>T3-02</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>terminale</t>
+          <t>premiere</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>droit</t>
+          <t>sciences de gestion</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Theme 7 : Comment le droit encadre-t-il le travail salarie '</t>
+          <t>Thème 3 : Création de valeur et performance</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Niveau 1 : Maitrise des concepts - Exercice 2</t>
+          <t>La création de valeur</t>
         </is>
       </c>
       <c r="F273" t="n">
         <v>2</v>
       </c>
       <c r="G273" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>Quelles sont les differences fondamentales entre un contrat de travail et un contrat den-</t>
+          <t>Valeur Ajoutée (VA)</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>Exercice source PDF (droit terminale).</t>
+          <t>Général</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>Quelles sont les differences fondamentales entre un contrat de travail et un contrat dentreprise (prestation de services) '</t>
+          <t>Qu'est-ce que la Valeur Ajoutée (VA) et comment la calcule-t-on de manière simplifiée ?</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t>droit | Theme 7 : Comment le droit encadre-t-il le travail salarie ' | Niveau 1 : Maitrise des concepts</t>
+          <t>valeur ajoutée | chiffre d'affaires | consommations intermédiaires | richesse</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>La distinction majeure reside dans le lien de subordination juridique present dans le contrat de travail, qui place le salarie sous lautorite de lemployeur. Dans un contrat dentreprise, le prestataire de services (un travailleur independant) conserve une totale independance dans lorganisation de son travail et les moyens mis en uvre pour atteindre le resultat demande par son client.</t>
+          <t>La valeur ajoutée mesure la véritable richesse créée par l'activité de l'entreprise elle-même. Elle se calcule par la différence entre le Chiffre d'Affaires (CA) et les Consommations Intermédiaires (CI, biens et services détruits ou transformés pendant le processus). Formule : VA = CA - CI.</t>
         </is>
       </c>
       <c r="M273" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>pdf-droit-t07-003</t>
+          <t>T3-03</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>terminale</t>
+          <t>premiere</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>droit</t>
+          <t>sciences de gestion</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Theme 7 : Comment le droit encadre-t-il le travail salarie '</t>
+          <t>Thème 3 : Création de valeur et performance</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Niveau 1 : Maitrise des concepts - Exercice 3</t>
+          <t>La création de valeur</t>
         </is>
       </c>
       <c r="F274" t="n">
         <v>3</v>
       </c>
       <c r="G274" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Lister les differents pouvoirs reconnus a lemployeur.</t>
+          <t>Valeur perçue</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>Exercice source PDF (droit terminale).</t>
+          <t>Général</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>Lister les differents pouvoirs reconnus a lemployeur.</t>
+          <t>Définir la "valeur perçue" par le client.</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t>droit | Theme 7 : Comment le droit encadre-t-il le travail salarie ' | Niveau 1 : Maitrise des concepts</t>
+          <t>valeur perçue | image de marque | notoriété | prix psychologique</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>Lemployeur detient trois grands pouvoirs issus de son droit de propriete et 5 du contrat: le pouvoir de direction (organiser le travail, fixer les objectifs et les methodes), le pouvoir reglementaire (edicter des regles generales et permanentes, notamment via le reglement interieur pour lhygiene, la securite et la discipline) et le pouvoir disciplinaire (droit de sanctionner une faute du salarie).</t>
+          <t>C'est la valeur subjective qu'un client attribue à un produit ou un service. Elle repose sur l'image de marque, la notoriété, la qualité ressentie et les recommandations sociales. C'est le prix maximum que le client est psychologiquement prêt à payer, qui peut être très supérieur au coût de fabrication réel (ex: les produits de luxe ou les smartphones haut de gamme).</t>
         </is>
       </c>
       <c r="M274" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>pdf-droit-t07-004</t>
+          <t>T3-04</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>terminale</t>
+          <t>premiere</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>droit</t>
+          <t>sciences de gestion</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Theme 7 : Comment le droit encadre-t-il le travail salarie '</t>
+          <t>Thème 3 : Création de valeur et performance</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Niveau 1 : Maitrise des concepts - Exercice 4</t>
+          <t>La performance</t>
         </is>
       </c>
       <c r="F275" t="n">
         <v>4</v>
       </c>
       <c r="G275" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Distinguer le licenciement pour motif personnel du licenciement pour motif economique.</t>
+          <t>Bilan Social</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>Exercice source PDF (droit terminale).</t>
+          <t>Général</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>Distinguer le licenciement pour motif personnel du licenciement pour motif economique.</t>
+          <t>Qu'est-ce qu'un "Bilan Social" et quelle performance permet-il de mesurer ?</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t>droit | Theme 7 : Comment le droit encadre-t-il le travail salarie ' | Niveau 1 : Maitrise des concepts</t>
+          <t>bilan social | performance sociale | conditions de travail | RH</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>Le licenciement pour motif personnel est inherent a la personne du salarie (ex: faute disciplinaire grave, incompetence, inaptitude physique). Le licenciement pour motif economique nest pas lie au salarie, mais resulte dune suppression ou transformation demploi causee par des difficultes economiques averees, des mutations technologiques ou la cessation dactivite de lentreprise.</t>
+          <t>Le bilan social est un document récapitulant les principales données chiffrées permettant d'apprécier la situation sociale d'une organisation (effectifs, rémunérations, accidents du travail, absentéisme, budget formation). Il permet de mesurer la performance sociale de l'entreprise vis-à-vis de ses salariés.</t>
         </is>
       </c>
       <c r="M275" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>pdf-droit-t07-005</t>
+          <t>T3-05</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>terminale</t>
+          <t>premiere</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>droit</t>
+          <t>sciences de gestion</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Theme 7 : Comment le droit encadre-t-il le travail salarie '</t>
+          <t>Thème 3 : Création de valeur et performance</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Niveau 1 : Maitrise des concepts - Exercice 5</t>
+          <t>La performance</t>
         </is>
       </c>
       <c r="F276" t="n">
         <v>5</v>
       </c>
       <c r="G276" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>Quest-ce quune convention collective et quel est son role vis-a-vis du Code du travail '</t>
+          <t>Performance globale</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>Exercice source PDF (droit terminale).</t>
+          <t>Général</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>Quest-ce quune convention collective et quel est son role vis-a-vis du Code du travail '</t>
+          <t>Quelles sont les composantes de la "Performance globale" d'une organisation ?</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t>droit | Theme 7 : Comment le droit encadre-t-il le travail salarie ' | Niveau 1 : Maitrise des concepts</t>
+          <t>performance globale | financière | commerciale | sociale | environnementale</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>Une convention collective est un accord ecrit negocie entre les syndicats de salaries et les organisations patronales dune branche dactivite (ex: Batiment, Restauration). Son role est dadapter les dispositions generales du Code du travail aux conditions particulieres de la profession. En principe, elle ne peut prevoir que des dispositions plus favorables aux salaries que la loi (principe de faveur), bien que des derogations existent aujourdhui.</t>
+          <t>Aujourd'hui, la performance ne se limite plus à la finance. La performance globale est un équilibre intégrant 4 dimensions : financière (rentabilité), commerciale (parts de marché), sociale (bien-être au travail) et environnementale (empreinte écologique réduite).</t>
         </is>
       </c>
       <c r="M276" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>pdf-droit-t07-006</t>
+          <t>T3-06</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>terminale</t>
+          <t>premiere</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>droit</t>
+          <t>sciences de gestion</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Theme 7 : Comment le droit encadre-t-il le travail salarie '</t>
+          <t>Thème 3 : Création de valeur et performance</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Niveau 2 : Application et analyse - Exercice 6</t>
+          <t>La création de valeur</t>
         </is>
       </c>
       <c r="F277" t="n">
@@ -18822,57 +18828,58 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>Cas pratique: M. Bernard, comptable chez ComptaPlus a Lyon, refuse detre mute a Paris alo</t>
+          <t>Calcul de Création de Valeur et Répartition</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>Exercice source PDF (droit terminale).</t>
+          <t>La boulangerie "PainDoré" a réalisé un Chiffre d'Affaires de 150 000 €. Pour cela, elle a acheté pour 40 000 € de farine, levure et électricité (Consommations Intermédiaires). Elle paie 50 000 € de salaires et charges, et verse 10 000 € d'impôts à l'État.</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>Cas pratique: M. Bernard, comptable chez ComptaPlus a Lyon, refuse detre mute a Paris alors que son contrat de travail contient une clause de mobilite. Analysez la situation et les consequences de son refus.</t>
+          <t>Calculez : a) La Valeur Ajoutée (VA) créée. b) La part de la VA (en %) redistribuée aux salariés.</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t>droit | Theme 7 : Comment le droit encadre-t-il le travail salarie ' | Niveau 2 : Application et analyse</t>
+          <t>valeur ajoutée | répartition | salariés | richesse</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>La clause de mobilite, si elle est indispensable aux interets de lentreprise et precise une zone geographique definie lors de la signature, est opposable au salarie. Le changement du lieu de travail dans cette zone nest quun changement des conditions de travail, que lemployeur peut imposer. Le refus de M. Bernard constitue donc un acte dinsubordination (une faute), justifiant un licenciement pour motif personnel disciplinaire.</t>
+          <t>a) Calcul de la Valeur Ajoutée (VA) : VA = CA - CI. VA = 150 000 - 40 000 = 110 000 €. La boulangerie a réellement créé 110 000 € de richesse.
+b) Part redistribuée aux salariés : (Salaires versés / Valeur Ajoutée) x 100. (50 000 / 110 000) x 100 ~ 45,45%. Les salariés captent environ 45,5% de la richesse créée. L'État en capte ~ 9% (10 000/110 000).</t>
         </is>
       </c>
       <c r="M277" t="n">
-        <v>275</v>
+        <v>260</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>pdf-droit-t07-007</t>
+          <t>T3-07</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>terminale</t>
+          <t>premiere</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>droit</t>
+          <t>sciences de gestion</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Theme 7 : Comment le droit encadre-t-il le travail salarie '</t>
+          <t>Thème 3 : Création de valeur et performance</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Niveau 2 : Application et analyse - Exercice 7</t>
+          <t>La performance</t>
         </is>
       </c>
       <c r="F278" t="n">
@@ -18883,57 +18890,57 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>Cas pratique: Le directeur de lentreprise WebDev lit systematiquement les e-mails ident</t>
+          <t>Calcul de Part de Marché et Performance Commerciale</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>Exercice source PDF (droit terminale).</t>
+          <t>Sur le marché local de la vente de vélos (estimé à 2 000 000 € de ventes totales), le magasin "CycloPlus" a réalisé un chiffre d'affaires de 500 000 €.</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>Cas pratique: Le directeur de lentreprise WebDev lit systematiquement les e-mails identifies comme Personnels envoyes par sa salariee Mme Petit depuis son ordinateur professionnel. Est-ce legal ' Expliquez la protection de la vie privee au travail.</t>
+          <t>Quel est son indicateur de performance commerciale principal ici ? Calculez-le.</t>
         </is>
       </c>
       <c r="K278" t="inlineStr">
         <is>
-          <t>droit | Theme 7 : Comment le droit encadre-t-il le travail salarie ' | Niveau 2 : Application et analyse</t>
+          <t>part de marché | chiffre d'affaires | concurrence | performance commerciale</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>Cette pratique est illegale. Bien que lemployeur puisse controler loutil informatique fourni a ses salaries, le salarie a droit au respect de sa vie privee meme au temps et au lieu de travail. Par consequent, les correspondances identifiees explicitement comme personnelles ou privees sont couvertes par le secret des correspondances. Lemployeur ne peut les ouvrir quen presence de la salariee ou apres lavoir dument appelee, sauf risque ou evenement exceptionnel pour lentreprise.</t>
+          <t>L'indicateur pertinent est la Part de Marché (en valeur). Formule : (CA de l'entreprise / CA total du marché) x 100. Calcul : (500 000 / 2 000 000) x 100 = 25%. "CycloPlus" détient 25% de part de marché, ce qui indique une très forte position concurrentielle sur son secteur.</t>
         </is>
       </c>
       <c r="M278" t="n">
-        <v>275</v>
+        <v>260</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>pdf-droit-t07-008</t>
+          <t>T3-08</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>terminale</t>
+          <t>premiere</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>droit</t>
+          <t>sciences de gestion</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Theme 7 : Comment le droit encadre-t-il le travail salarie '</t>
+          <t>Thème 3 : Création de valeur et performance</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Niveau 2 : Application et analyse - Exercice 8</t>
+          <t>La création de valeur</t>
         </is>
       </c>
       <c r="F279" t="n">
@@ -18944,57 +18951,57 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>Libertes collectives: Les salaries de lusine AutoParts decident darreter le travail pour</t>
+          <t>Marge et Rentabilité</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>Exercice source PDF (droit terminale).</t>
+          <t>L'entreprise "TechPhone" fabrique un téléphone dont le coût total de revient est de 200 €. Elle décide de le vendre au prix de 800 € grâce à une image de marque exceptionnelle.</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>Libertes collectives: Les salaries de lusine AutoParts decident darreter le travail pour reclamer une augmentation de salaire et bloquent totalement lacces a lusine. Qualifiez ce mouvement et verifiez sil respecte les conditions du droit de greve.</t>
+          <t>Identifiez la source de création de valeur et déduisez-en la marge unitaire.</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t>droit | Theme 7 : Comment le droit encadre-t-il le travail salarie ' | Niveau 2 : Application et analyse</t>
+          <t>valeur perçue | marge unitaire | profitabilité | prix</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>Larret de travail pour des revendications professionnelles (augmentation de salaire) est lexercice normal du droit de greve (liberte collective protegee par la Constitution). Cependant, le blocage total de lacces a lusine par des piquets de greve constitue une entrave a la liberte de travail des non-grevistes et de la direction. Ce comportement rend cette action illicite, ce qui peut justifier des sanctions disciplinaires (pour faute lourde) contre les auteurs des blocages.</t>
+          <t>La source de création de valeur repose entièrement sur la valeur perçue (image de marque, design, réputation) qui permet d'imposer un prix de vente très largement supérieur au coût de production. Marge unitaire = Prix de vente - Coût de revient = 800 - 200 = 600 € de marge brute par appareil, garantissant une immense performance financière (profitabilité).</t>
         </is>
       </c>
       <c r="M279" t="n">
-        <v>275</v>
+        <v>260</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>pdf-droit-t07-009</t>
+          <t>T3-09</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>terminale</t>
+          <t>premiere</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>droit</t>
+          <t>sciences de gestion</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Theme 7 : Comment le droit encadre-t-il le travail salarie '</t>
+          <t>Thème 3 : Création de valeur et performance</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Niveau 3 : Entrainement type Bac - Exercice 9</t>
+          <t>La performance</t>
         </is>
       </c>
       <c r="F280" t="n">
@@ -19005,57 +19012,59 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Mise en situation: Mme Y, secretaire medicale au cabinet SantePlus, est licenciee car ell</t>
+          <t>Cas d'entreprise "BioSaveurs"</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>Exercice source PDF (droit terminale).</t>
+          <t>Cette coopérative agricole produit des jus de fruits 100% bio. Récemment, la direction a investi lourdement dans des bouteilles en verre recyclé et consignables, ainsi que dans des salaires 15% au-dessus du SMIC pour ses ouvriers. Cependant, ses coûts de production ayant explosé, ses bénéfices nets (résultat financier) ont chuté de 30% cette année, inquiétant les banques.</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>Mise en situation: Mme Y, secretaire medicale au cabinet SantePlus, est licenciee car elle arrive systematiquement en retard depuis 3 mois malgre plusieurs avertissements. 6 Construisez largumentation juridique justifiant ce licenciement (cause reelle et serieuse, procedure).</t>
+          <t>À partir de ce cas, analysez comment les différentes dimensions de la performance peuvent être contradictoires.</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t>droit | Theme 7 : Comment le droit encadre-t-il le travail salarie ' | Niveau 3 : Entrainement type Bac</t>
+          <t>performance globale | contradiction | RSE | rentabilité | compromis</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>Pour etre valide, tout licenciement pour motif personnel doit reposer sur une cause reelle et serieuse. Reelle: les faits doivent etre objectifs, exacts et verifiables (ici, les retards systematiques depuis 3 mois sont tangibles, les avertissements prouvent lexactitude des faits). Serieuse: la faute commise doit rendre impossible la poursuite normale du contrat sans dommage pour lentreprise (ici, les retards repetes dune secretaire medicale desorganisent laccueil des patients et le fonctionnement du cabinet). Lemployeur est donc fonde a engager une procedure de licenciement disciplinaire (convocation, entretien prealable, lettre de notification motivee).</t>
+          <t>Analyse des performances par dimension : "BioSaveurs" excelle dans deux domaines. Performance sociale : en payant bien au-dessus du SMIC, elle fidélise et motive ses salariés. Performance environnementale : l'usage du verre consigné réduit drastiquement son empreinte écologique.
+La contradiction des performances : La recherche de l'efficience environnementale et sociale a un coût très élevé. L'achat de matériaux écologiques (verre vs plastique) et les hauts salaires augmentent les charges de l'entreprise. Conséquence : la marge se réduit et la performance financière s'effondre (-30% de bénéfices).
+Conclusion : Ce cas illustre le conflit d'intérêt entre les acteurs (les salariés et ONG écologiques sont satisfaits, mais les financeurs/banques sont inquiets). L'entreprise doit impérativement trouver un équilibre, par exemple en augmentant son prix de vente (en misant sur la valeur perçue du "produit éthique" par le consommateur) pour restaurer sa rentabilité financière sans renier ses engagements responsables. La performance globale est un compromis permanent.</t>
         </is>
       </c>
       <c r="M280" t="n">
-        <v>325</v>
+        <v>350</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>pdf-droit-t07-010</t>
+          <t>T3-10</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>terminale</t>
+          <t>premiere</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>droit</t>
+          <t>sciences de gestion</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Theme 7 : Comment le droit encadre-t-il le travail salarie '</t>
+          <t>Thème 3 : Création de valeur et performance</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Niveau 3 : Entrainement type Bac - Exercice 10</t>
+          <t>La création de valeur</t>
         </is>
       </c>
       <c r="F281" t="n">
@@ -19066,362 +19075,362 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>Developpement structure: Comment le droit du travail cherche-t-il a concilier le pouvoir</t>
+          <t>Question de réflexion (Valeur actionnariale)</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>Exercice source PDF (droit terminale).</t>
+          <t>Général</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>Developpement structure: Comment le droit du travail cherche-t-il a concilier le pouvoir de direction de lemployeur et le respect des libertes individuelles des salaries '</t>
+          <t>Pourquoi la maximisation de la seule valeur actionnariale (les dividendes) peut-elle menacer la pérennité de l'organisation à long terme ?</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
         <is>
-          <t>droit | Theme 7 : Comment le droit encadre-t-il le travail salarie ' | Niveau 3 : Entrainement type Bac</t>
+          <t>valeur actionnariale | dividendes | investissement | financiarisation | pérennité</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>Lemployeur est le proprietaire de lentreprise et doit pouvoir la diriger (imposer des horaires, des directives, controler lactivite). Cependant, le salarie ne renonce pas a ses droits fondamentaux en signant son contrat (liberte dexpression, vie privee, convictions religieuses). Pour concilier ces imperatifs, le droit du travail pose un principe de proportionnalite fondamental: Nul ne peut apporter aux droits des personnes et aux libertes individuelles et collectives de restrictions qui ne seraient pas justifiees par la nature de la tache a accomplir ni proportionnees au but recherche. Toute limitation imposee par lemployeur (ex: interdiction dutiliser son telephone personnel, code vestimentaire) doit donc repondre strictement a un imperatif de securite, dhygiene ou dimage lie au poste.</t>
+          <t>Si une entreprise répartit la quasi-totalité de sa valeur ajoutée sous forme de dividendes à ses actionnaires, elle s'appauvrit sur d'autres tableaux critiques. Elle ne conserve plus de marges d'autofinancement pour investir dans la Recherche &amp; Développement ou le numérique, perdant sa compétitivité future. De plus, au niveau social, bloquer les salaires pour verser des dividendes génère de la frustration, des grèves et la fuite des talents (turnover). À terme, cette vision court-termiste (financiarisation) détruit la valeur partenariale et sociale, condamnant l'entreprise au déclin.</t>
         </is>
       </c>
       <c r="M281" t="n">
-        <v>325</v>
+        <v>350</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>pdf-droit-t08-001</t>
+          <t>T4-01</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>terminale</t>
+          <t>premiere</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>droit</t>
+          <t>sciences de gestion</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Theme 8 : Dans quel cadre et comment entreprendre '</t>
+          <t>Thème 4 : Temps et risque</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Niveau 1 : Maitrise des concepts - Exercice 1</t>
+          <t>Le temps</t>
         </is>
       </c>
       <c r="F282" t="n">
         <v>1</v>
       </c>
       <c r="G282" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>Expliquer le principe de lunicite du patrimoine et son risque pour lentrepreneur individ</t>
+          <t>Temps et incertitude</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>Exercice source PDF (droit terminale).</t>
+          <t>Général</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>Expliquer le principe de lunicite du patrimoine et son risque pour lentrepreneur individuel.</t>
+          <t>Expliquer pourquoi le facteur "temps" est source d'incertitude pour le gestionnaire.</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t>droit | Theme 8 : Dans quel cadre et comment entreprendre ' | Niveau 1 : Maitrise des concepts</t>
+          <t>temps | incertitude | prévision | long terme</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>Historiquement, le principe de lunicite du patrimoine signifie quune personne juridique ne possede quun seul patrimoine, compose de lensemble de ses biens et de ses dettes, sans distinction entre sa vie personnelle et professionnelle. Le risque majeur pour lentrepreneur individuel classique etait quen cas de faillite de son activite, ses creanciers professionnels pouvaient saisir ses biens personnels (maison, epargne) pour se rembourser.</t>
+          <t>Plus la décision porte sur un horizon temporel éloigné (le long terme, ex: construire une usine pour dans 5 ans), plus il est difficile de prévoir avec certitude l'évolution de l'environnement (comportement des concurrents, ruptures technologiques, crises économiques). L'avenir étant par nature imprévisible, le décalage temporel génère un risque systématique.</t>
         </is>
       </c>
       <c r="M282" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>pdf-droit-t08-002</t>
+          <t>T4-02</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>terminale</t>
+          <t>premiere</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>droit</t>
+          <t>sciences de gestion</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Theme 8 : Dans quel cadre et comment entreprendre '</t>
+          <t>Thème 4 : Temps et risque</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Niveau 1 : Maitrise des concepts - Exercice 2</t>
+          <t>L'information et le risque</t>
         </is>
       </c>
       <c r="F283" t="n">
         <v>2</v>
       </c>
       <c r="G283" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Quest-ce que laffectio societatis dans le cadre dun contrat de societe '</t>
+          <t>Veille informationnelle</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>Exercice source PDF (droit terminale).</t>
+          <t>Général</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>Quest-ce que laffectio societatis dans le cadre dun contrat de societe '</t>
+          <t>Qu'est-ce qu'une "veille informationnelle" et à quoi sert-elle ?</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t>droit | Theme 8 : Dans quel cadre et comment entreprendre ' | Niveau 1 : Maitrise des concepts</t>
+          <t>veille informationnelle | anticipation | menaces | opportunités</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>Laffectio societatis est une notion jurisprudentielle qui designe la volonte commune des associes de collaborer activement, de facon volontaire et sur un pied degalite, a lexploitation de lentreprise et au succes du projet societaire. Cest lesprit dequipe indispensable a la qualification dun contrat de societe.</t>
+          <t>La veille est un processus de surveillance continue, systématique et organisée de l'environnement de l'entreprise (concurrentiel, technologique, juridique). Elle sert à capter les signaux faibles afin d'anticiper les menaces (nouveau concurrent) et de saisir les opportunités avant les autres, réduisant ainsi le risque lié à l'ignorance ou à l'obsolescence.</t>
         </is>
       </c>
       <c r="M283" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>pdf-droit-t08-003</t>
+          <t>T4-03</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>terminale</t>
+          <t>premiere</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>droit</t>
+          <t>sciences de gestion</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Theme 8 : Dans quel cadre et comment entreprendre '</t>
+          <t>Thème 4 : Temps et risque</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Niveau 1 : Maitrise des concepts - Exercice 3</t>
+          <t>Le risque</t>
         </is>
       </c>
       <c r="F284" t="n">
         <v>3</v>
       </c>
       <c r="G284" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Distinguer une entente illicite dun abus de position dominante.</t>
+          <t>Seuil de Rentabilité (SR)</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>Exercice source PDF (droit terminale).</t>
+          <t>Général</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>Distinguer une entente illicite dun abus de position dominante.</t>
+          <t>Définir la notion de Seuil de Rentabilité (SR) dans la gestion financière.</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t>droit | Theme 8 : Dans quel cadre et comment entreprendre ' | Niveau 1 : Maitrise des concepts</t>
+          <t>seuil de rentabilité | chiffre d'affaires | charges fixes | rentabilité</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>Une entente illicite (ou cartel) est un accord ou une concertation secrete entre plusieurs entreprises independantes visant a fausser la concurrence sur un marche (ex: fixation commune des prix, repartition des territoires). Labus de position dominante concerne une entreprise isolee qui profite de son pouvoir de marche ecrasant pour imposer des conditions deloyales, evincer ses concurrents ou empecher larrivee de nouveaux entrants.</t>
+          <t>Le seuil de rentabilité est le niveau de Chiffre d'Affaires qu'une entreprise doit impérativement atteindre pour couvrir l'intégralité de ses charges (fixes et variables). À ce niveau exact, le résultat de l'entreprise est nul (ni bénéfice, ni perte). C'est un indicateur de risque fondamental.</t>
         </is>
       </c>
       <c r="M284" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>pdf-droit-t08-004</t>
+          <t>T4-04</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>terminale</t>
+          <t>premiere</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>droit</t>
+          <t>sciences de gestion</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Theme 8 : Dans quel cadre et comment entreprendre '</t>
+          <t>Thème 4 : Temps et risque</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Niveau 1 : Maitrise des concepts - Exercice 4</t>
+          <t>Le risque</t>
         </is>
       </c>
       <c r="F285" t="n">
         <v>4</v>
       </c>
       <c r="G285" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>Identifier les obligations principales du franchiseur et du franchise dans un contrat de f</t>
+          <t>Facteurs de risques</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>Exercice source PDF (droit terminale).</t>
+          <t>Général</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>Identifier les obligations principales du franchiseur et du franchise dans un contrat de franchise.</t>
+          <t>Citer deux facteurs de risques externes et deux facteurs de risques internes pouvant frapper une organisation.</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t>droit | Theme 8 : Dans quel cadre et comment entreprendre ' | Niveau 1 : Maitrise des concepts</t>
+          <t>risques externes | risques internes | aléas | vulnérabilité</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>Le franchiseur est tenu de transmettre son savoir-faire secret et substantiel, 7 de mettre a disposition sa marque et son enseigne, et de fournir une assistance technique et commerciale continue. En contrepartie, le franchise a lobligation de payer un droit dentree et/ou des redevances (royalties), de respecter strictement le concept (cahier des charges) pour preserver limage du reseau, et de sapprovisionner parfois exclusivement aupres du franchiseur.</t>
+          <t>Externes : Rupture d'approvisionnement (crise géopolitique), rupture technologique (obsolescence subite du produit face à une innovation concurrente). Internes : Panne des machines (défaut de maintenance), grève du personnel (mauvais climat social).</t>
         </is>
       </c>
       <c r="M285" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>pdf-droit-t08-005</t>
+          <t>T4-05</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>terminale</t>
+          <t>premiere</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>droit</t>
+          <t>sciences de gestion</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Theme 8 : Dans quel cadre et comment entreprendre '</t>
+          <t>Thème 4 : Temps et risque</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Niveau 1 : Maitrise des concepts - Exercice 5</t>
+          <t>L'information et le risque</t>
         </is>
       </c>
       <c r="F286" t="n">
         <v>5</v>
       </c>
       <c r="G286" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Quelles sont les specificites dune societe cooperative (SCOP) par rapport a une societe co</t>
+          <t>Asymétrie d'information</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>Exercice source PDF (droit terminale).</t>
+          <t>Général</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>Quelles sont les specificites dune societe cooperative (SCOP) par rapport a une societe commerciale classique '</t>
+          <t>Qu'est-ce que l'asymétrie d'information au sein d'une organisation ?</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t>droit | Theme 8 : Dans quel cadre et comment entreprendre ' | Niveau 1 : Maitrise des concepts</t>
+          <t>asymétrie d'information | rétention | décision | communication</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>La SCOP se distingue par une finalite sociale et democratique. Les salaries sont les associes majoritaires (ils detiennent au moins 51% du capital). La prise de decision respecte le principe une personne = une voix, quel que soit le montant du capital detenu par lassocie. Enfin, une grande part des benefices est obligatoirement reinvestie dans lentreprise (reserves impartageables) ou redistribuee aux salaries, seloignant de la logique de profit pur pour les actionnaires.</t>
+          <t>L'asymétrie d'information intervient lorsqu'un acteur (ex: un manager de terrain) détient une information cruciale qu'il ne transmet pas à un autre acteur (ex: la direction générale). Cette rétention d'information (volontaire par pouvoir, ou involontaire par mauvaise communication) fausse la prise de décision globale qui se base alors sur des données erronées ou obsolètes.</t>
         </is>
       </c>
       <c r="M286" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>pdf-droit-t08-006</t>
+          <t>T4-06</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>terminale</t>
+          <t>premiere</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>droit</t>
+          <t>sciences de gestion</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Theme 8 : Dans quel cadre et comment entreprendre '</t>
+          <t>Thème 4 : Temps et risque</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Niveau 2 : Application et analyse - Exercice 6</t>
+          <t>Le risque</t>
         </is>
       </c>
       <c r="F287" t="n">
@@ -19432,57 +19441,60 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>Cas pratique: M. Durand, createur dune entreprise de menuiserie, souhaite proteger sa mai</t>
+          <t>Calcul du Seuil de Rentabilité</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>Exercice source PDF (droit terminale).</t>
+          <t>La start-up "EcoVelo" fabrique des bicyclettes électriques. Ses Charges Fixes (CF) annuelles (loyers de l'usine, salaires administratifs, assurances) s'élèvent à 100 000 €. Le Prix de Vente (PV) unitaire d'un vélo est de 800 €. Le Coût Variable (CV) unitaire pour fabriquer un vélo (pièces, main d'œuvre de fabrication) est de 300 €.</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>Cas pratique: M. Durand, createur dune entreprise de menuiserie, souhaite proteger sa maison personnelle en cas de faillite de son activite. Quels mecanismes juridiques ou choix de structure soffrent a lui '</t>
+          <t>Calculez : a) La Marge sur Coût Variable unitaire (MSCV unitaire). b) Le Taux de Marge sur Coût Variable (TMSCV). c) Le Seuil de Rentabilité en valeur (en €). d) Le Seuil de Rentabilité en volume (nombre de vélos à vendre).</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>droit | Theme 8 : Dans quel cadre et comment entreprendre ' | Niveau 2 : Application et analyse</t>
+          <t>MSCV | TMSCV | SR | seuil de rentabilité | volume</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>Plusieurs options juridiques sont possibles. Il peut opter pour la creation dune societe unipersonnelle (EURL ou SASU), ce qui cree une nouvelle personne morale (lentreprise) dotee de son propre patrimoine, limitant ainsi la responsabilite de M. Durand au montant de ses apports. Sil souhaite rester entrepreneur individuel, il beneficie desormais automatiquement du nouveau statut unique de lEI (depuis 2022) qui instaure une separation de plein droit entre le patrimoine professionnel (seul saisissable par les creanciers professionnels) et le patrimoine personnel, protegeant ainsi de fait sa maison.</t>
+          <t>a) MSCV unitaire : C'est la marge dégagée sur chaque vélo pour rembourser les charges fixes. MSCV = PV - CV. MSCV = 800 - 300 = 500 €. Chaque vélo vendu dégage 500 € nets.
+b) TMSCV : C'est le pourcentage que représente la marge par rapport au prix de vente. (MSCV / PV) x 100. (500 / 800) x 100 = 62,5%.
+c) Seuil de Rentabilité (SR) en valeur : Le CA à atteindre. Formule : CF / TMSCV. SR = 100 000 / 0,625 = 160 000 €. "EcoVelo" commencera à faire des bénéfices à partir de 160 000 € de chiffre d'affaires.
+d) Seuil de Rentabilité en volume : Le nombre d'unités à vendre. Formule : CF / MSCV unitaire (ou SR en € / Prix unitaire). 100 000 / 500 = 200 vélos. Il faut vendre exactement 200 vélos pour ne pas faire de perte.</t>
         </is>
       </c>
       <c r="M287" t="n">
-        <v>275</v>
+        <v>260</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>pdf-droit-t08-007</t>
+          <t>T4-07</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>terminale</t>
+          <t>premiere</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>droit</t>
+          <t>sciences de gestion</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Theme 8 : Dans quel cadre et comment entreprendre '</t>
+          <t>Thème 4 : Temps et risque</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Niveau 2 : Application et analyse - Exercice 7</t>
+          <t>Le temps</t>
         </is>
       </c>
       <c r="F288" t="n">
@@ -19493,57 +19505,57 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>Cas pratique: M. Blanc, ancien boulanger salarie chez La Bonne Miche, ouvre sa propre bou</t>
+          <t>Lien entre Temps et Valeur Financière</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>Exercice source PDF (droit terminale).</t>
+          <t>L'entreprise "DecoPro" a facturé des travaux pour 50 000 €. Le client ne paiera que dans 90 jours (délai de paiement). L'entreprise doit payer ses fournisseurs et ses salariés dès la fin du mois.</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>Cas pratique: M. Blanc, ancien boulanger salarie chez La Bonne Miche, ouvre sa propre boulangerie juste en face et imite les couleurs et lenseigne de son ancien employeur pour detourner la clientele. Qualifiez juridiquement ces faits (concurrence deloyale).</t>
+          <t>Expliquez le risque généré par ce décalage temporel.</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t>droit | Theme 8 : Dans quel cadre et comment entreprendre ' | Niveau 2 : Application et analyse</t>
+          <t>risque d'illiquidité | trésorerie | besoin en fonds de roulement | décalage temporel</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t>La libre concurrence permet a M. Blanc de sinstaller. Cependant, limitation servile de lenseigne et des couleurs de son ancien employeur, creant un risque reel de confusion dans lesprit de la clientele, constitue une faute civile. Si La Bonne Miche subit une perte de chiffre daffaires (prejudice) directement liee a ce comportement (lien de causalite), il sagit dune pratique de concurrence deloyale parasitaire, sanctionnable sur le fondement de la responsabilite extracontractuelle.</t>
+          <t>C'est un risque d'illiquidité (ou de défaillance de trésorerie). Le décalage temporel entre les décaissements (immédiats) et les encaissements (retardés de 90 jours) crée un "besoin en fonds de roulement". Même si l'entreprise est rentable sur le papier (valeur), l'absence de liquidités au moment T peut la conduire à l'incapacité de payer ses dettes, la menant directement à la cessation de paiement (faillite).</t>
         </is>
       </c>
       <c r="M288" t="n">
-        <v>275</v>
+        <v>260</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>pdf-droit-t08-008</t>
+          <t>T4-08</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>terminale</t>
+          <t>premiere</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>droit</t>
+          <t>sciences de gestion</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Theme 8 : Dans quel cadre et comment entreprendre '</t>
+          <t>Thème 4 : Temps et risque</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Niveau 2 : Application et analyse - Exercice 8</t>
+          <t>Le risque</t>
         </is>
       </c>
       <c r="F289" t="n">
@@ -19554,57 +19566,57 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>Analyse de partenariat: Lentreprise de logistique LogiTrans decide de confier le nettoy</t>
+          <t>Évaluation des risques et obsolescence</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>Exercice source PDF (droit terminale).</t>
+          <t>Une chaîne de location de DVD refuse d'investir dans la diffusion en ligne (streaming), considérant que son activité physique est encore très rentable aujourd'hui.</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>Analyse de partenariat: Lentreprise de logistique LogiTrans decide de confier le nettoyage et la securite de ses entrepots a la societe exterieure SecurNet. Qualifiez ce partenariat contractuel (sous-traitance).</t>
+          <t>Qualifiez l'attitude de la direction face au risque technologique et les conséquences possibles à moyen terme.</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t>droit | Theme 8 : Dans quel cadre et comment entreprendre ' | Niveau 2 : Application et analyse</t>
+          <t>risque technologique | obsolescence | rupture technologique | déni</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>Il sagit dun contrat dentreprise (ou contrat de prestation de services), souvent appele sous-traitance dans le langage courant. LogiTrans (le donneur dordre) externalise une tache specifique de son fonctionnement vers un partenaire (SecurNet) qui realisera la prestation en toute independance, sans aucun lien de subordination, en echange dune remuneration.</t>
+          <t>La direction refuse de sortir de sa "zone de confort" et occulte le risque de rupture technologique. Elle prend des décisions basées sur la valeur d'une information passée/présente sans recourir à la prospective. La conséquence est fatale : l'obsolescence ultra-rapide de son modèle d'affaires, conduisant à la disparition de l'entreprise (ex: le cas historique de Blockbuster face à Netflix).</t>
         </is>
       </c>
       <c r="M289" t="n">
-        <v>275</v>
+        <v>260</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>pdf-droit-t08-009</t>
+          <t>T4-09</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>terminale</t>
+          <t>premiere</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>droit</t>
+          <t>sciences de gestion</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Theme 8 : Dans quel cadre et comment entreprendre '</t>
+          <t>Thème 4 : Temps et risque</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Niveau 3 : Entrainement type Bac - Exercice 9</t>
+          <t>Le temps</t>
         </is>
       </c>
       <c r="F290" t="n">
@@ -19615,57 +19627,61 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>Mise en situation:Les operateurs telephoniques Alpha, Beta et Gamma se reunissent secrete</t>
+          <t>Cas d'entreprise "SolarMove"</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>Exercice source PDF (droit terminale).</t>
+          <t>L'entreprise fabrique des trottinettes solaires. Son cycle de production est très long (6 mois entre la conception et la vente). La directrice souhaite lancer une nouvelle gamme pour Noël, mais craint que la demande des consommateurs ait évolué entre-temps, ou que le fournisseur asiatique de batteries prenne du retard.</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>Mise en situation:Les operateurs telephoniques Alpha, Beta et Gamma se reunissent secretement pour fixer des prix minimums sur le marche et se repartir les zones geographiques. Formulez une argumentation juridique pour qualifier et sanctionner cette pratique selon le droit de la concurrence.</t>
+          <t>À l'aide de vos connaissances, conseillez la dirigeante sur les outils de gestion du temps et des risques à mettre en place pour sécuriser son projet.</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t>droit | Theme 8 : Dans quel cadre et comment entreprendre ' | Niveau 3 : Entrainement type Bac</t>
+          <t>gestion du temps | planification | gestion des risques | prospective</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>Faits: Trois entreprises majeures saccordent secretement sur les prix et les 8 territoires. Probleme de droit: De tels comportements concertes sont-ils licites sur un marche concurrentiel ' Regle de droit: Le droit interne et europeen prohibe les actions concertees, conventions, ou ententes expresses ou tacites dont lobjet ou leffet est dempecher, de restreindre ou de fausser le jeu de la concurrence sur un marche, notamment en fixant artificiellement les prix ou en repartissant les marches. Solution: Les operateurs commettent une entente illicite (cartel). Cette pratique, gravement prejudiciable aux consommateurs qui subissent des prix gonfles, est passible de tres lourdes sanctions pecuniaires (amendes) imposees par lAutorite de la concurrence.</t>
+          <t>Analyse des risques : Le long cycle de production génère deux risques temporels majeurs. Un risque externe commercial (évolution de la demande ou effet de mode qui passe) et un risque d'approvisionnement (dépendance technologique envers l'Asie et risque logistique). Rater la période de Noël (contrainte sectorielle saisonnière) serait une catastrophe financière.
+Outils de gestion proposés :
+1) Gestion du temps : La directrice doit impérativement utiliser un outil de planification (ex: un diagramme de Gantt ou un calendrier prévisionnel rétroactif) pour piloter l'enchaînement critique des tâches, intégrer des marges de manœuvre (jours de sécurité) et anticiper les retards logistiques.
+2) Gestion des risques / Prospective : Pour le risque commercial, il faut instaurer une veille tendancielle et réaliser des études de marché en amont. Pour le risque fournisseur, l'entreprise doit sécuriser la chaîne (stratégie multi-fournisseurs pour réduire la dépendance, ou relocaliser une partie de l'assemblage).
+3) Gestion financière : Élaborer un budget de trésorerie strict pour s'assurer que les 6 mois de dépenses sans rentrées d'argent pourront être supportés par l'entreprise.</t>
         </is>
       </c>
       <c r="M290" t="n">
-        <v>325</v>
+        <v>350</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>pdf-droit-t08-010</t>
+          <t>T4-10</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>terminale</t>
+          <t>premiere</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>droit</t>
+          <t>sciences de gestion</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Theme 8 : Dans quel cadre et comment entreprendre '</t>
+          <t>Thème 4 : Temps et risque</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Niveau 3 : Entrainement type Bac - Exercice 10</t>
+          <t>Le risque</t>
         </is>
       </c>
       <c r="F291" t="n">
@@ -19676,31 +19692,31 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>Developpement structure: Pourquoi la creation dune societe commerciale est-elle souvent</t>
+          <t>Développement structuré (Prise de risque)</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>Exercice source PDF (droit terminale).</t>
+          <t>Général</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>Developpement structure: Pourquoi la creation dune societe commerciale est-elle souvent privilegiee par les entrepreneurs face aux risques de lactivite economique '</t>
+          <t>"Prendre des risques est consubstantiel à la gestion d'une organisation." La recherche de la performance justifie-t-elle la prise de n'importe quel risque par les dirigeants ?</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>droit | Theme 8 : Dans quel cadre et comment entreprendre ' | Niveau 3 : Entrainement type Bac</t>
+          <t>prise de risque | responsabilité | RSE | limites | performance globale</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>Entreprendre comporte dimportants risques financiers et personnels. La creation dune societe commerciale (comme la SARL ou la SAS) permet de creer une fiction juridique: la personne morale. Celle-ci dispose de son propre patrimoine, de son propre nom et de ses propres droits. Linteret majeur est la limitation de responsabilite: en cas de faillite, lentrepreneur (lassocie) ne perd que le montant de ses apports au capital, ses biens personnels sont a labri (sauf faute de gestion ou caution personnelle). Par ailleurs, la forme societaire permet de sassocier pour lever des capitaux plus importants, dacceder plus facilement au credit bancaire, et de faciliter la transmission de lentreprise (vente de parts sociales), assurant ainsi la perennite de lactivite au-dela de la personne de lentrepreneur. 9</t>
+          <t>Sans prise de risque (investir, recruter, lancer un nouveau produit), l'entreprise stagne et meurt, car l'environnement économique est mouvant. L'innovation implique par essence le saut dans l'inconnu. Néanmoins, l'appétence au risque d'un dirigeant ne peut pas être aveugle et infinie. Les conséquences d'une mauvaise gestion des risques dépassent le seul cadre de l'entreprise : un risque inconsidéré peut provoquer un plan social (impact humain dramatique), la ruine des petits actionnaires ou une catastrophe écologique (empreinte environnementale, marée noire). Le dirigeant a donc une responsabilité morale, juridique et sociétale. La performance globale moderne impose un pilotage modéré et maîtrisé du risque (démarche RSE, plan de prévention), prouvant que la performance ne justifie pas le sacrifice de la sécurité humaine ou de l'écosystème.</t>
         </is>
       </c>
       <c r="M291" t="n">
-        <v>325</v>
+        <v>350</v>
       </c>
     </row>
   </sheetData>

--- a/public/STMG_HUB_Missions_Programmes_Officiels.xlsx
+++ b/public/STMG_HUB_Missions_Programmes_Officiels.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2923,6 +2923,2751 @@
         <v>350</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>MT1-01</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Thème 1 : Les organisations et l'activité de production de biens et de services</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Quelles ressources pour produire ?</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Ressources de Renault</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Pour lancer sa nouvelle R5 E-Tech électrique, le groupe Renault a investi massivement dans son usine de Douai (Renault ElectriCity) et a déposé plusieurs brevets sur la motorisation. Les équipes de R&amp;D ont travaillé 3 ans sur le projet.</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Identifiez et classez les ressources mobilisées par Renault pour ce projet de production.</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>ressources | tangibles | intangibles | production | innovation</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Ressources tangibles : financières (investissements massifs), matérielles (usine de Douai, chaînes de montage). Ressources intangibles : technologiques (brevets sur la motorisation), humaines (équipes R&amp;D, ingénieurs).</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>MT1-02</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Thème 1 : Les organisations et l'activité de production de biens et de services</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Quels produits pour quels besoins ?</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>2</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Démarche marketing Nespresso</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Nespresso a basé son succès sur la vente de dosettes de café premium via ses propres boutiques et son site web, répondant à une demande de café de haute qualité à domicile. Récemment, la marque a lancé la gamme Vertuo pour cibler les amateurs de cafés longs.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Caractérisez l'approche marketing de Nespresso lors du lancement de la gamme Vertuo.</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>démarche marketing | besoins | offre | approche anticipatrice</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Nespresso adopte une approche marketing réactive et d'adaptation. L'entreprise a détecté une évolution des besoins des consommateurs (amateurs de cafés longs, notamment sur les marchés nord-américains et européens) et a ajusté son offre en créant une nouvelle technologie (Vertuo) pour y répondre et conserver ses parts de marché face à la concurrence.</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>MT1-03</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Thème 1 : Les organisations et l'activité de production de biens et de services</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Comment assurer un fonctionnement cohérent ?</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>3</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Organisation du travail SNCF</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Pour faire face aux pics de fréquentation lors des départs en vacances, la SNCF réorganise temporairement le travail de ses agents en gare (Gilets Rouges). Ces agents, habituellement assignés à des tâches administratives, sont déployés sur les quais pour orienter les voyageurs.</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Repérez le mode d'organisation du travail mis en place par la SNCF pour répondre à cette contrainte.</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>organisation du travail | flexibilité | polyvalence | ressources humaines</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>La SNCF met en place une organisation du travail basée sur la flexibilité fonctionnelle interne et la polyvalence. Les agents changent temporairement d'affectation pour répondre à une forte variation de l'activité, permettant à l'organisation d'être réactive sans avoir à recruter des contrats courts.</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>MT1-04</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Thème 1 : Les organisations et l'activité de production de biens et de services</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Comment assurer un fonctionnement cohérent ?</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>4</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Coordination chez Decathlon</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Dans un grand magasin Decathlon, le directeur laisse une forte autonomie aux responsables de rayon (montagne, cycle, eau). Ces responsables se réunissent chaque lundi matin pour ajuster les opérations de la semaine et s'assurer que l'agencement global du magasin est cohérent.</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Analysez le principal mécanisme de coordination utilisé entre les responsables de rayon.</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>coordination | ajustement mutuel | décentralisation | fonctionnement</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Le principal mécanisme de coordination est l'ajustement mutuel. Les responsables de rayon se coordonnent par le biais d'une communication informelle et de réunions régulières (le lundi) pour résoudre les problèmes d'agencement, ce qui est adapté à un mode de gestion décentralisé favorisant l'autonomie.</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>MT1-05</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Thème 1 : Les organisations et l'activité de production de biens et de services</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Quels choix d'organisation de la production ?</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>5</v>
+      </c>
+      <c r="G46" t="n">
+        <v>2</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Logistique Air France</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Air France gère quotidiennement des milliers de plateaux-repas pour ses vols. La compagnie a confié cette mission à Servair. Les repas doivent être livrés exactement 2 heures avant le décollage pour garantir la chaîne du froid et éviter les retards des avions.</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Identifiez le type de flux de production mis en place et montrez son enjeu pour l'organisation.</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>logistique | flux tendus | chaîne logistique | qualité</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Il s'agit d'une production en flux tendus (ou juste-à-temps). L'enjeu est critique : la maîtrise de la chaîne logistique permet d'assurer la qualité du service (sécurité alimentaire) et d'éviter les coûts colossaux d'un retard de vol. Cela exige une coordination parfaite entre Air France et son sous-traitant.</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>MT1-06</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Thème 1 : Les organisations et l'activité de production de biens et de services</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Quels produits pour quels besoins ?</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>6</v>
+      </c>
+      <c r="G47" t="n">
+        <v>2</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Modèle économique Danone</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Danone a réorienté son offre vers des produits végétaux (gamme Alpro) et la santé par l'alimentation. Les marges sur les produits végétaux sont nettement supérieures à celles des produits laitiers classiques, attirant une clientèle prête à payer plus cher pour des bénéfices santé.</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Analysez comment ce choix stratégique modifie le modèle économique et la création de valeur de Danone.</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>modèle économique | création de valeur | positionnement | rentabilité</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Danone fait évoluer son business model en se positionnant sur un segment premium axé sur la santé (approche différenciatrice). La création de valeur financière est améliorée grâce à des marges unitaires plus fortes. La création de valeur perçue augmente car l'offre répond aux nouvelles attentes sociétales des consommateurs (bien-être, végétal).</t>
+        </is>
+      </c>
+      <c r="M47" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>MT1-07</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Thème 1 : Les organisations et l'activité de production de biens et de services</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Les transformations numériques, une chance pour la production ?</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>7</v>
+      </c>
+      <c r="G48" t="n">
+        <v>3</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Numérisation chez Michelin</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Michelin utilise l'intelligence artificielle pour analyser en temps réel les données de milliers de capteurs placés sur les machines de ses usines. L'algorithme anticipe les pannes avant qu'elles ne se produisent (maintenance prédictive).</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Diagnostiquez les avantages concurrentiels générés par l'utilisation de l'IA dans le processus de production de Michelin.</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>transformation numérique | intelligence artificielle | processus | avantage concurrentiel</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>L'intégration de l'IA permet à Michelin de réaliser de la maintenance prédictive (innovation de procédé). Avantages : réduction drastique des arrêts de production non planifiés, optimisation des coûts de maintenance, allongement de la durée de vie des équipements et garantie d'une production continue pour répondre aux commandes, constituant un avantage concurrentiel par les coûts et la fiabilité.</t>
+        </is>
+      </c>
+      <c r="M48" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>MT1-08</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Thème 1 : Les organisations et l'activité de production de biens et de services</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Quelles ressources pour produire ?</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>8</v>
+      </c>
+      <c r="G49" t="n">
+        <v>3</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>GPEC chez Orange</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Avec le déploiement de la 5G et de la fibre, Orange anticipe la disparition progressive des anciens métiers liés au réseau cuivre (ADSL). Le groupe doit former des milliers de techniciens aux nouvelles technologies sous peine de manquer de main-d'œuvre qualifiée.</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Évaluez le rôle de la GPEC (Gestion Prévisionnelle des Emplois et des Compétences) pour accompagner cette transition technologique.</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>GPEC | ressources humaines | compétences | anticipation | formation</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>La GPEC est vitale pour Orange afin d'adapter ses ressources humaines (intangibles) à sa stratégie technologique. Elle permet de diagnostiquer l'écart entre les compétences actuelles (réseau cuivre) et futures (5G/fibre). Son rôle est d'anticiper par un plan de formation interne massif (requalification) pour éviter des licenciements et garantir l'employabilité, tout en sécurisant la production de services.</t>
+        </is>
+      </c>
+      <c r="M49" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>MT1-09</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Thème 1 : Les organisations et l'activité de production de biens et de services</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Quelles ressources pour produire ?</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>9</v>
+      </c>
+      <c r="G50" t="n">
+        <v>3</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Financement L'Oréal</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Pour construire une nouvelle usine neutre en carbone en Europe, L'Oréal a besoin de 150 millions d'euros. Le groupe hésite entre utiliser ses importantes réserves de liquidités (autofinancement) ou recourir à un emprunt bancaire à des taux attractifs.</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Arbitrez entre ces deux modes de financement en justifiant votre choix au regard de la situation d'un grand groupe.</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>financement | investissement | autofinancement | emprunt | ressources financières</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>L'emprunt bancaire est souvent l'arbitrage privilégié si les taux d'intérêt sont bas (effet de levier positif), permettant à L'Oréal de conserver ses liquidités (autofinancement) pour d'autres opportunités stratégiques (rachat d'une startup, innovation). Cependant, l'autofinancement garantit une totale indépendance financière sans frais financiers. Une solution mixte (fonds propres + emprunt) est souvent la plus judicieuse pour répartir les risques.</t>
+        </is>
+      </c>
+      <c r="M50" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>MT1-10</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Thème 1 : Les organisations et l'activité de production de biens et de services</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Quels choix d'organisation de la production ?</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>10</v>
+      </c>
+      <c r="G51" t="n">
+        <v>4</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Externalisation Carrefour</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Carrefour constate que la gestion de sa gamme de plats préparés bio génère des coûts fixes très élevés dans ses propres usines, pesant sur la rentabilité. La direction envisage d'externaliser cette production à un sous-traitant spécialisé.</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Proposez les critères de décision que Carrefour doit prendre en compte avant d'externaliser cette activité.</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>organisation de la production | contrôle des coûts | externalisation | qualité</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Critères financiers : le coût complet de fabrication en interne vs le prix d'achat au sous-traitant. Critères qualitatifs : garantie du respect du cahier des charges bio et sécurité alimentaire. Critères stratégiques : le risque de perte de savoir-faire interne et la dépendance envers le fournisseur. Si le sous-traitant offre un coût spécifique plus bas avec une qualité certifiée, l'externalisation est pertinente.</t>
+        </is>
+      </c>
+      <c r="M51" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>MT1-11</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Thème 1 : Les organisations et l'activité de production de biens et de services</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Quels choix d'organisation de la production ?</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>11</v>
+      </c>
+      <c r="G52" t="n">
+        <v>4</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Flexibilité chez Zara</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Le succès de Zara (groupe Inditex) repose sur un modèle de production unique : renouveler les collections en boutique toutes les 3 semaines en s'appuyant sur des usines de proximité (Espagne, Portugal) capables de réagir instantanément aux ventes constatées.</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Analysez la pertinence de cette gestion logistique (flux tendus) face aux caractéristiques du marché de la mode.</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>logistique | flexibilité | réactivité | flux tendus</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Le marché de la mode est très volatil avec des cycles de vie de produits extrêmement courts. La production en flux poussés (produire de gros volumes à l'avance en Asie) engendre des invendus coûteux. Le choix de Zara (flux tendus et usines de proximité) garantit une hyper-réactivité, minimisant les coûts de stockage et les soldes. La pertinence est totale : la flexibilité devient le principal avantage concurrentiel.</t>
+        </is>
+      </c>
+      <c r="M52" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>MT1-12</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Thème 1 : Les organisations et l'activité de production de biens et de services</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Quels produits pour quels besoins ?</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>12</v>
+      </c>
+      <c r="G53" t="n">
+        <v>4</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Business model BlaBlaCar</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>BlaBlaCar ne possède aucun véhicule ni chauffeur. Son rôle est de mettre en relation des conducteurs particuliers et des passagers via une plateforme numérique, en prélevant une commission sur chaque trajet réservé.</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Diagnostiquez le modèle économique de BlaBlaCar et montrez comment il génère de la création de valeur.</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>modèle économique | plateforme | intermédiation | création de valeur</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Le modèle économique est un modèle de plateforme d'intermédiation (ou économie collaborative). La création de valeur financière provient des frais de service (commissions) sans supporter les coûts fixes de transport (pas de flotte à entretenir). La valeur perçue repose sur un service simple, sécurisé, économique pour les usagers et avec un fort impact environnemental positif (optimisation des sièges vides).</t>
+        </is>
+      </c>
+      <c r="M53" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>MT1-13</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Thème 1 : Les organisations et l'activité de production de biens et de services</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Quelles ressources pour produire ?</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>13</v>
+      </c>
+      <c r="G54" t="n">
+        <v>5</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Stratégie EDF</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>EDF doit démanteler ses anciennes centrales nucléaires et investir des milliards dans les énergies renouvelables (éolien, solaire) et les nouveaux réacteurs EPR, ce qui nécessite de modifier en profondeur son allocation de ressources sur les 20 prochaines années.</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Construisez une argumentation justifiant les choix de restructuration des ressources tangibles et intangibles qu'EDF doit opérer pour réussir cette transition.</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>décision stratégique | ressources | financement | investissement à long terme</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Argumentation : 1. Ressources financières : Les besoins d'investissement sont gigantesques. EDF devra mobiliser des financements externes (obligations vertes, soutien de l'État actionnaire). 2. Ressources intangibles : EDF doit pivoter d'une culture purement nucléaire vers les renouvelables (R&amp;D, rachat de brevets, GPEC pour former de nouveaux ingénieurs). 3. Ressources tangibles : Cession d'actifs vieillissants au profit de nouveaux parcs éoliens/solaires. La survie d'EDF dépend de sa capacité à piloter simultanément la fin de vie d'un outil industriel et l'émergence d'un nouveau, exigeant une réallocation totale du capital.</t>
+        </is>
+      </c>
+      <c r="M54" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>MT1-14</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Thème 1 : Les organisations et l'activité de production de biens et de services</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Les transformations numériques, une chance pour la production ?</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>14</v>
+      </c>
+      <c r="G55" t="n">
+        <v>5</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Workflow Doctolib</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Doctolib souhaite intégrer une nouvelle fonctionnalité : la pré-consultation numérique où un algorithme pose des questions médicales de base au patient avant son rendez-vous physique, afin de générer une fiche synthétique pour le médecin.</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Formulez un diagnostic sur l'impact de ce nouveau flux de travaux (workflow) sur l'organisation du travail du médecin et la valeur perçue par le patient.</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>workflow | transformation numérique | automatisation | santé</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Diagnostic : Pour le médecin (organisation du travail), ce workflow automatisé permet un gain de temps précieux lors de la consultation (suppression des questions administratives), favorisant un diagnostic plus rapide (efficience). Pour le patient (valeur perçue), cela donne un sentiment d'une prise en charge modernisée et personnalisée avant même le RDV. Cependant, le risque réside dans la déshumanisation du contact initial et la gestion sécurisée des données de santé très sensibles.</t>
+        </is>
+      </c>
+      <c r="M55" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>MT1-15</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Thème 1 : Les organisations et l'activité de production de biens et de services</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Comment assurer un fonctionnement cohérent ?</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>15</v>
+      </c>
+      <c r="G56" t="n">
+        <v>5</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Réorganisation La Poste</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Face à la chute drastique du volume du courrier papier, La Poste transforme ses facteurs en livreurs de colis d'e-commerce et prestataires de services de proximité (visite aux personnes âgées, portage de repas).</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Élaborez les axes majeurs du plan d'action que la direction doit mener pour assurer le fonctionnement cohérent de cette nouvelle organisation du travail.</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>organisation du travail | adaptation | polyvalence | stratégie de rupture</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Axes du plan d'action : 1. Ajustement des mécanismes de coordination : Les tournées doivent être repensées avec des outils numériques de routage en temps réel (standardisation des procédés par les algorithmes). 2. GPEC et formation : Accompagner les facteurs (enrichissement des tâches) pour développer des compétences relationnelles (services aux seniors) et logistiques (colis). 3. Adhésion : Communiquer sur le sens de cette mutation pour rassurer le personnel face au changement d'identité de leur métier historique, afin d'éviter une rupture du climat social.</t>
+        </is>
+      </c>
+      <c r="M56" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>MT2-01</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Thème 2 : Les organisations et les acteurs</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Comment fédérer les acteurs de l'organisation ?</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Culture d'entreprise Accor</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Le groupe hôtelier Accor promeut fortement le concept de 'Heartist' (contraction de Heart et Artist) auprès de ses collaborateurs. L'objectif est que chaque employé laisse s'exprimer sa personnalité pour offrir un accueil chaleureux et unique aux clients.</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Identifiez la notion de management illustrée ici et précisez son utilité pour l'organisation.</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>culture de l'organisation | valeurs partagées | cohésion | implication</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Il s'agit de la culture de l'organisation. Promouvoir le concept de 'Heartist' permet de diffuser des valeurs partagées au sein des hôtels Accor. L'utilité est de fédérer les salariés autour d'une vision commune de l'hospitalité, d'augmenter leur implication au travail et de se différencier de la concurrence par une qualité de service unique.</t>
+        </is>
+      </c>
+      <c r="M57" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>MT2-02</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Thème 2 : Les organisations et les acteurs</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Comment fédérer les acteurs de l'organisation ?</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>2</v>
+      </c>
+      <c r="G58" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Intérêts des acteurs Mairie de Paris</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>La Mairie de Paris a décidé de piétonniser plusieurs grandes avenues. Les associations écologistes s'en félicitent, tandis que les commerçants locaux craignent une baisse de leur chiffre d'affaires due aux difficultés d'accès pour les clients motorisés.</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Caractérisez les relations entre ces différentes parties prenantes.</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>intérêts divergents | parties prenantes | acteurs externes | conflit</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Il s'agit d'une situation où les intérêts des acteurs externes sont divergents, voire conflictuels. L'association écologiste recherche une amélioration de la qualité de vie et de l'environnement (intérêt sociétal), alors que les commerçants poursuivent un objectif de rentabilité économique. La Mairie doit arbitrer et gérer ces tensions lors de sa prise de décision.</t>
+        </is>
+      </c>
+      <c r="M58" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>MT2-03</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Thème 2 : Les organisations et les acteurs</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Comment fédérer les acteurs de l'organisation ?</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>3</v>
+      </c>
+      <c r="G59" t="n">
+        <v>1</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Style de direction Free / Iliad</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Xavier Niel, fondateur de Free, est connu pour prendre les décisions stratégiques finales de manière très directe. Il fixe le cap de manière audacieuse et exige de ses équipes des résultats rapides, tout en assumant seul la responsabilité des échecs.</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Caractérisez le style de direction décrit dans cette situation.</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>style de direction | leadership | autoritaire | prise de décision</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Le style de direction est principalement autoritaire (ou paternaliste / charismatique selon la proximité). Le pouvoir de décision est fortement centralisé autour de la personnalité du dirigeant fondateur. Ce style permet une grande réactivité et des décisions tranchées, bien adaptées à un marché des télécoms très agressif.</t>
+        </is>
+      </c>
+      <c r="M59" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>MT2-04</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Thème 2 : Les organisations et les acteurs</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Comment fédérer les acteurs de l'organisation ?</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>4</v>
+      </c>
+      <c r="G60" t="n">
+        <v>2</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>QVT chez Google France</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Google France offre à ses salariés des espaces de détente, des salles de sport gratuites, des repas sains à volonté et une grande flexibilité des horaires de travail. Les ingénieurs y passent de longues heures sans ressentir la pression traditionnelle.</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Analysez le lien entre ces dispositions de Qualité de Vie au Travail (QVT) et la performance recherchée par Google.</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>qualité de vie au travail | motivation | implication | performance sociale</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Google investit massivement dans la QVT pour répondre aux attentes de salariés très qualifiés. Ces avantages matériels et organisationnels sont des facteurs de motivation externes qui favorisent le bien-être. Un salarié épanoui est plus créatif, plus impliqué, et moins tenté de partir chez un concurrent (réduction du turnover). La performance sociale nourrit ici directement la performance de l'entreprise (innovation).</t>
+        </is>
+      </c>
+      <c r="M60" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>MT2-05</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Thème 2 : Les organisations et les acteurs</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Les transformations numériques, vecteur d'amélioration de la relation clients ?</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>5</v>
+      </c>
+      <c r="G61" t="n">
+        <v>2</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Parcours client IKEA</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Un client d'IKEA peut configurer sa cuisine en 3D sur l'application mobile depuis chez lui, la sauvegarder sur son compte, puis venir en magasin pour qu'un vendeur affine le projet sur tablette avant de valider la commande.</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Démontrez comment les outils numériques améliorent ici l'expérience d'achat du consommateur.</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>digitalisation | parcours client | interactivité | omnicanalité</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Le numérique permet la digitalisation du parcours client et crée une expérience omnicanale fluide (sans couture). Le client passe du virtuel (application) au physique (magasin) sans perdre ses données. Cela favorise l'interactivité, permet à l'entreprise de mieux connaître les besoins exacts du client, et au vendeur de conclure la vente avec un gain de temps considérable.</t>
+        </is>
+      </c>
+      <c r="M61" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>MT2-06</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Thème 2 : Les organisations et les acteurs</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Les transformations numériques, vecteur d'amélioration de la relation clients ?</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>6</v>
+      </c>
+      <c r="G62" t="n">
+        <v>2</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Administration électronique URSSAF</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>L'URSSAF a mis en place un portail 100% en ligne permettant aux auto-entrepreneurs de déclarer leur chiffre d'affaires et de payer leurs cotisations en trois clics chaque mois, remplaçant les formulaires papier.</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Identifiez les avantages de cette administration électronique pour l'usager et pour l'organisme public.</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>administration électronique | simplification | usager | efficience</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Pour l'usager : simplification extrême des démarches, gain de temps, accessibilité 24h/24, traçabilité des paiements. Pour l'URSSAF : automatisation des processus, réduction massive des coûts de traitement papier, diminution des erreurs de saisie manuelle et recouvrement plus rapide des cotisations (efficience du service public).</t>
+        </is>
+      </c>
+      <c r="M62" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>MT2-07</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Thème 2 : Les organisations et les acteurs</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Communique-t-on de la même manière avec tous les acteurs ?</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>7</v>
+      </c>
+      <c r="G63" t="n">
+        <v>3</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Communication interne Sanofi</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Lors de la fusion de deux départements de recherche, les équipes de Sanofi étaient démotivées par un sentiment d'opacité. La direction a lancé un réseau social d'entreprise interne et des webinaires hebdomadaires de questions-réponses avec le PDG.</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Diagnostiquez le rôle de cette stratégie de communication interne face à la situation de crise.</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>communication interne | adhésion | transparence | outils collaboratifs</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>La fusion a généré de l'anxiété et une perte de repères. La stratégie de communication interne (réseau social + webinaires) a un rôle fonctionnel de transparence et un rôle social d'adhésion. En permettant une communication descendante claire (les explications du PDG) et ascendante (les Q&amp;A des salariés), l'entreprise désamorce les rumeurs, restaure la confiance et favorise la cohésion des nouvelles équipes fusionnées.</t>
+        </is>
+      </c>
+      <c r="M63" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>MT2-08</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Thème 2 : Les organisations et les acteurs</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Communique-t-on de la même manière avec tous les acteurs ?</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>8</v>
+      </c>
+      <c r="G64" t="n">
+        <v>3</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Communication financière BNP Paribas</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>BNP Paribas publie chaque trimestre un rapport d'activité très détaillé, des infographies de synthèse sur son site web et organise des conférences téléphoniques avec les analystes financiers du monde entier.</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Identifiez les cibles de cette communication financière et expliquez l'importance stratégique de cette démarche.</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>communication financière | transparence | actionnaires | investisseurs</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Les cibles sont les acteurs financiers : actionnaires (actuels et potentiels), analystes boursiers, agences de notation et banques partenaires. L'enjeu est stratégique : une communication financière transparente, fiable et régulière permet de rassurer les marchés sur la santé de la banque, d'attirer des investisseurs, de soutenir le cours de l'action en bourse et de respecter les contraintes légales d'information financière.</t>
+        </is>
+      </c>
+      <c r="M64" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>MT2-09</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Thème 2 : Les organisations et les acteurs</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Les transformations numériques, vecteur d'amélioration de la relation clients ?</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>9</v>
+      </c>
+      <c r="G65" t="n">
+        <v>3</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Big Data Netflix</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>L'algorithme de Netflix analyse le temps de visionnage, les pauses, et les types de séries regardées par chaque utilisateur pour créer des recommandations hyper-personnalisées et même décider des futures séries à produire (comme House of Cards).</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Évaluez comment l'exploitation des traces numériques modifie la définition de l'offre chez Netflix.</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>traces numériques | comportement du consommateur | big data | personnalisation</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Netflix passe d'une logique d'offre de masse à un marketing individualisé. L'exploitation intensive des traces numériques (Big Data) offre une connaissance client prédictive parfaite. Cela permet non seulement de personnaliser l'interface (fidélisation maximale), mais surtout de limiter le risque d'échec lors de la création de nouveaux produits, car l'offre est littéralement définie par les comportements constatés des abonnés.</t>
+        </is>
+      </c>
+      <c r="M65" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>MT2-10</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Thème 2 : Les organisations et les acteurs</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Comment fédérer les acteurs de l'organisation ?</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>10</v>
+      </c>
+      <c r="G66" t="n">
+        <v>4</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Travail collaboratif Airbus</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Airbus fabrique ses avions en répartissant la production entre l'Allemagne, l'Espagne, le Royaume-Uni et la France. Les ingénieurs doivent travailler simultanément sur les mêmes plans 3D sans jamais se rencontrer physiquement.</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Proposez et justifiez une solution d'outils de coopération pour surmonter cette contrainte géographique.</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>coopération | outils collaboratifs | mode projet | intelligence collective</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Airbus doit déployer un environnement de travail collaboratif intégré (Cloud computing sécurisé et PLM - Product Lifecycle Management). Cela inclut des plateformes de partage de maquettes 3D en temps réel, des outils de messagerie instantanée, et des visioconférences immersives. Ces modes d'action coopératifs virtuels sont indispensables pour synchroniser les équipes (mode projet), partager l'intelligence collective et éviter les erreurs d'assemblage fatales entre pays.</t>
+        </is>
+      </c>
+      <c r="M66" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>MT2-11</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Thème 2 : Les organisations et les acteurs</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Comment fédérer les acteurs de l'organisation ?</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>11</v>
+      </c>
+      <c r="G67" t="n">
+        <v>4</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Fidélisation chez Ubisoft</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Les développeurs de jeux vidéo chez Ubisoft sont très sollicités par des studios concurrents américains offrant des salaires 30% plus élevés. Ubisoft ne peut pas s'aligner financièrement sur ces offres.</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Construisez un argumentaire managérial basé sur des facteurs de motivation alternatifs pour fidéliser ces talents.</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>fidélisation | facteurs de motivation | qualité de vie au travail | rémunération</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Argumentaire : Si la rémunération (facteur externe) est plafonnée, Ubisoft doit miser sur les facteurs de motivation internes et la marque employeur. 1. Contenu du travail : offrir l'opportunité de travailler sur des franchises mondiales prestigieuses (Assassin's Creed) avec des technologies de pointe. 2. Ambiance et QVT : proposer une culture d'entreprise forte, créative, avec du télétravail flexible et des locaux innovants. 3. Évolution : garantir des formations continues et des parcours de carrière rapides vers des postes de Lead Designer.</t>
+        </is>
+      </c>
+      <c r="M67" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>MT2-12</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Thème 2 : Les organisations et les acteurs</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Comment fédérer les acteurs de l'organisation ?</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>12</v>
+      </c>
+      <c r="G68" t="n">
+        <v>4</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Arbitrage TotalEnergies</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Lors d'une année de profits records, le conseil d'administration de TotalEnergies souhaite augmenter les dividendes versés aux actionnaires. Simultanément, les syndicats de salariés menacent de faire grève s'ils n'obtiennent pas d'augmentation générale des salaires face à l'inflation.</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Proposez une solution de gestion permettant à la direction de concilier ces attentes divergentes.</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>intérêts divergents | conflit | actionnaires | salariés | arbitrage</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>La direction est face à un arbitrage classique entre performance financière (actionnaires) et performance sociale (salariés). Solution : Valider une hausse modérée des dividendes pour rassurer les marchés, et octroyer en parallèle une prime exceptionnelle de pouvoir d'achat (ou participation/intéressement) aux salariés. Lier l'effort financier aux résultats exceptionnels permet de récompenser les deux parties prenantes sans augmenter définitivement les coûts fixes (salaires de base).</t>
+        </is>
+      </c>
+      <c r="M68" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>MT2-13</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Thème 2 : Les organisations et les acteurs</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Communique-t-on de la même manière avec tous les acteurs ?</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>13</v>
+      </c>
+      <c r="G69" t="n">
+        <v>5</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Gestion de crise Amazon</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Une enquête d'un grand média dénonce des conditions de travail dégradées et des destructions de produits neufs dans les entrepôts logistiques d'Amazon en France. La polémique s'enflamme sur les réseaux sociaux (bad buzz).</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Élaborez la stratégie de communication externe qu'Amazon doit déployer pour protéger sa e-réputation.</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>communication de crise | e-réputation | communication externe | bad buzz</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Stratégie de crise : 1. Réactivité : communiquer immédiatement (communiqué de presse) pour ne pas laisser le vide s'installer. 2. Transparence : reconnaître les faits avérés, contester les exagérations avec des chiffres précis. 3. Preuve (Earned/Owned media) : inviter la presse et des influenceurs à visiter des entrepôts pour montrer la réalité (journées portes ouvertes). 4. Actions correctives : annoncer publiquement de nouveaux partenariats avec des associations pour donner les invendus plutôt que de les détruire, transformant la crise en opportunité RSE.</t>
+        </is>
+      </c>
+      <c r="M69" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>MT2-14</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Thème 2 : Les organisations et les acteurs</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Les transformations numériques, vecteur d'amélioration de la relation clients ?</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>14</v>
+      </c>
+      <c r="G70" t="n">
+        <v>5</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Stratégie omnicanale Sephora</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Sephora réalise d'excellents résultats sur son site e-commerce, mais observe une baisse de fréquentation physique de ses magasins. Le comité de direction hésite : fermer des magasins pour tout miser sur le web, ou réinvestir dans le réseau physique.</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Argumentez en faveur du maintien et de la modernisation des boutiques physiques dans une logique d'expérience client globale.</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>omnicanalité | digitalisation de la relation client | expérience de consommation</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Argumentation : Fermer les boutiques serait une erreur car la cosmétique nécessite du test, du conseil humain et de l'expérience sensorielle. Sephora doit adopter une stratégie omnicanale où le physique et le digital se renforcent. Les boutiques doivent être digitalisées (miroirs virtuels, bornes de commande) et devenir des lieux d'expérience (masterclass maquillage, click &amp; collect). Le magasin physique n'est plus un simple lieu de stock, mais la vitrine événementielle de la marque employeur et de la relation client.</t>
+        </is>
+      </c>
+      <c r="M70" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>MT2-15</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Thème 2 : Les organisations et les acteurs</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Comment fédérer les acteurs de l'organisation ?</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>15</v>
+      </c>
+      <c r="G71" t="n">
+        <v>5</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Conduite du changement SNCF Réseau</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>SNCF Réseau doit faire face à l'ouverture à la concurrence européenne. Les agents historiques, attachés au monopole d'État, vivent cette transformation comme une menace pour leur statut et leur culture d'entreprise. Une grève dure se prépare.</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Proposez un plan managérial systémique (direction, communication, QVT) pour fédérer les salariés autour de ce changement subi.</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>cohésion | conduite du changement | culture de l'organisation | dialogue social</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Plan systémique : 1. Direction et Dialogue social : Le management doit passer d'un style autoritaire/bureaucratique à un style consultatif. Organiser des tables rondes avec les syndicats pour co-construire les nouvelles méthodes de travail (éviter l'approche top-down). 2. Culture : Faire évoluer la culture interne en valorisant l'expertise historique des cheminots comme un atout concurrentiel face aux nouveaux entrants. 3. Communication interne et QVT : Rassurer sur le maintien des acquis fondamentaux, tout en finançant des formations massives pour monter en compétences. L'enjeu est de transformer la peur de la concurrence en défi collectif stimulant.</t>
+        </is>
+      </c>
+      <c r="M71" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>MT3-01</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Thème 3 : Les organisations et la société</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Les organisations peuvent-elles s'affranchir des questions de société ?</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" t="n">
+        <v>1</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Mécénat chez LVMH</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Le groupe LVMH a versé un don exceptionnel de 200 millions d'euros pour la reconstruction de la cathédrale Notre-Dame de Paris à la suite de l'incendie de 2019. Le groupe soutient également de nombreuses expositions artistiques.</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Identifiez cette pratique et déduisez-en l'objectif poursuivi par l'organisation envers la société.</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>mécénat | organisation civique | image | intérêt général</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Il s'agit d'une action de mécénat (soutien financier, humain ou matériel sans contrepartie directe explicite). LVMH s'inscrit ainsi comme une organisation civique. L'objectif est de participer à la préservation du patrimoine (intérêt général), tout en renforçant son image institutionnelle de leader français responsable, ancré dans l'art et l'histoire.</t>
+        </is>
+      </c>
+      <c r="M72" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>MT3-02</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Thème 3 : Les organisations et la société</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Les changements de modes de vie s'imposent-ils aux organisations ?</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>2</v>
+      </c>
+      <c r="G73" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Modes de consommation Vinted</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>L'application Vinted permet à des millions de particuliers de vendre et d'acheter des vêtements de seconde main directement depuis leur smartphone, contournant les magasins traditionnels d'habillement.</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Caractérisez ce nouveau mode de consommation qui bouleverse le secteur textile.</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>modes de consommation | économie collaborative | économie circulaire</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Ce modèle repose sur l'économie collaborative (mise en relation de pair à pair via une plateforme) et l'économie circulaire (réemploi, seconde main, lutte contre le gaspillage). Ce changement de mode de vie, privilégiant l'usage et l'anti-consumérisme au neuf, s'impose aux marques de prêt-à-porter classiques qui voient leurs ventes baisser.</t>
+        </is>
+      </c>
+      <c r="M73" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>MT3-03</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Thème 3 : Les organisations et la société</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Les transformations numériques, de nouvelles responsabilités ?</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>3</v>
+      </c>
+      <c r="G74" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Données personnelles CNIL</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Suite à une plainte, la CNIL a lourdement sanctionné une entreprise de e-commerce car cette dernière conservait les numéros de carte bancaire de ses clients sans leur consentement clair, dans une base de données mal sécurisée.</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Repérez le cadre réglementaire enfreint par l'entreprise et la nature de sa responsabilité.</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>données personnelles | RGPD | protection | responsabilité</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>L'entreprise a enfreint le RGPD (Règlement Général sur la Protection des Données). L'organisation a manqué à sa responsabilité juridique et éthique de protection des données de ses usagers (défaut de consentement, défaut de sécurité), démontrant que la numérisation crée de strictes obligations de conformité.</t>
+        </is>
+      </c>
+      <c r="M74" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>MT3-04</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Thème 3 : Les organisations et la société</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Les organisations peuvent-elles s'affranchir des questions de société ?</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>4</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Éthique Ben &amp; Jerry's</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>La marque de glaces Ben &amp; Jerry's s'approvisionne en cacao, sucre et vanille uniquement via le commerce équitable, garantissant un revenu décent aux petits producteurs mondiaux. Elle milite également activement pour les droits des réfugiés.</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Diagnostiquez la manière dont cette entreprise intègre l'éthique dans sa stratégie.</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>éthique | RSE | commerce équitable | valeurs</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Ben &amp; Jerry's place l'éthique et la RSE au cœur de son business model. L'entreprise ne s'affranchit pas des questions de société, elle s'en empare (rémunération juste au Sud, militantisme). Ce n'est pas du simple 'social washing', car ces valeurs impactent directement sa chaîne d'approvisionnement (commerce équitable) et forgent une identité de marque militante fortement appréciée par sa cible.</t>
+        </is>
+      </c>
+      <c r="M75" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>MT3-05</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Thème 3 : Les organisations et la société</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Les changements de modes de vie s'imposent-ils aux organisations ?</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>5</v>
+      </c>
+      <c r="G76" t="n">
+        <v>2</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>L'application Yuka</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>L'application Yuka scanne les codes-barres des produits alimentaires pour évaluer leur impact sur la santé. Suite au succès de l'application, l'enseigne Intermarché a supprimé des dizaines d'additifs controversés de ses produits de marque distributeur.</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Expliquez comment le succès de cette application illustre l'évolution des rapports de force entre consommateurs et organisations.</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>modes de consommation | transparence | pouvoir du consommateur | adaptation</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Yuka illustre l'exigence croissante de transparence et de consommation responsable (alimentation saine). Le numérique donne un outil d'information puissant au consommateur, inversant le rapport de force. Les entreprises (comme Intermarché) sont contraintes de s'adapter très rapidement à ces nouveaux modes de vie pour éviter un boycott massif de leurs produits mal notés.</t>
+        </is>
+      </c>
+      <c r="M76" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>MT3-06</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Thème 3 : Les organisations et la société</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Quelles relations entre les organisations et leur écosystème ?</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>6</v>
+      </c>
+      <c r="G77" t="n">
+        <v>2</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Écosystème Aérospace Valley</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>À Toulouse, le pôle de compétitivité 'Aerospace Valley' regroupe le géant Airbus, des centaines de PME sous-traitantes, des écoles d'ingénieurs (ISAE-SUPAERO) et des laboratoires de recherche publics, tous géographiquement proches.</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Analysez l'intérêt pour une PME de s'implanter au sein de cette grappe d'entreprises (cluster).</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>écosystème | grappe d'entreprises | cluster | innovation | territoire</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>L'implantation dans ce cluster est un avantage stratégique. L'écosystème crée une synergie : la PME bénéficie d'un vivier de compétences (écoles), de partenariats de recherche, et d'un accès direct aux commandes d'Airbus. Cette proximité géographique et relationnelle stimule l'innovation collective et renforce la compétitivité de tout le territoire toulousain.</t>
+        </is>
+      </c>
+      <c r="M77" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>MT3-07</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Thème 3 : Les organisations et la société</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Les organisations peuvent-elles s'affranchir des questions de société ?</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>7</v>
+      </c>
+      <c r="G78" t="n">
+        <v>3</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Égalité Société Générale</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>La Société Générale a mis en place un programme strict pour identifier et combler les écarts de salaires inexpliqués entre les hommes et les femmes à poste égal. De plus, elle impose qu'il y ait au moins 40% de femmes dans ses comités de direction.</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Diagnostiquez les enjeux de cette politique de lutte contre les discriminations pour la banque.</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>discriminations | égalité hommes-femmes | éthique | RSE | attractivité</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>L'enjeu est triple. Juridique : se conformer à la loi (index égalité professionnelle). Éthique/Sociétal : répondre aux attentes de la société civile en matière de justice sociale, en corrigeant le 'plafond de verre' dans le secteur bancaire. RH/Managérial : la diversité dans les instances dirigeantes améliore la qualité de décision (diversité des profils) et renforce la marque employeur pour attirer des talents féminins de haut niveau.</t>
+        </is>
+      </c>
+      <c r="M78" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>MT3-08</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Thème 3 : Les organisations et la société</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Les transformations numériques, de nouvelles responsabilités ?</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>8</v>
+      </c>
+      <c r="G79" t="n">
+        <v>3</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Algorithmes Criteo</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Criteo, fleuron technologique français, utilise des algorithmes complexes pour afficher des bannières publicitaires ciblées aux internautes en fonction de leur navigation passée. Des associations dénoncent l'opacité de ces outils de ciblage.</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Évaluez le risque éthique lié à l'utilisation de ces technologies et la responsabilité de l'entreprise.</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>transparence des algorithmes | données personnelles | éthique | numérique</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Le ciblage comportemental soulève la question de la transparence des algorithmes (effet 'boîte noire'). Le risque éthique est la manipulation du consommateur à son insu et l'intrusion massive dans sa vie privée. La responsabilité de Criteo est d'expliquer de manière pédagogique le fonctionnement de ses algorithmes et de garantir le droit à l'opposition (opt-out), faute de quoi elle risque une perte de légitimité sociale.</t>
+        </is>
+      </c>
+      <c r="M79" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>MT3-09</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Thème 3 : Les organisations et la société</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Quelles relations entre les organisations et leur écosystème ?</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>9</v>
+      </c>
+      <c r="G80" t="n">
+        <v>3</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Relocalisation Stellantis</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Le groupe automobile Stellantis (Peugeot-Fiat) a décidé de relocaliser la fabrication d'une partie de ses moteurs électriques en France, sur le site de Trémery (Moselle), après des années de délocalisation en Asie.</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Analysez les impacts croisés de cette décision stratégique d'implantation pour l'entreprise et pour le territoire local.</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>stratégie d'implantation | territoire | relocalisation | externalités positives</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Pour Stellantis : l'entreprise sécurise sa chaîne d'approvisionnement (moins de dépendance asiatique), raccourcit ses délais logistiques et bénéficie du label 'Fabriqué en France' très vendeur. Pour le territoire de Trémery : la relocalisation génère des externalités positives massives (maintien/création d'emplois industriels, rentrées fiscales pour la collectivité locale, dynamisation du tissu de sous-traitants régionaux). L'interaction est vertueuse.</t>
+        </is>
+      </c>
+      <c r="M80" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>MT3-10</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Thème 3 : Les organisations et la société</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Les changements de modes de vie s'imposent-ils aux organisations ?</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>10</v>
+      </c>
+      <c r="G81" t="n">
+        <v>4</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Modèle Back Market</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Back Market est une plateforme française spécialisée dans la vente de smartphones et ordinateurs reconditionnés (réparés et remis à neuf). Elle connaît une croissance explosive face à l'achat de produits électroniques neufs.</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Argumentez en quoi le modèle d'affaires de Back Market est une réponse pertinente aux préoccupations écologiques de la société actuelle.</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>modes de consommation | économie circulaire | développement durable | obsolescence</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Argumentation : La société prend conscience de l'empreinte écologique désastreuse de l'électronique (extraction de métaux rares, e-déchets, obsolescence programmée). Back Market capte cette attente par l'économie circulaire : le produit est remis dans le circuit plutôt que jeté. L'entreprise crée de la valeur économique (forte croissance) tout en générant de la valeur écologique, offrant au consommateur responsable un acte d'achat déculpabilisant et moins cher.</t>
+        </is>
+      </c>
+      <c r="M81" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>MT3-11</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Thème 3 : Les organisations et la société</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Les organisations peuvent-elles s'affranchir des questions de société ?</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>11</v>
+      </c>
+      <c r="G82" t="n">
+        <v>4</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Pression sociétale McDonald's</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>McDonald's France fait face à de violentes critiques sur la quantité d'emballages jetables utilisés et sur la diététique de ses menus enfants. L'enseigne risque de perdre une grande partie de sa clientèle familiale soucieuse de l'environnement et de la santé.</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Proposez et justifiez un plan d'action RSE (Responsabilité Sociétale des Entreprises) pour McDonald's face à ces pressions.</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>RSE | pressions sociétales | éthique | image de marque</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Plan d'action RSE : 1. Environnement : Remplacer l'ensemble de la vaisselle jetable (plastique/carton) par de la vaisselle lavable et réutilisable pour la consommation sur place (action déjà amorcée par contrainte légale, mais à valoriser en communication). 2. Santé : Améliorer le 'Nutri-Score' des menus, baisser les taux de sel/sucre et proposer systématiquement des alternatives bio/végétales. L'enjeu vital est d'éviter le décrochage avec les normes sociétales (éviter d'être l'incarnation de la 'malbouffe polluante').</t>
+        </is>
+      </c>
+      <c r="M82" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>MT3-12</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Thème 3 : Les organisations et la société</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Les transformations numériques, de nouvelles responsabilités ?</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>12</v>
+      </c>
+      <c r="G83" t="n">
+        <v>4</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Cybersécurité chez Ledger</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>L'entreprise française Ledger conçoit des portefeuilles physiques ultra-sécurisés (clés USB) pour protéger les cryptomonnaies de ses clients contre le piratage, dans un environnement numérique marqué par de fréquents piratages de plateformes d'échange.</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Évaluez comment la prise en compte des menaces du cyberespace constitue le cœur de la proposition de valeur de Ledger.</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>cybersécurité | blockchain | données stratégiques | protection</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Dans l'univers de la blockchain, le vol de données (clés privées) signifie la perte définitive de l'argent. La menace cyber est totale. Ledger ne vend pas qu'une clé USB, elle vend de la confiance et de la sécurité cryptographique absolue. Sa responsabilité de protection des données est son business model même. Son avantage concurrentiel mondial repose sur son expertise technologique garantissant l'inviolabilité du patrimoine numérique de ses clients.</t>
+        </is>
+      </c>
+      <c r="M83" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>MT3-13</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Thème 3 : Les organisations et la société</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Les organisations peuvent-elles s'affranchir des questions de société ?</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>13</v>
+      </c>
+      <c r="G84" t="n">
+        <v>5</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Arbitrage complexe Veolia</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Veolia exploite une usine d'incinération de déchets très rentable qui emploie 300 personnes dans un bassin peu dynamique. Cependant, les nouvelles normes environnementales révèlent que l'usine émet un niveau de pollution atmosphérique jugé nocif pour les riverains. La mise aux normes coûterait la moitié du chiffre d'affaires.</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Argumentez la décision stratégique que doit prendre le PDG en équilibrant les responsabilités économiques, sociales et environnementales de son groupe.</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>éthique | RSE | externalités négatives | arbitrage stratégique</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Argumentation : Veolia ne peut pas s'affranchir de ses externalités négatives (pollution). Ne rien faire engagerait sa responsabilité juridique et détruirait son image de champion de l'environnement (green washing). Fermer l'usine entraînerait un désastre social (300 chômeurs). Décision : Le PDG doit engager les travaux de mise aux normes, quitte à dégrader la rentabilité à court terme. Il doit négocier des aides avec l'État ou la région (écosystème) pour co-financer l'investissement, prouvant que la pérennité de l'entreprise repose sur un équilibre entre santé publique, emploi local et profitabilité.</t>
+        </is>
+      </c>
+      <c r="M84" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>MT3-14</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Thème 3 : Les organisations et la société</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Quelles relations entre les organisations et leur écosystème ?</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>14</v>
+      </c>
+      <c r="G85" t="n">
+        <v>5</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Partenariats Biocoop</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Le réseau de magasins bio Biocoop refuse d'acheter des produits cotés en bourse ou transportés par avion. L'enseigne souhaite développer de nouveaux magasins dans une région agricole, en exigeant que les gérants tissent des contrats équitables exclusifs avec des maraîchers locaux situés à moins de 150 km.</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Élaborez un diagnostic sur la manière dont Biocoop construit volontairement un écosystème d'affaires restrictif mais créateur de valeur.</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>écosystème d'affaires | partenariats | stratégie locale | valeurs</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Diagnostic : Biocoop rejette la logique de l'hypermarché globalisé. En imposant la proximité et l'équité, l'enseigne crée un écosystème d'affaires très intégré et territorialisé. C'est restrictif (moins de produits, pas de fruits hors saison) mais extrêmement puissant. Cela sécurise les revenus des producteurs partenaires (confiance, circuits courts) et crée une valeur d'estime inattaquable auprès d'une clientèle militante. L'entreprise structure son territoire et prouve que son modèle éthique est viable économiquement.</t>
+        </is>
+      </c>
+      <c r="M85" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>MT3-15</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Thème 3 : Les organisations et la société</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Quelles relations entre les organisations et leur écosystème ?</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>15</v>
+      </c>
+      <c r="G86" t="n">
+        <v>5</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Écosystème d'innovation Renault</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Pour produire ses futures voitures électriques, Renault a initié le pôle 'Software République' en s'associant avec des concurrents, des fournisseurs informatiques (Atos, Dassault Systèmes) et des instituts de recherche publics, partageant ainsi ses recherches sur la batterie et l'intelligence artificielle.</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Construisez un argumentaire démontrant que, face à la concurrence technologique (Tesla, constructeurs chinois), la survie d'une entreprise traditionnelle passe par la création d'un écosystème d'innovation ouvert plutôt que par le secret industriel.</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>écosystème d'innovation | coopération | compétitivité | alliances stratégiques</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Argumentaire : La voiture de demain est un 'ordinateur sur roues'. Renault, constructeur traditionnel, n'a pas les ressources financières ni le temps pour développer seul l'expertise logicielle, les puces et les batteries face aux géants américains et asiatiques (risques de rupture technologique). S'isoler dans le secret industriel serait fatal. La création d'un écosystème d'innovation (Software République) permet de mutualiser les risques financiers, de croiser des compétences ultra-spécialisées (synergie public/privé/tech) et d'accélérer la R&amp;D. La coopétition (coopérer avec des rivaux) devient la condition de survie de l'industrie européenne.</t>
+        </is>
+      </c>
+      <c r="M86" t="n">
+        <v>350</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/public/STMG_HUB_Missions_Programmes_Officiels.xlsx
+++ b/public/STMG_HUB_Missions_Programmes_Officiels.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M86"/>
+  <dimension ref="A1:M131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5668,6 +5668,2751 @@
         <v>350</v>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>MT1-16</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Thème 1 : Les organisations et l'activité de production de biens et de services</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>1.2. Quelles ressources pour produire ?</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Définir le FRNG, BFR et la TN</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Le directeur financier de Sanofi analyse le bilan de l'entreprise pour préparer un nouvel investissement. Il a besoin de s'assurer de l'équilibre financier global de la structure avant d'emprunter.</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Définissez les notions de Fonds de Roulement Net Global (FRNG), Besoin en Fonds de Roulement (BFR) et Trésorerie Nette (TN).</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>FRNG | BFR | trésorerie nette | équilibre financier | définition</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Le FRNG représente l'excédent de ressources à long terme (capitaux propres, emprunts) après financement des actifs immobilisés. Le BFR est le besoin de financement généré par le cycle d'exploitation (stocks + créances - dettes fournisseurs). La TN est la différence entre le FRNG et le BFR : elle représente les liquidités réellement disponibles (si FRNG &gt; BFR).</t>
+        </is>
+      </c>
+      <c r="M87" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>MT1-17</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Thème 1 : Les organisations et l'activité de production de biens et de services</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>1.3. Quels choix d'organisation de la production pour concilier flexibilité, qualité et maîtrise des coûts ?</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>2</v>
+      </c>
+      <c r="G88" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Définir les méthodes de calcul de coûts</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>L'entreprise Renault fabrique plusieurs modèles de voitures dans son usine de Flins. La direction industrielle hésite sur la méthode comptable à utiliser pour évaluer la rentabilité d'un modèle spécifique.</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Définissez la méthode du coût complet et la méthode du coût spécifique.</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>coût complet | coût spécifique | charges directes | charges indirectes | définition</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Le coût complet consiste à imputer à un produit la totalité des charges (directes et indirectes) qu'il a générées, nécessitant des clés de répartition pour les charges communes. Le coût spécifique impute à un produit ses charges variables et uniquement les charges fixes directes qui lui sont propres, permettant de dégager une marge sur coût spécifique.</t>
+        </is>
+      </c>
+      <c r="M88" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>MT1-18</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Thème 1 : Les organisations et l'activité de production de biens et de services</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>1.1. Quels produits ou quels services pour quels besoins ?</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>3</v>
+      </c>
+      <c r="G89" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Indicateurs de création de valeur</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Le groupe LVMH présente son rapport annuel. Il y figure notamment le Chiffre d'Affaires, l'Excédent Brut d'Exploitation (EBE) et le Résultat Net.</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>À l'aide de ces indicateurs extraits du compte de résultat, expliquez comment l'entreprise mesure la création de valeur financière.</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>création de valeur | compte de résultat | indicateurs | valeur ajoutée | EBE</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>L'entreprise utilise les indicateurs du compte de résultat pour évaluer sa valeur financière. Le Chiffre d'Affaires mesure le volume des ventes. La Valeur Ajoutée (déduite des consommations intermédiaires) mesure la richesse réellement créée par son activité. L'EBE évalue la ressource tirée uniquement de l'exploitation, et le Résultat Net indique le bénéfice final (ou perte) distribuable ou mis en réserve.</t>
+        </is>
+      </c>
+      <c r="M89" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>MT1-19</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Thème 1 : Les organisations et l'activité de production de biens et de services</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>1.2. Quelles ressources pour produire ?</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>4</v>
+      </c>
+      <c r="G90" t="n">
+        <v>2</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Calcul simple de Trésorerie Nette</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>La maison Hermès dispose pour son dernier exercice d'un Fonds de Roulement Net Global (FRNG) de 500 millions d'euros et d'un Besoin en Fonds de Roulement (BFR) de 200 millions d'euros.</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Calculez la Trésorerie Nette (TN) d'Hermès et interprétez ce résultat.</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>calcul | trésorerie nette | FRNG | BFR | analyse financière</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Calcul de la Trésorerie Nette : TN = FRNG - BFR. TN = 500 millions - 200 millions = 300 millions d'euros. Interprétation : La trésorerie nette est positive et très abondante. Hermès dégage un excédent de ressources à long terme largement suffisant pour couvrir ses besoins d'exploitation, ce qui témoigne d'une excellente santé financière et d'une forte capacité à investir ou à faire face aux imprévus.</t>
+        </is>
+      </c>
+      <c r="M90" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>MT1-20</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Thème 1 : Les organisations et l'activité de production de biens et de services</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>1.3. Quels choix d'organisation de la production pour concilier flexibilité, qualité et maîtrise des coûts ?</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>5</v>
+      </c>
+      <c r="G91" t="n">
+        <v>2</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Pertinence du coût spécifique</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Air France étudie la rentabilité d'une ligne spécifique entre Paris et Tokyo. La compagnie identifie des charges variables (kérosène, repas) et des charges fixes directes (location de l'emplacement à l'aéroport de Tokyo).</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Analysez la pertinence de la méthode des coûts spécifiques pour décider du maintien ou non de cette ligne aérienne.</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>contrôle des coûts | coût spécifique | prise de décision | marge | charges fixes directes</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>La méthode des coûts spécifiques est très pertinente ici. Elle permet de calculer la marge sur coût spécifique en soustrayant du chiffre d'affaires de la ligne ses charges variables et ses charges fixes directes (location, personnel dédié). Si cette marge est positive, la ligne contribue à absorber les charges fixes communes d'Air France (siège social). Si elle est négative, la ligne détruit de la valeur et sa fermeture doit être envisagée.</t>
+        </is>
+      </c>
+      <c r="M91" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>MT1-21</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Thème 1 : Les organisations et l'activité de production de biens et de services</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>1.3. Quels choix d'organisation de la production pour concilier flexibilité, qualité et maîtrise des coûts ?</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>6</v>
+      </c>
+      <c r="G92" t="n">
+        <v>2</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Logistique et flux tendus</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Decathlon approvisionne ses magasins européens à partir de ses entrepôts centraux. Pour certains produits très demandés (vélos), la production n'est lancée qu'une fois la commande magasin validée, afin de réduire les stocks.</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Identifiez ce mode d'organisation logistique et expliquez ses avantages pour l'entreprise.</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>logistique | flux tendus | stockage | demande | réactivité</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Decathlon utilise ici la production en flux tendus (ou juste-à-temps), déclenchée par la demande (flux tirés). Les avantages sont une forte diminution des coûts liés au stockage (frais d'entrepôt, invendus, obsolescence) et une meilleure flexibilité, car la production s'adapte en temps réel aux besoins exacts des clients.</t>
+        </is>
+      </c>
+      <c r="M92" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>MT1-22</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Thème 1 : Les organisations et l'activité de production de biens et de services</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>1.5. Comment assurer un fonctionnement cohérent des organisations ?</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>7</v>
+      </c>
+      <c r="G93" t="n">
+        <v>3</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Mécanismes de coordination</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Dans un centre d'appels Orange, les téléconseillers doivent suivre des scripts (scénarios) très précis pour chaque type d'appel client, et la durée maximale de chaque appel est paramétrée dans l'ordinateur.</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Identifiez le mécanisme de coordination mis en œuvre par Orange et précisez ses objectifs.</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>coordination | standardisation des procédés | procédures | contrôle</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Le mécanisme de coordination est la standardisation des procédés de travail (modèle de Mintzberg). Les étapes de l'action sont programmées à l'avance (scripts, durée imposée). L'objectif pour Orange est d'assurer une qualité de service uniforme, de faciliter la formation des nouveaux conseillers et de maximiser la productivité globale par le contrôle strict du temps.</t>
+        </is>
+      </c>
+      <c r="M93" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>MT1-23</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Thème 1 : Les organisations et l'activité de production de biens et de services</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>1.4. Les transformations numériques, une chance pour la production ?</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>8</v>
+      </c>
+      <c r="G94" t="n">
+        <v>3</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Numérisation et objets connectés</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>L'usine Michelin de Clermont-Ferrand utilise des capteurs IoT (objets connectés) sur ses machines pour mesurer les vibrations et la température. Ces données remontent dans le Cloud pour être analysées en temps réel.</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Expliquez comment l'intégration de ces nouvelles technologies (objets connectés, cloud) améliore le processus de production.</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>transformations numériques | objets connectés | cloud computing | automatisation | maintenance</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Les objets connectés (IoT) permettent de collecter des données massives sur l'état des machines. L'informatique en nuage (Cloud) permet de stocker et d'analyser ces flux d'informations en temps réel. Cela améliore le processus de production en autorisant une maintenance prédictive : l'entreprise anticipe les pannes avant qu'elles ne surviennent, réduisant ainsi les arrêts coûteux des chaînes de fabrication.</t>
+        </is>
+      </c>
+      <c r="M94" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>MT1-24</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Thème 1 : Les organisations et l'activité de production de biens et de services</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>1.1. Quels produits ou quels services pour quels besoins ?</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>9</v>
+      </c>
+      <c r="G95" t="n">
+        <v>3</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Modèle économique Freemium</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Deezer propose une application d'écoute de musique. L'offre de base est gratuite mais comporte des publicités et des sauts de titres limités. L'offre Premium est payante et débloque toutes les fonctionnalités.</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Analysez ce modèle économique et montrez comment l'entreprise crée de la valeur avec l'offre gratuite.</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>modèle économique | freemium | création de valeur | publicité | conversion</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Deezer utilise un modèle économique 'Freemium' (contraction de free et premium). La création de valeur avec l'offre gratuite se fait indirectement : d'une part, grâce aux revenus générés par la vente d'espaces publicitaires, et d'autre part, en captant massivement des utilisateurs (effet de réseau) dont une partie finira par se convertir en abonnés payants pour améliorer leur expérience utilisateur.</t>
+        </is>
+      </c>
+      <c r="M95" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>MT1-25</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Thème 1 : Les organisations et l'activité de production de biens et de services</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>1.2. Quelles ressources pour produire ?</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>10</v>
+      </c>
+      <c r="G96" t="n">
+        <v>4</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Analyse du BFR négatif</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Carrefour encaisse quotidiennement l'argent de ses clients aux caisses (paiement comptant), alors que l'enseigne paie ses fournisseurs agroalimentaires à 60 jours. La rotation de ses stocks est très rapide.</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Diagnostiquez l'impact de ce fonctionnement sur le Besoin en Fonds de Roulement (BFR) de Carrefour et sa Trésorerie Nette.</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>BFR négatif | ressources de financement | grande distribution | trésorerie nette</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>En encaissant ses clients avant de payer ses fournisseurs, et grâce à une rotation rapide des stocks, Carrefour génère des dettes d'exploitation supérieures à ses actifs d'exploitation. Le BFR est donc négatif : ce n'est plus un besoin de financement, mais une véritable 'ressource en fonds de roulement'. Cela impacte très positivement la Trésorerie Nette, qui devient abondante et permet à l'enseigne de placer cet argent ou d'autofinancer de nouveaux magasins sans emprunter.</t>
+        </is>
+      </c>
+      <c r="M96" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>MT1-26</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Thème 1 : Les organisations et l'activité de production de biens et de services</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>1.5. Comment assurer un fonctionnement cohérent des organisations ?</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>11</v>
+      </c>
+      <c r="G97" t="n">
+        <v>4</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Lean management et polyvalence</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Dans l'usine Toyota de Valenciennes, les ouvriers sont formés pour occuper plusieurs postes sur la chaîne de montage (polyvalence) et sont encouragés à arrêter la chaîne et proposer des solutions s'ils détectent un défaut.</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Évaluez l'impact de cette organisation du travail (Lean management) sur la flexibilité et la qualité de la production.</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>organisation du travail | lean management | polyvalence | flexibilité | qualité</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Cette organisation (inspirée du Toyotisme et du Lean Management) s'oppose à la spécialisation extrême du Taylorisme. La polyvalence offre une grande flexibilité RH (remplacement immédiat en cas d'absence). Le fait de responsabiliser les ouvriers dans la détection des défauts (enrichissement des tâches) permet d'améliorer la qualité continue du produit final et de réduire les rebuts, tout en valorisant l'expertise du salarié.</t>
+        </is>
+      </c>
+      <c r="M97" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>MT1-27</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Thème 1 : Les organisations et l'activité de production de biens et de services</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>1.1. Quels produits ou quels services pour quels besoins ?</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>12</v>
+      </c>
+      <c r="G98" t="n">
+        <v>4</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Innovation de procédé</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Air Liquide a modifié sa façon de produire de l'hydrogène industriel en intégrant une nouvelle technologie de capture du CO2 au sein même de ses usines, sans changer les caractéristiques du gaz vendu aux clients finaux.</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Qualifiez ce type d'innovation et justifiez l'intérêt pour l'organisation de mener ce type d'action stratégique.</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>innovation de procédé | méthode de production | impact environnemental | rentabilité</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>Il s'agit d'une innovation de procédé. L'entreprise ne crée pas un nouveau produit, mais modifie considérablement la méthode de production. L'intérêt stratégique est double : réduire les coûts liés aux taxes carbone (maîtrise des coûts) et améliorer la performance environnementale du groupe (RSE), ce qui constitue un avantage concurrentiel face aux normes écologiques de plus en plus strictes.</t>
+        </is>
+      </c>
+      <c r="M98" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>MT1-28</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Thème 1 : Les organisations et l'activité de production de biens et de services</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>1.2. Quelles ressources pour produire ?</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>13</v>
+      </c>
+      <c r="G99" t="n">
+        <v>5</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Arbitrage de financement</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Le groupe EDF doit financer la construction de six nouveaux réacteurs nucléaires EPR (coût estimé : plus de 50 milliards d'euros). Le groupe hésite entre l'autofinancement, un endettement massif ou une augmentation de capital avec l'aide de l'État.</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Construisez une argumentation pour aider la direction financière d'EDF à arbitrer entre ces trois ressources financières.</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>financement | investissement | ressources financières | augmentation de capital | endettement</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Argumentation : 1. L'autofinancement est impossible car les sommes (50 mds) dépassent largement les capacités des réserves d'EDF, et cela assécherait sa trésorerie. 2. L'emprunt bancaire classique (endettement massif) est très risqué car EDF est déjà lourdement endettée ; les charges d'intérêt dégraderaient fortement son résultat net. 3. L'augmentation de capital (fonds propres) soutenue par l'État est l'option la plus stratégique et soutenable. Elle renforce le FRNG sans créer de charges financières (pas d'intérêts), offrant la solidité nécessaire à un investissement sur très long terme (plus de 20 ans).</t>
+        </is>
+      </c>
+      <c r="M99" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>MT1-29</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Thème 1 : Les organisations et l'activité de production de biens et de services</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>1.3. Quels choix d'organisation de la production pour concilier flexibilité, qualité et maîtrise des coûts ?</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>14</v>
+      </c>
+      <c r="G100" t="n">
+        <v>5</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Externalisation stratégique</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Airbus se concentre sur l'assemblage final des avions et la conception (R&amp;D). La fabrication de l'immense majorité des pièces (sièges, câblages, moteurs) est externalisée auprès de sous-traitants mondiaux spécialisés.</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Formulez un diagnostic critique de ce choix d'organisation de la production (Faire ou Faire faire).</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>externalisation | sous-traitance | contrôle des coûts | dépendance | stratégie</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Diagnostic : En choisissant le 'Faire faire' (externalisation), Airbus transforme des coûts fixes (usines) en coûts variables (achat de pièces). Cela accroît sa flexibilité financière et permet de bénéficier de l'expertise de pointe des sous-traitants. Cependant, cette stratégie présente des limites critiques : Airbus devient fortement dépendant de ses partenaires. Le moindre retard d'un sous-traitant (ou un défaut de qualité) peut paralyser toute la chaîne de montage finale, mettant en péril les délais de livraison et l'image du constructeur.</t>
+        </is>
+      </c>
+      <c r="M100" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>MT1-30</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Thème 1 : Les organisations et l'activité de production de biens et de services</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>1.5. Comment assurer un fonctionnement cohérent des organisations ?</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>15</v>
+      </c>
+      <c r="G101" t="n">
+        <v>5</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Diagnostic organisationnel complet</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>La Poste voit le volume de son courrier chuter. Pour s'adapter, elle développe la livraison de colis express et confie de nouveaux services aux facteurs (visite aux personnes âgées). Ces changements nécessitent de nouveaux outils numériques et des formations spécifiques.</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Élaborez un diagnostic systémique sur la manière dont La Poste doit faire évoluer la répartition des tâches, la coordination et la GPEC pour réussir ce virage stratégique.</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>organisation du travail | GPEC | coordination | adaptation | transformation</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Diagnostic systémique : 1. Répartition des tâches : Le métier de facteur s'enrichit (polyvalence). La Poste doit redéfinir les fiches de poste pour intégrer le commerce et le lien social. 2. Coordination : Les mécanismes passent d'une standardisation pure à un ajustement plus souple via des smartphones connectés gérant des tournées dynamiques. 3. GPEC (Ressources) : La Poste doit impérativement cartographier ses besoins futurs en compétences numériques et relationnelles, et déployer un plan de formation massif pour accompagner les agents historiques vers ces nouveaux métiers, garantissant ainsi l'adaptation aux besoins de l'organisation.</t>
+        </is>
+      </c>
+      <c r="M101" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>MT2-16</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Thème 2 : Les organisations et les acteurs</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>2.1. Comment fédérer les acteurs de l'organisation ?</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" t="n">
+        <v>1</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Définir la culture d'organisation</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>L'entreprise alimentaire Michel et Augustin a créé une culture d'entreprise très forte : les employés sont appelés 'les trublions', les réunions se font dans des canapés, et le ton de l'entreprise se veut volontairement jeune, décalé et transparent.</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Définissez ce qu'est la culture d'une organisation et montrez son utilité dans ce contexte.</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>culture de l'organisation | valeurs partagées | rites | cohésion | identité</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>La culture d'une organisation est l'ensemble des valeurs, des normes, des mythes et des rituels (ici, le vocabulaire 'trublions', le ton décalé) partagés par l'ensemble de ses membres. Son utilité est fondamentale : elle fédère les acteurs autour d'une identité forte, favorise le sentiment d'appartenance (cohésion interne) et contribue à forger une 'marque employeur' attractive.</t>
+        </is>
+      </c>
+      <c r="M102" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>MT2-17</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Thème 2 : Les organisations et les acteurs</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>2.1. Comment fédérer les acteurs de l'organisation ?</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>2</v>
+      </c>
+      <c r="G103" t="n">
+        <v>1</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Définir le style de direction</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Chez Tesla, le PDG Elon Musk impose directement ses visions techniques aux ingénieurs, fixe des délais souvent jugés irréalistes, et centralise la quasi-totalité des prises de décision stratégiques finales.</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Définissez ce qu'est un style de direction et qualifiez celui adopté dans cette situation.</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>style de direction | autoritaire | pouvoir de décision | centralisation</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>Un style de direction définit la manière dont un dirigeant exerce le pouvoir, prend des décisions et interagit avec ses subordonnés. Ici, le style est autoritaire (ou directif). Le pouvoir de décision est extrêmement centralisé, la communication est descendante et la pression sur les résultats est forte, laissant peu d'autonomie formelle aux salariés.</t>
+        </is>
+      </c>
+      <c r="M103" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>MT2-18</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Thème 2 : Les organisations et les acteurs</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>2.3. Communique-t-on de la même manière avec tous les acteurs ?</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>3</v>
+      </c>
+      <c r="G104" t="n">
+        <v>1</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Définir l'e-réputation</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Sur les réseaux sociaux, Burger King France répond souvent aux critiques ou aux messages des internautes avec un humour sarcastique. L'entreprise surveille constamment ce qui se dit sur elle pour maîtriser son image en ligne.</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Définissez les notions d'identité numérique et d'e-réputation.</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>e-réputation | identité numérique | image | communication externe | réseaux sociaux</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>L'identité numérique correspond aux traces et aux contenus volontairement produits par l'organisation sur internet (sites, posts sur les réseaux sociaux). L'e-réputation, en revanche, est l'image perçue ou subie par l'organisation, construite à partir des avis, commentaires et rumeurs générés par les internautes. L'enjeu est d'aligner cette réputation subie avec l'identité voulue.</t>
+        </is>
+      </c>
+      <c r="M104" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>MT2-19</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Thème 2 : Les organisations et les acteurs</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>2.1. Comment fédérer les acteurs de l'organisation ?</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>4</v>
+      </c>
+      <c r="G105" t="n">
+        <v>2</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Intérêts divergents SNCF</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>La direction de la SNCF annonce une réforme visant à modifier les critères d'avancement professionnel pour privilégier la performance individuelle. Les syndicats de cheminots, attachés à l'avancement à l'ancienneté, appellent à la grève.</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Caractérisez la nature des relations entre les acteurs dans cette organisation.</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>intérêts divergents | conflit social | acteurs internes | syndicats | direction</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>Les relations sont conflictuelles en raison d'intérêts divergents entre les acteurs internes. La direction poursuit un objectif de performance et d'efficacité organisationnelle (logique de mérite). Les syndicats de salariés poursuivent un objectif de protection des acquis sociaux, de sécurité de l'emploi et d'équité collective (logique d'ancienneté). Cet antagonisme nécessite d'être régulé par le management et le dialogue social.</t>
+        </is>
+      </c>
+      <c r="M105" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>MT2-20</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Thème 2 : Les organisations et les acteurs</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>2.2. Les transformations numériques, vecteur d'amélioration de la relation avec les clients et usagers ?</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>5</v>
+      </c>
+      <c r="G106" t="n">
+        <v>2</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Traces numériques Fnac</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Lorsqu'un client navigue sur le site de la Fnac en cherchant des appareils photo, le site mémorise son parcours. Lors de sa connexion suivante, le site lui affiche en page d'accueil des promotions ciblées sur des objectifs photographiques et des sacoches.</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Identifiez le procédé technique utilisé et expliquez en quoi il améliore la relation client.</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>traces numériques | digitalisation | personnalisation | données | parcours client</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>L'entreprise collecte et exploite les traces numériques (historique de navigation, cookies) laissées par le consommateur. Cela améliore la relation client en permettant une hyper-personnalisation de l'offre (Marketing One-to-One). Le client bénéficie de recommandations pertinentes qui facilitent son parcours d'achat, augmentant ainsi les chances de conversion et sa satisfaction.</t>
+        </is>
+      </c>
+      <c r="M106" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>MT2-21</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Thème 2 : Les organisations et les acteurs</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>2.1. Comment fédérer les acteurs de l'organisation ?</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>6</v>
+      </c>
+      <c r="G107" t="n">
+        <v>2</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>QVT et motivation Doctolib</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Doctolib permet à 100% de ses salariés de faire du télétravail jusqu'à trois jours par semaine et finance une partie de l'équipement à domicile. La direction organise également des événements mensuels (team building).</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Analysez l'impact de ces mesures sur la motivation et la fidélisation des salariés.</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>qualité de vie au travail | motivation interne | télétravail | flexibilité | fidélisation</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>Ces mesures agissent directement sur la Qualité de Vie au Travail (QVT) en offrant flexibilité et équilibre vie pro / vie perso. Le télétravail agit comme un puissant facteur de motivation (confiance, autonomie). L'organisation favorise ainsi l'implication de ses talents et limite le turn-over, la fidélisation étant un défi majeur dans le secteur très concurrentiel des technologies de la santé.</t>
+        </is>
+      </c>
+      <c r="M107" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>MT2-22</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Thème 2 : Les organisations et les acteurs</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>2.3. Communique-t-on de la même manière avec tous les acteurs ?</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>7</v>
+      </c>
+      <c r="G108" t="n">
+        <v>3</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Communication financière TotalEnergies</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>À la fin de chaque exercice, TotalEnergies publie un rapport annuel complet détaillant ses bénéfices, son plan d'affaires (business plan) à 5 ans pour la transition énergétique, et organise une réunion avec ses principaux actionnaires.</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Analysez l'importance stratégique de cette communication financière pour l'organisation.</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>communication financière | transparence | investisseurs | actionnaires | business plan</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>La communication financière est stratégique car elle s'adresse aux apporteurs de capitaux (actionnaires, banques, investisseurs). Le but n'est pas de vendre du pétrole, mais de vendre de la confiance. Le partage du business plan montre la solidité de la stratégie future. Une information transparente et normée permet de soutenir le cours en bourse et de faciliter les futurs financements de l'entreprise.</t>
+        </is>
+      </c>
+      <c r="M108" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>MT2-23</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Thème 2 : Les organisations et les acteurs</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>2.1. Comment fédérer les acteurs de l'organisation ?</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>8</v>
+      </c>
+      <c r="G109" t="n">
+        <v>3</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Outils collaboratifs Dassault Systèmes</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Chez Dassault Systèmes, les développeurs utilisent un intranet et des espaces de travail virtuels collaboratifs pour concevoir de nouveaux logiciels de 3D. Ils partagent des codes, co-éditent des documents et interagissent via une messagerie instantanée interne sécurisée.</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Évaluez l'apport des outils numériques collaboratifs dans la mise en œuvre de la coopération au sein de l'organisation.</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>coopération | outils collaboratifs | intranet | modes d'action coopératifs | numérique</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>La coopération ne se décrète pas, elle nécessite des processus et des outils adaptés. L'apport des outils collaboratifs (intranet, messagerie) est de décloisonner l'entreprise, de permettre le travail asynchrone et à distance, et de faciliter le partage instantané des connaissances. Ils créent des interdépendances fluides entre les ingénieurs, constituant ainsi un levier indispensable pour l'innovation et l'efficacité des modes d'actions coopératifs.</t>
+        </is>
+      </c>
+      <c r="M109" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>MT2-24</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Thème 2 : Les organisations et les acteurs</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>2.3. Communique-t-on de la même manière avec tous les acteurs ?</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>9</v>
+      </c>
+      <c r="G110" t="n">
+        <v>3</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Marque employeur L'Oréal</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>L'Oréal a lancé une campagne de communication mondiale intitulée 'Freedom to go Beyond', avec des vidéos immersives sur YouTube et LinkedIn montrant le quotidien inspirant de ses jeunes chefs de produit et chercheurs.</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Identifiez le concept de communication RH illustré ici et expliquez ses objectifs vis-à-vis des acteurs externes.</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>marque employeur | recrutement | communication RH | image | attractivité</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>Il s'agit du concept de 'Marque employeur' (employer branding). L'objectif de L'Oréal n'est pas de communiquer sur ses cosmétiques (com' commerciale), mais de valoriser son image en tant que lieu de travail attractif. Vis-à-vis des acteurs externes (les jeunes diplômés et futurs talents), cette communication vise à séduire, à se différencier des concurrents et à faciliter les futures campagnes de recrutement de profils de haut niveau.</t>
+        </is>
+      </c>
+      <c r="M110" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>MT2-25</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Thème 2 : Les organisations et les acteurs</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>2.2. Les transformations numériques, vecteur d'amélioration de la relation avec les clients et usagers ?</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>10</v>
+      </c>
+      <c r="G111" t="n">
+        <v>4</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Digitalisation parcours client Sephora</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Sephora a équipé ses vendeurs en magasin de terminaux tactiles permettant de retrouver l'historique d'achat en ligne du client. Le client peut aussi utiliser un miroir virtuel en réalité augmentée pour essayer virtuellement du maquillage.</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Diagnostiquez les avantages de cette digitalisation du parcours client pour le consommateur et pour l'organisation.</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>digitalisation | expérience client | omnicanalité | innovation | personnalisation</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>Pour le consommateur : la valeur perçue augmente considérablement grâce à une expérience ludique (miroir) et un service sans couture (le vendeur connaît ses goûts). C'est une omnicanalité parfaite. Pour Sephora : l'organisation collecte de nouvelles données comportementales, modernise son image de marque, fluidifie le passage en caisse et augmente très fortement ses taux de conversion en magasin (chiffre d'affaires).</t>
+        </is>
+      </c>
+      <c r="M111" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>MT2-26</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Thème 2 : Les organisations et les acteurs</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>2.3. Communique-t-on de la même manière avec tous les acteurs ?</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>11</v>
+      </c>
+      <c r="G112" t="n">
+        <v>4</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Stratégie de communication globale Decathlon</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Pour lancer une nouvelle tente de camping, Decathlon achète des spots publicitaires à la TV (Paid Media), publie des tutoriels de montage sur son propre site web (Owned Media) et espère que les campeurs partageront leurs vidéos d'utilisation sur TikTok (Earned Media).</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Analysez la pertinence de cette approche POEM (Paid, Owned, Earned Media) pour la stratégie de communication globale de Decathlon.</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>communication globale | POEM | publicité | réseaux sociaux | e-réputation</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>L'approche POEM est très pertinente car elle crée une communication globale et intégrée. Le 'Paid Media' (TV) assure une forte visibilité de masse immédiate. Le 'Owned Media' (site web) garantit une information maîtrisée et experte (réassurance du client). Le 'Earned Media' (TikTok) apporte la caution des pairs et la viralité, renforçant la crédibilité du produit par le bouche-à-oreille numérique, le tout optimisant le budget communication de la marque.</t>
+        </is>
+      </c>
+      <c r="M112" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>MT2-27</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Thème 2 : Les organisations et les acteurs</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>2.1. Comment fédérer les acteurs de l'organisation ?</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>12</v>
+      </c>
+      <c r="G113" t="n">
+        <v>4</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Facteurs de motivation Ubisoft</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Chez Ubisoft, éditeur de jeux vidéo, les augmentations de salaires sont limitées. Pour compenser, la direction offre à ses développeurs des jours de temps libre pour travailler sur des projets personnels créatifs, et organise des concours internes de création.</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Démontrez pourquoi l'entreprise privilégie les facteurs de motivation internes face aux limites de la rémunération (facteur externe).</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>motivation | facteurs internes | facteurs externes | reconnaissance | implication</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>La rémunération (facteur externe) est un levier limité financièrement et dont l'effet motivant s'estompe vite. Ubisoft privilégie les facteurs internes de motivation liés au contenu même du travail : l'autonomie, l'enrichissement des tâches et la stimulation intellectuelle (concours, projets perso). Ces facteurs répondent au besoin d'accomplissement de ces profils créatifs, générant une implication profonde et une fidélisation que l'argent seul ne peut garantir.</t>
+        </is>
+      </c>
+      <c r="M113" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>MT2-28</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Thème 2 : Les organisations et les acteurs</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>2.3. Communique-t-on de la même manière avec tous les acteurs ?</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>13</v>
+      </c>
+      <c r="G114" t="n">
+        <v>5</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Gestion de crise Lactalis</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>L'entreprise Lactalis fait face à un scandale sanitaire (lait infantile contaminé). Au début de la crise, l'entreprise communique très peu et refuse de répondre aux journalistes, ce qui déclenche un 'bad buzz' retentissant sur les réseaux sociaux et un effondrement de la confiance client.</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Élaborez un diagnostic critique de cette gestion de crise et proposez les axes d'une communication externe corrective appropriée.</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>communication de crise | bad buzz | e-réputation | transparence | confiance</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>Diagnostic : La stratégie du silence de Lactalis est un échec majeur en gestion de crise. L'absence de communication officielle laisse le champ libre aux rumeurs et aux réseaux sociaux (bad buzz), détruisant l'e-réputation et l'image de marque. Axes correctifs : 1. Communication immédiate et transparente : le PDG doit s'exprimer publiquement, assumer la responsabilité et présenter des excuses. 2. Preuve d'action : annoncer le rappel immédiat des produits et l'ouverture d'une enquête indépendante. L'enjeu est de restaurer la confiance perdue des consommateurs.</t>
+        </is>
+      </c>
+      <c r="M114" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>MT2-29</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Thème 2 : Les organisations et les acteurs</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>2.1. Comment fédérer les acteurs de l'organisation ?</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>14</v>
+      </c>
+      <c r="G115" t="n">
+        <v>5</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Arbitrage complexe Stellantis</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Après une année record, Stellantis distribue d'importants dividendes à ses actionnaires. Simultanément, la direction refuse une augmentation des salaires de base aux ouvriers, invoquant la nécessité d'investir dans l'électrique. Les syndicats bloquent plusieurs usines stratégiques.</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Construisez une argumentation managériale pour aider la direction à arbitrer ce conflit et à réaligner les intérêts divergents sans compromettre la stratégie à long terme.</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>conflit social | intérêts divergents | arbitrage | dialogue social | actionnaires</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>Argumentation : La direction fait face à un blocage qui menace la production immédiate. Arbitrer uniquement en faveur des actionnaires (dividendes) détruit le climat social. Arbitrer uniquement par une forte hausse des salaires fixes grève les capacités d'investissement (électrique). La solution passe par le dialogue social et le compromis : la direction doit lier la rémunération à la performance exceptionnelle via des dispositifs collectifs (primes d'intéressement, participation). Cela permet de récompenser l'effort des salariés à l'instant T tout en préservant la structure des coûts fixes à long terme.</t>
+        </is>
+      </c>
+      <c r="M115" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>MT2-30</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Thème 2 : Les organisations et les acteurs</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>2.3. Communique-t-on de la même manière avec tous les acteurs ?</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>15</v>
+      </c>
+      <c r="G116" t="n">
+        <v>5</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Plan de communication global Accor</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Le groupe hôtelier Accor lance une initiative majeure : supprimer tous les plastiques à usage unique de ses hôtels dans le monde. Ce projet implique les fournisseurs, les 260 000 collaborateurs et les clients finaux.</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Concevez la stratégie de communication globale et intégrée (ascendante, descendante et externe) nécessaire pour assurer le succès de cette initiative.</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>communication globale | communication interne | communication externe | RSE | adhésion</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>Stratégie globale : 1. Communication interne descendante : Une note du PDG via l'intranet expliquant les objectifs RSE de l'entreprise pour donner le cap. 2. Communication interne ascendante/horizontale : Mettre en place des boîtes à idées ou forums sur le RSE (Réseau Social d'Entreprise) pour que le personnel de terrain propose des solutions de remplacement du plastique (adhésion). 3. Communication externe : Campagne sur les réseaux sociaux et affichages dans les chambres pour informer les clients de cette politique écoresponsable, valorisant ainsi l'image de marque du groupe auprès de son écosystème.</t>
+        </is>
+      </c>
+      <c r="M116" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>MT3-16</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Thème 3 : Les organisations et la société</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>3.1. Les organisations peuvent-elles s'affranchir des questions de société ?</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>1</v>
+      </c>
+      <c r="G117" t="n">
+        <v>1</v>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Définir la Déontologie et l'Éthique</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Les employés de la banque Société Générale doivent signer un code de bonne conduite qui leur interdit formellement d'utiliser les informations financières de leurs clients à des fins d'enrichissement personnel.</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Définissez les notions d'éthique et de déontologie dans le contexte des affaires.</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>éthique | déontologie | règles de conduite | transparence | responsabilité</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>L'éthique est une réflexion morale sur les valeurs et les principes (bien/mal, juste/injuste) qui guident l'action d'une entreprise dans la société. La déontologie est l'ensemble des règles, des devoirs et des obligations professionnelles, souvent formalisés dans une charte ou un code de conduite, que doivent respecter les collaborateurs d'une organisation dans l'exercice de leur métier.</t>
+        </is>
+      </c>
+      <c r="M117" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>MT3-17</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Thème 3 : Les organisations et la société</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>3.1. Les organisations peuvent-elles s'affranchir des questions de société ?</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>2</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Définir le Greenwashing</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>La marque H&amp;M a lancé une collection 'Conscious' avec des étiquettes vertes, tout en continuant à produire des millions de vêtements à bas coût dans des pays en voie de développement (fast-fashion). Des ONG accusent la marque de tromperie.</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Définissez le concept de 'greenwashing' (écoblanchiment).</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>greenwashing | RSE | communication | éthique | image trompeuse</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>Le greenwashing (ou écoblanchiment) est une pratique de communication trompeuse utilisée par une organisation. Elle consiste à verdir artificiellement son image et à mettre en avant des arguments écologiques ou de développement durable, alors que la réalité de ses pratiques de production et de son modèle économique reste polluante ou non éthique.</t>
+        </is>
+      </c>
+      <c r="M118" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>MT3-18</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Thème 3 : Les organisations et la société</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>3.1. Les organisations peuvent-elles s'affranchir des questions de société ?</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>3</v>
+      </c>
+      <c r="G119" t="n">
+        <v>1</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Définir le mécénat</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>La Fondation TotalEnergies finance chaque année des programmes de restauration de monuments historiques en France et des bourses pour l'éducation des jeunes issus de milieux défavorisés.</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Définissez le mécénat et précisez son but principal par rapport au sponsoring (parrainage).</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>mécénat | fondation | intérêt général | organisation civique | image institutionnelle</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>Le mécénat est le soutien matériel, humain ou financier apporté sans contrepartie publicitaire directe à une œuvre ou une personne pour l'exercice d'activités d'intérêt général (culture, éducation, solidarité). À la différence du sponsoring qui vise des retombées commerciales directes, le mécénat relève du rôle civique de l'organisation et vise à asseoir son image institutionnelle sur le long terme.</t>
+        </is>
+      </c>
+      <c r="M119" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>MT3-19</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Thème 3 : Les organisations et la société</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>3.1. Les organisations peuvent-elles s'affranchir des questions de société ?</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>4</v>
+      </c>
+      <c r="G120" t="n">
+        <v>2</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Discriminations et Égalité Kering</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Le groupe de luxe Kering (Gucci, YSL) publie chaque année son index de l'égalité professionnelle et a mis en place un congé paternité de 14 semaines payé à 100 % dans le monde entier pour réduire les biais de recrutement liés à la maternité.</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Analysez l'enjeu de cette lutte contre les discriminations dans les relations de travail.</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>discriminations | égalité hommes-femmes | RSE | éthique | marque employeur</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>L'enjeu est à la fois éthique, légal et managérial. Éthiquement, l'organisation s'engage concrètement pour l'égalité femmes-hommes. Sur le plan managérial, supprimer le 'risque maternité' lors des recrutements garantit que Kering attire et promeut les meilleurs talents uniquement sur leurs compétences. Cela renforce puissamment la marque employeur et la cohésion interne.</t>
+        </is>
+      </c>
+      <c r="M120" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>MT3-20</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Thème 3 : Les organisations et la société</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>3.2. Les changements de modes de vie s'imposent-ils aux organisations ?</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>5</v>
+      </c>
+      <c r="G121" t="n">
+        <v>2</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Économie de la fonctionnalité Michelin</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Michelin propose à de grandes flottes de camions de ne plus acheter leurs pneus, mais de payer un abonnement calculé selon le nombre de kilomètres parcourus. Michelin reste propriétaire des pneus et se charge de l'entretien.</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Identifiez ce nouveau modèle économique et montrez en quoi il répond aux évolutions de la société.</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>économie de la fonctionnalité | usage | services | développement durable | modes de consommation</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>Il s'agit de l'économie de la fonctionnalité, qui privilégie la vente de l'usage d'un bien plutôt que sa propriété. Ce changement de mode de consommation répond aux enjeux de développement durable : Michelin a tout intérêt à fabriquer des pneus très résistants et à les rechapables pour maximiser ses marges, luttant ainsi mécaniquement contre le gaspillage et l'obsolescence programmée.</t>
+        </is>
+      </c>
+      <c r="M121" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>MT3-21</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Thème 3 : Les organisations et la société</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>3.3. Les transformations numériques, de nouvelles responsabilités pour les organisations ?</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>6</v>
+      </c>
+      <c r="G122" t="n">
+        <v>2</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>RGPD et données Cdiscount</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Le site de e-commerce Cdiscount collecte des millions de données (nom, adresse, historique d'achats). Suite à l'application du RGPD européen, l'entreprise a dû nommer un DPO (Délégué à la Protection des Données) et instaurer des pop-ups de consentement clairs.</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Précisez l'obligation légale illustrée ici et les risques encourus par l'organisation en cas de non-respect.</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>données personnelles | RGPD | sécurité | confidentialité | sanctions</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>L'organisation a l'obligation légale de protéger les données personnelles de ses clients, d'en garantir la confidentialité et d'obtenir leur consentement explicite (règles du RGPD). En cas de manquement ou de fuite de données, l'entreprise s'expose à de très lourdes sanctions financières de la CNIL (jusqu'à 4% du CA mondial) et à une destruction irrémédiable de son image de marque.</t>
+        </is>
+      </c>
+      <c r="M122" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>MT3-22</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Thème 3 : Les organisations et la société</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>3.4. Quelles relations entre les organisations et leur écosystème ?</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>7</v>
+      </c>
+      <c r="G123" t="n">
+        <v>3</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Pôle de compétitivité Aerospace Valley</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>À Toulouse, le cluster 'Aerospace Valley' regroupe Airbus, de nombreuses PME sous-traitantes de l'aéronautique, l'école d'ingénieurs ISAE-SUPAERO, et reçoit des financements de la Région Occitanie.</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Diagnostiquez les avantages de cette proximité géographique (écosystème territorial) pour les organisations impliquées.</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>écosystème d'innovation | grappe d'entreprises | cluster | territoire | compétitivité</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>Cette concentration d'acteurs (cluster ou grappe d'entreprises) crée de fortes externalités positives. Airbus trouve un vivier de sous-traitants réactifs et qualifiés. Les PME accèdent à des donneurs d'ordres mondiaux. Les écoles forment des ingénieurs directement employables. Cette synergie d'écosystème favorise le partage des savoirs, l'innovation collective et renforce l'attractivité et la compétitivité économique de tout le territoire toulousain.</t>
+        </is>
+      </c>
+      <c r="M123" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>MT3-23</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Thème 3 : Les organisations et la société</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>3.3. Les transformations numériques, de nouvelles responsabilités pour les organisations ?</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>8</v>
+      </c>
+      <c r="G124" t="n">
+        <v>3</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Blockchain et traçabilité Carrefour</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Carrefour utilise la technologie de la blockchain (chaîne de blocs) pour tracer l'intégralité du parcours d'un poulet fermier. En scannant un QR code en magasin, le consommateur accède à des données infalsifiables sur le lieu d'élevage, l'alimentation et la date d'abattage.</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Expliquez comment cette technologie numérique permet à l'entreprise de répondre à une préoccupation de la société.</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>blockchain | traçabilité | transparence | sécurité alimentaire | numérique</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>La société exige de plus en plus de transparence et de sécurité alimentaire (modes de consommation). La blockchain est une technologie de stockage et de transmission d'informations transparente, sécurisée et décentralisée. Son caractère infalsifiable permet à Carrefour d'offrir une garantie de traçabilité absolue, rassurant le consommateur et se démarquant éthiquement de ses concurrents par la preuve technologique.</t>
+        </is>
+      </c>
+      <c r="M124" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>MT3-24</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Thème 3 : Les organisations et la société</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>3.2. Les changements de modes de vie s'imposent-ils aux organisations ?</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>9</v>
+      </c>
+      <c r="G125" t="n">
+        <v>3</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Économie circulaire Back Market</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Back Market ne vend aucun produit électronique neuf. La plateforme française met en relation des reconditionneurs professionnels et des consommateurs pour donner une seconde vie aux smartphones et ordinateurs.</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Démontrez en quoi le modèle de cette entreprise s'inscrit dans les attentes écologiques de la société actuelle.</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>économie circulaire | modes de consommation | développement durable | obsolescence | plateforme</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>Face aux préoccupations climatiques et à la dénonciation de l'obsolescence programmée des appareils électroniques (gaspillage, métaux rares), Back Market a bâti son modèle sur l'économie circulaire. Plutôt que la destruction (modèle linéaire), l'entreprise favorise la réparation et le réemploi. Elle capte ainsi l'attente d'une consommation plus responsable et durable, tout en offrant un avantage prix au client.</t>
+        </is>
+      </c>
+      <c r="M125" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>MT3-25</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Thème 3 : Les organisations et la société</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>3.4. Quelles relations entre les organisations et leur écosystème ?</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>10</v>
+      </c>
+      <c r="G126" t="n">
+        <v>4</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Stratégie d'implantation Le Slip Français</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>L'entreprise textile Le Slip Français a fait le choix stratégique de fabriquer 100% de ses produits en France, en s'appuyant sur un réseau de PME partenaires réparties dans différentes régions françaises, alors que ses concurrents produisent en Asie.</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Évaluez les effets de cette stratégie d'implantation sur l'écosystème local et sur l'image de l'organisation.</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>stratégie d'implantation | relocalisation | écosystème | tissu économique | image de marque</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>Effets sur l'écosystème local : l'organisation dynamise le territoire en maintenant ou créant des emplois industriels, et soutient la survie d'un savoir-faire textile français menacé. Effets sur l'image : cette démarche de relocalisation est l'ADN de la marque. Bien que ses coûts de production soient plus élevés, elle crée une immense valeur perçue éthique et civique, justifiant un prix de vente premium auprès de consommateurs militants.</t>
+        </is>
+      </c>
+      <c r="M126" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>MT3-26</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Thème 3 : Les organisations et la société</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>3.3. Les transformations numériques, de nouvelles responsabilités pour les organisations ?</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>11</v>
+      </c>
+      <c r="G127" t="n">
+        <v>4</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Transparence des algorithmes Parcoursup</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Le Ministère de l'Enseignement Supérieur a été contraint, sous la pression d'associations et d'étudiants, de rendre publics les codes sources des algorithmes locaux utilisés par certaines universités pour trier les dossiers des candidats sur la plateforme Parcoursup.</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Analysez l'enjeu sociétal majeur que soulève le traitement des données par ce type d'algorithme public.</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>transparence des algorithmes | administration publique | équité | biais | données</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>L'automatisation des processus de décision (orientation de milliers de jeunes) par des algorithmes pose un enjeu démocratique d'équité. L'opacité (l'effet 'boîte noire') génère de la défiance et des suspicions de biais sociaux ou géographiques. La transparence des algorithmes est une nouvelle responsabilité incontournable pour l'administration publique : elle seule permet de garantir que les critères de sélection soient audités, justes et non discriminatoires.</t>
+        </is>
+      </c>
+      <c r="M127" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>MT3-27</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Thème 3 : Les organisations et la société</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>3.2. Les changements de modes de vie s'imposent-ils aux organisations ?</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>12</v>
+      </c>
+      <c r="G128" t="n">
+        <v>4</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Économie collaborative BlaBlaCar</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Face au coût élevé des trajets en train et à l'usage individuel de la voiture, BlaBlaCar a popularisé le covoiturage en France. Aujourd'hui, l'entreprise diversifie son offre avec BlaBlaCar Daily pour les trajets quotidiens domicile-travail.</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Expliquez comment cette organisation a su transformer une évolution des rapports sociaux en un modèle économique pérenne.</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>économie collaborative | plateforme | covoiturage | modes de vie | mobilité</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>BlaBlaCar a capté le passage d'une société de la possession (avoir sa voiture) à une société du partage et de la fonctionnalité (économie collaborative). En numérisant la mise en relation (la plateforme), l'entreprise a monétisé le partage des frais de transport. En s'attaquant désormais aux trajets quotidiens, elle s'adapte à un nouveau besoin sociétal massif (congestion urbaine, pouvoir d'achat, écologie) en devenant un acteur global de la mobilité partagée.</t>
+        </is>
+      </c>
+      <c r="M128" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>MT3-28</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Thème 3 : Les organisations et la société</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>3.1. Les organisations peuvent-elles s'affranchir des questions de société ?</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>13</v>
+      </c>
+      <c r="G129" t="n">
+        <v>5</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Entreprise à mission Danone</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Sous l'impulsion de son ancien PDG Emmanuel Faber, Danone est devenue la première grande entreprise française cotée en Bourse à adopter le statut d''Entreprise à mission'. Ses objectifs sociaux et environnementaux sont désormais inscrits dans ses statuts légaux.</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>Argumentez en quoi cette décision constitue une évolution profonde de la finalité traditionnelle de l'entreprise face aux attentes de la société.</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>éthique | RSE | entreprise à mission | finalité | parties prenantes | gouvernance</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>Argumentation : Traditionnellement, la finalité d'une entreprise privée est de maximiser le profit pour ses actionnaires. En devenant une 'Entreprise à mission' (loi PACTE), Danone modifie légalement sa raison d'être : la performance économique est désormais mise au même niveau que la performance sociale et environnementale. C'est une réponse structurelle forte : l'entreprise ne s'affranchit plus de son impact sur la société, elle accepte d'être auditée sur ses engagements (santé, climat) et d'en rendre compte à toutes ses parties prenantes, et non plus aux seuls financiers.</t>
+        </is>
+      </c>
+      <c r="M129" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>MT3-29</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Thème 3 : Les organisations et la société</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>3.4. Quelles relations entre les organisations et leur écosystème ?</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>14</v>
+      </c>
+      <c r="G130" t="n">
+        <v>5</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Écosystème d'innovation Station F</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>À Paris, le campus Station F fondé par Xavier Niel héberge plus de 1000 start-ups. On y trouve également des bureaux de fonds d'investissement, de grandes entreprises comme LVMH, des experts comptables et des représentants de l'administration publique (French Tech).</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>Élaborez un diagnostic sur la manière dont ce dispositif crée un écosystème d'affaires global et renforce le développement des jeunes entreprises.</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>écosystème d'affaires | innovation | start-up | synergies | réseau d'acteurs</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>Diagnostic : Station F dépasse le simple incubateur pour former un écosystème d'affaires complet. L'agrégation physique d'acteurs extrêmement diversifiés (start-ups, grands groupes, financeurs, pouvoirs publics) lève les barrières à l'entrée. Les jeunes pousses bénéficient de synergies immédiates : financement rapide, mentorat par des leaders mondiaux (comme LVMH), accès simplifié aux aides publiques. Ce brassage d'idées et de capitaux sur un même territoire décuple l'agilité, la capacité d'innovation et le taux de survie de ces entreprises.</t>
+        </is>
+      </c>
+      <c r="M130" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>MT3-30</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>terminale</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Thème 3 : Les organisations et la société</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>3.1. Les organisations peuvent-elles s'affranchir des questions de société ?</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>15</v>
+      </c>
+      <c r="G131" t="n">
+        <v>5</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Diagnostic Éthique et RSE Amazon</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Amazon France met en avant sa création de milliers d'emplois locaux et sa promesse de devenir neutre en carbone. En parallèle, l'entreprise est accusée d'évasion fiscale agressive, de détruire le petit commerce de proximité et d'imposer des cadences infernales dans ses entrepôts.</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>Construisez une argumentation nuancée pour évaluer la réalité de la démarche RSE d'Amazon face aux accusations de 'social washing' et 'greenwashing'.</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>éthique | RSE | social washing | optimisation fiscale | contradictions stratégiques</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>Argumentation : D'un côté, Amazon a un impact positif indéniable sur l'écosystème territorial via la création d'emplois directs massifs et d'infrastructures. De l'autre côté, son modèle est traversé par de profondes contradictions éthiques. L'optimisation fiscale prive l'État de ressources (comportement non civique). Les conditions de travail dégradées contredisent ses discours sur la performance sociale. Enfin, son modèle ultra-logistique de surconsommation questionne son engagement écologique. On peut donc diagnostiquer une forme de social/green washing : les actions RSE d'Amazon, bien que réelles (panneaux solaires), peinent à compenser les externalités négatives structurelles de son business model global.</t>
+        </is>
+      </c>
+      <c r="M131" t="n">
+        <v>350</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
